--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46277.85047859472</v>
+        <v>46278.45226946501</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46278.45226946501</v>
+        <v>46278.66584346357</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46278.66584346357</v>
+        <v>46278.85802902432</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46278.85802902432</v>
+        <v>46279.47170602889</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46279.47170602889</v>
+        <v>46279.74952800129</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46279.74952800129</v>
+        <v>46279.90437092604</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46279.90437092604</v>
+        <v>46280.44770300074</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46280.44770300074</v>
+        <v>46280.69574188061</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46280.69574188061</v>
+        <v>46280.87911322548</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46280.87911322548</v>
+        <v>46281.43935155082</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46281.43935155082</v>
+        <v>46281.69135720526</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46281.69135720526</v>
+        <v>46281.88043480548</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46281.88043480548</v>
+        <v>46282.44626227675</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46282.44626227675</v>
+        <v>46282.69511413512</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46282.69511413512</v>
+        <v>46282.88234905835</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46282.88234905835</v>
+        <v>46283.42948317102</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46283.42948317102</v>
+        <v>46283.67494779126</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46283.67494779126</v>
+        <v>46283.86336683057</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46283.86336683057</v>
+        <v>46284.41713297579</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46284.41713297579</v>
+        <v>46284.65522364937</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46284.65522364937</v>
+        <v>46284.84896204456</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46284.84896204456</v>
+        <v>46285.43096524826</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46285.43096524826</v>
+        <v>46285.65957527111</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46285.65957527111</v>
+        <v>46285.85849775343</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46285.85849775343</v>
+        <v>46286.48095256364</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46286.48095256364</v>
+        <v>46286.75494179611</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46286.75494179611</v>
+        <v>46286.91175708228</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46286.91175708228</v>
+        <v>46287.44387911425</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46287.44387911425</v>
+        <v>46287.69557856757</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46287.69557856757</v>
+        <v>46287.87971711098</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46287.87971711098</v>
+        <v>46288.43862596113</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46288.43862596113</v>
+        <v>46288.69111809758</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46288.69111809758</v>
+        <v>46288.89000629279</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46288.89000629279</v>
+        <v>46289.45030340259</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46289.45030340259</v>
+        <v>46289.70470568574</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46289.70470568574</v>
+        <v>46289.89060796656</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46289.89060796656</v>
+        <v>46290.45359635824</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46290.45359635824</v>
+        <v>46290.70704536723</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46290.70704536723</v>
+        <v>46290.89034573107</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46290.89034573107</v>
+        <v>46291.4400583465</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46291.4400583465</v>
+        <v>46291.67350495508</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46291.67350495508</v>
+        <v>46291.87107462751</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46291.87107462751</v>
+        <v>46292.46221319425</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46292.46221319425</v>
+        <v>46292.69857354155</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46292.69857354155</v>
+        <v>46292.882496821</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46292.882496821</v>
+        <v>46293.51825591372</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46293.51825591372</v>
+        <v>46293.81314157465</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46293.81314157465</v>
+        <v>46293.96344580717</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46293.96344580717</v>
+        <v>46294.49427798158</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46294.49427798158</v>
+        <v>46294.74836716126</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46294.74836716126</v>
+        <v>46294.9206282918</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46294.9206282918</v>
+        <v>46295.48496023367</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46295.48496023367</v>
+        <v>46295.74514745661</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46295.74514745661</v>
+        <v>46295.92036288875</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46295.92036288875</v>
+        <v>46296.50534020082</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46296.50534020082</v>
+        <v>46296.7634829125</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46296.7634829125</v>
+        <v>46296.9393672869</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46296.9393672869</v>
+        <v>46297.48504167596</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46297.48504167596</v>
+        <v>46297.73901472352</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46297.73901472352</v>
+        <v>46297.9181869597</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46297.9181869597</v>
+        <v>46298.45279894592</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46298.45279894592</v>
+        <v>46298.66883076997</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46298.66883076997</v>
+        <v>46298.86958689565</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46298.86958689565</v>
+        <v>46299.4823479342</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46299.4823479342</v>
+        <v>46299.69712648874</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46299.69712648874</v>
+        <v>46299.8803737572</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46299.8803737572</v>
+        <v>46300.5464582083</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46300.5464582083</v>
+        <v>46300.85943036267</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46300.85943036267</v>
+        <v>46300.99746365726</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46300.99746365726</v>
+        <v>46301.52022068301</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46301.52022068301</v>
+        <v>46301.75791538948</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -694,7 +694,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46301.75791538948</v>
+        <v>46301.94011925073</v>
       </c>
     </row>
     <row r="8">
@@ -1608,21 +1608,21 @@
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>46057</v>
+        <v>46067</v>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>investrends.ch</t>
+          <t>geldmeisterin.com</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Private Debt: Warum Prozesse wichtiger sind als Prognosen</t>
+          <t>Mikrokredite als Anlagealternative</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
@@ -1635,22 +1635,22 @@
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>https://investrends.ch/aktuell/investments/private-debt-warum-prozesse-wichtiger-sind-als-prognosen/</t>
+          <t>https://podcasters.spotify.com/pod/show/geldmeisterin/episodes/Mikrokredite-als-Anlagealternative-e3f11ln</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Payoff</t>
+          <t>investrends.ch</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Mikrofinanz als Private Debt: Besicherte KMU-Kredite statt «Entwicklungshilfe»</t>
+          <t>Private Debt: Warum Prozesse wichtiger sind als Prognosen</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -1668,51 +1668,55 @@
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>https://www.payoff.ch/news/mikrofinanz-als-private-debt-besicherte-kmu-kredite-statt-entwicklungshilfe</t>
+          <t>https://investrends.ch/aktuell/investments/private-debt-warum-prozesse-wichtiger-sind-als-prognosen/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>46049</v>
+        <v>46055</v>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Markt Einblicke</t>
+          <t>Payoff</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Mikrofinanzanleihen 2026: Stabile Renditen aus der Realwirtschaft</t>
+          <t>Mikrofinanz als Private Debt: Besicherte KMU-Kredite statt «Entwicklungshilfe»</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>Print</t>
+          <t>Online</t>
         </is>
       </c>
       <c r="F37" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="G37" s="4" t="inlineStr"/>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>https://www.payoff.ch/news/mikrofinanz-als-private-debt-besicherte-kmu-kredite-statt-entwicklungshilfe</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>46044</v>
+        <v>46049</v>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Frankfurter Allgemeine Zeitung</t>
+          <t>Markt Einblicke</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Beim Klimaschutz mehr Marktwirtschaft wagen</t>
+          <t>Mikrofinanzanleihen 2026: Stabile Renditen aus der Realwirtschaft</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -1722,35 +1726,31 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Print</t>
         </is>
       </c>
       <c r="F38" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G38" s="4" t="inlineStr">
-        <is>
-          <t>https://www.faz.net/pro/weltwirtschaft/klima-ressourcen/klimapolitik-sollte-auf-mikrofinanzierung-statt-grossprojekte-setzen-accg-200431361.html</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="G38" s="4" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>46038</v>
+        <v>46044</v>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>E-fundresearch</t>
+          <t>Frankfurter Allgemeine Zeitung</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Umfrage: Welche Chancen und Risiken Experten 2026 in den Private Markets sehen</t>
+          <t>Beim Klimaschutz mehr Marktwirtschaft wagen</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>DACH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
@@ -1759,31 +1759,31 @@
         </is>
       </c>
       <c r="F39" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>https://e-fundresearch.com/funds/artikel/57840-umfrage-welche-chancen-und-risiken-experten-2026-in-den-private-markets-sehen?page=5</t>
+          <t>https://www.faz.net/pro/weltwirtschaft/klima-ressourcen/klimapolitik-sollte-auf-mikrofinanzierung-statt-grossprojekte-setzen-accg-200431361.html</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>46035</v>
+        <v>46038</v>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Finews</t>
+          <t>E-fundresearch</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Start 2026: Disziplin als Renditequelle bei KMU-Private Debt</t>
+          <t>Umfrage: Welche Chancen und Risiken Experten 2026 in den Private Markets sehen</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>DACH</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
@@ -1792,31 +1792,31 @@
         </is>
       </c>
       <c r="F40" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>https://www.finews.ch/news/finanzplatz/70792-start2026-assetmanagement-mk-global-kapital-michele-mattioda-privat-debt-kmu-mikro</t>
+          <t>https://e-fundresearch.com/funds/artikel/57840-umfrage-welche-chancen-und-risiken-experten-2026-in-den-private-markets-sehen?page=5</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>46029</v>
+        <v>46035</v>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Markt Einblicke</t>
+          <t>Finews</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Mikrofinanzanleihen 2026: Stabile Renditen aus der Realwirtschaft</t>
+          <t>Start 2026: Disziplin als Renditequelle bei KMU-Private Debt</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
@@ -1825,26 +1825,26 @@
         </is>
       </c>
       <c r="F41" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>https://markteinblicke.de/127407/2026/01/mikrofinanzanleihen-2026-stabile-renditen-aus-der-realwirtschaft/</t>
+          <t>https://www.finews.ch/news/finanzplatz/70792-start2026-assetmanagement-mk-global-kapital-michele-mattioda-privat-debt-kmu-mikro</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>portfolio institutionell</t>
+          <t>Markt Einblicke</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Große Wirkung mit kleinen Krediten</t>
+          <t>Mikrofinanzanleihen 2026: Stabile Renditen aus der Realwirtschaft</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1858,31 +1858,31 @@
         </is>
       </c>
       <c r="F42" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>https://www.portfolio-institutionell.de/grosse-wirkung-mit-kleinen-krediten/</t>
+          <t>https://markteinblicke.de/127407/2026/01/mikrofinanzanleihen-2026-stabile-renditen-aus-der-realwirtschaft/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>46000</v>
+        <v>46028</v>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>investrends.ch</t>
+          <t>portfolio institutionell</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Neue Managementgesellschaft für den Impact-Fonds ALTERNATIVE</t>
+          <t>Große Wirkung mit kleinen Krediten</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
@@ -1891,26 +1891,26 @@
         </is>
       </c>
       <c r="F43" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>https://investrends.ch/aktuell/investments/neue-managementgesellschaft-fur-den-impact-fonds-alternative/</t>
+          <t>https://www.portfolio-institutionell.de/grosse-wirkung-mit-kleinen-krediten/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Moneycab</t>
+          <t>investrends.ch</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>MK Global Kapital wird per 1. Januar Managementgesellschaft für den Impact-Fonds ALTERNATIVE</t>
+          <t>Neue Managementgesellschaft für den Impact-Fonds ALTERNATIVE</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1928,27 +1928,27 @@
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>https://www.moneycab.com/finanz/mk-global-kapital-wird-per-1-januar-managementgesellschaft-fuer-den-impact-fonds-alternative/</t>
+          <t>https://investrends.ch/aktuell/investments/neue-managementgesellschaft-fur-den-impact-fonds-alternative/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>45997</v>
+        <v>45999</v>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>bondguide.de</t>
+          <t>Moneycab</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Mikro Kapital Management: Impact Investing ist kein Charity</t>
+          <t>MK Global Kapital wird per 1. Januar Managementgesellschaft für den Impact-Fonds ALTERNATIVE</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
@@ -1961,27 +1961,27 @@
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>https://www.bondguide.de/topnews/mikro-kapital-management-impact-investing-ist-kein-charity/</t>
+          <t>https://www.moneycab.com/finanz/mk-global-kapital-wird-per-1-januar-managementgesellschaft-fuer-den-impact-fonds-alternative/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>45985</v>
+        <v>45997</v>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Finews</t>
+          <t>bondguide.de</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist über Mikrofinanzen: Sollten vom hohen Ross herunterkommen</t>
+          <t>Mikro Kapital Management: Impact Investing ist kein Charity</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
@@ -1990,26 +1990,26 @@
         </is>
       </c>
       <c r="F46" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>https://www.finews.ch/news/finanzplatz/70147-mikro-capital-johannes-feist-kuenstliche-intelligenz-blockchain-rumaenien-europa-mikrofinanzen-finanzplatz-schweiz</t>
+          <t>https://www.bondguide.de/topnews/mikro-kapital-management-impact-investing-ist-kein-charity/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>45973</v>
+        <v>45985</v>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>investrends.ch</t>
+          <t>Finews</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Mikrofinanz ist Private Debt mit direkter Verbindung zur Realwirtschaft</t>
+          <t>Johannes Feist über Mikrofinanzen: Sollten vom hohen Ross herunterkommen</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -2023,26 +2023,26 @@
         </is>
       </c>
       <c r="F47" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>https://investrends.ch/aktuell/investments/mikrofinanz-ist-private-debt-mit-direkter-verbindung-zur-realwirtschaft/</t>
+          <t>https://www.finews.ch/news/finanzplatz/70147-mikro-capital-johannes-feist-kuenstliche-intelligenz-blockchain-rumaenien-europa-mikrofinanzen-finanzplatz-schweiz</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>45848</v>
+        <v>45973</v>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Handelszeitung</t>
+          <t>investrends.ch</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Zwischen ESG-Müdigkeit und Wirkungsanspruch</t>
+          <t>Mikrofinanz ist Private Debt mit direkter Verbindung zur Realwirtschaft</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -2056,42 +2056,75 @@
         </is>
       </c>
       <c r="F48" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>https://www.handelszeitung.ch/specials/nachhaltiges-investieren-2024/zwischen-esg-mudigkeit-und-wirkungsanspruch-841576</t>
+          <t>https://investrends.ch/aktuell/investments/mikrofinanz-ist-private-debt-mit-direkter-verbindung-zur-realwirtschaft/</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
+        <v>45848</v>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>Handelszeitung</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>Zwischen ESG-Müdigkeit und Wirkungsanspruch</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t>https://www.handelszeitung.ch/specials/nachhaltiges-investieren-2024/zwischen-esg-mudigkeit-und-wirkungsanspruch-841576</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="n">
         <v>45292</v>
       </c>
-      <c r="B49" s="4" t="inlineStr">
+      <c r="B50" s="4" t="inlineStr">
         <is>
           <t>FONDS exklusiv Österreich</t>
         </is>
       </c>
-      <c r="C49" s="4" t="inlineStr">
+      <c r="C50" s="4" t="inlineStr">
         <is>
           <t>Schwellenländer: Worauf es jetzt ankommt</t>
         </is>
       </c>
-      <c r="D49" s="4" t="inlineStr">
+      <c r="D50" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="E49" s="4" t="inlineStr">
-        <is>
-          <t>Online</t>
-        </is>
-      </c>
-      <c r="F49" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G49" s="4" t="inlineStr">
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="G50" s="4" t="inlineStr">
         <is>
           <t>https://www.fondsexklusiv.at/schwellenlaender-worauf-es-jetzt-ankommt/</t>
         </is>
@@ -2132,7 +2165,7 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Source: Sheet '2026 Clippings' (A9:G49)</t>
+          <t>Source: Sheet '2026 Clippings' (A9:G50)</t>
         </is>
       </c>
     </row>
@@ -2150,7 +2183,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6">
@@ -2242,7 +2275,7 @@
         <v>12</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>0.2926829268292683</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
@@ -2260,10 +2293,10 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>0.7073170731707317</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
@@ -2311,7 +2344,7 @@
         </is>
       </c>
       <c r="F17" s="8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -2398,7 +2431,7 @@
         <v>3</v>
       </c>
       <c r="C27" s="11" t="n">
-        <v>0.07317073170731707</v>
+        <v>0.07142857142857142</v>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
@@ -2406,10 +2439,10 @@
         </is>
       </c>
       <c r="F27" s="8" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G27" s="11" t="n">
-        <v>0.9512195121951219</v>
+        <v>0.9523809523809523</v>
       </c>
     </row>
     <row r="28">
@@ -2422,7 +2455,7 @@
         <v>12</v>
       </c>
       <c r="C28" s="11" t="n">
-        <v>0.2926829268292683</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
@@ -2433,7 +2466,7 @@
         <v>1</v>
       </c>
       <c r="G28" s="11" t="n">
-        <v>0.02439024390243903</v>
+        <v>0.02380952380952381</v>
       </c>
     </row>
     <row r="29">
@@ -2443,10 +2476,10 @@
         </is>
       </c>
       <c r="B29" s="8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C29" s="11" t="n">
-        <v>0.5853658536585366</v>
+        <v>0.5952380952380952</v>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
@@ -2457,7 +2490,7 @@
         <v>1</v>
       </c>
       <c r="G29" s="11" t="n">
-        <v>0.02439024390243903</v>
+        <v>0.02380952380952381</v>
       </c>
     </row>
     <row r="30">
@@ -2470,7 +2503,7 @@
         <v>2</v>
       </c>
       <c r="C30" s="11" t="n">
-        <v>0.04878048780487805</v>
+        <v>0.04761904761904762</v>
       </c>
     </row>
   </sheetData>

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46301.94011925073</v>
+        <v>46302.5157661269</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46302.5157661269</v>
+        <v>46302.78144578783</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46302.78144578783</v>
+        <v>46302.95654079701</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46302.95654079701</v>
+        <v>46303.52215053337</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46303.52215053337</v>
+        <v>46303.78012012633</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46303.78012012633</v>
+        <v>46303.96540430078</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46303.96540430078</v>
+        <v>46304.51425756748</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46304.51425756748</v>
+        <v>46304.75991723718</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46304.75991723718</v>
+        <v>46304.93721726281</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46304.93721726281</v>
+        <v>46305.48520652144</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46305.48520652144</v>
+        <v>46305.71738470473</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46305.71738470473</v>
+        <v>46305.8931424658</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46305.8931424658</v>
+        <v>46306.49455021004</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46306.49455021004</v>
+        <v>46306.73331464766</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46306.73331464766</v>
+        <v>46306.9052528637</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46306.9052528637</v>
+        <v>46307.58220516433</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46307.58220516433</v>
+        <v>46307.88164097974</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46307.88164097974</v>
+        <v>46308.0183307082</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46308.0183307082</v>
+        <v>46308.55195306211</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46308.55195306211</v>
+        <v>46308.79744447085</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46308.79744447085</v>
+        <v>46308.93709951331</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46308.93709951331</v>
+        <v>46309.45481440047</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46309.45481440047</v>
+        <v>46309.70592384648</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46309.70592384648</v>
+        <v>46309.89503984305</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46309.89503984305</v>
+        <v>46310.44225164128</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46310.44225164128</v>
+        <v>46310.69658422504</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46310.69658422504</v>
+        <v>46310.88249984037</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46310.88249984037</v>
+        <v>46311.43317913901</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="2026 Clippings" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Analysis 2026" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026 Clippings" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Analysis 2026" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -177,14 +177,14 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -208,18 +208,18 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Analysis 2026'!$E$12:$E$20</f>
+              <f>'Analysis 2026'!$E$12:$E$25</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Analysis 2026'!$F$12:$F$20</f>
+              <f>'Analysis 2026'!$F$12:$F$25</f>
             </numRef>
           </val>
         </ser>
@@ -240,8 +240,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -267,8 +267,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -294,19 +294,19 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="10"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Tier-Verteilung</a:t>
+              <a:t>Sprecher</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -324,18 +324,18 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <cat>
             <numRef>
-              <f>'Analysis 2026'!$A$12:$A$13</f>
+              <f>'Analysis 2026'!$A$12:$A$15</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Analysis 2026'!$B$12:$B$13</f>
+              <f>'Analysis 2026'!$B$12:$B$15</f>
             </numRef>
           </val>
         </ser>
@@ -357,12 +357,12 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>34</row>
+      <row>39</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="6480000" cy="3600000"/>
@@ -372,9 +372,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -384,7 +384,7 @@
     <from>
       <col>4</col>
       <colOff>0</colOff>
-      <row>34</row>
+      <row>39</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="4320000" cy="3600000"/>
@@ -394,9 +394,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId2"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -694,7 +694,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:G74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -702,7 +702,7 @@
     <col width="70" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
     <col width="80" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46310.88249984037</v>
+        <v>46311.43477349239</v>
       </c>
     </row>
     <row r="8">
@@ -743,7 +743,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Tier</t>
+          <t>Spokesperson</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -754,16 +754,16 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>46256</v>
+        <v>46311</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>BondGuide</t>
+          <t>Windmesse</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Niedrigwasser zeigt die Geografie des Kreditrisikos</t>
+          <t>COP30: Klimafinanzierung muss endlich in den Unternehmen ankommen</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -776,18 +776,20 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F9" s="4" t="n">
-        <v>2</v>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>https://www.bondguide.de/topnews/niedrigwasser-zeigt-die-geografie-des-kreditrisikos/</t>
+          <t>https://w3.windmesse.de/windenergie/news/48059-cop30-klimafinanzierung-muss-endlich-in-den-unternehmen-ankommen</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>46234</v>
+        <v>46304</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
@@ -796,7 +798,7 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist, CEO MK Global Kapital, im Interview</t>
+          <t>Die Obligation ist tokenisiert. Doch womit wird sie bezahlt?</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
@@ -809,27 +811,29 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F10" s="4" t="n">
-        <v>2</v>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>Louiza Savchenko</t>
+        </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>https://www.moneycab.com/interviews/ceo-interviews/johannes-feist-ceo-mk-global-kapital-im-interview/</t>
+          <t>https://www.moneycab.com/dossiers/die-obligation-ist-tokenisiert-doch-womit-wird-sie-bezahlt/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>46231</v>
+        <v>46304</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>BondGuide</t>
+          <t>finanznachrichten.de</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Private Credit: Was Anleiheinvestoren hinter dem Kupon prüfen sollten</t>
+          <t>Die Obligation ist tokenisiert. Doch womit wird sie bezahlt?</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -842,27 +846,29 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F11" s="4" t="n">
-        <v>2</v>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Louiza Savchenko</t>
+        </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>https://www.bondguide.de/topnews/private-credit-was-anleiheinvestoren-hinter-dem-kupon-pruefen-sollten/</t>
+          <t>https://www.finanznachrichten.de/nachrichten-2026-10/69801367-die-obligation-ist-tokenisiert-doch-womit-wird-sie-bezahlt-095.htm</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>46105</v>
+        <v>46294</v>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Frankfurter Allgemeine Zeitung</t>
+          <t>Markt Einblicke</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Sorgen um Privatkredite: Finanzkrise oder silberne Aera?</t>
+          <t>Nach dem Ernteeinbruch: Warum es jetzt auf die richtige Finanzierung ankommt</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -875,27 +881,29 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F12" s="4" t="n">
-        <v>1</v>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>https://www.faz.net/pro/meine-finanzen/zinsen/sorgen-um-privatkredite-finanzkrise-oder-silberne-aera-110376123.html</t>
+          <t>https://markteinblicke.de/133297/2026/09/nach-dem-ernteeinbruch-warum-es-jetzt-auf-die-richtige-finanzierung-ankommt/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>46105</v>
+        <v>46273</v>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>DAS INVESTMENT</t>
+          <t>Private Banking Magazin</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Private Credit unter Druck: Wenn das Geld nicht mehr herauskommt</t>
+          <t>In Usbekistan fehlen kleinen Firmen 6 Milliarden Dollar Kredit. Johannes Feist erklärt, wann Anleger davon profitieren – und wann sie besser Abstand halten.</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -908,32 +916,34 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F13" s="4" t="n">
-        <v>1</v>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>https://www.dasinvestment.com/private-credit-unter-druck-wenn-das-geld-nicht-mehr-herauskommt/</t>
+          <t>https://www.private-banking-magazin.de/private-credit-zentralasien-lokale-unternehmenskredite/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>46105</v>
+        <v>46256</v>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>FONDS exklusiv Oesterreich</t>
+          <t>BondGuide</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Private Credit-Debatte entfacht</t>
+          <t>Niedrigwasser zeigt die Geografie des Kreditrisikos</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -941,32 +951,34 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F14" s="4" t="n">
-        <v>2</v>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>https://www.fondsexklusiv.at/private-credit-debatte-entfacht/</t>
+          <t>https://www.bondguide.de/topnews/niedrigwasser-zeigt-die-geografie-des-kreditrisikos/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>46102</v>
+        <v>46251</v>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Der Standard</t>
+          <t>Finanz und Wirtschaft</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Pakistan spart Milliarden an fossilen Importen: Wie hat es das gemacht?</t>
+          <t>Die Schweiz finanziert Wasserresilienz überall – nur nicht im Inland</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -974,32 +986,34 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F15" s="4" t="n">
-        <v>1</v>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>Louiza Savchenko</t>
+        </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>https://www.derstandard.de/story/3000000313347/pakistan-spart-milliarden-an-fossilen-importen-wie-hat-es-das-gemacht</t>
+          <t>https://www.fuw.ch/wasserrisiko-was-die-schweiz-von-zentralasien-lernen-kann-152625611421</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>46102</v>
+        <v>46247</v>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Finews</t>
+          <t>Markt Einblicke</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Tokenisierung: Louzia Savchenko ueber Innovation und MK Global Kapital</t>
+          <t>Mikrofinanzanleihen: Worauf es bei Kreditqualität und Struktur ankommt</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -1007,32 +1021,34 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F16" s="4" t="n">
-        <v>1</v>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>https://www.finews.ch/news/finanzplatz/71578-finews-first-tokenisierung-louzia-savchenko-finanzplatz-schweiz-innovation-mk-global-kapital</t>
+          <t>https://markteinblicke.de/132318/2026/08/mikrofinanzanleihen-worauf-es-bei-kreditqualitaet-und-struktur-ankommt/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>46100</v>
+        <v>46238</v>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Moneycab</t>
+          <t>Markt Einblicke</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Nicht nur Öl: Wo der Iran-Konflikt Emerging Markets wirklich trifft</t>
+          <t>Euro-Kupon, lokale Cashflows: Wo das Währungsrisiko wirklich liegt</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -1040,32 +1056,34 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F17" s="4" t="n">
-        <v>2</v>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>https://www.moneycab.com/finanz/nicht-nur-oel-wo-der-iran-konflikt-emerging-markets-wirklich-trifft/</t>
+          <t>https://markteinblicke.de/132045/2026/08/euro-kupon-lokale-cashflows-wo-das-waehrungsrisiko-wirklich-liegt/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>46100</v>
+        <v>46234</v>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Institutional Money</t>
+          <t>Moneycab</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Was der Iran-Schock fuer Emerging Markets veraendert</t>
+          <t>Johannes Feist, CEO MK Global Kapital, im Interview</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -1073,27 +1091,29 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F18" s="4" t="n">
-        <v>1</v>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>https://www.institutional-money.com/news/maerkte/headline/was-der-iran-schock-fuer-emerging-markets-veraendert-249420</t>
+          <t>https://www.moneycab.com/interviews/ceo-interviews/johannes-feist-ceo-mk-global-kapital-im-interview/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>46100</v>
+        <v>46234</v>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>fixed-income.org</t>
+          <t>finanznachrichten.de</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Was der Iran-Schock fuer Emerging Markets veraendert</t>
+          <t>Johannes Feist, CEO MK Global Kapital, im Interview</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -1106,27 +1126,29 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F19" s="4" t="n">
-        <v>2</v>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>https://www.fixed-income.org/investment/was-der-iran-schock-fuer-emerging-markets-veraendert.html</t>
+          <t>https://www.finanznachrichten.de/nachrichten-2026-07/69177994-johannes-feist-ceo-mk-global-kapital-im-interview-095.htm</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>46098</v>
+        <v>46231</v>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>finanznachrichten.de</t>
+          <t>BondGuide</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Private Credit ist nicht gleich Private Credit: Wo die Risiken wirklich liegen</t>
+          <t>Private Credit: Was Anleiheinvestoren hinter dem Kupon prüfen sollten</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -1139,32 +1161,34 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F20" s="4" t="n">
-        <v>2</v>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>https://www.finanznachrichten.de/nachrichten-2026-03/67998176-private-credit-ist-nicht-gleich-private-credit-wo-die-risiken-wirklich-liegen-144.htm</t>
+          <t>https://www.bondguide.de/topnews/private-credit-was-anleiheinvestoren-hinter-dem-kupon-pruefen-sollten/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>46098</v>
+        <v>46183</v>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>cash-online.de</t>
+          <t>Finews</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Gastkommentar: Der blinde Fleck der Private-Credit-Debatte</t>
+          <t>Johannes Feist: «Einer meiner unerfüllter Träume ist der Sportfliegerschein»</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -1172,27 +1196,29 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F21" s="4" t="n">
-        <v>2</v>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>https://www.cash-online.de/a/gastkommentar-der-blinde-fleck-der-private-credit-debatte-713724/</t>
+          <t>https://www.finews.ch/themen/high-end/72456-johannes-feist-einer-meiner-unerfuellter-traeume-ist-der-sportfliegerschein-ceo-global-kapital</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>46097</v>
+        <v>46169</v>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>FONDS exklusiv</t>
+          <t>Markt Einblicke</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Private Credit-Debatte entfacht</t>
+          <t>Warum der Blick auf den Ölpreis nicht reicht</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -1205,65 +1231,69 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F22" s="4" t="n">
-        <v>2</v>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>https://www.fondsexklusiv.de/private-credit-debatte-entfacht/</t>
+          <t>https://markteinblicke.de/130696/2026/05/warum-der-blick-auf-den-oelpreis-nicht-reicht/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>46097</v>
+        <v>46164</v>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Kreditwesen (Verlagsgruppe Knapp-Richardi)</t>
+          <t>Moneycab</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Mikrofinanz als Anlageklasse</t>
+          <t>Nicht die Grösse des Kredits entscheidet, sondern seine Wirkung</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Print &amp; Online</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="n">
-        <v>2</v>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>https://www.kreditwesen.de/kreditwesen/themenschwerpunkte/aufsaetze/mikrofinanz-anlageklasse-id107511.html</t>
+          <t>https://www.moneycab.com/dossiers/nicht-die-groesse-des-kredits-entscheidet-sondern-seine-wirkung/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>46091</v>
+        <v>46149</v>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Swiss Finance AI</t>
+          <t>Markt Einblicke</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Warum tokenisierte Anleihen mehr sind als ein Trend</t>
+          <t>Mikrofinanz-Anleihen: Ein wachsender Markt</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
@@ -1271,27 +1301,29 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F24" s="4" t="n">
-        <v>2</v>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>https://www.swissfinanceai.ch/blog/swiss-finance/warum-tokenisierte-anleihen-mehr-sind-als-ein-trend</t>
+          <t>https://markteinblicke.de/130263/2026/05/mikrofinanz-anleihen-ein-wachsender-markt/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>46085</v>
+        <v>46125</v>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>markteinblicke.de</t>
+          <t>cash-online.de</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Tokenisierte Anleihen: Mehr Governance erforderlich</t>
+          <t>Tokenisierte Anleihen: Was sich für Anleger ändert und was nicht</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -1304,27 +1336,29 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F25" s="4" t="n">
-        <v>1</v>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>Louiza Savchenko</t>
+        </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>https://markteinblicke.de/128943/2026/03/tokenisierte-anleihen-mehr-governance-erforderlich/</t>
+          <t>https://www.cash-online.de/a/tokenisierte-anleihen-was-sich-fuer-anleger-aendert-und-was-nicht-715994/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>46085</v>
+        <v>46105</v>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>gruenderkueche.de</t>
+          <t>Frankfurter Allgemeine Zeitung</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Weltfrauentag: Unternehmerinnen fehlt weiterhin der Zugang zu Kapital</t>
+          <t>Sorgen um Privatkredite: Finanzkrise oder silberne Aera?</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -1337,27 +1371,25 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F26" s="4" t="n">
-        <v>2</v>
-      </c>
+      <c r="F26" s="4" t="inlineStr"/>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>https://www.gruenderkueche.de/news/finanzen-news/weltfrauentag-unternehmerinnen-fehlt-weiterhin-der-zugang-zu-kapital/</t>
+          <t>https://www.faz.net/pro/meine-finanzen/zinsen/sorgen-um-privatkredite-finanzkrise-oder-silberne-aera-110376123.html</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>46083</v>
+        <v>46105</v>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>altii.de</t>
+          <t>DAS INVESTMENT</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Unternehmerinnen fehlt weltweit der Zugang zu Kapital</t>
+          <t>Private Credit unter Druck: Wenn das Geld nicht mehr herauskommt</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
@@ -1370,32 +1402,30 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F27" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="F27" s="4" t="inlineStr"/>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>https://www.altii.de/edai-71550571-cb6c-4c09-93da-bd99b822c245/</t>
+          <t>https://www.dasinvestment.com/private-credit-unter-druck-wenn-das-geld-nicht-mehr-herauskommt/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>46077</v>
+        <v>46105</v>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>dfpa.info</t>
+          <t>FONDS exklusiv Oesterreich</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Wenn Geschäftsbanken passen, helfen Mikrofinanzfonds</t>
+          <t>Private Credit-Debatte entfacht</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
@@ -1403,32 +1433,34 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F28" s="4" t="n">
-        <v>2</v>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>https://www.dfpa.info/top-story/wenn-geschaeftsbanken-passen-helfen-mikrofinanzfonds.html</t>
+          <t>https://www.fondsexklusiv.at/private-credit-debatte-entfacht/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>46076</v>
+        <v>46102</v>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>exxecnews.org</t>
+          <t>Der Standard</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Teil I: Wenn Geschäftsbanken passen, helfen Mikrofinanzfonds</t>
+          <t>Pakistan spart Milliarden an fossilen Importen: Wie hat es das gemacht?</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
@@ -1436,32 +1468,30 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F29" s="4" t="n">
-        <v>2</v>
-      </c>
+      <c r="F29" s="4" t="inlineStr"/>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>https://exxecnews.org/wp-content/uploads/2026/02/Ausgabe-05_2026.pdf</t>
+          <t>https://www.derstandard.de/story/3000000313347/pakistan-spart-milliarden-an-fossilen-importen-wie-hat-es-das-gemacht</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>46071</v>
+        <v>46102</v>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>dfpa.info</t>
+          <t>Finews</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Mikrofinanz: Besonderheit Anleihen mit festem Zins</t>
+          <t>Tokenisierung: Louzia Savchenko ueber Innovation und MK Global Kapital</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
@@ -1469,32 +1499,34 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F30" s="4" t="n">
-        <v>2</v>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>Louiza Savchenko</t>
+        </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>https://www.dfpa.info/interview/mikrofinanz-besonderheit-anleihen-mit-festem-zins.html</t>
+          <t>https://www.finews.ch/news/finanzplatz/71578-finews-first-tokenisierung-louzia-savchenko-finanzplatz-schweiz-innovation-mk-global-kapital</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>46069</v>
+        <v>46101</v>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Börsen-Kurier</t>
+          <t>BondGuide</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Privates Kapital für noch nicht entwickelte Märkte</t>
+          <t>Private Credit ist nicht gleich Private Credit: wo die Risiken wirklich liegen</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>DACH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -1502,28 +1534,34 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F31" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G31" s="4" t="inlineStr"/>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bondguide.de/topnews/private-credit-ist-nicht-gleich-private-credit-wo-die-risiken-wirklich-liegen/</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>46067</v>
+        <v>46100</v>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>finanznachrichten.de</t>
+          <t>Moneycab</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Security Conference München 2026: öffentliche Mittel als Hebel nutzen</t>
+          <t>Nicht nur Öl: Wo der Iran-Konflikt Emerging Markets wirklich trifft</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
@@ -1531,27 +1569,29 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F32" s="4" t="n">
-        <v>2</v>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>https://www.finanznachrichten.de/nachrichten-2026-02/67704129-security-conference-muenchen-2026-oeffentliche-mittel-als-hebel-nutzen-144.htm</t>
+          <t>https://www.moneycab.com/finanz/nicht-nur-oel-wo-der-iran-konflikt-emerging-markets-wirklich-trifft/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>46067</v>
+        <v>46100</v>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>bondguide.de</t>
+          <t>Institutional Money</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Security Conference München 2026: öffentliche Mittel als Hebel nutzen</t>
+          <t>Was der Iran-Schock fuer Emerging Markets veraendert</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -1564,27 +1604,25 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F33" s="4" t="n">
-        <v>2</v>
-      </c>
+      <c r="F33" s="4" t="inlineStr"/>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>https://www.bondguide.de/topnews/security-conference-muenchen-2026-oeffentliche-mittel-als-hebel-nutzen/</t>
+          <t>https://www.institutional-money.com/news/maerkte/headline/was-der-iran-schock-fuer-emerging-markets-veraendert-249420</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>46067</v>
+        <v>46100</v>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>geldmeisterin.com</t>
+          <t>fixed-income.org</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Mikrokredite gerade jetzt zur Risikostreuung</t>
+          <t>Was der Iran-Schock fuer Emerging Markets veraendert</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -1597,27 +1635,29 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F34" s="4" t="n">
-        <v>2</v>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>https://www.geldmeisterin.com/index.php/2026/02/14/mikrokredite-gerade-jetzt-zur-risikostreuung/</t>
+          <t>https://www.fixed-income.org/investment/was-der-iran-schock-fuer-emerging-markets-veraendert.html</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>46067</v>
+        <v>46098</v>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>geldmeisterin.com</t>
+          <t>finanznachrichten.de</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Mikrokredite als Anlagealternative</t>
+          <t>Private Credit ist nicht gleich Private Credit: Wo die Risiken wirklich liegen</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -1630,32 +1670,34 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F35" s="4" t="n">
-        <v>2</v>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>https://podcasters.spotify.com/pod/show/geldmeisterin/episodes/Mikrokredite-als-Anlagealternative-e3f11ln</t>
+          <t>https://www.finanznachrichten.de/nachrichten-2026-03/67998176-private-credit-ist-nicht-gleich-private-credit-wo-die-risiken-wirklich-liegen-144.htm</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>46057</v>
+        <v>46098</v>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>investrends.ch</t>
+          <t>cash-online.de</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Private Debt: Warum Prozesse wichtiger sind als Prognosen</t>
+          <t>Gastkommentar: Der blinde Fleck der Private-Credit-Debatte</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
@@ -1663,32 +1705,34 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F36" s="4" t="n">
-        <v>2</v>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>https://investrends.ch/aktuell/investments/private-debt-warum-prozesse-wichtiger-sind-als-prognosen/</t>
+          <t>https://www.cash-online.de/a/gastkommentar-der-blinde-fleck-der-private-credit-debatte-713724/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>46055</v>
+        <v>46097</v>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Payoff</t>
+          <t>FONDS exklusiv</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Mikrofinanz als Private Debt: Besicherte KMU-Kredite statt «Entwicklungshilfe»</t>
+          <t>Private Credit-Debatte entfacht</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
@@ -1696,27 +1740,29 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F37" s="4" t="n">
-        <v>2</v>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>https://www.payoff.ch/news/mikrofinanz-als-private-debt-besicherte-kmu-kredite-statt-entwicklungshilfe</t>
+          <t>https://www.fondsexklusiv.de/private-credit-debatte-entfacht/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>46049</v>
+        <v>46097</v>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Markt Einblicke</t>
+          <t>Kreditwesen (Verlagsgruppe Knapp-Richardi)</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Mikrofinanzanleihen 2026: Stabile Renditen aus der Realwirtschaft</t>
+          <t>Mikrofinanz als Anlageklasse</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -1726,31 +1772,37 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>Print</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G38" s="4" t="inlineStr"/>
+          <t>Print &amp; Online</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>https://www.kreditwesen.de/kreditwesen/themenschwerpunkte/aufsaetze/mikrofinanz-anlageklasse-id107511.html</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>46044</v>
+        <v>46094</v>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Frankfurter Allgemeine Zeitung</t>
+          <t>investrends.ch</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Beim Klimaschutz mehr Marktwirtschaft wagen</t>
+          <t>Der blinde Fleck der Private-Credit-Debatte</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
@@ -1758,32 +1810,34 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F39" s="4" t="n">
-        <v>1</v>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>https://www.faz.net/pro/weltwirtschaft/klima-ressourcen/klimapolitik-sollte-auf-mikrofinanzierung-statt-grossprojekte-setzen-accg-200431361.html</t>
+          <t>https://investrends.ch/aktuell/investments/der-blinde-fleck-der-private-credit-debatte/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>46038</v>
+        <v>46093</v>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>E-fundresearch</t>
+          <t>Finanzen100.de</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Umfrage: Welche Chancen und Risiken Experten 2026 in den Private Markets sehen</t>
+          <t>Um den vollen Funktionsumfang dieser Webseite zu erfahren, benötigen Sie JavaScript.</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>DACH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
@@ -1791,27 +1845,29 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F40" s="4" t="n">
-        <v>2</v>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>https://e-fundresearch.com/funds/artikel/57840-umfrage-welche-chancen-und-risiken-experten-2026-in-den-private-markets-sehen?page=5</t>
+          <t>https://www.finanzen100.de/premium/bernecker-boersenkompass/marktkommentar-der-trugschluss-der-sicheren-haefen_H1356104965_6799449/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>46035</v>
+        <v>46091</v>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Finews</t>
+          <t>Swiss Finance AI</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Start 2026: Disziplin als Renditequelle bei KMU-Private Debt</t>
+          <t>Warum tokenisierte Anleihen mehr sind als ein Trend</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -1824,27 +1880,25 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F41" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="F41" s="4" t="inlineStr"/>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>https://www.finews.ch/news/finanzplatz/70792-start2026-assetmanagement-mk-global-kapital-michele-mattioda-privat-debt-kmu-mikro</t>
+          <t>https://www.swissfinanceai.ch/blog/swiss-finance/warum-tokenisierte-anleihen-mehr-sind-als-ein-trend</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>46029</v>
+        <v>46085</v>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Markt Einblicke</t>
+          <t>markteinblicke.de</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Mikrofinanzanleihen 2026: Stabile Renditen aus der Realwirtschaft</t>
+          <t>Tokenisierte Anleihen: Mehr Governance erforderlich</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1857,27 +1911,29 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F42" s="4" t="n">
-        <v>2</v>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>Louiza Savchenko</t>
+        </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>https://markteinblicke.de/127407/2026/01/mikrofinanzanleihen-2026-stabile-renditen-aus-der-realwirtschaft/</t>
+          <t>https://markteinblicke.de/128943/2026/03/tokenisierte-anleihen-mehr-governance-erforderlich/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>46028</v>
+        <v>46085</v>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>portfolio institutionell</t>
+          <t>gruenderkueche.de</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Große Wirkung mit kleinen Krediten</t>
+          <t>Weltfrauentag: Unternehmerinnen fehlt weiterhin der Zugang zu Kapital</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1890,32 +1946,34 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F43" s="4" t="n">
-        <v>1</v>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>Louiza Savchenko</t>
+        </is>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>https://www.portfolio-institutionell.de/grosse-wirkung-mit-kleinen-krediten/</t>
+          <t>https://www.gruenderkueche.de/news/finanzen-news/weltfrauentag-unternehmerinnen-fehlt-weiterhin-der-zugang-zu-kapital/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>46000</v>
+        <v>46083</v>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>investrends.ch</t>
+          <t>altii.de</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Neue Managementgesellschaft für den Impact-Fonds ALTERNATIVE</t>
+          <t>Unternehmerinnen fehlt weltweit der Zugang zu Kapital</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
@@ -1923,32 +1981,30 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F44" s="4" t="n">
-        <v>2</v>
-      </c>
+      <c r="F44" s="4" t="inlineStr"/>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>https://investrends.ch/aktuell/investments/neue-managementgesellschaft-fur-den-impact-fonds-alternative/</t>
+          <t>https://www.altii.de/edai-71550571-cb6c-4c09-93da-bd99b822c245/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>45999</v>
+        <v>46083</v>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Moneycab</t>
+          <t>dfpa.info</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>MK Global Kapital wird per 1. Januar Managementgesellschaft für den Impact-Fonds ALTERNATIVE</t>
+          <t>Unternehmerinnen fehlt weltweit der Zugang zu Kapital</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
@@ -1956,27 +2012,29 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F45" s="4" t="n">
-        <v>2</v>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>Louiza Savchenko</t>
+        </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>https://www.moneycab.com/finanz/mk-global-kapital-wird-per-1-januar-managementgesellschaft-fuer-den-impact-fonds-alternative/</t>
+          <t>https://www.dfpa.info/maerkte-studien-news/unternehmerinnen-fehlt-weltweit-der-zugang-zu-kapital/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>45997</v>
+        <v>46077</v>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>bondguide.de</t>
+          <t>dfpa.info</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Mikro Kapital Management: Impact Investing ist kein Charity</t>
+          <t>Wenn Geschäftsbanken passen, helfen Mikrofinanzfonds</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1989,32 +2047,34 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F46" s="4" t="n">
-        <v>2</v>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>https://www.bondguide.de/topnews/mikro-kapital-management-impact-investing-ist-kein-charity/</t>
+          <t>https://www.dfpa.info/top-story/wenn-geschaeftsbanken-passen-helfen-mikrofinanzfonds.html</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>45985</v>
+        <v>46076</v>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Finews</t>
+          <t>exxecnews.org</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist über Mikrofinanzen: Sollten vom hohen Ross herunterkommen</t>
+          <t>Teil I: Wenn Geschäftsbanken passen, helfen Mikrofinanzfonds</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
@@ -2022,32 +2082,30 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F47" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="F47" s="4" t="inlineStr"/>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>https://www.finews.ch/news/finanzplatz/70147-mikro-capital-johannes-feist-kuenstliche-intelligenz-blockchain-rumaenien-europa-mikrofinanzen-finanzplatz-schweiz</t>
+          <t>https://exxecnews.org/wp-content/uploads/2026/02/Ausgabe-05_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>45973</v>
+        <v>46071</v>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>investrends.ch</t>
+          <t>dfpa.info</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Mikrofinanz ist Private Debt mit direkter Verbindung zur Realwirtschaft</t>
+          <t>Mikrofinanz: Besonderheit Anleihen mit festem Zins</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
@@ -2055,32 +2113,34 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F48" s="4" t="n">
-        <v>2</v>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>https://investrends.ch/aktuell/investments/mikrofinanz-ist-private-debt-mit-direkter-verbindung-zur-realwirtschaft/</t>
+          <t>https://www.dfpa.info/interview/mikrofinanz-besonderheit-anleihen-mit-festem-zins.html</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>45848</v>
+        <v>46069</v>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Handelszeitung</t>
+          <t>Börsen-Kurier</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Zwischen ESG-Müdigkeit und Wirkungsanspruch</t>
+          <t>Privates Kapital für noch nicht entwickelte Märkte</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>DACH</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
@@ -2088,43 +2148,863 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F49" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G49" s="4" t="inlineStr">
-        <is>
-          <t>https://www.handelszeitung.ch/specials/nachhaltiges-investieren-2024/zwischen-esg-mudigkeit-und-wirkungsanspruch-841576</t>
-        </is>
-      </c>
+      <c r="F49" s="4" t="inlineStr"/>
+      <c r="G49" s="4" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
+        <v>46069</v>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>boerse-social.com</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>Börse-Inputs auf Spotify zu u.a. Do&amp;Co, Bawag, Nervigem und Mikrokrediten</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t>https://boerse-social.com/2026/02/16/borse-inputs_auf_spotify_zu_ua_doco_bawag_nervigem_und_mikrokrediten_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="n">
+        <v>46067</v>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>finanznachrichten.de</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>Security Conference München 2026: öffentliche Mittel als Hebel nutzen</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="inlineStr">
+        <is>
+          <t>https://www.finanznachrichten.de/nachrichten-2026-02/67704129-security-conference-muenchen-2026-oeffentliche-mittel-als-hebel-nutzen-144.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="n">
+        <v>46067</v>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>bondguide.de</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>Security Conference München 2026: öffentliche Mittel als Hebel nutzen</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bondguide.de/topnews/security-conference-muenchen-2026-oeffentliche-mittel-als-hebel-nutzen/</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="n">
+        <v>46067</v>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>geldmeisterin.com</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>Mikrokredite gerade jetzt zur Risikostreuung</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G53" s="4" t="inlineStr">
+        <is>
+          <t>https://www.geldmeisterin.com/index.php/2026/02/14/mikrokredite-gerade-jetzt-zur-risikostreuung/</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="n">
+        <v>46067</v>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>geldmeisterin.com</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>Mikrokredite als Anlagealternative</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="inlineStr">
+        <is>
+          <t>https://podcasters.spotify.com/pod/show/geldmeisterin/episodes/Mikrokredite-als-Anlagealternative-e3f11ln</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="3" t="n">
+        <v>46057</v>
+      </c>
+      <c r="B55" s="4" t="inlineStr">
+        <is>
+          <t>investrends.ch</t>
+        </is>
+      </c>
+      <c r="C55" s="4" t="inlineStr">
+        <is>
+          <t>Private Debt: Warum Prozesse wichtiger sind als Prognosen</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F55" s="4" t="inlineStr">
+        <is>
+          <t>Michele Mattioda</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="inlineStr">
+        <is>
+          <t>https://investrends.ch/aktuell/investments/private-debt-warum-prozesse-wichtiger-sind-als-prognosen/</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="3" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>Payoff</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>Mikrofinanz als Private Debt: Besicherte KMU-Kredite statt «Entwicklungshilfe»</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="inlineStr">
+        <is>
+          <t>https://www.payoff.ch/news/mikrofinanz-als-private-debt-besicherte-kmu-kredite-statt-entwicklungshilfe</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="B57" s="4" t="inlineStr">
+        <is>
+          <t>Markt Einblicke</t>
+        </is>
+      </c>
+      <c r="C57" s="4" t="inlineStr">
+        <is>
+          <t>Mikrofinanzanleihen 2026: Stabile Renditen aus der Realwirtschaft</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>Print</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr"/>
+      <c r="G57" s="4" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="3" t="n">
+        <v>46044</v>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>Frankfurter Allgemeine Zeitung</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>Beim Klimaschutz mehr Marktwirtschaft wagen</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F58" s="4" t="inlineStr"/>
+      <c r="G58" s="4" t="inlineStr">
+        <is>
+          <t>https://www.faz.net/pro/weltwirtschaft/klima-ressourcen/klimapolitik-sollte-auf-mikrofinanzierung-statt-grossprojekte-setzen-accg-200431361.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="3" t="n">
+        <v>46038</v>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>E-fundresearch</t>
+        </is>
+      </c>
+      <c r="C59" s="4" t="inlineStr">
+        <is>
+          <t>Umfrage: Welche Chancen und Risiken Experten 2026 in den Private Markets sehen</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>DACH</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F59" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t>https://e-fundresearch.com/funds/artikel/57840-umfrage-welche-chancen-und-risiken-experten-2026-in-den-private-markets-sehen?page=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="3" t="n">
+        <v>46035</v>
+      </c>
+      <c r="B60" s="4" t="inlineStr">
+        <is>
+          <t>Finews</t>
+        </is>
+      </c>
+      <c r="C60" s="4" t="inlineStr">
+        <is>
+          <t>Start 2026: Disziplin als Renditequelle bei KMU-Private Debt</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F60" s="4" t="inlineStr">
+        <is>
+          <t>Michele Mattioda</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="inlineStr">
+        <is>
+          <t>https://www.finews.ch/news/finanzplatz/70792-start2026-assetmanagement-mk-global-kapital-michele-mattioda-privat-debt-kmu-mikro</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="3" t="n">
+        <v>46029</v>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>Markt Einblicke</t>
+        </is>
+      </c>
+      <c r="C61" s="4" t="inlineStr">
+        <is>
+          <t>Mikrofinanzanleihen 2026: Stabile Renditen aus der Realwirtschaft</t>
+        </is>
+      </c>
+      <c r="D61" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E61" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t>https://markteinblicke.de/127407/2026/01/mikrofinanzanleihen-2026-stabile-renditen-aus-der-realwirtschaft/</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="n">
+        <v>46028</v>
+      </c>
+      <c r="B62" s="4" t="inlineStr">
+        <is>
+          <t>portfolio institutionell</t>
+        </is>
+      </c>
+      <c r="C62" s="4" t="inlineStr">
+        <is>
+          <t>Große Wirkung mit kleinen Krediten</t>
+        </is>
+      </c>
+      <c r="D62" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G62" s="4" t="inlineStr">
+        <is>
+          <t>https://www.portfolio-institutionell.de/grosse-wirkung-mit-kleinen-krediten/</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="3" t="n">
+        <v>46000</v>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>investrends.ch</t>
+        </is>
+      </c>
+      <c r="C63" s="4" t="inlineStr">
+        <is>
+          <t>Neue Managementgesellschaft für den Impact-Fonds ALTERNATIVE</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G63" s="4" t="inlineStr">
+        <is>
+          <t>https://investrends.ch/aktuell/investments/neue-managementgesellschaft-fur-den-impact-fonds-alternative/</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="3" t="n">
+        <v>45999</v>
+      </c>
+      <c r="B64" s="4" t="inlineStr">
+        <is>
+          <t>Moneycab</t>
+        </is>
+      </c>
+      <c r="C64" s="4" t="inlineStr">
+        <is>
+          <t>MK Global Kapital wird per 1. Januar Managementgesellschaft für den Impact-Fonds ALTERNATIVE</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="E64" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F64" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G64" s="4" t="inlineStr">
+        <is>
+          <t>https://www.moneycab.com/finanz/mk-global-kapital-wird-per-1-januar-managementgesellschaft-fuer-den-impact-fonds-alternative/</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="n">
+        <v>45999</v>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>dfpa.info</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>MK Global Kapital wird Managementgesellschaft für Impact-Fonds "Alternative"</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G65" s="4" t="inlineStr">
+        <is>
+          <t>https://www.dfpa.info/investmentfonds-news/mk-global-kapital-wird-managementgesellschaft-fuer-impact-fonds-alternative/</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="n">
+        <v>45997</v>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>bondguide.de</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>Mikro Kapital Management: Impact Investing ist kein Charity</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bondguide.de/topnews/mikro-kapital-management-impact-investing-ist-kein-charity/</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="n">
+        <v>45996</v>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>finanznachrichten.de</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>Mikro Kapital Management: "Impact Investing ist kein Charity"</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G67" s="4" t="inlineStr">
+        <is>
+          <t>https://www.finanznachrichten.de/nachrichten-2025-12/67161108-mikro-kapital-management-impact-investing-ist-kein-charity-144.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="n">
+        <v>45995</v>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>dfpa.info</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>Mikro Kapital platziert erstmals Anleihe an Luxemburger Börse</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G68" s="4" t="inlineStr">
+        <is>
+          <t>https://www.dfpa.info/investmentfonds-news/mikro-kapital-platziert-erstmals-emtn-anleihen-des-fonds-alternative-an-luxemburger-boerse/</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="n">
+        <v>45985</v>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>Finews</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist über Mikrofinanzen: Sollten vom hohen Ross herunterkommen</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G69" s="4" t="inlineStr">
+        <is>
+          <t>https://www.finews.ch/news/finanzplatz/70147-mikro-capital-johannes-feist-kuenstliche-intelligenz-blockchain-rumaenien-europa-mikrofinanzen-finanzplatz-schweiz</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="n">
+        <v>45973</v>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>investrends.ch</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>Mikrofinanz ist Private Debt mit direkter Verbindung zur Realwirtschaft</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G70" s="4" t="inlineStr">
+        <is>
+          <t>https://investrends.ch/aktuell/investments/mikrofinanz-ist-private-debt-mit-direkter-verbindung-zur-realwirtschaft/</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="n">
+        <v>45968</v>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>Frankfurter Rundschau</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>Merz in Brasilien: Bundeskanzler fordert „globale Kraftanstrengung“ für Klimaschutz bei COP30</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G71" s="4" t="inlineStr">
+        <is>
+          <t>https://www.fr.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>BondGuide</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>Klimafinanzierung bei COP 30: von Zusagen zu Wirkung entfalten</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G72" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bondguide.de/topnews/klimafinanzierung-bei-cop-30-von-zusagen-zu-wirkung-entfalten/</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="3" t="n">
+        <v>45848</v>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>Handelszeitung</t>
+        </is>
+      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>Zwischen ESG-Müdigkeit und Wirkungsanspruch</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr"/>
+      <c r="G73" s="4" t="inlineStr">
+        <is>
+          <t>https://www.handelszeitung.ch/specials/nachhaltiges-investieren-2024/zwischen-esg-mudigkeit-und-wirkungsanspruch-841576</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="3" t="n">
         <v>45292</v>
       </c>
-      <c r="B50" s="4" t="inlineStr">
+      <c r="B74" s="4" t="inlineStr">
         <is>
           <t>FONDS exklusiv Österreich</t>
         </is>
       </c>
-      <c r="C50" s="4" t="inlineStr">
+      <c r="C74" s="4" t="inlineStr">
         <is>
           <t>Schwellenländer: Worauf es jetzt ankommt</t>
         </is>
       </c>
-      <c r="D50" s="4" t="inlineStr">
+      <c r="D74" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>Online</t>
-        </is>
-      </c>
-      <c r="F50" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G50" s="4" t="inlineStr">
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G74" s="4" t="inlineStr">
         <is>
           <t>https://www.fondsexklusiv.at/schwellenlaender-worauf-es-jetzt-ankommt/</t>
         </is>
@@ -2144,7 +3024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2165,7 +3045,7 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Source: Sheet '2026 Clippings' (A9:G50)</t>
+          <t>Source: Sheet '2026 Clippings' (A9:G74)</t>
         </is>
       </c>
     </row>
@@ -2183,7 +3063,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>42</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6">
@@ -2203,7 +3083,7 @@
         </is>
       </c>
       <c r="B7" s="10" t="n">
-        <v>46256</v>
+        <v>46311</v>
       </c>
     </row>
     <row r="8">
@@ -2213,7 +3093,7 @@
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9">
@@ -2229,7 +3109,7 @@
     <row r="10">
       <c r="A10" s="7" t="inlineStr">
         <is>
-          <t>Tier-1 / Tier-2 Analysis</t>
+          <t>Clippings by Spokesperson</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
@@ -2241,7 +3121,7 @@
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>Tier</t>
+          <t>Spokesperson</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
@@ -2268,14 +3148,14 @@
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>Tier 1</t>
+          <t>Johannes Feist</t>
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.6818181818181818</v>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
@@ -2289,14 +3169,14 @@
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>Tier 2</t>
+          <t>Louiza Savchenko</t>
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>0.7142857142857143</v>
+        <v>0.1212121212121212</v>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
@@ -2308,23 +3188,45 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>Michele Mattioda</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" s="11" t="n">
+        <v>0.0303030303030303</v>
+      </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
           <t>2025-11</t>
         </is>
       </c>
       <c r="F14" s="8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>(kein Sprecher erkannt)</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="C15" s="11" t="n">
+        <v>0.1666666666666667</v>
+      </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
           <t>2025-12</t>
         </is>
       </c>
       <c r="F15" s="8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -2344,7 +3246,7 @@
         </is>
       </c>
       <c r="F17" s="8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18">
@@ -2354,156 +3256,206 @@
         </is>
       </c>
       <c r="F18" s="8" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19">
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="F19" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20">
       <c r="E20" s="8" t="inlineStr">
         <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="F20" s="8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="F21" s="8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="F22" s="8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="E23" s="8" t="inlineStr">
+        <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="F20" s="8" t="n">
+      <c r="F23" s="8" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="F24" s="8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>Clippings by Country</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>Clippings by Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>Share</t>
+        </is>
+      </c>
+      <c r="E31" s="9" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="F31" s="9" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="G31" s="9" t="inlineStr">
+        <is>
+          <t>Share</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C32" s="11" t="n">
+        <v>0.04545454545454546</v>
+      </c>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F32" s="8" t="n">
+        <v>64</v>
+      </c>
+      <c r="G32" s="11" t="n">
+        <v>0.9696969696969697</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="C33" s="11" t="n">
+        <v>0.2575757575757576</v>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>Print</t>
+        </is>
+      </c>
+      <c r="F33" s="8" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="7" t="inlineStr">
-        <is>
-          <t>Clippings by Country</t>
-        </is>
-      </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>Clippings by Type</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>Country</t>
-        </is>
-      </c>
-      <c r="B26" s="9" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
-      </c>
-      <c r="C26" s="9" t="inlineStr">
-        <is>
-          <t>Share</t>
-        </is>
-      </c>
-      <c r="E26" s="9" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="F26" s="9" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
-      </c>
-      <c r="G26" s="9" t="inlineStr">
-        <is>
-          <t>Share</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="8" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="B27" s="8" t="n">
-        <v>3</v>
-      </c>
-      <c r="C27" s="11" t="n">
-        <v>0.07142857142857142</v>
-      </c>
-      <c r="E27" s="8" t="inlineStr">
-        <is>
-          <t>Online</t>
-        </is>
-      </c>
-      <c r="F27" s="8" t="n">
-        <v>40</v>
-      </c>
-      <c r="G27" s="11" t="n">
-        <v>0.9523809523809523</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>CH</t>
-        </is>
-      </c>
-      <c r="B28" s="8" t="n">
-        <v>12</v>
-      </c>
-      <c r="C28" s="11" t="n">
-        <v>0.2857142857142857</v>
-      </c>
-      <c r="E28" s="8" t="inlineStr">
-        <is>
-          <t>Print</t>
-        </is>
-      </c>
-      <c r="F28" s="8" t="n">
+      <c r="G33" s="11" t="n">
+        <v>0.01515151515151515</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="n">
+        <v>44</v>
+      </c>
+      <c r="C34" s="11" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>Print &amp; Online</t>
+        </is>
+      </c>
+      <c r="F34" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="G28" s="11" t="n">
-        <v>0.02380952380952381</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="8" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="B29" s="8" t="n">
-        <v>25</v>
-      </c>
-      <c r="C29" s="11" t="n">
-        <v>0.5952380952380952</v>
-      </c>
-      <c r="E29" s="8" t="inlineStr">
-        <is>
-          <t>Print &amp; Online</t>
-        </is>
-      </c>
-      <c r="F29" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" s="11" t="n">
-        <v>0.02380952380952381</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="8" t="inlineStr">
+      <c r="G34" s="11" t="n">
+        <v>0.01515151515151515</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>DACH</t>
         </is>
       </c>
-      <c r="B30" s="8" t="n">
+      <c r="B35" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="C30" s="11" t="n">
-        <v>0.04761904761904762</v>
+      <c r="C35" s="11" t="n">
+        <v>0.0303030303030303</v>
       </c>
     </row>
   </sheetData>

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46311.43477349239</v>
+        <v>46311.55189469051</v>
       </c>
     </row>
     <row r="8">
@@ -754,21 +754,21 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>46311</v>
+        <v>46304</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Windmesse</t>
+          <t>Moneycab</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>COP30: Klimafinanzierung muss endlich in den Unternehmen ankommen</t>
+          <t>Die Obligation ist tokenisiert. Doch womit wird sie bezahlt?</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -778,12 +778,12 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist</t>
+          <t>Louiza Savchenko</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>https://w3.windmesse.de/windenergie/news/48059-cop30-klimafinanzierung-muss-endlich-in-den-unternehmen-ankommen</t>
+          <t>https://www.moneycab.com/dossiers/die-obligation-ist-tokenisiert-doch-womit-wird-sie-bezahlt/</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Moneycab</t>
+          <t>finanznachrichten.de</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -818,22 +818,22 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>https://www.moneycab.com/dossiers/die-obligation-ist-tokenisiert-doch-womit-wird-sie-bezahlt/</t>
+          <t>https://www.finanznachrichten.de/nachrichten-2026-10/69801367-die-obligation-ist-tokenisiert-doch-womit-wird-sie-bezahlt-095.htm</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>46304</v>
+        <v>46294</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>finanznachrichten.de</t>
+          <t>Markt Einblicke</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Die Obligation ist tokenisiert. Doch womit wird sie bezahlt?</t>
+          <t>Nach dem Ernteeinbruch: Warum es jetzt auf die richtige Finanzierung ankommt</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -848,27 +848,27 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Louiza Savchenko</t>
+          <t>Johannes Feist</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>https://www.finanznachrichten.de/nachrichten-2026-10/69801367-die-obligation-ist-tokenisiert-doch-womit-wird-sie-bezahlt-095.htm</t>
+          <t>https://markteinblicke.de/133297/2026/09/nach-dem-ernteeinbruch-warum-es-jetzt-auf-die-richtige-finanzierung-ankommt/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>46294</v>
+        <v>46273</v>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Markt Einblicke</t>
+          <t>Private Banking Magazin</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Nach dem Ernteeinbruch: Warum es jetzt auf die richtige Finanzierung ankommt</t>
+          <t>Private Credit in Zentralasien</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -888,22 +888,22 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>https://markteinblicke.de/133297/2026/09/nach-dem-ernteeinbruch-warum-es-jetzt-auf-die-richtige-finanzierung-ankommt/</t>
+          <t>https://www.private-banking-magazin.de/private-credit-zentralasien-lokale-unternehmenskredite/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>46273</v>
+        <v>46256</v>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Private Banking Magazin</t>
+          <t>BondGuide</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>In Usbekistan fehlen kleinen Firmen 6 Milliarden Dollar Kredit. Johannes Feist erklärt, wann Anleger davon profitieren – und wann sie besser Abstand halten.</t>
+          <t>Niedrigwasser zeigt die Geografie des Kreditrisikos</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -923,27 +923,27 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>https://www.private-banking-magazin.de/private-credit-zentralasien-lokale-unternehmenskredite/</t>
+          <t>https://www.bondguide.de/topnews/niedrigwasser-zeigt-die-geografie-des-kreditrisikos/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>46256</v>
+        <v>46251</v>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>BondGuide</t>
+          <t>Finanz und Wirtschaft</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Niedrigwasser zeigt die Geografie des Kreditrisikos</t>
+          <t>Die Schweiz finanziert Wasserresilienz überall – nur nicht im Inland</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -953,32 +953,32 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist</t>
+          <t>Louiza Savchenko</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>https://www.bondguide.de/topnews/niedrigwasser-zeigt-die-geografie-des-kreditrisikos/</t>
+          <t>https://www.fuw.ch/wasserrisiko-was-die-schweiz-von-zentralasien-lernen-kann-152625611421</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>46251</v>
+        <v>46247</v>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Finanz und Wirtschaft</t>
+          <t>Markt Einblicke</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Die Schweiz finanziert Wasserresilienz überall – nur nicht im Inland</t>
+          <t>Mikrofinanzanleihen: Worauf es bei Kreditqualität und Struktur ankommt</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -988,18 +988,18 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Louiza Savchenko</t>
+          <t>Johannes Feist</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>https://www.fuw.ch/wasserrisiko-was-die-schweiz-von-zentralasien-lernen-kann-152625611421</t>
+          <t>https://markteinblicke.de/132318/2026/08/mikrofinanzanleihen-worauf-es-bei-kreditqualitaet-und-struktur-ankommt/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>46247</v>
+        <v>46238</v>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Mikrofinanzanleihen: Worauf es bei Kreditqualität und Struktur ankommt</t>
+          <t>Euro-Kupon, lokale Cashflows: Wo das Währungsrisiko wirklich liegt</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -1028,27 +1028,27 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>https://markteinblicke.de/132318/2026/08/mikrofinanzanleihen-worauf-es-bei-kreditqualitaet-und-struktur-ankommt/</t>
+          <t>https://markteinblicke.de/132045/2026/08/euro-kupon-lokale-cashflows-wo-das-waehrungsrisiko-wirklich-liegt/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>46238</v>
+        <v>46234</v>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Markt Einblicke</t>
+          <t>Moneycab</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Euro-Kupon, lokale Cashflows: Wo das Währungsrisiko wirklich liegt</t>
+          <t>Johannes Feist, CEO MK Global Kapital, im Interview</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>https://markteinblicke.de/132045/2026/08/euro-kupon-lokale-cashflows-wo-das-waehrungsrisiko-wirklich-liegt/</t>
+          <t>https://www.moneycab.com/interviews/ceo-interviews/johannes-feist-ceo-mk-global-kapital-im-interview/</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Moneycab</t>
+          <t>finanznachrichten.de</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -1083,7 +1083,7 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -1098,22 +1098,22 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>https://www.moneycab.com/interviews/ceo-interviews/johannes-feist-ceo-mk-global-kapital-im-interview/</t>
+          <t>https://www.finanznachrichten.de/nachrichten-2026-07/69177994-johannes-feist-ceo-mk-global-kapital-im-interview-095.htm</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>46234</v>
+        <v>46231</v>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>finanznachrichten.de</t>
+          <t>BondGuide</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist, CEO MK Global Kapital, im Interview</t>
+          <t>Private Credit: Was Anleiheinvestoren hinter dem Kupon prüfen sollten</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -1133,27 +1133,27 @@
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>https://www.finanznachrichten.de/nachrichten-2026-07/69177994-johannes-feist-ceo-mk-global-kapital-im-interview-095.htm</t>
+          <t>https://www.bondguide.de/topnews/private-credit-was-anleiheinvestoren-hinter-dem-kupon-pruefen-sollten/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>46231</v>
+        <v>46183</v>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>BondGuide</t>
+          <t>Finews</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Private Credit: Was Anleiheinvestoren hinter dem Kupon prüfen sollten</t>
+          <t>Johannes Feist: «Einer meiner unerfüllter Träume ist der Sportfliegerschein»</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -1168,27 +1168,27 @@
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>https://www.bondguide.de/topnews/private-credit-was-anleiheinvestoren-hinter-dem-kupon-pruefen-sollten/</t>
+          <t>https://www.finews.ch/themen/high-end/72456-johannes-feist-einer-meiner-unerfuellter-traeume-ist-der-sportfliegerschein-ceo-global-kapital</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>46183</v>
+        <v>46169</v>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Finews</t>
+          <t>Markt Einblicke</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist: «Einer meiner unerfüllter Träume ist der Sportfliegerschein»</t>
+          <t>Warum der Blick auf den Ölpreis nicht reicht</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -1203,27 +1203,27 @@
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>https://www.finews.ch/themen/high-end/72456-johannes-feist-einer-meiner-unerfuellter-traeume-ist-der-sportfliegerschein-ceo-global-kapital</t>
+          <t>https://markteinblicke.de/130696/2026/05/warum-der-blick-auf-den-oelpreis-nicht-reicht/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>46169</v>
+        <v>46164</v>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Markt Einblicke</t>
+          <t>Moneycab</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Warum der Blick auf den Ölpreis nicht reicht</t>
+          <t>Nicht die Grösse des Kredits entscheidet, sondern seine Wirkung</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
@@ -1238,27 +1238,27 @@
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>https://markteinblicke.de/130696/2026/05/warum-der-blick-auf-den-oelpreis-nicht-reicht/</t>
+          <t>https://www.moneycab.com/dossiers/nicht-die-groesse-des-kredits-entscheidet-sondern-seine-wirkung/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>46164</v>
+        <v>46149</v>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Moneycab</t>
+          <t>Markt Einblicke</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Nicht die Grösse des Kredits entscheidet, sondern seine Wirkung</t>
+          <t>Mikrofinanz-Anleihen: Ein wachsender Markt</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
@@ -1273,22 +1273,22 @@
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>https://www.moneycab.com/dossiers/nicht-die-groesse-des-kredits-entscheidet-sondern-seine-wirkung/</t>
+          <t>https://markteinblicke.de/130263/2026/05/mikrofinanz-anleihen-ein-wachsender-markt/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>46149</v>
+        <v>46125</v>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Markt Einblicke</t>
+          <t>cash-online.de</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Mikrofinanz-Anleihen: Ein wachsender Markt</t>
+          <t>Tokenisierte Anleihen: Was sich für Anleger ändert und was nicht</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -1303,27 +1303,27 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist</t>
+          <t>Louiza Savchenko</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>https://markteinblicke.de/130263/2026/05/mikrofinanz-anleihen-ein-wachsender-markt/</t>
+          <t>https://www.cash-online.de/a/tokenisierte-anleihen-was-sich-fuer-anleger-aendert-und-was-nicht-715994/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>46125</v>
+        <v>46105</v>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>cash-online.de</t>
+          <t>Frankfurter Allgemeine Zeitung</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Tokenisierte Anleihen: Was sich für Anleger ändert und was nicht</t>
+          <t>Sorgen um Privatkredite: Finanzkrise oder silberne Aera?</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -1336,14 +1336,10 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>Louiza Savchenko</t>
-        </is>
-      </c>
+      <c r="F25" s="4" t="inlineStr"/>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>https://www.cash-online.de/a/tokenisierte-anleihen-was-sich-fuer-anleger-aendert-und-was-nicht-715994/</t>
+          <t>https://www.faz.net/pro/meine-finanzen/zinsen/sorgen-um-privatkredite-finanzkrise-oder-silberne-aera-110376123.html</t>
         </is>
       </c>
     </row>
@@ -1353,12 +1349,12 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Frankfurter Allgemeine Zeitung</t>
+          <t>DAS INVESTMENT</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Sorgen um Privatkredite: Finanzkrise oder silberne Aera?</t>
+          <t>Private Credit unter Druck: Wenn das Geld nicht mehr herauskommt</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -1374,7 +1370,7 @@
       <c r="F26" s="4" t="inlineStr"/>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>https://www.faz.net/pro/meine-finanzen/zinsen/sorgen-um-privatkredite-finanzkrise-oder-silberne-aera-110376123.html</t>
+          <t>https://www.dasinvestment.com/private-credit-unter-druck-wenn-das-geld-nicht-mehr-herauskommt/</t>
         </is>
       </c>
     </row>
@@ -1384,17 +1380,17 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>DAS INVESTMENT</t>
+          <t>FONDS exklusiv Oesterreich</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Private Credit unter Druck: Wenn das Geld nicht mehr herauskommt</t>
+          <t>Private Credit-Debatte entfacht</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -1402,25 +1398,29 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr"/>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>https://www.dasinvestment.com/private-credit-unter-druck-wenn-das-geld-nicht-mehr-herauskommt/</t>
+          <t>https://www.fondsexklusiv.at/private-credit-debatte-entfacht/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>46105</v>
+        <v>46102</v>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>FONDS exklusiv Oesterreich</t>
+          <t>Der Standard</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Private Credit-Debatte entfacht</t>
+          <t>Pakistan spart Milliarden an fossilen Importen: Wie hat es das gemacht?</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
@@ -1433,14 +1433,10 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F28" s="4" t="inlineStr">
-        <is>
-          <t>Johannes Feist</t>
-        </is>
-      </c>
+      <c r="F28" s="4" t="inlineStr"/>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>https://www.fondsexklusiv.at/private-credit-debatte-entfacht/</t>
+          <t>https://www.derstandard.de/story/3000000313347/pakistan-spart-milliarden-an-fossilen-importen-wie-hat-es-das-gemacht</t>
         </is>
       </c>
     </row>
@@ -1450,17 +1446,17 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Der Standard</t>
+          <t>Finews</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Pakistan spart Milliarden an fossilen Importen: Wie hat es das gemacht?</t>
+          <t>Tokenisierung: Louzia Savchenko ueber Innovation und MK Global Kapital</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
@@ -1468,30 +1464,34 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F29" s="4" t="inlineStr"/>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>Louiza Savchenko</t>
+        </is>
+      </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>https://www.derstandard.de/story/3000000313347/pakistan-spart-milliarden-an-fossilen-importen-wie-hat-es-das-gemacht</t>
+          <t>https://www.finews.ch/news/finanzplatz/71578-finews-first-tokenisierung-louzia-savchenko-finanzplatz-schweiz-innovation-mk-global-kapital</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>46102</v>
+        <v>46101</v>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Finews</t>
+          <t>BondGuide</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Tokenisierung: Louzia Savchenko ueber Innovation und MK Global Kapital</t>
+          <t>Private Credit ist nicht gleich Private Credit: wo die Risiken wirklich liegen</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
@@ -1501,32 +1501,32 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>Louiza Savchenko</t>
+          <t>Johannes Feist</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>https://www.finews.ch/news/finanzplatz/71578-finews-first-tokenisierung-louzia-savchenko-finanzplatz-schweiz-innovation-mk-global-kapital</t>
+          <t>https://www.bondguide.de/topnews/private-credit-ist-nicht-gleich-private-credit-wo-die-risiken-wirklich-liegen/</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>46101</v>
+        <v>46100</v>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>BondGuide</t>
+          <t>Moneycab</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Private Credit ist nicht gleich Private Credit: wo die Risiken wirklich liegen</t>
+          <t>Nicht nur Öl: Wo der Iran-Konflikt Emerging Markets wirklich trifft</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>https://www.bondguide.de/topnews/private-credit-ist-nicht-gleich-private-credit-wo-die-risiken-wirklich-liegen/</t>
+          <t>https://www.moneycab.com/finanz/nicht-nur-oel-wo-der-iran-konflikt-emerging-markets-wirklich-trifft/</t>
         </is>
       </c>
     </row>
@@ -1551,17 +1551,17 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Moneycab</t>
+          <t>Institutional Money</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Nicht nur Öl: Wo der Iran-Konflikt Emerging Markets wirklich trifft</t>
+          <t>Was der Iran-Schock fuer Emerging Markets veraendert</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
@@ -1569,14 +1569,10 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>Johannes Feist</t>
-        </is>
-      </c>
+      <c r="F32" s="4" t="inlineStr"/>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>https://www.moneycab.com/finanz/nicht-nur-oel-wo-der-iran-konflikt-emerging-markets-wirklich-trifft/</t>
+          <t>https://www.institutional-money.com/news/maerkte/headline/was-der-iran-schock-fuer-emerging-markets-veraendert-249420</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1582,7 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Institutional Money</t>
+          <t>fixed-income.org</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -1604,25 +1600,29 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F33" s="4" t="inlineStr"/>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>https://www.institutional-money.com/news/maerkte/headline/was-der-iran-schock-fuer-emerging-markets-veraendert-249420</t>
+          <t>https://www.fixed-income.org/investment/was-der-iran-schock-fuer-emerging-markets-veraendert.html</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>46100</v>
+        <v>46098</v>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>fixed-income.org</t>
+          <t>finanznachrichten.de</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Was der Iran-Schock fuer Emerging Markets veraendert</t>
+          <t>Private Credit ist nicht gleich Private Credit: Wo die Risiken wirklich liegen</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
@@ -1642,7 +1642,7 @@
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>https://www.fixed-income.org/investment/was-der-iran-schock-fuer-emerging-markets-veraendert.html</t>
+          <t>https://www.finanznachrichten.de/nachrichten-2026-03/67998176-private-credit-ist-nicht-gleich-private-credit-wo-die-risiken-wirklich-liegen-144.htm</t>
         </is>
       </c>
     </row>
@@ -1652,12 +1652,12 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>finanznachrichten.de</t>
+          <t>cash-online.de</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Private Credit ist nicht gleich Private Credit: Wo die Risiken wirklich liegen</t>
+          <t>Gastkommentar: Der blinde Fleck der Private-Credit-Debatte</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -1677,22 +1677,22 @@
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>https://www.finanznachrichten.de/nachrichten-2026-03/67998176-private-credit-ist-nicht-gleich-private-credit-wo-die-risiken-wirklich-liegen-144.htm</t>
+          <t>https://www.cash-online.de/a/gastkommentar-der-blinde-fleck-der-private-credit-debatte-713724/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>46098</v>
+        <v>46097</v>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>cash-online.de</t>
+          <t>FONDS exklusiv</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Gastkommentar: Der blinde Fleck der Private-Credit-Debatte</t>
+          <t>Private Credit-Debatte entfacht</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -1712,7 +1712,7 @@
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>https://www.cash-online.de/a/gastkommentar-der-blinde-fleck-der-private-credit-debatte-713724/</t>
+          <t>https://www.fondsexklusiv.de/private-credit-debatte-entfacht/</t>
         </is>
       </c>
     </row>
@@ -1722,12 +1722,12 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>FONDS exklusiv</t>
+          <t>Kreditwesen (Verlagsgruppe Knapp-Richardi)</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Private Credit-Debatte entfacht</t>
+          <t>Mikrofinanz als Anlageklasse</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Print &amp; Online</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
@@ -1747,32 +1747,32 @@
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>https://www.fondsexklusiv.de/private-credit-debatte-entfacht/</t>
+          <t>https://www.kreditwesen.de/kreditwesen/themenschwerpunkte/aufsaetze/mikrofinanz-anlageklasse-id107511.html</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>46097</v>
+        <v>46094</v>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Kreditwesen (Verlagsgruppe Knapp-Richardi)</t>
+          <t>investrends.ch</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Mikrofinanz als Anlageklasse</t>
+          <t>Der blinde Fleck der Private-Credit-Debatte</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>Print &amp; Online</t>
+          <t>Online</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
@@ -1782,27 +1782,27 @@
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>https://www.kreditwesen.de/kreditwesen/themenschwerpunkte/aufsaetze/mikrofinanz-anlageklasse-id107511.html</t>
+          <t>https://investrends.ch/aktuell/investments/der-blinde-fleck-der-private-credit-debatte/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>46094</v>
+        <v>46093</v>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>investrends.ch</t>
+          <t>Finanzen100.de</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Der blinde Fleck der Private-Credit-Debatte</t>
+          <t>Marktkommentar: Der Trugschluss der sicheren Häfen</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
@@ -1817,27 +1817,27 @@
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>https://investrends.ch/aktuell/investments/der-blinde-fleck-der-private-credit-debatte/</t>
+          <t>https://www.finanzen100.de/premium/bernecker-boersenkompass/marktkommentar-der-trugschluss-der-sicheren-haefen_H1356104965_6799449/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>46093</v>
+        <v>46091</v>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Finanzen100.de</t>
+          <t>Swiss Finance AI</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Um den vollen Funktionsumfang dieser Webseite zu erfahren, benötigen Sie JavaScript.</t>
+          <t>Warum tokenisierte Anleihen mehr sind als ein Trend</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
@@ -1845,34 +1845,30 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>Johannes Feist</t>
-        </is>
-      </c>
+      <c r="F40" s="4" t="inlineStr"/>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>https://www.finanzen100.de/premium/bernecker-boersenkompass/marktkommentar-der-trugschluss-der-sicheren-haefen_H1356104965_6799449/</t>
+          <t>https://www.swissfinanceai.ch/blog/swiss-finance/warum-tokenisierte-anleihen-mehr-sind-als-ein-trend</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>46091</v>
+        <v>46085</v>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Swiss Finance AI</t>
+          <t>markteinblicke.de</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Warum tokenisierte Anleihen mehr sind als ein Trend</t>
+          <t>Tokenisierte Anleihen: Mehr Governance erforderlich</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
@@ -1880,10 +1876,14 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F41" s="4" t="inlineStr"/>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>Louiza Savchenko</t>
+        </is>
+      </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>https://www.swissfinanceai.ch/blog/swiss-finance/warum-tokenisierte-anleihen-mehr-sind-als-ein-trend</t>
+          <t>https://markteinblicke.de/128943/2026/03/tokenisierte-anleihen-mehr-governance-erforderlich/</t>
         </is>
       </c>
     </row>
@@ -1893,12 +1893,12 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>markteinblicke.de</t>
+          <t>gruenderkueche.de</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Tokenisierte Anleihen: Mehr Governance erforderlich</t>
+          <t>Weltfrauentag: Unternehmerinnen fehlt weiterhin der Zugang zu Kapital</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1918,22 +1918,22 @@
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>https://markteinblicke.de/128943/2026/03/tokenisierte-anleihen-mehr-governance-erforderlich/</t>
+          <t>https://www.gruenderkueche.de/news/finanzen-news/weltfrauentag-unternehmerinnen-fehlt-weiterhin-der-zugang-zu-kapital/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>46085</v>
+        <v>46083</v>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>gruenderkueche.de</t>
+          <t>altii.de</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Weltfrauentag: Unternehmerinnen fehlt weiterhin der Zugang zu Kapital</t>
+          <t>Unternehmerinnen fehlt weltweit der Zugang zu Kapital</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1946,14 +1946,10 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t>Louiza Savchenko</t>
-        </is>
-      </c>
+      <c r="F43" s="4" t="inlineStr"/>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>https://www.gruenderkueche.de/news/finanzen-news/weltfrauentag-unternehmerinnen-fehlt-weiterhin-der-zugang-zu-kapital/</t>
+          <t>https://www.altii.de/edai-71550571-cb6c-4c09-93da-bd99b822c245/</t>
         </is>
       </c>
     </row>
@@ -1963,7 +1959,7 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>altii.de</t>
+          <t>dfpa.info</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -1981,16 +1977,20 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F44" s="4" t="inlineStr"/>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>Louiza Savchenko</t>
+        </is>
+      </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>https://www.altii.de/edai-71550571-cb6c-4c09-93da-bd99b822c245/</t>
+          <t>https://www.dfpa.info/maerkte-studien-news/unternehmerinnen-fehlt-weltweit-der-zugang-zu-kapital/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>46083</v>
+        <v>46077</v>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Unternehmerinnen fehlt weltweit der Zugang zu Kapital</t>
+          <t>Wenn Geschäftsbanken passen, helfen Mikrofinanzfonds</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -2014,27 +2014,27 @@
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>Louiza Savchenko</t>
+          <t>Johannes Feist</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>https://www.dfpa.info/maerkte-studien-news/unternehmerinnen-fehlt-weltweit-der-zugang-zu-kapital/</t>
+          <t>https://www.dfpa.info/top-story/wenn-geschaeftsbanken-passen-helfen-mikrofinanzfonds.html</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>46077</v>
+        <v>46076</v>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>dfpa.info</t>
+          <t>exxecnews.org</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Wenn Geschäftsbanken passen, helfen Mikrofinanzfonds</t>
+          <t>Teil I: Wenn Geschäftsbanken passen, helfen Mikrofinanzfonds</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -2047,29 +2047,25 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F46" s="4" t="inlineStr">
-        <is>
-          <t>Johannes Feist</t>
-        </is>
-      </c>
+      <c r="F46" s="4" t="inlineStr"/>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>https://www.dfpa.info/top-story/wenn-geschaeftsbanken-passen-helfen-mikrofinanzfonds.html</t>
+          <t>https://exxecnews.org/wp-content/uploads/2026/02/Ausgabe-05_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>46076</v>
+        <v>46071</v>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>exxecnews.org</t>
+          <t>dfpa.info</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Teil I: Wenn Geschäftsbanken passen, helfen Mikrofinanzfonds</t>
+          <t>Mikrofinanz: Besonderheit Anleihen mit festem Zins</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -2082,30 +2078,34 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F47" s="4" t="inlineStr"/>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>https://exxecnews.org/wp-content/uploads/2026/02/Ausgabe-05_2026.pdf</t>
+          <t>https://www.dfpa.info/interview/mikrofinanz-besonderheit-anleihen-mit-festem-zins.html</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>46071</v>
+        <v>46069</v>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>dfpa.info</t>
+          <t>Börsen-Kurier</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Mikrofinanz: Besonderheit Anleihen mit festem Zins</t>
+          <t>Privates Kapital für noch nicht entwickelte Märkte</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>DACH</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
@@ -2113,16 +2113,8 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F48" s="4" t="inlineStr">
-        <is>
-          <t>Johannes Feist</t>
-        </is>
-      </c>
-      <c r="G48" s="4" t="inlineStr">
-        <is>
-          <t>https://www.dfpa.info/interview/mikrofinanz-besonderheit-anleihen-mit-festem-zins.html</t>
-        </is>
-      </c>
+      <c r="F48" s="4" t="inlineStr"/>
+      <c r="G48" s="4" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
@@ -2130,17 +2122,17 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Börsen-Kurier</t>
+          <t>boerse-social.com</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Privates Kapital für noch nicht entwickelte Märkte</t>
+          <t>Börse-Inputs auf Spotify zu u.a. Do&amp;Co, Bawag, Nervigem und Mikrokrediten</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>DACH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
@@ -2148,21 +2140,29 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F49" s="4" t="inlineStr"/>
-      <c r="G49" s="4" t="inlineStr"/>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t>https://boerse-social.com/2026/02/16/borse-inputs_auf_spotify_zu_ua_doco_bawag_nervigem_und_mikrokrediten_1</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
-        <v>46069</v>
+        <v>46067</v>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>boerse-social.com</t>
+          <t>finanznachrichten.de</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>Börse-Inputs auf Spotify zu u.a. Do&amp;Co, Bawag, Nervigem und Mikrokrediten</t>
+          <t>Security Conference München 2026: öffentliche Mittel als Hebel nutzen</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -2182,7 +2182,7 @@
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>https://boerse-social.com/2026/02/16/borse-inputs_auf_spotify_zu_ua_doco_bawag_nervigem_und_mikrokrediten_1</t>
+          <t>https://www.finanznachrichten.de/nachrichten-2026-02/67704129-security-conference-muenchen-2026-oeffentliche-mittel-als-hebel-nutzen-144.htm</t>
         </is>
       </c>
     </row>
@@ -2192,7 +2192,7 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>finanznachrichten.de</t>
+          <t>bondguide.de</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>https://www.finanznachrichten.de/nachrichten-2026-02/67704129-security-conference-muenchen-2026-oeffentliche-mittel-als-hebel-nutzen-144.htm</t>
+          <t>https://www.bondguide.de/topnews/security-conference-muenchen-2026-oeffentliche-mittel-als-hebel-nutzen/</t>
         </is>
       </c>
     </row>
@@ -2227,12 +2227,12 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>bondguide.de</t>
+          <t>geldmeisterin.com</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>Security Conference München 2026: öffentliche Mittel als Hebel nutzen</t>
+          <t>Mikrokredite gerade jetzt zur Risikostreuung</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>https://www.bondguide.de/topnews/security-conference-muenchen-2026-oeffentliche-mittel-als-hebel-nutzen/</t>
+          <t>https://www.geldmeisterin.com/index.php/2026/02/14/mikrokredite-gerade-jetzt-zur-risikostreuung/</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Mikrokredite gerade jetzt zur Risikostreuung</t>
+          <t>Mikrokredite als Anlagealternative</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -2287,27 +2287,27 @@
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>https://www.geldmeisterin.com/index.php/2026/02/14/mikrokredite-gerade-jetzt-zur-risikostreuung/</t>
+          <t>https://podcasters.spotify.com/pod/show/geldmeisterin/episodes/Mikrokredite-als-Anlagealternative-e3f11ln</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
-        <v>46067</v>
+        <v>46057</v>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>geldmeisterin.com</t>
+          <t>investrends.ch</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>Mikrokredite als Anlagealternative</t>
+          <t>Private Debt: Warum Prozesse wichtiger sind als Prognosen</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
@@ -2317,27 +2317,27 @@
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist</t>
+          <t>Michele Mattioda</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>https://podcasters.spotify.com/pod/show/geldmeisterin/episodes/Mikrokredite-als-Anlagealternative-e3f11ln</t>
+          <t>https://investrends.ch/aktuell/investments/private-debt-warum-prozesse-wichtiger-sind-als-prognosen/</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
-        <v>46057</v>
+        <v>46055</v>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>investrends.ch</t>
+          <t>Payoff</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>Private Debt: Warum Prozesse wichtiger sind als Prognosen</t>
+          <t>Mikrofinanz als Private Debt: Besicherte KMU-Kredite statt «Entwicklungshilfe»</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -2352,62 +2352,54 @@
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>Michele Mattioda</t>
+          <t>Johannes Feist</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>https://investrends.ch/aktuell/investments/private-debt-warum-prozesse-wichtiger-sind-als-prognosen/</t>
+          <t>https://www.payoff.ch/news/mikrofinanz-als-private-debt-besicherte-kmu-kredite-statt-entwicklungshilfe</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
-        <v>46055</v>
+        <v>46049</v>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Payoff</t>
+          <t>Markt Einblicke</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>Mikrofinanz als Private Debt: Besicherte KMU-Kredite statt «Entwicklungshilfe»</t>
+          <t>Mikrofinanzanleihen 2026: Stabile Renditen aus der Realwirtschaft</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>Online</t>
-        </is>
-      </c>
-      <c r="F56" s="4" t="inlineStr">
-        <is>
-          <t>Johannes Feist</t>
-        </is>
-      </c>
-      <c r="G56" s="4" t="inlineStr">
-        <is>
-          <t>https://www.payoff.ch/news/mikrofinanz-als-private-debt-besicherte-kmu-kredite-statt-entwicklungshilfe</t>
-        </is>
-      </c>
+          <t>Print</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr"/>
+      <c r="G56" s="4" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
-        <v>46049</v>
+        <v>46044</v>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Markt Einblicke</t>
+          <t>Frankfurter Allgemeine Zeitung</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Mikrofinanzanleihen 2026: Stabile Renditen aus der Realwirtschaft</t>
+          <t>Beim Klimaschutz mehr Marktwirtschaft wagen</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -2417,29 +2409,33 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>Print</t>
+          <t>Online</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr"/>
-      <c r="G57" s="4" t="inlineStr"/>
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t>https://www.faz.net/pro/weltwirtschaft/klima-ressourcen/klimapolitik-sollte-auf-mikrofinanzierung-statt-grossprojekte-setzen-accg-200431361.html</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
-        <v>46044</v>
+        <v>46038</v>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Frankfurter Allgemeine Zeitung</t>
+          <t>E-fundresearch</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>Beim Klimaschutz mehr Marktwirtschaft wagen</t>
+          <t>Umfrage: Welche Chancen und Risiken Experten 2026 in den Private Markets sehen</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>DACH</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
@@ -2447,30 +2443,34 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F58" s="4" t="inlineStr"/>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>https://www.faz.net/pro/weltwirtschaft/klima-ressourcen/klimapolitik-sollte-auf-mikrofinanzierung-statt-grossprojekte-setzen-accg-200431361.html</t>
+          <t>https://e-fundresearch.com/funds/artikel/57840-umfrage-welche-chancen-und-risiken-experten-2026-in-den-private-markets-sehen?page=5</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
-        <v>46038</v>
+        <v>46035</v>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>E-fundresearch</t>
+          <t>Finews</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Umfrage: Welche Chancen und Risiken Experten 2026 in den Private Markets sehen</t>
+          <t>Start 2026: Disziplin als Renditequelle bei KMU-Private Debt</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>DACH</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
@@ -2480,32 +2480,32 @@
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist</t>
+          <t>Michele Mattioda</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>https://e-fundresearch.com/funds/artikel/57840-umfrage-welche-chancen-und-risiken-experten-2026-in-den-private-markets-sehen?page=5</t>
+          <t>https://www.finews.ch/news/finanzplatz/70792-start2026-assetmanagement-mk-global-kapital-michele-mattioda-privat-debt-kmu-mikro</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
-        <v>46035</v>
+        <v>46029</v>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Finews</t>
+          <t>Markt Einblicke</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Start 2026: Disziplin als Renditequelle bei KMU-Private Debt</t>
+          <t>Mikrofinanzanleihen 2026: Stabile Renditen aus der Realwirtschaft</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
@@ -2515,27 +2515,27 @@
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>Michele Mattioda</t>
+          <t>Johannes Feist</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>https://www.finews.ch/news/finanzplatz/70792-start2026-assetmanagement-mk-global-kapital-michele-mattioda-privat-debt-kmu-mikro</t>
+          <t>https://markteinblicke.de/127407/2026/01/mikrofinanzanleihen-2026-stabile-renditen-aus-der-realwirtschaft/</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
-        <v>46029</v>
+        <v>46028</v>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Markt Einblicke</t>
+          <t>portfolio institutionell</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Mikrofinanzanleihen 2026: Stabile Renditen aus der Realwirtschaft</t>
+          <t>Große Wirkung mit kleinen Krediten</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -2555,27 +2555,27 @@
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>https://markteinblicke.de/127407/2026/01/mikrofinanzanleihen-2026-stabile-renditen-aus-der-realwirtschaft/</t>
+          <t>https://www.portfolio-institutionell.de/grosse-wirkung-mit-kleinen-krediten/</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
-        <v>46028</v>
+        <v>46000</v>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>portfolio institutionell</t>
+          <t>investrends.ch</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Große Wirkung mit kleinen Krediten</t>
+          <t>Neue Managementgesellschaft für den Impact-Fonds ALTERNATIVE</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
@@ -2590,22 +2590,22 @@
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>https://www.portfolio-institutionell.de/grosse-wirkung-mit-kleinen-krediten/</t>
+          <t>https://investrends.ch/aktuell/investments/neue-managementgesellschaft-fur-den-impact-fonds-alternative/</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
-        <v>46000</v>
+        <v>45999</v>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>investrends.ch</t>
+          <t>Moneycab</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Neue Managementgesellschaft für den Impact-Fonds ALTERNATIVE</t>
+          <t>MK Global Kapital wird per 1. Januar Managementgesellschaft für den Impact-Fonds ALTERNATIVE</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -2625,7 +2625,7 @@
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>https://investrends.ch/aktuell/investments/neue-managementgesellschaft-fur-den-impact-fonds-alternative/</t>
+          <t>https://www.moneycab.com/finanz/mk-global-kapital-wird-per-1-januar-managementgesellschaft-fuer-den-impact-fonds-alternative/</t>
         </is>
       </c>
     </row>
@@ -2635,17 +2635,17 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Moneycab</t>
+          <t>dfpa.info</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>MK Global Kapital wird per 1. Januar Managementgesellschaft für den Impact-Fonds ALTERNATIVE</t>
+          <t>MK Global Kapital wird Managementgesellschaft für Impact-Fonds "Alternative"</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
@@ -2660,22 +2660,22 @@
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>https://www.moneycab.com/finanz/mk-global-kapital-wird-per-1-januar-managementgesellschaft-fuer-den-impact-fonds-alternative/</t>
+          <t>https://www.dfpa.info/investmentfonds-news/mk-global-kapital-wird-managementgesellschaft-fuer-impact-fonds-alternative/</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
-        <v>45999</v>
+        <v>45997</v>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>dfpa.info</t>
+          <t>bondguide.de</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>MK Global Kapital wird Managementgesellschaft für Impact-Fonds "Alternative"</t>
+          <t>Mikro Kapital Management: Impact Investing ist kein Charity</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -2695,22 +2695,22 @@
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>https://www.dfpa.info/investmentfonds-news/mk-global-kapital-wird-managementgesellschaft-fuer-impact-fonds-alternative/</t>
+          <t>https://www.bondguide.de/topnews/mikro-kapital-management-impact-investing-ist-kein-charity/</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
-        <v>45997</v>
+        <v>45996</v>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>bondguide.de</t>
+          <t>finanznachrichten.de</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>Mikro Kapital Management: Impact Investing ist kein Charity</t>
+          <t>Mikro Kapital Management: "Impact Investing ist kein Charity"</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -2730,22 +2730,22 @@
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>https://www.bondguide.de/topnews/mikro-kapital-management-impact-investing-ist-kein-charity/</t>
+          <t>https://www.finanznachrichten.de/nachrichten-2025-12/67161108-mikro-kapital-management-impact-investing-ist-kein-charity-144.htm</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
-        <v>45996</v>
+        <v>45995</v>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>finanznachrichten.de</t>
+          <t>dfpa.info</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Mikro Kapital Management: "Impact Investing ist kein Charity"</t>
+          <t>Mikro Kapital platziert erstmals Anleihe an Luxemburger Börse</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -2765,27 +2765,27 @@
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>https://www.finanznachrichten.de/nachrichten-2025-12/67161108-mikro-kapital-management-impact-investing-ist-kein-charity-144.htm</t>
+          <t>https://www.dfpa.info/investmentfonds-news/mikro-kapital-platziert-erstmals-emtn-anleihen-des-fonds-alternative-an-luxemburger-boerse/</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="n">
-        <v>45995</v>
+        <v>45985</v>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>dfpa.info</t>
+          <t>Finews</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>Mikro Kapital platziert erstmals Anleihe an Luxemburger Börse</t>
+          <t>Johannes Feist über Mikrofinanzen: Sollten vom hohen Ross herunterkommen</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
@@ -2800,22 +2800,22 @@
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>https://www.dfpa.info/investmentfonds-news/mikro-kapital-platziert-erstmals-emtn-anleihen-des-fonds-alternative-an-luxemburger-boerse/</t>
+          <t>https://www.finews.ch/news/finanzplatz/70147-mikro-capital-johannes-feist-kuenstliche-intelligenz-blockchain-rumaenien-europa-mikrofinanzen-finanzplatz-schweiz</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
-        <v>45985</v>
+        <v>45973</v>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Finews</t>
+          <t>investrends.ch</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist über Mikrofinanzen: Sollten vom hohen Ross herunterkommen</t>
+          <t>Mikrofinanz ist Private Debt mit direkter Verbindung zur Realwirtschaft</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -2835,27 +2835,27 @@
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>https://www.finews.ch/news/finanzplatz/70147-mikro-capital-johannes-feist-kuenstliche-intelligenz-blockchain-rumaenien-europa-mikrofinanzen-finanzplatz-schweiz</t>
+          <t>https://investrends.ch/aktuell/investments/mikrofinanz-ist-private-debt-mit-direkter-verbindung-zur-realwirtschaft/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="n">
-        <v>45973</v>
+        <v>45968</v>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>investrends.ch</t>
+          <t>Frankfurter Rundschau</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>Mikrofinanz ist Private Debt mit direkter Verbindung zur Realwirtschaft</t>
+          <t>Merz in Brasilien: Bundeskanzler fordert „globale Kraftanstrengung“ für Klimaschutz bei COP30</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
@@ -2870,22 +2870,22 @@
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>https://investrends.ch/aktuell/investments/mikrofinanz-ist-private-debt-mit-direkter-verbindung-zur-realwirtschaft/</t>
+          <t>https://www.fr.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
-        <v>45968</v>
+        <v>45967</v>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Frankfurter Rundschau</t>
+          <t>Windmesse</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>Merz in Brasilien: Bundeskanzler fordert „globale Kraftanstrengung“ für Klimaschutz bei COP30</t>
+          <t>COP30: Klimafinanzierung muss endlich in den Unternehmen ankommen</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>https://www.fr.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://w3.windmesse.de/windenergie/news/48059-cop30-klimafinanzierung-muss-endlich-in-den-unternehmen-ankommen</t>
         </is>
       </c>
     </row>
@@ -3083,7 +3083,7 @@
         </is>
       </c>
       <c r="B7" s="10" t="n">
-        <v>46311</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="8">
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="F14" s="8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="F25" s="8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -694,7 +694,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G74"/>
+  <dimension ref="A1:G79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46311.55189469051</v>
+        <v>46311.56268766701</v>
       </c>
     </row>
     <row r="8">
@@ -754,16 +754,16 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>46304</v>
+        <v>46309</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Moneycab</t>
+          <t>Netmilk Studio</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Die Obligation ist tokenisiert. Doch womit wird sie bezahlt?</t>
+          <t>Progetti: siti web, brand identity e packaging</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -776,34 +776,30 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>Louiza Savchenko</t>
-        </is>
-      </c>
+      <c r="F9" s="4" t="inlineStr"/>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>https://www.moneycab.com/dossiers/die-obligation-ist-tokenisiert-doch-womit-wird-sie-bezahlt/</t>
+          <t>https://netmilk.ch/progetti/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>46304</v>
+        <v>46309</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>finanznachrichten.de</t>
+          <t>Moneycab</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Die Obligation ist tokenisiert. Doch womit wird sie bezahlt?</t>
+          <t>Kommentare Archives</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -818,22 +814,22 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>https://www.finanznachrichten.de/nachrichten-2026-10/69801367-die-obligation-ist-tokenisiert-doch-womit-wird-sie-bezahlt-095.htm</t>
+          <t>https://www.moneycab.com/category/kommentare/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>46294</v>
+        <v>46306</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Markt Einblicke</t>
+          <t>finanznachrichten.de</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Nach dem Ernteeinbruch: Warum es jetzt auf die richtige Finanzierung ankommt</t>
+          <t>Moneycab | Nachrichten</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -848,32 +844,32 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist</t>
+          <t>Louiza Savchenko</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>https://markteinblicke.de/133297/2026/09/nach-dem-ernteeinbruch-warum-es-jetzt-auf-die-richtige-finanzierung-ankommt/</t>
+          <t>https://www.finanznachrichten.de/nachrichten-medien/moneycab.htm</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>46273</v>
+        <v>46304</v>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Private Banking Magazin</t>
+          <t>Moneycab</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Private Credit in Zentralasien</t>
+          <t>Die Obligation ist tokenisiert. Doch womit wird sie bezahlt?</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -883,27 +879,27 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist</t>
+          <t>Louiza Savchenko</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>https://www.private-banking-magazin.de/private-credit-zentralasien-lokale-unternehmenskredite/</t>
+          <t>https://www.moneycab.com/dossiers/die-obligation-ist-tokenisiert-doch-womit-wird-sie-bezahlt/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>46256</v>
+        <v>46304</v>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>BondGuide</t>
+          <t>finanznachrichten.de</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Niedrigwasser zeigt die Geografie des Kreditrisikos</t>
+          <t>Die Obligation ist tokenisiert. Doch womit wird sie bezahlt?</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -918,32 +914,32 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist</t>
+          <t>Louiza Savchenko</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>https://www.bondguide.de/topnews/niedrigwasser-zeigt-die-geografie-des-kreditrisikos/</t>
+          <t>https://www.finanznachrichten.de/nachrichten-2026-10/69801367-die-obligation-ist-tokenisiert-doch-womit-wird-sie-bezahlt-095.htm</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>46251</v>
+        <v>46300</v>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Finanz und Wirtschaft</t>
+          <t>SALES JOBS</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Die Schweiz finanziert Wasserresilienz überall – nur nicht im Inland</t>
+          <t>Работа оператором в Узбекистане: 23 вакансии — Call-markaz / operator</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -951,20 +947,16 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>Louiza Savchenko</t>
-        </is>
-      </c>
+      <c r="F14" s="4" t="inlineStr"/>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>https://www.fuw.ch/wasserrisiko-was-die-schweiz-von-zentralasien-lernen-kann-152625611421</t>
+          <t>https://salesjobs.uz/lavozim/operator</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>46247</v>
+        <v>46294</v>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
@@ -973,7 +965,7 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Mikrofinanzanleihen: Worauf es bei Kreditqualität und Struktur ankommt</t>
+          <t>Nach dem Ernteeinbruch: Warum es jetzt auf die richtige Finanzierung ankommt</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -993,22 +985,22 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>https://markteinblicke.de/132318/2026/08/mikrofinanzanleihen-worauf-es-bei-kreditqualitaet-und-struktur-ankommt/</t>
+          <t>https://markteinblicke.de/133297/2026/09/nach-dem-ernteeinbruch-warum-es-jetzt-auf-die-richtige-finanzierung-ankommt/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>46238</v>
+        <v>46273</v>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Markt Einblicke</t>
+          <t>Private Banking Magazin</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Euro-Kupon, lokale Cashflows: Wo das Währungsrisiko wirklich liegt</t>
+          <t>Private Credit in Zentralasien</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -1028,27 +1020,27 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>https://markteinblicke.de/132045/2026/08/euro-kupon-lokale-cashflows-wo-das-waehrungsrisiko-wirklich-liegt/</t>
+          <t>https://www.private-banking-magazin.de/private-credit-zentralasien-lokale-unternehmenskredite/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>46234</v>
+        <v>46256</v>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Moneycab</t>
+          <t>BondGuide</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist, CEO MK Global Kapital, im Interview</t>
+          <t>Niedrigwasser zeigt die Geografie des Kreditrisikos</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -1063,27 +1055,27 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>https://www.moneycab.com/interviews/ceo-interviews/johannes-feist-ceo-mk-global-kapital-im-interview/</t>
+          <t>https://www.bondguide.de/topnews/niedrigwasser-zeigt-die-geografie-des-kreditrisikos/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>46234</v>
+        <v>46251</v>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>finanznachrichten.de</t>
+          <t>Finanz und Wirtschaft</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist, CEO MK Global Kapital, im Interview</t>
+          <t>Die Schweiz finanziert Wasserresilienz überall – nur nicht im Inland</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -1093,27 +1085,27 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist</t>
+          <t>Louiza Savchenko</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>https://www.finanznachrichten.de/nachrichten-2026-07/69177994-johannes-feist-ceo-mk-global-kapital-im-interview-095.htm</t>
+          <t>https://www.fuw.ch/wasserrisiko-was-die-schweiz-von-zentralasien-lernen-kann-152625611421</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>46231</v>
+        <v>46247</v>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>BondGuide</t>
+          <t>Markt Einblicke</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Private Credit: Was Anleiheinvestoren hinter dem Kupon prüfen sollten</t>
+          <t>Mikrofinanzanleihen: Worauf es bei Kreditqualität und Struktur ankommt</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -1133,27 +1125,27 @@
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>https://www.bondguide.de/topnews/private-credit-was-anleiheinvestoren-hinter-dem-kupon-pruefen-sollten/</t>
+          <t>https://markteinblicke.de/132318/2026/08/mikrofinanzanleihen-worauf-es-bei-kreditqualitaet-und-struktur-ankommt/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>46183</v>
+        <v>46238</v>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Finews</t>
+          <t>Markt Einblicke</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist: «Einer meiner unerfüllter Träume ist der Sportfliegerschein»</t>
+          <t>Euro-Kupon, lokale Cashflows: Wo das Währungsrisiko wirklich liegt</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -1168,27 +1160,27 @@
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>https://www.finews.ch/themen/high-end/72456-johannes-feist-einer-meiner-unerfuellter-traeume-ist-der-sportfliegerschein-ceo-global-kapital</t>
+          <t>https://markteinblicke.de/132045/2026/08/euro-kupon-lokale-cashflows-wo-das-waehrungsrisiko-wirklich-liegt/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>46169</v>
+        <v>46234</v>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Markt Einblicke</t>
+          <t>Moneycab</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Warum der Blick auf den Ölpreis nicht reicht</t>
+          <t>Johannes Feist, CEO MK Global Kapital, im Interview</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -1203,27 +1195,27 @@
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>https://markteinblicke.de/130696/2026/05/warum-der-blick-auf-den-oelpreis-nicht-reicht/</t>
+          <t>https://www.moneycab.com/interviews/ceo-interviews/johannes-feist-ceo-mk-global-kapital-im-interview/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>46164</v>
+        <v>46234</v>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Moneycab</t>
+          <t>finanznachrichten.de</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Nicht die Grösse des Kredits entscheidet, sondern seine Wirkung</t>
+          <t>Johannes Feist, CEO MK Global Kapital, im Interview</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
@@ -1238,22 +1230,22 @@
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>https://www.moneycab.com/dossiers/nicht-die-groesse-des-kredits-entscheidet-sondern-seine-wirkung/</t>
+          <t>https://www.finanznachrichten.de/nachrichten-2026-07/69177994-johannes-feist-ceo-mk-global-kapital-im-interview-095.htm</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>46149</v>
+        <v>46231</v>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Markt Einblicke</t>
+          <t>BondGuide</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Mikrofinanz-Anleihen: Ein wachsender Markt</t>
+          <t>Private Credit: Was Anleiheinvestoren hinter dem Kupon prüfen sollten</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -1273,22 +1265,22 @@
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>https://markteinblicke.de/130263/2026/05/mikrofinanz-anleihen-ein-wachsender-markt/</t>
+          <t>https://www.bondguide.de/topnews/private-credit-was-anleiheinvestoren-hinter-dem-kupon-pruefen-sollten/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>46125</v>
+        <v>46197</v>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>cash-online.de</t>
+          <t>background.tagesspiegel</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Tokenisierte Anleihen: Was sich für Anleger ändert und was nicht</t>
+          <t>Digitale Kreditvergabe : Kreditzugang ist mehr als ein Score</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -1308,27 +1300,27 @@
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>https://www.cash-online.de/a/tokenisierte-anleihen-was-sich-fuer-anleger-aendert-und-was-nicht-715994/</t>
+          <t>https://background.tagesspiegel.de/finance/briefing/kreditzugang-ist-mehr-als-ein-score</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>46105</v>
+        <v>46183</v>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Frankfurter Allgemeine Zeitung</t>
+          <t>Finews</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Sorgen um Privatkredite: Finanzkrise oder silberne Aera?</t>
+          <t>Johannes Feist: «Einer meiner unerfüllter Träume ist der Sportfliegerschein»</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
@@ -1336,25 +1328,29 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F25" s="4" t="inlineStr"/>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>https://www.faz.net/pro/meine-finanzen/zinsen/sorgen-um-privatkredite-finanzkrise-oder-silberne-aera-110376123.html</t>
+          <t>https://www.finews.ch/themen/high-end/72456-johannes-feist-einer-meiner-unerfuellter-traeume-ist-der-sportfliegerschein-ceo-global-kapital</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>46105</v>
+        <v>46169</v>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>DAS INVESTMENT</t>
+          <t>Markt Einblicke</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Private Credit unter Druck: Wenn das Geld nicht mehr herauskommt</t>
+          <t>Warum der Blick auf den Ölpreis nicht reicht</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -1367,30 +1363,34 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr"/>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>https://www.dasinvestment.com/private-credit-unter-druck-wenn-das-geld-nicht-mehr-herauskommt/</t>
+          <t>https://markteinblicke.de/130696/2026/05/warum-der-blick-auf-den-oelpreis-nicht-reicht/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>46105</v>
+        <v>46164</v>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>FONDS exklusiv Oesterreich</t>
+          <t>Moneycab</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Private Credit-Debatte entfacht</t>
+          <t>Nicht die Grösse des Kredits entscheidet, sondern seine Wirkung</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -1405,27 +1405,27 @@
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>https://www.fondsexklusiv.at/private-credit-debatte-entfacht/</t>
+          <t>https://www.moneycab.com/dossiers/nicht-die-groesse-des-kredits-entscheidet-sondern-seine-wirkung/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>46102</v>
+        <v>46149</v>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Der Standard</t>
+          <t>Markt Einblicke</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Pakistan spart Milliarden an fossilen Importen: Wie hat es das gemacht?</t>
+          <t>Mikrofinanz-Anleihen: Ein wachsender Markt</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
@@ -1433,30 +1433,34 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F28" s="4" t="inlineStr"/>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>https://www.derstandard.de/story/3000000313347/pakistan-spart-milliarden-an-fossilen-importen-wie-hat-es-das-gemacht</t>
+          <t>https://markteinblicke.de/130263/2026/05/mikrofinanz-anleihen-ein-wachsender-markt/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>46102</v>
+        <v>46125</v>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Finews</t>
+          <t>cash-online.de</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Tokenisierung: Louzia Savchenko ueber Innovation und MK Global Kapital</t>
+          <t>Tokenisierte Anleihen: Was sich für Anleger ändert und was nicht</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
@@ -1471,22 +1475,22 @@
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>https://www.finews.ch/news/finanzplatz/71578-finews-first-tokenisierung-louzia-savchenko-finanzplatz-schweiz-innovation-mk-global-kapital</t>
+          <t>https://www.cash-online.de/a/tokenisierte-anleihen-was-sich-fuer-anleger-aendert-und-was-nicht-715994/</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>46101</v>
+        <v>46105</v>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>BondGuide</t>
+          <t>Frankfurter Allgemeine Zeitung</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Private Credit ist nicht gleich Private Credit: wo die Risiken wirklich liegen</t>
+          <t>Sorgen um Privatkredite: Finanzkrise oder silberne Aera?</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -1499,34 +1503,30 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F30" s="4" t="inlineStr">
-        <is>
-          <t>Johannes Feist</t>
-        </is>
-      </c>
+      <c r="F30" s="4" t="inlineStr"/>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>https://www.bondguide.de/topnews/private-credit-ist-nicht-gleich-private-credit-wo-die-risiken-wirklich-liegen/</t>
+          <t>https://www.faz.net/pro/meine-finanzen/zinsen/sorgen-um-privatkredite-finanzkrise-oder-silberne-aera-110376123.html</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>46100</v>
+        <v>46105</v>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Moneycab</t>
+          <t>DAS INVESTMENT</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Nicht nur Öl: Wo der Iran-Konflikt Emerging Markets wirklich trifft</t>
+          <t>Private Credit unter Druck: Wenn das Geld nicht mehr herauskommt</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
@@ -1534,34 +1534,30 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>Johannes Feist</t>
-        </is>
-      </c>
+      <c r="F31" s="4" t="inlineStr"/>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>https://www.moneycab.com/finanz/nicht-nur-oel-wo-der-iran-konflikt-emerging-markets-wirklich-trifft/</t>
+          <t>https://www.dasinvestment.com/private-credit-unter-druck-wenn-das-geld-nicht-mehr-herauskommt/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>46100</v>
+        <v>46105</v>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Institutional Money</t>
+          <t>FONDS exklusiv Oesterreich</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Was der Iran-Schock fuer Emerging Markets veraendert</t>
+          <t>Private Credit-Debatte entfacht</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
@@ -1569,30 +1565,34 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F32" s="4" t="inlineStr"/>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>https://www.institutional-money.com/news/maerkte/headline/was-der-iran-schock-fuer-emerging-markets-veraendert-249420</t>
+          <t>https://www.fondsexklusiv.at/private-credit-debatte-entfacht/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>46100</v>
+        <v>46102</v>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>fixed-income.org</t>
+          <t>Der Standard</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Was der Iran-Schock fuer Emerging Markets veraendert</t>
+          <t>Pakistan spart Milliarden an fossilen Importen: Wie hat es das gemacht?</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
@@ -1600,34 +1600,30 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>Johannes Feist</t>
-        </is>
-      </c>
+      <c r="F33" s="4" t="inlineStr"/>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>https://www.fixed-income.org/investment/was-der-iran-schock-fuer-emerging-markets-veraendert.html</t>
+          <t>https://www.derstandard.de/story/3000000313347/pakistan-spart-milliarden-an-fossilen-importen-wie-hat-es-das-gemacht</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>46098</v>
+        <v>46102</v>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>finanznachrichten.de</t>
+          <t>Finews</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Private Credit ist nicht gleich Private Credit: Wo die Risiken wirklich liegen</t>
+          <t>Tokenisierung: Louzia Savchenko ueber Innovation und MK Global Kapital</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
@@ -1637,27 +1633,27 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist</t>
+          <t>Louiza Savchenko</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>https://www.finanznachrichten.de/nachrichten-2026-03/67998176-private-credit-ist-nicht-gleich-private-credit-wo-die-risiken-wirklich-liegen-144.htm</t>
+          <t>https://www.finews.ch/news/finanzplatz/71578-finews-first-tokenisierung-louzia-savchenko-finanzplatz-schweiz-innovation-mk-global-kapital</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>46098</v>
+        <v>46101</v>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>cash-online.de</t>
+          <t>BondGuide</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Gastkommentar: Der blinde Fleck der Private-Credit-Debatte</t>
+          <t>Private Credit ist nicht gleich Private Credit: wo die Risiken wirklich liegen</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -1677,27 +1673,27 @@
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>https://www.cash-online.de/a/gastkommentar-der-blinde-fleck-der-private-credit-debatte-713724/</t>
+          <t>https://www.bondguide.de/topnews/private-credit-ist-nicht-gleich-private-credit-wo-die-risiken-wirklich-liegen/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>46097</v>
+        <v>46100</v>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>FONDS exklusiv</t>
+          <t>Moneycab</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Private Credit-Debatte entfacht</t>
+          <t>Nicht nur Öl: Wo der Iran-Konflikt Emerging Markets wirklich trifft</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
@@ -1712,22 +1708,22 @@
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>https://www.fondsexklusiv.de/private-credit-debatte-entfacht/</t>
+          <t>https://www.moneycab.com/finanz/nicht-nur-oel-wo-der-iran-konflikt-emerging-markets-wirklich-trifft/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>46097</v>
+        <v>46100</v>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Kreditwesen (Verlagsgruppe Knapp-Richardi)</t>
+          <t>Institutional Money</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Mikrofinanz als Anlageklasse</t>
+          <t>Was der Iran-Schock fuer Emerging Markets veraendert</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -1737,37 +1733,33 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>Print &amp; Online</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>Johannes Feist</t>
-        </is>
-      </c>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr"/>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>https://www.kreditwesen.de/kreditwesen/themenschwerpunkte/aufsaetze/mikrofinanz-anlageklasse-id107511.html</t>
+          <t>https://www.institutional-money.com/news/maerkte/headline/was-der-iran-schock-fuer-emerging-markets-veraendert-249420</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>46094</v>
+        <v>46100</v>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>investrends.ch</t>
+          <t>fixed-income.org</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Der blinde Fleck der Private-Credit-Debatte</t>
+          <t>Was der Iran-Schock fuer Emerging Markets veraendert</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
@@ -1782,22 +1774,22 @@
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>https://investrends.ch/aktuell/investments/der-blinde-fleck-der-private-credit-debatte/</t>
+          <t>https://www.fixed-income.org/investment/was-der-iran-schock-fuer-emerging-markets-veraendert.html</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>46093</v>
+        <v>46098</v>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Finanzen100.de</t>
+          <t>finanznachrichten.de</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Marktkommentar: Der Trugschluss der sicheren Häfen</t>
+          <t>Private Credit ist nicht gleich Private Credit: Wo die Risiken wirklich liegen</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -1817,27 +1809,27 @@
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>https://www.finanzen100.de/premium/bernecker-boersenkompass/marktkommentar-der-trugschluss-der-sicheren-haefen_H1356104965_6799449/</t>
+          <t>https://www.finanznachrichten.de/nachrichten-2026-03/67998176-private-credit-ist-nicht-gleich-private-credit-wo-die-risiken-wirklich-liegen-144.htm</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>46091</v>
+        <v>46098</v>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Swiss Finance AI</t>
+          <t>cash-online.de</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Warum tokenisierte Anleihen mehr sind als ein Trend</t>
+          <t>Gastkommentar: Der blinde Fleck der Private-Credit-Debatte</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
@@ -1845,25 +1837,29 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F40" s="4" t="inlineStr"/>
+      <c r="F40" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>https://www.swissfinanceai.ch/blog/swiss-finance/warum-tokenisierte-anleihen-mehr-sind-als-ein-trend</t>
+          <t>https://www.cash-online.de/a/gastkommentar-der-blinde-fleck-der-private-credit-debatte-713724/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>46085</v>
+        <v>46097</v>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>markteinblicke.de</t>
+          <t>FONDS exklusiv</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Tokenisierte Anleihen: Mehr Governance erforderlich</t>
+          <t>Private Credit-Debatte entfacht</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -1878,27 +1874,27 @@
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>Louiza Savchenko</t>
+          <t>Johannes Feist</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>https://markteinblicke.de/128943/2026/03/tokenisierte-anleihen-mehr-governance-erforderlich/</t>
+          <t>https://www.fondsexklusiv.de/private-credit-debatte-entfacht/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>46085</v>
+        <v>46097</v>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>gruenderkueche.de</t>
+          <t>Kreditwesen (Verlagsgruppe Knapp-Richardi)</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Weltfrauentag: Unternehmerinnen fehlt weiterhin der Zugang zu Kapital</t>
+          <t>Mikrofinanz als Anlageklasse</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1908,37 +1904,37 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Print &amp; Online</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>Louiza Savchenko</t>
+          <t>Johannes Feist</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>https://www.gruenderkueche.de/news/finanzen-news/weltfrauentag-unternehmerinnen-fehlt-weiterhin-der-zugang-zu-kapital/</t>
+          <t>https://www.kreditwesen.de/kreditwesen/themenschwerpunkte/aufsaetze/mikrofinanz-anlageklasse-id107511.html</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>46083</v>
+        <v>46094</v>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>altii.de</t>
+          <t>investrends.ch</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Unternehmerinnen fehlt weltweit der Zugang zu Kapital</t>
+          <t>Der blinde Fleck der Private-Credit-Debatte</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
@@ -1946,25 +1942,29 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F43" s="4" t="inlineStr"/>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>https://www.altii.de/edai-71550571-cb6c-4c09-93da-bd99b822c245/</t>
+          <t>https://investrends.ch/aktuell/investments/der-blinde-fleck-der-private-credit-debatte/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>46083</v>
+        <v>46093</v>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>dfpa.info</t>
+          <t>Finanzen100.de</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Unternehmerinnen fehlt weltweit der Zugang zu Kapital</t>
+          <t>Marktkommentar: Der Trugschluss der sicheren Häfen</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1979,32 +1979,32 @@
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>Louiza Savchenko</t>
+          <t>Johannes Feist</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>https://www.dfpa.info/maerkte-studien-news/unternehmerinnen-fehlt-weltweit-der-zugang-zu-kapital/</t>
+          <t>https://www.finanzen100.de/premium/bernecker-boersenkompass/marktkommentar-der-trugschluss-der-sicheren-haefen_H1356104965_6799449/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>46077</v>
+        <v>46091</v>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>dfpa.info</t>
+          <t>Swiss Finance AI</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Wenn Geschäftsbanken passen, helfen Mikrofinanzfonds</t>
+          <t>Warum tokenisierte Anleihen mehr sind als ein Trend</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
@@ -2012,29 +2012,25 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>Johannes Feist</t>
-        </is>
-      </c>
+      <c r="F45" s="4" t="inlineStr"/>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>https://www.dfpa.info/top-story/wenn-geschaeftsbanken-passen-helfen-mikrofinanzfonds.html</t>
+          <t>https://www.swissfinanceai.ch/blog/swiss-finance/warum-tokenisierte-anleihen-mehr-sind-als-ein-trend</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>46076</v>
+        <v>46085</v>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>exxecnews.org</t>
+          <t>markteinblicke.de</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Teil I: Wenn Geschäftsbanken passen, helfen Mikrofinanzfonds</t>
+          <t>Tokenisierte Anleihen: Mehr Governance erforderlich</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -2047,25 +2043,29 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F46" s="4" t="inlineStr"/>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>Louiza Savchenko</t>
+        </is>
+      </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>https://exxecnews.org/wp-content/uploads/2026/02/Ausgabe-05_2026.pdf</t>
+          <t>https://markteinblicke.de/128943/2026/03/tokenisierte-anleihen-mehr-governance-erforderlich/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>46071</v>
+        <v>46085</v>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>dfpa.info</t>
+          <t>gruenderkueche.de</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Mikrofinanz: Besonderheit Anleihen mit festem Zins</t>
+          <t>Weltfrauentag: Unternehmerinnen fehlt weiterhin der Zugang zu Kapital</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -2080,32 +2080,32 @@
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist</t>
+          <t>Louiza Savchenko</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>https://www.dfpa.info/interview/mikrofinanz-besonderheit-anleihen-mit-festem-zins.html</t>
+          <t>https://www.gruenderkueche.de/news/finanzen-news/weltfrauentag-unternehmerinnen-fehlt-weiterhin-der-zugang-zu-kapital/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>46069</v>
+        <v>46083</v>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Börsen-Kurier</t>
+          <t>altii.de</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Privates Kapital für noch nicht entwickelte Märkte</t>
+          <t>Unternehmerinnen fehlt weltweit der Zugang zu Kapital</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>DACH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
@@ -2114,20 +2114,24 @@
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr"/>
-      <c r="G48" s="4" t="inlineStr"/>
+      <c r="G48" s="4" t="inlineStr">
+        <is>
+          <t>https://www.altii.de/edai-71550571-cb6c-4c09-93da-bd99b822c245/</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>46069</v>
+        <v>46083</v>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>boerse-social.com</t>
+          <t>dfpa.info</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Börse-Inputs auf Spotify zu u.a. Do&amp;Co, Bawag, Nervigem und Mikrokrediten</t>
+          <t>Unternehmerinnen fehlt weltweit der Zugang zu Kapital</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -2142,27 +2146,27 @@
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist</t>
+          <t>Louiza Savchenko</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>https://boerse-social.com/2026/02/16/borse-inputs_auf_spotify_zu_ua_doco_bawag_nervigem_und_mikrokrediten_1</t>
+          <t>https://www.dfpa.info/maerkte-studien-news/unternehmerinnen-fehlt-weltweit-der-zugang-zu-kapital/</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
-        <v>46067</v>
+        <v>46077</v>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>finanznachrichten.de</t>
+          <t>dfpa.info</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>Security Conference München 2026: öffentliche Mittel als Hebel nutzen</t>
+          <t>Wenn Geschäftsbanken passen, helfen Mikrofinanzfonds</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -2182,22 +2186,22 @@
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>https://www.finanznachrichten.de/nachrichten-2026-02/67704129-security-conference-muenchen-2026-oeffentliche-mittel-als-hebel-nutzen-144.htm</t>
+          <t>https://www.dfpa.info/top-story/wenn-geschaeftsbanken-passen-helfen-mikrofinanzfonds.html</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
-        <v>46067</v>
+        <v>46076</v>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>bondguide.de</t>
+          <t>exxecnews.org</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Security Conference München 2026: öffentliche Mittel als Hebel nutzen</t>
+          <t>Teil I: Wenn Geschäftsbanken passen, helfen Mikrofinanzfonds</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -2210,29 +2214,25 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F51" s="4" t="inlineStr">
-        <is>
-          <t>Johannes Feist</t>
-        </is>
-      </c>
+      <c r="F51" s="4" t="inlineStr"/>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>https://www.bondguide.de/topnews/security-conference-muenchen-2026-oeffentliche-mittel-als-hebel-nutzen/</t>
+          <t>https://exxecnews.org/wp-content/uploads/2026/02/Ausgabe-05_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
-        <v>46067</v>
+        <v>46071</v>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>geldmeisterin.com</t>
+          <t>dfpa.info</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>Mikrokredite gerade jetzt zur Risikostreuung</t>
+          <t>Mikrofinanz: Besonderheit Anleihen mit festem Zins</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -2252,27 +2252,27 @@
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>https://www.geldmeisterin.com/index.php/2026/02/14/mikrokredite-gerade-jetzt-zur-risikostreuung/</t>
+          <t>https://www.dfpa.info/interview/mikrofinanz-besonderheit-anleihen-mit-festem-zins.html</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
-        <v>46067</v>
+        <v>46069</v>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>geldmeisterin.com</t>
+          <t>Börsen-Kurier</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Mikrokredite als Anlagealternative</t>
+          <t>Privates Kapital für noch nicht entwickelte Märkte</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>DACH</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
@@ -2280,34 +2280,26 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F53" s="4" t="inlineStr">
-        <is>
-          <t>Johannes Feist</t>
-        </is>
-      </c>
-      <c r="G53" s="4" t="inlineStr">
-        <is>
-          <t>https://podcasters.spotify.com/pod/show/geldmeisterin/episodes/Mikrokredite-als-Anlagealternative-e3f11ln</t>
-        </is>
-      </c>
+      <c r="F53" s="4" t="inlineStr"/>
+      <c r="G53" s="4" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
-        <v>46057</v>
+        <v>46069</v>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>investrends.ch</t>
+          <t>boerse-social.com</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>Private Debt: Warum Prozesse wichtiger sind als Prognosen</t>
+          <t>Börse-Inputs auf Spotify zu u.a. Do&amp;Co, Bawag, Nervigem und Mikrokrediten</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
@@ -2317,32 +2309,32 @@
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>Michele Mattioda</t>
+          <t>Johannes Feist</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>https://investrends.ch/aktuell/investments/private-debt-warum-prozesse-wichtiger-sind-als-prognosen/</t>
+          <t>https://boerse-social.com/2026/02/16/borse-inputs_auf_spotify_zu_ua_doco_bawag_nervigem_und_mikrokrediten_1</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
-        <v>46055</v>
+        <v>46067</v>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Payoff</t>
+          <t>finanznachrichten.de</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>Mikrofinanz als Private Debt: Besicherte KMU-Kredite statt «Entwicklungshilfe»</t>
+          <t>Security Conference München 2026: öffentliche Mittel als Hebel nutzen</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
@@ -2357,22 +2349,22 @@
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>https://www.payoff.ch/news/mikrofinanz-als-private-debt-besicherte-kmu-kredite-statt-entwicklungshilfe</t>
+          <t>https://www.finanznachrichten.de/nachrichten-2026-02/67704129-security-conference-muenchen-2026-oeffentliche-mittel-als-hebel-nutzen-144.htm</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
-        <v>46049</v>
+        <v>46067</v>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Markt Einblicke</t>
+          <t>bondguide.de</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>Mikrofinanzanleihen 2026: Stabile Renditen aus der Realwirtschaft</t>
+          <t>Security Conference München 2026: öffentliche Mittel als Hebel nutzen</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -2382,24 +2374,32 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>Print</t>
-        </is>
-      </c>
-      <c r="F56" s="4" t="inlineStr"/>
-      <c r="G56" s="4" t="inlineStr"/>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bondguide.de/topnews/security-conference-muenchen-2026-oeffentliche-mittel-als-hebel-nutzen/</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
-        <v>46044</v>
+        <v>46067</v>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Frankfurter Allgemeine Zeitung</t>
+          <t>geldmeisterin.com</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Beim Klimaschutz mehr Marktwirtschaft wagen</t>
+          <t>Mikrokredite gerade jetzt zur Risikostreuung</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -2412,30 +2412,34 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F57" s="4" t="inlineStr"/>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>https://www.faz.net/pro/weltwirtschaft/klima-ressourcen/klimapolitik-sollte-auf-mikrofinanzierung-statt-grossprojekte-setzen-accg-200431361.html</t>
+          <t>https://www.geldmeisterin.com/index.php/2026/02/14/mikrokredite-gerade-jetzt-zur-risikostreuung/</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
-        <v>46038</v>
+        <v>46067</v>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>E-fundresearch</t>
+          <t>geldmeisterin.com</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>Umfrage: Welche Chancen und Risiken Experten 2026 in den Private Markets sehen</t>
+          <t>Mikrokredite als Anlagealternative</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>DACH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
@@ -2450,22 +2454,22 @@
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>https://e-fundresearch.com/funds/artikel/57840-umfrage-welche-chancen-und-risiken-experten-2026-in-den-private-markets-sehen?page=5</t>
+          <t>https://podcasters.spotify.com/pod/show/geldmeisterin/episodes/Mikrokredite-als-Anlagealternative-e3f11ln</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
-        <v>46035</v>
+        <v>46057</v>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Finews</t>
+          <t>investrends.ch</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Start 2026: Disziplin als Renditequelle bei KMU-Private Debt</t>
+          <t>Private Debt: Warum Prozesse wichtiger sind als Prognosen</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -2485,27 +2489,27 @@
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>https://www.finews.ch/news/finanzplatz/70792-start2026-assetmanagement-mk-global-kapital-michele-mattioda-privat-debt-kmu-mikro</t>
+          <t>https://investrends.ch/aktuell/investments/private-debt-warum-prozesse-wichtiger-sind-als-prognosen/</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
-        <v>46029</v>
+        <v>46055</v>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Markt Einblicke</t>
+          <t>Payoff</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Mikrofinanzanleihen 2026: Stabile Renditen aus der Realwirtschaft</t>
+          <t>Mikrofinanz als Private Debt: Besicherte KMU-Kredite statt «Entwicklungshilfe»</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
@@ -2520,22 +2524,22 @@
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>https://markteinblicke.de/127407/2026/01/mikrofinanzanleihen-2026-stabile-renditen-aus-der-realwirtschaft/</t>
+          <t>https://www.payoff.ch/news/mikrofinanz-als-private-debt-besicherte-kmu-kredite-statt-entwicklungshilfe</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
-        <v>46028</v>
+        <v>46049</v>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>portfolio institutionell</t>
+          <t>Markt Einblicke</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Große Wirkung mit kleinen Krediten</t>
+          <t>Mikrofinanzanleihen 2026: Stabile Renditen aus der Realwirtschaft</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -2545,37 +2549,29 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>Online</t>
-        </is>
-      </c>
-      <c r="F61" s="4" t="inlineStr">
-        <is>
-          <t>Johannes Feist</t>
-        </is>
-      </c>
-      <c r="G61" s="4" t="inlineStr">
-        <is>
-          <t>https://www.portfolio-institutionell.de/grosse-wirkung-mit-kleinen-krediten/</t>
-        </is>
-      </c>
+          <t>Print</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr"/>
+      <c r="G61" s="4" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
-        <v>46000</v>
+        <v>46044</v>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>investrends.ch</t>
+          <t>Frankfurter Allgemeine Zeitung</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Neue Managementgesellschaft für den Impact-Fonds ALTERNATIVE</t>
+          <t>Beim Klimaschutz mehr Marktwirtschaft wagen</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
@@ -2583,34 +2579,30 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F62" s="4" t="inlineStr">
-        <is>
-          <t>Johannes Feist</t>
-        </is>
-      </c>
+      <c r="F62" s="4" t="inlineStr"/>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>https://investrends.ch/aktuell/investments/neue-managementgesellschaft-fur-den-impact-fonds-alternative/</t>
+          <t>https://www.faz.net/pro/weltwirtschaft/klima-ressourcen/klimapolitik-sollte-auf-mikrofinanzierung-statt-grossprojekte-setzen-accg-200431361.html</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
-        <v>45999</v>
+        <v>46038</v>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Moneycab</t>
+          <t>E-fundresearch</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>MK Global Kapital wird per 1. Januar Managementgesellschaft für den Impact-Fonds ALTERNATIVE</t>
+          <t>Umfrage: Welche Chancen und Risiken Experten 2026 in den Private Markets sehen</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>DACH</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
@@ -2625,27 +2617,27 @@
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>https://www.moneycab.com/finanz/mk-global-kapital-wird-per-1-januar-managementgesellschaft-fuer-den-impact-fonds-alternative/</t>
+          <t>https://e-fundresearch.com/funds/artikel/57840-umfrage-welche-chancen-und-risiken-experten-2026-in-den-private-markets-sehen?page=5</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
-        <v>45999</v>
+        <v>46035</v>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>dfpa.info</t>
+          <t>Finews</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>MK Global Kapital wird Managementgesellschaft für Impact-Fonds "Alternative"</t>
+          <t>Start 2026: Disziplin als Renditequelle bei KMU-Private Debt</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
@@ -2655,27 +2647,27 @@
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist</t>
+          <t>Michele Mattioda</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>https://www.dfpa.info/investmentfonds-news/mk-global-kapital-wird-managementgesellschaft-fuer-impact-fonds-alternative/</t>
+          <t>https://www.finews.ch/news/finanzplatz/70792-start2026-assetmanagement-mk-global-kapital-michele-mattioda-privat-debt-kmu-mikro</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
-        <v>45997</v>
+        <v>46029</v>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>bondguide.de</t>
+          <t>Markt Einblicke</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Mikro Kapital Management: Impact Investing ist kein Charity</t>
+          <t>Mikrofinanzanleihen 2026: Stabile Renditen aus der Realwirtschaft</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -2695,22 +2687,22 @@
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>https://www.bondguide.de/topnews/mikro-kapital-management-impact-investing-ist-kein-charity/</t>
+          <t>https://markteinblicke.de/127407/2026/01/mikrofinanzanleihen-2026-stabile-renditen-aus-der-realwirtschaft/</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
-        <v>45996</v>
+        <v>46028</v>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>finanznachrichten.de</t>
+          <t>portfolio institutionell</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>Mikro Kapital Management: "Impact Investing ist kein Charity"</t>
+          <t>Große Wirkung mit kleinen Krediten</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -2730,27 +2722,27 @@
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>https://www.finanznachrichten.de/nachrichten-2025-12/67161108-mikro-kapital-management-impact-investing-ist-kein-charity-144.htm</t>
+          <t>https://www.portfolio-institutionell.de/grosse-wirkung-mit-kleinen-krediten/</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
-        <v>45995</v>
+        <v>46000</v>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>dfpa.info</t>
+          <t>investrends.ch</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Mikro Kapital platziert erstmals Anleihe an Luxemburger Börse</t>
+          <t>Neue Managementgesellschaft für den Impact-Fonds ALTERNATIVE</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
@@ -2765,22 +2757,22 @@
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>https://www.dfpa.info/investmentfonds-news/mikro-kapital-platziert-erstmals-emtn-anleihen-des-fonds-alternative-an-luxemburger-boerse/</t>
+          <t>https://investrends.ch/aktuell/investments/neue-managementgesellschaft-fur-den-impact-fonds-alternative/</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="n">
-        <v>45985</v>
+        <v>45999</v>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Finews</t>
+          <t>Moneycab</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist über Mikrofinanzen: Sollten vom hohen Ross herunterkommen</t>
+          <t>MK Global Kapital wird per 1. Januar Managementgesellschaft für den Impact-Fonds ALTERNATIVE</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -2800,27 +2792,27 @@
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>https://www.finews.ch/news/finanzplatz/70147-mikro-capital-johannes-feist-kuenstliche-intelligenz-blockchain-rumaenien-europa-mikrofinanzen-finanzplatz-schweiz</t>
+          <t>https://www.moneycab.com/finanz/mk-global-kapital-wird-per-1-januar-managementgesellschaft-fuer-den-impact-fonds-alternative/</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
-        <v>45973</v>
+        <v>45999</v>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>investrends.ch</t>
+          <t>dfpa.info</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>Mikrofinanz ist Private Debt mit direkter Verbindung zur Realwirtschaft</t>
+          <t>MK Global Kapital wird Managementgesellschaft für Impact-Fonds "Alternative"</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
@@ -2835,22 +2827,22 @@
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>https://investrends.ch/aktuell/investments/mikrofinanz-ist-private-debt-mit-direkter-verbindung-zur-realwirtschaft/</t>
+          <t>https://www.dfpa.info/investmentfonds-news/mk-global-kapital-wird-managementgesellschaft-fuer-impact-fonds-alternative/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="n">
-        <v>45968</v>
+        <v>45997</v>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Frankfurter Rundschau</t>
+          <t>bondguide.de</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>Merz in Brasilien: Bundeskanzler fordert „globale Kraftanstrengung“ für Klimaschutz bei COP30</t>
+          <t>Mikro Kapital Management: Impact Investing ist kein Charity</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -2870,22 +2862,22 @@
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>https://www.fr.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.bondguide.de/topnews/mikro-kapital-management-impact-investing-ist-kein-charity/</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
-        <v>45967</v>
+        <v>45996</v>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Windmesse</t>
+          <t>finanznachrichten.de</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>COP30: Klimafinanzierung muss endlich in den Unternehmen ankommen</t>
+          <t>Mikro Kapital Management: "Impact Investing ist kein Charity"</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -2905,22 +2897,22 @@
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>https://w3.windmesse.de/windenergie/news/48059-cop30-klimafinanzierung-muss-endlich-in-den-unternehmen-ankommen</t>
+          <t>https://www.finanznachrichten.de/nachrichten-2025-12/67161108-mikro-kapital-management-impact-investing-ist-kein-charity-144.htm</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="n">
-        <v>45967</v>
+        <v>45995</v>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>BondGuide</t>
+          <t>dfpa.info</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>Klimafinanzierung bei COP 30: von Zusagen zu Wirkung entfalten</t>
+          <t>Mikro Kapital platziert erstmals Anleihe an Luxemburger Börse</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -2940,22 +2932,22 @@
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
-          <t>https://www.bondguide.de/topnews/klimafinanzierung-bei-cop-30-von-zusagen-zu-wirkung-entfalten/</t>
+          <t>https://www.dfpa.info/investmentfonds-news/mikro-kapital-platziert-erstmals-emtn-anleihen-des-fonds-alternative-an-luxemburger-boerse/</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="n">
-        <v>45848</v>
+        <v>45985</v>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Handelszeitung</t>
+          <t>Finews</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>Zwischen ESG-Müdigkeit und Wirkungsanspruch</t>
+          <t>Johannes Feist über Mikrofinanzen: Sollten vom hohen Ross herunterkommen</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -2968,43 +2960,218 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F73" s="4" t="inlineStr"/>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>https://www.handelszeitung.ch/specials/nachhaltiges-investieren-2024/zwischen-esg-mudigkeit-und-wirkungsanspruch-841576</t>
+          <t>https://www.finews.ch/news/finanzplatz/70147-mikro-capital-johannes-feist-kuenstliche-intelligenz-blockchain-rumaenien-europa-mikrofinanzen-finanzplatz-schweiz</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="n">
+        <v>45973</v>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>investrends.ch</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>Mikrofinanz ist Private Debt mit direkter Verbindung zur Realwirtschaft</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G74" s="4" t="inlineStr">
+        <is>
+          <t>https://investrends.ch/aktuell/investments/mikrofinanz-ist-private-debt-mit-direkter-verbindung-zur-realwirtschaft/</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="3" t="n">
+        <v>45968</v>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>Frankfurter Rundschau</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>Merz in Brasilien: Bundeskanzler fordert „globale Kraftanstrengung“ für Klimaschutz bei COP30</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G75" s="4" t="inlineStr">
+        <is>
+          <t>https://www.fr.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>Windmesse</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>COP30: Klimafinanzierung muss endlich in den Unternehmen ankommen</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G76" s="4" t="inlineStr">
+        <is>
+          <t>https://w3.windmesse.de/windenergie/news/48059-cop30-klimafinanzierung-muss-endlich-in-den-unternehmen-ankommen</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>BondGuide</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>Klimafinanzierung bei COP 30: von Zusagen zu Wirkung entfalten</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G77" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bondguide.de/topnews/klimafinanzierung-bei-cop-30-von-zusagen-zu-wirkung-entfalten/</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="n">
+        <v>45848</v>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>Handelszeitung</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>Zwischen ESG-Müdigkeit und Wirkungsanspruch</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F78" s="4" t="inlineStr"/>
+      <c r="G78" s="4" t="inlineStr">
+        <is>
+          <t>https://www.handelszeitung.ch/specials/nachhaltiges-investieren-2024/zwischen-esg-mudigkeit-und-wirkungsanspruch-841576</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="n">
         <v>45292</v>
       </c>
-      <c r="B74" s="4" t="inlineStr">
+      <c r="B79" s="4" t="inlineStr">
         <is>
           <t>FONDS exklusiv Österreich</t>
         </is>
       </c>
-      <c r="C74" s="4" t="inlineStr">
+      <c r="C79" s="4" t="inlineStr">
         <is>
           <t>Schwellenländer: Worauf es jetzt ankommt</t>
         </is>
       </c>
-      <c r="D74" s="4" t="inlineStr">
+      <c r="D79" s="4" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="E74" s="4" t="inlineStr">
-        <is>
-          <t>Online</t>
-        </is>
-      </c>
-      <c r="F74" s="4" t="inlineStr">
-        <is>
-          <t>Johannes Feist</t>
-        </is>
-      </c>
-      <c r="G74" s="4" t="inlineStr">
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G79" s="4" t="inlineStr">
         <is>
           <t>https://www.fondsexklusiv.at/schwellenlaender-worauf-es-jetzt-ankommt/</t>
         </is>
@@ -3045,7 +3212,7 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Source: Sheet '2026 Clippings' (A9:G74)</t>
+          <t>Source: Sheet '2026 Clippings' (A9:G79)</t>
         </is>
       </c>
     </row>
@@ -3063,7 +3230,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6">
@@ -3083,7 +3250,7 @@
         </is>
       </c>
       <c r="B7" s="10" t="n">
-        <v>46304</v>
+        <v>46309</v>
       </c>
     </row>
     <row r="8">
@@ -3093,7 +3260,7 @@
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9">
@@ -3155,7 +3322,7 @@
         <v>45</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>0.6818181818181818</v>
+        <v>0.6338028169014085</v>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
@@ -3173,10 +3340,10 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>0.1212121212121212</v>
+        <v>0.1549295774647887</v>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
@@ -3197,7 +3364,7 @@
         <v>2</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>0.0303030303030303</v>
+        <v>0.02816901408450704</v>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
@@ -3215,10 +3382,10 @@
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.1830985915492958</v>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
@@ -3286,7 +3453,7 @@
         </is>
       </c>
       <c r="F21" s="8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -3326,7 +3493,7 @@
         </is>
       </c>
       <c r="F25" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="30">
@@ -3383,7 +3550,7 @@
         <v>3</v>
       </c>
       <c r="C32" s="11" t="n">
-        <v>0.04545454545454546</v>
+        <v>0.04225352112676056</v>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
@@ -3391,10 +3558,10 @@
         </is>
       </c>
       <c r="F32" s="8" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G32" s="11" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.971830985915493</v>
       </c>
     </row>
     <row r="33">
@@ -3404,10 +3571,10 @@
         </is>
       </c>
       <c r="B33" s="8" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C33" s="11" t="n">
-        <v>0.2575757575757576</v>
+        <v>0.2676056338028169</v>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
@@ -3418,7 +3585,7 @@
         <v>1</v>
       </c>
       <c r="G33" s="11" t="n">
-        <v>0.01515151515151515</v>
+        <v>0.01408450704225352</v>
       </c>
     </row>
     <row r="34">
@@ -3428,10 +3595,10 @@
         </is>
       </c>
       <c r="B34" s="8" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C34" s="11" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6619718309859155</v>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
@@ -3442,7 +3609,7 @@
         <v>1</v>
       </c>
       <c r="G34" s="11" t="n">
-        <v>0.01515151515151515</v>
+        <v>0.01408450704225352</v>
       </c>
     </row>
     <row r="35">
@@ -3455,7 +3622,7 @@
         <v>2</v>
       </c>
       <c r="C35" s="11" t="n">
-        <v>0.0303030303030303</v>
+        <v>0.02816901408450704</v>
       </c>
     </row>
   </sheetData>

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -694,7 +694,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G79"/>
+  <dimension ref="A1:G75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46311.56268766701</v>
+        <v>46311.57077370148</v>
       </c>
     </row>
     <row r="8">
@@ -754,16 +754,16 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>46309</v>
+        <v>46304</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Netmilk Studio</t>
+          <t>Moneycab</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Progetti: siti web, brand identity e packaging</t>
+          <t>Die Obligation ist tokenisiert. Doch womit wird sie bezahlt?</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -776,30 +776,34 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>Louiza Savchenko</t>
+        </is>
+      </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>https://netmilk.ch/progetti/</t>
+          <t>https://www.moneycab.com/dossiers/die-obligation-ist-tokenisiert-doch-womit-wird-sie-bezahlt/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
-        <v>46309</v>
+        <v>46304</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Moneycab</t>
+          <t>finanznachrichten.de</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Kommentare Archives</t>
+          <t>Die Obligation ist tokenisiert. Doch womit wird sie bezahlt?</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -814,22 +818,22 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>https://www.moneycab.com/category/kommentare/</t>
+          <t>https://www.finanznachrichten.de/nachrichten-2026-10/69801367-die-obligation-ist-tokenisiert-doch-womit-wird-sie-bezahlt-095.htm</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>46306</v>
+        <v>46294</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>finanznachrichten.de</t>
+          <t>Markt Einblicke</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Moneycab | Nachrichten</t>
+          <t>Nach dem Ernteeinbruch: Warum es jetzt auf die richtige Finanzierung ankommt</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -844,32 +848,32 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Louiza Savchenko</t>
+          <t>Johannes Feist</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>https://www.finanznachrichten.de/nachrichten-medien/moneycab.htm</t>
+          <t>https://markteinblicke.de/133297/2026/09/nach-dem-ernteeinbruch-warum-es-jetzt-auf-die-richtige-finanzierung-ankommt/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>46304</v>
+        <v>46273</v>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Moneycab</t>
+          <t>Private Banking Magazin</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Die Obligation ist tokenisiert. Doch womit wird sie bezahlt?</t>
+          <t>Private Credit in Zentralasien</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -879,27 +883,27 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Louiza Savchenko</t>
+          <t>Johannes Feist</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>https://www.moneycab.com/dossiers/die-obligation-ist-tokenisiert-doch-womit-wird-sie-bezahlt/</t>
+          <t>https://www.private-banking-magazin.de/private-credit-zentralasien-lokale-unternehmenskredite/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>46304</v>
+        <v>46256</v>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>finanznachrichten.de</t>
+          <t>BondGuide</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Die Obligation ist tokenisiert. Doch womit wird sie bezahlt?</t>
+          <t>Niedrigwasser zeigt die Geografie des Kreditrisikos</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -914,32 +918,32 @@
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Louiza Savchenko</t>
+          <t>Johannes Feist</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>https://www.finanznachrichten.de/nachrichten-2026-10/69801367-die-obligation-ist-tokenisiert-doch-womit-wird-sie-bezahlt-095.htm</t>
+          <t>https://www.bondguide.de/topnews/niedrigwasser-zeigt-die-geografie-des-kreditrisikos/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>46300</v>
+        <v>46251</v>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>SALES JOBS</t>
+          <t>Finanz und Wirtschaft</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Работа оператором в Узбекистане: 23 вакансии — Call-markaz / operator</t>
+          <t>Die Schweiz finanziert Wasserresilienz überall – nur nicht im Inland</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -947,16 +951,20 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F14" s="4" t="inlineStr"/>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>Louiza Savchenko</t>
+        </is>
+      </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>https://salesjobs.uz/lavozim/operator</t>
+          <t>https://www.fuw.ch/wasserrisiko-was-die-schweiz-von-zentralasien-lernen-kann-152625611421</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>46294</v>
+        <v>46247</v>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
@@ -965,7 +973,7 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Nach dem Ernteeinbruch: Warum es jetzt auf die richtige Finanzierung ankommt</t>
+          <t>Mikrofinanzanleihen: Worauf es bei Kreditqualität und Struktur ankommt</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -985,22 +993,22 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>https://markteinblicke.de/133297/2026/09/nach-dem-ernteeinbruch-warum-es-jetzt-auf-die-richtige-finanzierung-ankommt/</t>
+          <t>https://markteinblicke.de/132318/2026/08/mikrofinanzanleihen-worauf-es-bei-kreditqualitaet-und-struktur-ankommt/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>46273</v>
+        <v>46238</v>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Private Banking Magazin</t>
+          <t>Markt Einblicke</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Private Credit in Zentralasien</t>
+          <t>Euro-Kupon, lokale Cashflows: Wo das Währungsrisiko wirklich liegt</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -1020,27 +1028,27 @@
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>https://www.private-banking-magazin.de/private-credit-zentralasien-lokale-unternehmenskredite/</t>
+          <t>https://markteinblicke.de/132045/2026/08/euro-kupon-lokale-cashflows-wo-das-waehrungsrisiko-wirklich-liegt/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>46256</v>
+        <v>46234</v>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>BondGuide</t>
+          <t>Moneycab</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Niedrigwasser zeigt die Geografie des Kreditrisikos</t>
+          <t>Johannes Feist, CEO MK Global Kapital, im Interview</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -1055,27 +1063,27 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>https://www.bondguide.de/topnews/niedrigwasser-zeigt-die-geografie-des-kreditrisikos/</t>
+          <t>https://www.moneycab.com/interviews/ceo-interviews/johannes-feist-ceo-mk-global-kapital-im-interview/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>46251</v>
+        <v>46234</v>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Finanz und Wirtschaft</t>
+          <t>finanznachrichten.de</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Die Schweiz finanziert Wasserresilienz überall – nur nicht im Inland</t>
+          <t>Johannes Feist, CEO MK Global Kapital, im Interview</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
@@ -1085,27 +1093,27 @@
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Louiza Savchenko</t>
+          <t>Johannes Feist</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>https://www.fuw.ch/wasserrisiko-was-die-schweiz-von-zentralasien-lernen-kann-152625611421</t>
+          <t>https://www.finanznachrichten.de/nachrichten-2026-07/69177994-johannes-feist-ceo-mk-global-kapital-im-interview-095.htm</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>46247</v>
+        <v>46231</v>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Markt Einblicke</t>
+          <t>BondGuide</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Mikrofinanzanleihen: Worauf es bei Kreditqualität und Struktur ankommt</t>
+          <t>Private Credit: Was Anleiheinvestoren hinter dem Kupon prüfen sollten</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -1125,22 +1133,22 @@
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>https://markteinblicke.de/132318/2026/08/mikrofinanzanleihen-worauf-es-bei-kreditqualitaet-und-struktur-ankommt/</t>
+          <t>https://www.bondguide.de/topnews/private-credit-was-anleiheinvestoren-hinter-dem-kupon-pruefen-sollten/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>46238</v>
+        <v>46197</v>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Markt Einblicke</t>
+          <t>background.tagesspiegel</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Euro-Kupon, lokale Cashflows: Wo das Währungsrisiko wirklich liegt</t>
+          <t>Digitale Kreditvergabe : Kreditzugang ist mehr als ein Score</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
@@ -1155,27 +1163,27 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist</t>
+          <t>Louiza Savchenko</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>https://markteinblicke.de/132045/2026/08/euro-kupon-lokale-cashflows-wo-das-waehrungsrisiko-wirklich-liegt/</t>
+          <t>https://background.tagesspiegel.de/finance/briefing/kreditzugang-ist-mehr-als-ein-score</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>46234</v>
+        <v>46183</v>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Moneycab</t>
+          <t>Finews</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist, CEO MK Global Kapital, im Interview</t>
+          <t>Johannes Feist: «Einer meiner unerfüllter Träume ist der Sportfliegerschein»</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
@@ -1195,22 +1203,22 @@
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>https://www.moneycab.com/interviews/ceo-interviews/johannes-feist-ceo-mk-global-kapital-im-interview/</t>
+          <t>https://www.finews.ch/themen/high-end/72456-johannes-feist-einer-meiner-unerfuellter-traeume-ist-der-sportfliegerschein-ceo-global-kapital</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>46234</v>
+        <v>46169</v>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>finanznachrichten.de</t>
+          <t>Markt Einblicke</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist, CEO MK Global Kapital, im Interview</t>
+          <t>Warum der Blick auf den Ölpreis nicht reicht</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -1230,27 +1238,27 @@
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>https://www.finanznachrichten.de/nachrichten-2026-07/69177994-johannes-feist-ceo-mk-global-kapital-im-interview-095.htm</t>
+          <t>https://markteinblicke.de/130696/2026/05/warum-der-blick-auf-den-oelpreis-nicht-reicht/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>46231</v>
+        <v>46164</v>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>BondGuide</t>
+          <t>Moneycab</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Private Credit: Was Anleiheinvestoren hinter dem Kupon prüfen sollten</t>
+          <t>Nicht die Grösse des Kredits entscheidet, sondern seine Wirkung</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
@@ -1265,22 +1273,22 @@
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>https://www.bondguide.de/topnews/private-credit-was-anleiheinvestoren-hinter-dem-kupon-pruefen-sollten/</t>
+          <t>https://www.moneycab.com/dossiers/nicht-die-groesse-des-kredits-entscheidet-sondern-seine-wirkung/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>46197</v>
+        <v>46149</v>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>background.tagesspiegel</t>
+          <t>Markt Einblicke</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Digitale Kreditvergabe : Kreditzugang ist mehr als ein Score</t>
+          <t>Mikrofinanz-Anleihen: Ein wachsender Markt</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -1295,32 +1303,32 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Louiza Savchenko</t>
+          <t>Johannes Feist</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>https://background.tagesspiegel.de/finance/briefing/kreditzugang-ist-mehr-als-ein-score</t>
+          <t>https://markteinblicke.de/130263/2026/05/mikrofinanz-anleihen-ein-wachsender-markt/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>46183</v>
+        <v>46125</v>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Finews</t>
+          <t>cash-online.de</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist: «Einer meiner unerfüllter Träume ist der Sportfliegerschein»</t>
+          <t>Tokenisierte Anleihen: Was sich für Anleger ändert und was nicht</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
@@ -1330,27 +1338,27 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist</t>
+          <t>Louiza Savchenko</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>https://www.finews.ch/themen/high-end/72456-johannes-feist-einer-meiner-unerfuellter-traeume-ist-der-sportfliegerschein-ceo-global-kapital</t>
+          <t>https://www.cash-online.de/a/tokenisierte-anleihen-was-sich-fuer-anleger-aendert-und-was-nicht-715994/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>46169</v>
+        <v>46105</v>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Markt Einblicke</t>
+          <t>Frankfurter Allgemeine Zeitung</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Warum der Blick auf den Ölpreis nicht reicht</t>
+          <t>Sorgen um Privatkredite: Finanzkrise oder silberne Aera?</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -1363,34 +1371,30 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
-          <t>Johannes Feist</t>
-        </is>
-      </c>
+      <c r="F26" s="4" t="inlineStr"/>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>https://markteinblicke.de/130696/2026/05/warum-der-blick-auf-den-oelpreis-nicht-reicht/</t>
+          <t>https://www.faz.net/pro/meine-finanzen/zinsen/sorgen-um-privatkredite-finanzkrise-oder-silberne-aera-110376123.html</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>46164</v>
+        <v>46105</v>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Moneycab</t>
+          <t>DAS INVESTMENT</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Nicht die Grösse des Kredits entscheidet, sondern seine Wirkung</t>
+          <t>Private Credit unter Druck: Wenn das Geld nicht mehr herauskommt</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -1398,34 +1402,30 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>Johannes Feist</t>
-        </is>
-      </c>
+      <c r="F27" s="4" t="inlineStr"/>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>https://www.moneycab.com/dossiers/nicht-die-groesse-des-kredits-entscheidet-sondern-seine-wirkung/</t>
+          <t>https://www.dasinvestment.com/private-credit-unter-druck-wenn-das-geld-nicht-mehr-herauskommt/</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>46149</v>
+        <v>46105</v>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Markt Einblicke</t>
+          <t>FONDS exklusiv Oesterreich</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Mikrofinanz-Anleihen: Ein wachsender Markt</t>
+          <t>Private Credit-Debatte entfacht</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
@@ -1440,27 +1440,27 @@
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>https://markteinblicke.de/130263/2026/05/mikrofinanz-anleihen-ein-wachsender-markt/</t>
+          <t>https://www.fondsexklusiv.at/private-credit-debatte-entfacht/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>46125</v>
+        <v>46102</v>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>cash-online.de</t>
+          <t>Der Standard</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Tokenisierte Anleihen: Was sich für Anleger ändert und was nicht</t>
+          <t>Pakistan spart Milliarden an fossilen Importen: Wie hat es das gemacht?</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
@@ -1468,34 +1468,30 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>Louiza Savchenko</t>
-        </is>
-      </c>
+      <c r="F29" s="4" t="inlineStr"/>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>https://www.cash-online.de/a/tokenisierte-anleihen-was-sich-fuer-anleger-aendert-und-was-nicht-715994/</t>
+          <t>https://www.derstandard.de/story/3000000313347/pakistan-spart-milliarden-an-fossilen-importen-wie-hat-es-das-gemacht</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>46105</v>
+        <v>46102</v>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Frankfurter Allgemeine Zeitung</t>
+          <t>Finews</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Sorgen um Privatkredite: Finanzkrise oder silberne Aera?</t>
+          <t>Tokenisierung: Louzia Savchenko ueber Innovation und MK Global Kapital</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
@@ -1503,25 +1499,29 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F30" s="4" t="inlineStr"/>
+      <c r="F30" s="4" t="inlineStr">
+        <is>
+          <t>Louiza Savchenko</t>
+        </is>
+      </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>https://www.faz.net/pro/meine-finanzen/zinsen/sorgen-um-privatkredite-finanzkrise-oder-silberne-aera-110376123.html</t>
+          <t>https://www.finews.ch/news/finanzplatz/71578-finews-first-tokenisierung-louzia-savchenko-finanzplatz-schweiz-innovation-mk-global-kapital</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>46105</v>
+        <v>46101</v>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>DAS INVESTMENT</t>
+          <t>BondGuide</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Private Credit unter Druck: Wenn das Geld nicht mehr herauskommt</t>
+          <t>Private Credit ist nicht gleich Private Credit: wo die Risiken wirklich liegen</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -1534,30 +1534,34 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F31" s="4" t="inlineStr"/>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>https://www.dasinvestment.com/private-credit-unter-druck-wenn-das-geld-nicht-mehr-herauskommt/</t>
+          <t>https://www.bondguide.de/topnews/private-credit-ist-nicht-gleich-private-credit-wo-die-risiken-wirklich-liegen/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>46105</v>
+        <v>46100</v>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>FONDS exklusiv Oesterreich</t>
+          <t>Moneycab</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Private Credit-Debatte entfacht</t>
+          <t>Nicht nur Öl: Wo der Iran-Konflikt Emerging Markets wirklich trifft</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
@@ -1572,27 +1576,27 @@
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>https://www.fondsexklusiv.at/private-credit-debatte-entfacht/</t>
+          <t>https://www.moneycab.com/finanz/nicht-nur-oel-wo-der-iran-konflikt-emerging-markets-wirklich-trifft/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>46102</v>
+        <v>46100</v>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Der Standard</t>
+          <t>Institutional Money</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Pakistan spart Milliarden an fossilen Importen: Wie hat es das gemacht?</t>
+          <t>Was der Iran-Schock fuer Emerging Markets veraendert</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
@@ -1603,27 +1607,27 @@
       <c r="F33" s="4" t="inlineStr"/>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>https://www.derstandard.de/story/3000000313347/pakistan-spart-milliarden-an-fossilen-importen-wie-hat-es-das-gemacht</t>
+          <t>https://www.institutional-money.com/news/maerkte/headline/was-der-iran-schock-fuer-emerging-markets-veraendert-249420</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>46102</v>
+        <v>46100</v>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Finews</t>
+          <t>fixed-income.org</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Tokenisierung: Louzia Savchenko ueber Innovation und MK Global Kapital</t>
+          <t>Was der Iran-Schock fuer Emerging Markets veraendert</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
@@ -1633,27 +1637,27 @@
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>Louiza Savchenko</t>
+          <t>Johannes Feist</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>https://www.finews.ch/news/finanzplatz/71578-finews-first-tokenisierung-louzia-savchenko-finanzplatz-schweiz-innovation-mk-global-kapital</t>
+          <t>https://www.fixed-income.org/investment/was-der-iran-schock-fuer-emerging-markets-veraendert.html</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>46101</v>
+        <v>46098</v>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>BondGuide</t>
+          <t>finanznachrichten.de</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Private Credit ist nicht gleich Private Credit: wo die Risiken wirklich liegen</t>
+          <t>Private Credit ist nicht gleich Private Credit: Wo die Risiken wirklich liegen</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -1673,27 +1677,27 @@
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>https://www.bondguide.de/topnews/private-credit-ist-nicht-gleich-private-credit-wo-die-risiken-wirklich-liegen/</t>
+          <t>https://www.finanznachrichten.de/nachrichten-2026-03/67998176-private-credit-ist-nicht-gleich-private-credit-wo-die-risiken-wirklich-liegen-144.htm</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>46100</v>
+        <v>46098</v>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Moneycab</t>
+          <t>cash-online.de</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Nicht nur Öl: Wo der Iran-Konflikt Emerging Markets wirklich trifft</t>
+          <t>Gastkommentar: Der blinde Fleck der Private-Credit-Debatte</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
@@ -1708,22 +1712,22 @@
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>https://www.moneycab.com/finanz/nicht-nur-oel-wo-der-iran-konflikt-emerging-markets-wirklich-trifft/</t>
+          <t>https://www.cash-online.de/a/gastkommentar-der-blinde-fleck-der-private-credit-debatte-713724/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>46100</v>
+        <v>46097</v>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Institutional Money</t>
+          <t>FONDS exklusiv</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Was der Iran-Schock fuer Emerging Markets veraendert</t>
+          <t>Private Credit-Debatte entfacht</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -1736,25 +1740,29 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F37" s="4" t="inlineStr"/>
+      <c r="F37" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>https://www.institutional-money.com/news/maerkte/headline/was-der-iran-schock-fuer-emerging-markets-veraendert-249420</t>
+          <t>https://www.fondsexklusiv.de/private-credit-debatte-entfacht/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>46100</v>
+        <v>46097</v>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>fixed-income.org</t>
+          <t>Kreditwesen (Verlagsgruppe Knapp-Richardi)</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Was der Iran-Schock fuer Emerging Markets veraendert</t>
+          <t>Mikrofinanz als Anlageklasse</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -1764,7 +1772,7 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Print &amp; Online</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
@@ -1774,27 +1782,27 @@
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>https://www.fixed-income.org/investment/was-der-iran-schock-fuer-emerging-markets-veraendert.html</t>
+          <t>https://www.kreditwesen.de/kreditwesen/themenschwerpunkte/aufsaetze/mikrofinanz-anlageklasse-id107511.html</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>46098</v>
+        <v>46094</v>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>finanznachrichten.de</t>
+          <t>investrends.ch</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Private Credit ist nicht gleich Private Credit: Wo die Risiken wirklich liegen</t>
+          <t>Der blinde Fleck der Private-Credit-Debatte</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
@@ -1809,22 +1817,22 @@
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>https://www.finanznachrichten.de/nachrichten-2026-03/67998176-private-credit-ist-nicht-gleich-private-credit-wo-die-risiken-wirklich-liegen-144.htm</t>
+          <t>https://investrends.ch/aktuell/investments/der-blinde-fleck-der-private-credit-debatte/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>46098</v>
+        <v>46093</v>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>cash-online.de</t>
+          <t>Finanzen100.de</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Gastkommentar: Der blinde Fleck der Private-Credit-Debatte</t>
+          <t>Marktkommentar: Der Trugschluss der sicheren Häfen</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -1844,27 +1852,27 @@
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>https://www.cash-online.de/a/gastkommentar-der-blinde-fleck-der-private-credit-debatte-713724/</t>
+          <t>https://www.finanzen100.de/premium/bernecker-boersenkompass/marktkommentar-der-trugschluss-der-sicheren-haefen_H1356104965_6799449/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>46097</v>
+        <v>46091</v>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>FONDS exklusiv</t>
+          <t>Swiss Finance AI</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Private Credit-Debatte entfacht</t>
+          <t>Warum tokenisierte Anleihen mehr sind als ein Trend</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
@@ -1872,29 +1880,25 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>Johannes Feist</t>
-        </is>
-      </c>
+      <c r="F41" s="4" t="inlineStr"/>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>https://www.fondsexklusiv.de/private-credit-debatte-entfacht/</t>
+          <t>https://www.swissfinanceai.ch/blog/swiss-finance/warum-tokenisierte-anleihen-mehr-sind-als-ein-trend</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>46097</v>
+        <v>46085</v>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Kreditwesen (Verlagsgruppe Knapp-Richardi)</t>
+          <t>markteinblicke.de</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Mikrofinanz als Anlageklasse</t>
+          <t>Tokenisierte Anleihen: Mehr Governance erforderlich</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1904,37 +1908,37 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>Print &amp; Online</t>
+          <t>Online</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist</t>
+          <t>Louiza Savchenko</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>https://www.kreditwesen.de/kreditwesen/themenschwerpunkte/aufsaetze/mikrofinanz-anlageklasse-id107511.html</t>
+          <t>https://markteinblicke.de/128943/2026/03/tokenisierte-anleihen-mehr-governance-erforderlich/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>46094</v>
+        <v>46085</v>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>investrends.ch</t>
+          <t>gruenderkueche.de</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Der blinde Fleck der Private-Credit-Debatte</t>
+          <t>Weltfrauentag: Unternehmerinnen fehlt weiterhin der Zugang zu Kapital</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
@@ -1944,27 +1948,27 @@
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist</t>
+          <t>Louiza Savchenko</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>https://investrends.ch/aktuell/investments/der-blinde-fleck-der-private-credit-debatte/</t>
+          <t>https://www.gruenderkueche.de/news/finanzen-news/weltfrauentag-unternehmerinnen-fehlt-weiterhin-der-zugang-zu-kapital/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>46093</v>
+        <v>46083</v>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Finanzen100.de</t>
+          <t>altii.de</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Marktkommentar: Der Trugschluss der sicheren Häfen</t>
+          <t>Unternehmerinnen fehlt weltweit der Zugang zu Kapital</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1977,34 +1981,30 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>Johannes Feist</t>
-        </is>
-      </c>
+      <c r="F44" s="4" t="inlineStr"/>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>https://www.finanzen100.de/premium/bernecker-boersenkompass/marktkommentar-der-trugschluss-der-sicheren-haefen_H1356104965_6799449/</t>
+          <t>https://www.altii.de/edai-71550571-cb6c-4c09-93da-bd99b822c245/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>46091</v>
+        <v>46083</v>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Swiss Finance AI</t>
+          <t>dfpa.info</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Warum tokenisierte Anleihen mehr sind als ein Trend</t>
+          <t>Unternehmerinnen fehlt weltweit der Zugang zu Kapital</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
@@ -2012,25 +2012,29 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F45" s="4" t="inlineStr"/>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>Louiza Savchenko</t>
+        </is>
+      </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>https://www.swissfinanceai.ch/blog/swiss-finance/warum-tokenisierte-anleihen-mehr-sind-als-ein-trend</t>
+          <t>https://www.dfpa.info/maerkte-studien-news/unternehmerinnen-fehlt-weltweit-der-zugang-zu-kapital/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>46085</v>
+        <v>46077</v>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>markteinblicke.de</t>
+          <t>dfpa.info</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Tokenisierte Anleihen: Mehr Governance erforderlich</t>
+          <t>Wenn Geschäftsbanken passen, helfen Mikrofinanzfonds</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -2045,27 +2049,27 @@
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>Louiza Savchenko</t>
+          <t>Johannes Feist</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>https://markteinblicke.de/128943/2026/03/tokenisierte-anleihen-mehr-governance-erforderlich/</t>
+          <t>https://www.dfpa.info/top-story/wenn-geschaeftsbanken-passen-helfen-mikrofinanzfonds.html</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>46085</v>
+        <v>46076</v>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>gruenderkueche.de</t>
+          <t>exxecnews.org</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Weltfrauentag: Unternehmerinnen fehlt weiterhin der Zugang zu Kapital</t>
+          <t>Teil I: Wenn Geschäftsbanken passen, helfen Mikrofinanzfonds</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -2078,29 +2082,25 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F47" s="4" t="inlineStr">
-        <is>
-          <t>Louiza Savchenko</t>
-        </is>
-      </c>
+      <c r="F47" s="4" t="inlineStr"/>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>https://www.gruenderkueche.de/news/finanzen-news/weltfrauentag-unternehmerinnen-fehlt-weiterhin-der-zugang-zu-kapital/</t>
+          <t>https://exxecnews.org/wp-content/uploads/2026/02/Ausgabe-05_2026.pdf</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>46083</v>
+        <v>46071</v>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>altii.de</t>
+          <t>dfpa.info</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Unternehmerinnen fehlt weltweit der Zugang zu Kapital</t>
+          <t>Mikrofinanz: Besonderheit Anleihen mit festem Zins</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -2113,30 +2113,34 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F48" s="4" t="inlineStr"/>
+      <c r="F48" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>https://www.altii.de/edai-71550571-cb6c-4c09-93da-bd99b822c245/</t>
+          <t>https://www.dfpa.info/interview/mikrofinanz-besonderheit-anleihen-mit-festem-zins.html</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>46083</v>
+        <v>46069</v>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>dfpa.info</t>
+          <t>Börsen-Kurier</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Unternehmerinnen fehlt weltweit der Zugang zu Kapital</t>
+          <t>Privates Kapital für noch nicht entwickelte Märkte</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>DACH</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
@@ -2144,29 +2148,21 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F49" s="4" t="inlineStr">
-        <is>
-          <t>Louiza Savchenko</t>
-        </is>
-      </c>
-      <c r="G49" s="4" t="inlineStr">
-        <is>
-          <t>https://www.dfpa.info/maerkte-studien-news/unternehmerinnen-fehlt-weltweit-der-zugang-zu-kapital/</t>
-        </is>
-      </c>
+      <c r="F49" s="4" t="inlineStr"/>
+      <c r="G49" s="4" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
-        <v>46077</v>
+        <v>46069</v>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>dfpa.info</t>
+          <t>boerse-social.com</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>Wenn Geschäftsbanken passen, helfen Mikrofinanzfonds</t>
+          <t>Börse-Inputs auf Spotify zu u.a. Do&amp;Co, Bawag, Nervigem und Mikrokrediten</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -2186,22 +2182,22 @@
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>https://www.dfpa.info/top-story/wenn-geschaeftsbanken-passen-helfen-mikrofinanzfonds.html</t>
+          <t>https://boerse-social.com/2026/02/16/borse-inputs_auf_spotify_zu_ua_doco_bawag_nervigem_und_mikrokrediten_1</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
-        <v>46076</v>
+        <v>46067</v>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>exxecnews.org</t>
+          <t>finanznachrichten.de</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Teil I: Wenn Geschäftsbanken passen, helfen Mikrofinanzfonds</t>
+          <t>Security Conference München 2026: öffentliche Mittel als Hebel nutzen</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -2214,25 +2210,29 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F51" s="4" t="inlineStr"/>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>https://exxecnews.org/wp-content/uploads/2026/02/Ausgabe-05_2026.pdf</t>
+          <t>https://www.finanznachrichten.de/nachrichten-2026-02/67704129-security-conference-muenchen-2026-oeffentliche-mittel-als-hebel-nutzen-144.htm</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
-        <v>46071</v>
+        <v>46067</v>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>dfpa.info</t>
+          <t>bondguide.de</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>Mikrofinanz: Besonderheit Anleihen mit festem Zins</t>
+          <t>Security Conference München 2026: öffentliche Mittel als Hebel nutzen</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
@@ -2252,27 +2252,27 @@
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>https://www.dfpa.info/interview/mikrofinanz-besonderheit-anleihen-mit-festem-zins.html</t>
+          <t>https://www.bondguide.de/topnews/security-conference-muenchen-2026-oeffentliche-mittel-als-hebel-nutzen/</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
-        <v>46069</v>
+        <v>46067</v>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Börsen-Kurier</t>
+          <t>geldmeisterin.com</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Privates Kapital für noch nicht entwickelte Märkte</t>
+          <t>Mikrokredite gerade jetzt zur Risikostreuung</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>DACH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
@@ -2280,21 +2280,29 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F53" s="4" t="inlineStr"/>
-      <c r="G53" s="4" t="inlineStr"/>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G53" s="4" t="inlineStr">
+        <is>
+          <t>https://www.geldmeisterin.com/index.php/2026/02/14/mikrokredite-gerade-jetzt-zur-risikostreuung/</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
-        <v>46069</v>
+        <v>46067</v>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>boerse-social.com</t>
+          <t>geldmeisterin.com</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>Börse-Inputs auf Spotify zu u.a. Do&amp;Co, Bawag, Nervigem und Mikrokrediten</t>
+          <t>Mikrokredite als Anlagealternative</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -2314,27 +2322,27 @@
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>https://boerse-social.com/2026/02/16/borse-inputs_auf_spotify_zu_ua_doco_bawag_nervigem_und_mikrokrediten_1</t>
+          <t>https://podcasters.spotify.com/pod/show/geldmeisterin/episodes/Mikrokredite-als-Anlagealternative-e3f11ln</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
-        <v>46067</v>
+        <v>46057</v>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>finanznachrichten.de</t>
+          <t>investrends.ch</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>Security Conference München 2026: öffentliche Mittel als Hebel nutzen</t>
+          <t>Private Debt: Warum Prozesse wichtiger sind als Prognosen</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
@@ -2344,32 +2352,32 @@
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist</t>
+          <t>Michele Mattioda</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>https://www.finanznachrichten.de/nachrichten-2026-02/67704129-security-conference-muenchen-2026-oeffentliche-mittel-als-hebel-nutzen-144.htm</t>
+          <t>https://investrends.ch/aktuell/investments/private-debt-warum-prozesse-wichtiger-sind-als-prognosen/</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
-        <v>46067</v>
+        <v>46055</v>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>bondguide.de</t>
+          <t>Payoff</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>Security Conference München 2026: öffentliche Mittel als Hebel nutzen</t>
+          <t>Mikrofinanz als Private Debt: Besicherte KMU-Kredite statt «Entwicklungshilfe»</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
@@ -2384,22 +2392,22 @@
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>https://www.bondguide.de/topnews/security-conference-muenchen-2026-oeffentliche-mittel-als-hebel-nutzen/</t>
+          <t>https://www.payoff.ch/news/mikrofinanz-als-private-debt-besicherte-kmu-kredite-statt-entwicklungshilfe</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
-        <v>46067</v>
+        <v>46049</v>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>geldmeisterin.com</t>
+          <t>Markt Einblicke</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Mikrokredite gerade jetzt zur Risikostreuung</t>
+          <t>Mikrofinanzanleihen 2026: Stabile Renditen aus der Realwirtschaft</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -2409,32 +2417,24 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>Online</t>
-        </is>
-      </c>
-      <c r="F57" s="4" t="inlineStr">
-        <is>
-          <t>Johannes Feist</t>
-        </is>
-      </c>
-      <c r="G57" s="4" t="inlineStr">
-        <is>
-          <t>https://www.geldmeisterin.com/index.php/2026/02/14/mikrokredite-gerade-jetzt-zur-risikostreuung/</t>
-        </is>
-      </c>
+          <t>Print</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr"/>
+      <c r="G57" s="4" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
-        <v>46067</v>
+        <v>46044</v>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>geldmeisterin.com</t>
+          <t>Frankfurter Allgemeine Zeitung</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>Mikrokredite als Anlagealternative</t>
+          <t>Beim Klimaschutz mehr Marktwirtschaft wagen</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -2447,34 +2447,30 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F58" s="4" t="inlineStr">
-        <is>
-          <t>Johannes Feist</t>
-        </is>
-      </c>
+      <c r="F58" s="4" t="inlineStr"/>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>https://podcasters.spotify.com/pod/show/geldmeisterin/episodes/Mikrokredite-als-Anlagealternative-e3f11ln</t>
+          <t>https://www.faz.net/pro/weltwirtschaft/klima-ressourcen/klimapolitik-sollte-auf-mikrofinanzierung-statt-grossprojekte-setzen-accg-200431361.html</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
-        <v>46057</v>
+        <v>46038</v>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>investrends.ch</t>
+          <t>E-fundresearch</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Private Debt: Warum Prozesse wichtiger sind als Prognosen</t>
+          <t>Umfrage: Welche Chancen und Risiken Experten 2026 in den Private Markets sehen</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>DACH</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
@@ -2484,27 +2480,27 @@
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>Michele Mattioda</t>
+          <t>Johannes Feist</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>https://investrends.ch/aktuell/investments/private-debt-warum-prozesse-wichtiger-sind-als-prognosen/</t>
+          <t>https://e-fundresearch.com/funds/artikel/57840-umfrage-welche-chancen-und-risiken-experten-2026-in-den-private-markets-sehen?page=5</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
-        <v>46055</v>
+        <v>46035</v>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Payoff</t>
+          <t>Finews</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Mikrofinanz als Private Debt: Besicherte KMU-Kredite statt «Entwicklungshilfe»</t>
+          <t>Start 2026: Disziplin als Renditequelle bei KMU-Private Debt</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -2519,18 +2515,18 @@
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist</t>
+          <t>Michele Mattioda</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>https://www.payoff.ch/news/mikrofinanz-als-private-debt-besicherte-kmu-kredite-statt-entwicklungshilfe</t>
+          <t>https://www.finews.ch/news/finanzplatz/70792-start2026-assetmanagement-mk-global-kapital-michele-mattioda-privat-debt-kmu-mikro</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
-        <v>46049</v>
+        <v>46029</v>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
@@ -2549,24 +2545,32 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>Print</t>
-        </is>
-      </c>
-      <c r="F61" s="4" t="inlineStr"/>
-      <c r="G61" s="4" t="inlineStr"/>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F61" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t>https://markteinblicke.de/127407/2026/01/mikrofinanzanleihen-2026-stabile-renditen-aus-der-realwirtschaft/</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
-        <v>46044</v>
+        <v>46028</v>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Frankfurter Allgemeine Zeitung</t>
+          <t>portfolio institutionell</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Beim Klimaschutz mehr Marktwirtschaft wagen</t>
+          <t>Große Wirkung mit kleinen Krediten</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -2579,30 +2583,34 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F62" s="4" t="inlineStr"/>
+      <c r="F62" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>https://www.faz.net/pro/weltwirtschaft/klima-ressourcen/klimapolitik-sollte-auf-mikrofinanzierung-statt-grossprojekte-setzen-accg-200431361.html</t>
+          <t>https://www.portfolio-institutionell.de/grosse-wirkung-mit-kleinen-krediten/</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
-        <v>46038</v>
+        <v>46000</v>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>E-fundresearch</t>
+          <t>investrends.ch</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Umfrage: Welche Chancen und Risiken Experten 2026 in den Private Markets sehen</t>
+          <t>Neue Managementgesellschaft für den Impact-Fonds ALTERNATIVE</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>DACH</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
@@ -2617,22 +2625,22 @@
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>https://e-fundresearch.com/funds/artikel/57840-umfrage-welche-chancen-und-risiken-experten-2026-in-den-private-markets-sehen?page=5</t>
+          <t>https://investrends.ch/aktuell/investments/neue-managementgesellschaft-fur-den-impact-fonds-alternative/</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
-        <v>46035</v>
+        <v>45999</v>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Finews</t>
+          <t>Moneycab</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>Start 2026: Disziplin als Renditequelle bei KMU-Private Debt</t>
+          <t>MK Global Kapital wird per 1. Januar Managementgesellschaft für den Impact-Fonds ALTERNATIVE</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
@@ -2647,27 +2655,27 @@
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>Michele Mattioda</t>
+          <t>Johannes Feist</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>https://www.finews.ch/news/finanzplatz/70792-start2026-assetmanagement-mk-global-kapital-michele-mattioda-privat-debt-kmu-mikro</t>
+          <t>https://www.moneycab.com/finanz/mk-global-kapital-wird-per-1-januar-managementgesellschaft-fuer-den-impact-fonds-alternative/</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
-        <v>46029</v>
+        <v>45999</v>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Markt Einblicke</t>
+          <t>dfpa.info</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Mikrofinanzanleihen 2026: Stabile Renditen aus der Realwirtschaft</t>
+          <t>MK Global Kapital wird Managementgesellschaft für Impact-Fonds "Alternative"</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -2687,22 +2695,22 @@
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>https://markteinblicke.de/127407/2026/01/mikrofinanzanleihen-2026-stabile-renditen-aus-der-realwirtschaft/</t>
+          <t>https://www.dfpa.info/investmentfonds-news/mk-global-kapital-wird-managementgesellschaft-fuer-impact-fonds-alternative/</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
-        <v>46028</v>
+        <v>45997</v>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>portfolio institutionell</t>
+          <t>bondguide.de</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>Große Wirkung mit kleinen Krediten</t>
+          <t>Mikro Kapital Management: Impact Investing ist kein Charity</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -2722,27 +2730,27 @@
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>https://www.portfolio-institutionell.de/grosse-wirkung-mit-kleinen-krediten/</t>
+          <t>https://www.bondguide.de/topnews/mikro-kapital-management-impact-investing-ist-kein-charity/</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
-        <v>46000</v>
+        <v>45996</v>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>investrends.ch</t>
+          <t>finanznachrichten.de</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Neue Managementgesellschaft für den Impact-Fonds ALTERNATIVE</t>
+          <t>Mikro Kapital Management: "Impact Investing ist kein Charity"</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
@@ -2757,27 +2765,27 @@
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>https://investrends.ch/aktuell/investments/neue-managementgesellschaft-fur-den-impact-fonds-alternative/</t>
+          <t>https://www.finanznachrichten.de/nachrichten-2025-12/67161108-mikro-kapital-management-impact-investing-ist-kein-charity-144.htm</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="n">
-        <v>45999</v>
+        <v>45995</v>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Moneycab</t>
+          <t>dfpa.info</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>MK Global Kapital wird per 1. Januar Managementgesellschaft für den Impact-Fonds ALTERNATIVE</t>
+          <t>Mikro Kapital platziert erstmals Anleihe an Luxemburger Börse</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
@@ -2792,27 +2800,27 @@
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>https://www.moneycab.com/finanz/mk-global-kapital-wird-per-1-januar-managementgesellschaft-fuer-den-impact-fonds-alternative/</t>
+          <t>https://www.dfpa.info/investmentfonds-news/mikro-kapital-platziert-erstmals-emtn-anleihen-des-fonds-alternative-an-luxemburger-boerse/</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
-        <v>45999</v>
+        <v>45985</v>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>dfpa.info</t>
+          <t>Finews</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>MK Global Kapital wird Managementgesellschaft für Impact-Fonds "Alternative"</t>
+          <t>Johannes Feist über Mikrofinanzen: Sollten vom hohen Ross herunterkommen</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
@@ -2827,27 +2835,27 @@
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>https://www.dfpa.info/investmentfonds-news/mk-global-kapital-wird-managementgesellschaft-fuer-impact-fonds-alternative/</t>
+          <t>https://www.finews.ch/news/finanzplatz/70147-mikro-capital-johannes-feist-kuenstliche-intelligenz-blockchain-rumaenien-europa-mikrofinanzen-finanzplatz-schweiz</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="n">
-        <v>45997</v>
+        <v>45973</v>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>bondguide.de</t>
+          <t>investrends.ch</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>Mikro Kapital Management: Impact Investing ist kein Charity</t>
+          <t>Mikrofinanz ist Private Debt mit direkter Verbindung zur Realwirtschaft</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
@@ -2862,22 +2870,22 @@
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>https://www.bondguide.de/topnews/mikro-kapital-management-impact-investing-ist-kein-charity/</t>
+          <t>https://investrends.ch/aktuell/investments/mikrofinanz-ist-private-debt-mit-direkter-verbindung-zur-realwirtschaft/</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
-        <v>45996</v>
+        <v>45968</v>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>finanznachrichten.de</t>
+          <t>Frankfurter Rundschau</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>Mikro Kapital Management: "Impact Investing ist kein Charity"</t>
+          <t>Merz in Brasilien: Bundeskanzler fordert „globale Kraftanstrengung“ für Klimaschutz bei COP30</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -2897,22 +2905,22 @@
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>https://www.finanznachrichten.de/nachrichten-2025-12/67161108-mikro-kapital-management-impact-investing-ist-kein-charity-144.htm</t>
+          <t>https://www.fr.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="n">
-        <v>45995</v>
+        <v>45967</v>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>dfpa.info</t>
+          <t>Windmesse</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>Mikro Kapital platziert erstmals Anleihe an Luxemburger Börse</t>
+          <t>COP30: Klimafinanzierung muss endlich in den Unternehmen ankommen</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -2932,27 +2940,27 @@
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
-          <t>https://www.dfpa.info/investmentfonds-news/mikro-kapital-platziert-erstmals-emtn-anleihen-des-fonds-alternative-an-luxemburger-boerse/</t>
+          <t>https://w3.windmesse.de/windenergie/news/48059-cop30-klimafinanzierung-muss-endlich-in-den-unternehmen-ankommen</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="n">
-        <v>45985</v>
+        <v>45967</v>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>Finews</t>
+          <t>BondGuide</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist über Mikrofinanzen: Sollten vom hohen Ross herunterkommen</t>
+          <t>Klimafinanzierung bei COP 30: von Zusagen zu Wirkung entfalten</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
@@ -2967,22 +2975,22 @@
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>https://www.finews.ch/news/finanzplatz/70147-mikro-capital-johannes-feist-kuenstliche-intelligenz-blockchain-rumaenien-europa-mikrofinanzen-finanzplatz-schweiz</t>
+          <t>https://www.bondguide.de/topnews/klimafinanzierung-bei-cop-30-von-zusagen-zu-wirkung-entfalten/</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="n">
-        <v>45973</v>
+        <v>45848</v>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>investrends.ch</t>
+          <t>Handelszeitung</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>Mikrofinanz ist Private Debt mit direkter Verbindung zur Realwirtschaft</t>
+          <t>Zwischen ESG-Müdigkeit und Wirkungsanspruch</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -2995,34 +3003,30 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F74" s="4" t="inlineStr">
-        <is>
-          <t>Johannes Feist</t>
-        </is>
-      </c>
+      <c r="F74" s="4" t="inlineStr"/>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>https://investrends.ch/aktuell/investments/mikrofinanz-ist-private-debt-mit-direkter-verbindung-zur-realwirtschaft/</t>
+          <t>https://www.handelszeitung.ch/specials/nachhaltiges-investieren-2024/zwischen-esg-mudigkeit-und-wirkungsanspruch-841576</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="n">
-        <v>45968</v>
+        <v>45292</v>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>Frankfurter Rundschau</t>
+          <t>FONDS exklusiv Österreich</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>Merz in Brasilien: Bundeskanzler fordert „globale Kraftanstrengung“ für Klimaschutz bei COP30</t>
+          <t>Schwellenländer: Worauf es jetzt ankommt</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
@@ -3036,142 +3040,6 @@
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr">
-        <is>
-          <t>https://www.fr.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="3" t="n">
-        <v>45967</v>
-      </c>
-      <c r="B76" s="4" t="inlineStr">
-        <is>
-          <t>Windmesse</t>
-        </is>
-      </c>
-      <c r="C76" s="4" t="inlineStr">
-        <is>
-          <t>COP30: Klimafinanzierung muss endlich in den Unternehmen ankommen</t>
-        </is>
-      </c>
-      <c r="D76" s="4" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="E76" s="4" t="inlineStr">
-        <is>
-          <t>Online</t>
-        </is>
-      </c>
-      <c r="F76" s="4" t="inlineStr">
-        <is>
-          <t>Johannes Feist</t>
-        </is>
-      </c>
-      <c r="G76" s="4" t="inlineStr">
-        <is>
-          <t>https://w3.windmesse.de/windenergie/news/48059-cop30-klimafinanzierung-muss-endlich-in-den-unternehmen-ankommen</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="3" t="n">
-        <v>45967</v>
-      </c>
-      <c r="B77" s="4" t="inlineStr">
-        <is>
-          <t>BondGuide</t>
-        </is>
-      </c>
-      <c r="C77" s="4" t="inlineStr">
-        <is>
-          <t>Klimafinanzierung bei COP 30: von Zusagen zu Wirkung entfalten</t>
-        </is>
-      </c>
-      <c r="D77" s="4" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="E77" s="4" t="inlineStr">
-        <is>
-          <t>Online</t>
-        </is>
-      </c>
-      <c r="F77" s="4" t="inlineStr">
-        <is>
-          <t>Johannes Feist</t>
-        </is>
-      </c>
-      <c r="G77" s="4" t="inlineStr">
-        <is>
-          <t>https://www.bondguide.de/topnews/klimafinanzierung-bei-cop-30-von-zusagen-zu-wirkung-entfalten/</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="3" t="n">
-        <v>45848</v>
-      </c>
-      <c r="B78" s="4" t="inlineStr">
-        <is>
-          <t>Handelszeitung</t>
-        </is>
-      </c>
-      <c r="C78" s="4" t="inlineStr">
-        <is>
-          <t>Zwischen ESG-Müdigkeit und Wirkungsanspruch</t>
-        </is>
-      </c>
-      <c r="D78" s="4" t="inlineStr">
-        <is>
-          <t>CH</t>
-        </is>
-      </c>
-      <c r="E78" s="4" t="inlineStr">
-        <is>
-          <t>Online</t>
-        </is>
-      </c>
-      <c r="F78" s="4" t="inlineStr"/>
-      <c r="G78" s="4" t="inlineStr">
-        <is>
-          <t>https://www.handelszeitung.ch/specials/nachhaltiges-investieren-2024/zwischen-esg-mudigkeit-und-wirkungsanspruch-841576</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="3" t="n">
-        <v>45292</v>
-      </c>
-      <c r="B79" s="4" t="inlineStr">
-        <is>
-          <t>FONDS exklusiv Österreich</t>
-        </is>
-      </c>
-      <c r="C79" s="4" t="inlineStr">
-        <is>
-          <t>Schwellenländer: Worauf es jetzt ankommt</t>
-        </is>
-      </c>
-      <c r="D79" s="4" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="E79" s="4" t="inlineStr">
-        <is>
-          <t>Online</t>
-        </is>
-      </c>
-      <c r="F79" s="4" t="inlineStr">
-        <is>
-          <t>Johannes Feist</t>
-        </is>
-      </c>
-      <c r="G79" s="4" t="inlineStr">
         <is>
           <t>https://www.fondsexklusiv.at/schwellenlaender-worauf-es-jetzt-ankommt/</t>
         </is>
@@ -3212,7 +3080,7 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Source: Sheet '2026 Clippings' (A9:G79)</t>
+          <t>Source: Sheet '2026 Clippings' (A9:G75)</t>
         </is>
       </c>
     </row>
@@ -3230,7 +3098,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6">
@@ -3250,7 +3118,7 @@
         </is>
       </c>
       <c r="B7" s="10" t="n">
-        <v>46309</v>
+        <v>46304</v>
       </c>
     </row>
     <row r="8">
@@ -3260,7 +3128,7 @@
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9">
@@ -3322,7 +3190,7 @@
         <v>45</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>0.6338028169014085</v>
+        <v>0.6716417910447762</v>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
@@ -3340,10 +3208,10 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>0.1549295774647887</v>
+        <v>0.1343283582089552</v>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
@@ -3364,7 +3232,7 @@
         <v>2</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>0.02816901408450704</v>
+        <v>0.02985074626865672</v>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
@@ -3382,10 +3250,10 @@
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>0.1830985915492958</v>
+        <v>0.1641791044776119</v>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
@@ -3493,7 +3361,7 @@
         </is>
       </c>
       <c r="F25" s="8" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -3550,7 +3418,7 @@
         <v>3</v>
       </c>
       <c r="C32" s="11" t="n">
-        <v>0.04225352112676056</v>
+        <v>0.04477611940298507</v>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
@@ -3558,10 +3426,10 @@
         </is>
       </c>
       <c r="F32" s="8" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="G32" s="11" t="n">
-        <v>0.971830985915493</v>
+        <v>0.9701492537313433</v>
       </c>
     </row>
     <row r="33">
@@ -3571,10 +3439,10 @@
         </is>
       </c>
       <c r="B33" s="8" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C33" s="11" t="n">
-        <v>0.2676056338028169</v>
+        <v>0.2537313432835821</v>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
@@ -3585,7 +3453,7 @@
         <v>1</v>
       </c>
       <c r="G33" s="11" t="n">
-        <v>0.01408450704225352</v>
+        <v>0.01492537313432836</v>
       </c>
     </row>
     <row r="34">
@@ -3595,10 +3463,10 @@
         </is>
       </c>
       <c r="B34" s="8" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C34" s="11" t="n">
-        <v>0.6619718309859155</v>
+        <v>0.6716417910447762</v>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
@@ -3609,7 +3477,7 @@
         <v>1</v>
       </c>
       <c r="G34" s="11" t="n">
-        <v>0.01408450704225352</v>
+        <v>0.01492537313432836</v>
       </c>
     </row>
     <row r="35">
@@ -3622,7 +3490,7 @@
         <v>2</v>
       </c>
       <c r="C35" s="11" t="n">
-        <v>0.02816901408450704</v>
+        <v>0.02985074626865672</v>
       </c>
     </row>
   </sheetData>

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -214,12 +214,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Analysis 2026'!$E$12:$E$25</f>
+              <f>'Analysis 2026'!$E$12:$E$24</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Analysis 2026'!$F$12:$F$25</f>
+              <f>'Analysis 2026'!$F$12:$F$24</f>
             </numRef>
           </val>
         </ser>
@@ -362,7 +362,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>39</row>
+      <row>38</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="6480000" cy="3600000"/>
@@ -384,7 +384,7 @@
     <from>
       <col>4</col>
       <colOff>0</colOff>
-      <row>39</row>
+      <row>38</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="4320000" cy="3600000"/>
@@ -694,7 +694,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G75"/>
+  <dimension ref="A1:G140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46311.57077370148</v>
+        <v>46311.76219818254</v>
       </c>
     </row>
     <row r="8">
@@ -999,16 +999,16 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>46238</v>
+        <v>46246</v>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Markt Einblicke</t>
+          <t>FUELS+LUBES+ENERGY</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Euro-Kupon, lokale Cashflows: Wo das Währungsrisiko wirklich liegt</t>
+          <t>Der Ölpreis und die Kapitalmärkte</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Print</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -1026,29 +1026,25 @@
           <t>Johannes Feist</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr">
-        <is>
-          <t>https://markteinblicke.de/132045/2026/08/euro-kupon-lokale-cashflows-wo-das-waehrungsrisiko-wirklich-liegt/</t>
-        </is>
-      </c>
+      <c r="G16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>46234</v>
+        <v>46245</v>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Moneycab</t>
+          <t>e-fundresearch</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist, CEO MK Global Kapital, im Interview</t>
+          <t>Experten-Umfrage: Worüber im zweiten Halbjahr 2026 keiner redet (Teil 2/2)</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>DACH</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -1063,22 +1059,22 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>https://www.moneycab.com/interviews/ceo-interviews/johannes-feist-ceo-mk-global-kapital-im-interview/</t>
+          <t>https://e-fundresearch.com/managers/artikel/60333-experten-umfrage-worueber-im-zweiten-halbjahr-2026-keiner-redet-teil-22</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>46234</v>
+        <v>46241</v>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>finanznachrichten.de</t>
+          <t>marktEINBLICKE</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist, CEO MK Global Kapital, im Interview</t>
+          <t>Euro-Kupon, lokale Cashflows: Wo das Währungsrisiko wirklich liegt</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -1088,7 +1084,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>E-Paper</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -1098,22 +1094,22 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>https://www.finanznachrichten.de/nachrichten-2026-07/69177994-johannes-feist-ceo-mk-global-kapital-im-interview-095.htm</t>
+          <t>https://markteinblicke.de/wp-content/uploads/meg/mEGeldanlage_2026_15.pdf</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>46231</v>
+        <v>46238</v>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>BondGuide</t>
+          <t>Markt Einblicke</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Private Credit: Was Anleiheinvestoren hinter dem Kupon prüfen sollten</t>
+          <t>Euro-Kupon, lokale Cashflows: Wo das Währungsrisiko wirklich liegt</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
@@ -1133,27 +1129,27 @@
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>https://www.bondguide.de/topnews/private-credit-was-anleiheinvestoren-hinter-dem-kupon-pruefen-sollten/</t>
+          <t>https://markteinblicke.de/132045/2026/08/euro-kupon-lokale-cashflows-wo-das-waehrungsrisiko-wirklich-liegt/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>46197</v>
+        <v>46234</v>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>background.tagesspiegel</t>
+          <t>Moneycab</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Digitale Kreditvergabe : Kreditzugang ist mehr als ein Score</t>
+          <t>Johannes Feist, CEO MK Global Kapital, im Interview</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -1163,32 +1159,32 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>Louiza Savchenko</t>
+          <t>Johannes Feist</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>https://background.tagesspiegel.de/finance/briefing/kreditzugang-ist-mehr-als-ein-score</t>
+          <t>https://www.moneycab.com/interviews/ceo-interviews/johannes-feist-ceo-mk-global-kapital-im-interview/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>46183</v>
+        <v>46234</v>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Finews</t>
+          <t>finanznachrichten.de</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist: «Einer meiner unerfüllter Träume ist der Sportfliegerschein»</t>
+          <t>Johannes Feist, CEO MK Global Kapital, im Interview</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -1203,22 +1199,22 @@
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>https://www.finews.ch/themen/high-end/72456-johannes-feist-einer-meiner-unerfuellter-traeume-ist-der-sportfliegerschein-ceo-global-kapital</t>
+          <t>https://www.finanznachrichten.de/nachrichten-2026-07/69177994-johannes-feist-ceo-mk-global-kapital-im-interview-095.htm</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>46169</v>
+        <v>46231</v>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Markt Einblicke</t>
+          <t>BondGuide</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Warum der Blick auf den Ölpreis nicht reicht</t>
+          <t>Private Credit: Was Anleiheinvestoren hinter dem Kupon prüfen sollten</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -1238,32 +1234,32 @@
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>https://markteinblicke.de/130696/2026/05/warum-der-blick-auf-den-oelpreis-nicht-reicht/</t>
+          <t>https://www.bondguide.de/topnews/private-credit-was-anleiheinvestoren-hinter-dem-kupon-pruefen-sollten/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>46164</v>
+        <v>46231</v>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>Moneycab</t>
+          <t>ExportManager OST</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Nicht die Grösse des Kredits entscheidet, sondern seine Wirkung</t>
+          <t>Wenn der klassische Bankkredit schlecht greift</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Print &amp; Digital</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -1271,24 +1267,20 @@
           <t>Johannes Feist</t>
         </is>
       </c>
-      <c r="G23" s="4" t="inlineStr">
-        <is>
-          <t>https://www.moneycab.com/dossiers/nicht-die-groesse-des-kredits-entscheidet-sondern-seine-wirkung/</t>
-        </is>
-      </c>
+      <c r="G23" s="4" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>46149</v>
+        <v>46231</v>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Markt Einblicke</t>
+          <t>finanznachrichten.de</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Mikrofinanz-Anleihen: Ein wachsender Markt</t>
+          <t>Private Credit: Was Anleiheinvestoren hinter dem Kupon prüfen sollten</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -1308,27 +1300,27 @@
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>https://markteinblicke.de/130263/2026/05/mikrofinanz-anleihen-ein-wachsender-markt/</t>
+          <t>https://www.finanznachrichten.de/nachrichten-2026-07/69141450-private-credit-was-anleiheinvestoren-hinter-dem-kupon-pruefen-sollten-144.htm</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>46125</v>
+        <v>46205</v>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>cash-online.de</t>
+          <t>Finews</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Tokenisierte Anleihen: Was sich für Anleger ändert und was nicht</t>
+          <t>Ferienlektüre: Was Finanzprofis diesen Sommer lesen</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
@@ -1343,22 +1335,22 @@
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>https://www.cash-online.de/a/tokenisierte-anleihen-was-sich-fuer-anleger-aendert-und-was-nicht-715994/</t>
+          <t>https://www.finews.ch/themen/leben-karriere/72628-sommer-buchempfehlungen-2026-von-persoenlichkeiten-aus-der-finanzbranche-roman-sommerlektuere-lesen-ferien-andreas-feller-thomas-studhalter-karsten-dirk-steffens-anna-bretschneider-finanzplatz-schweiz</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>46105</v>
+        <v>46198</v>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Frankfurter Allgemeine Zeitung</t>
+          <t>background.tagesspiegel</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Sorgen um Privatkredite: Finanzkrise oder silberne Aera?</t>
+          <t>Digitale Kreditvergabe : Kreditzugang ist mehr als ein Score</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -1371,30 +1363,34 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F26" s="4" t="inlineStr"/>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>Louiza Savchenko</t>
+        </is>
+      </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>https://www.faz.net/pro/meine-finanzen/zinsen/sorgen-um-privatkredite-finanzkrise-oder-silberne-aera-110376123.html</t>
+          <t>https://background.tagesspiegel.de/finance/briefing/kreditzugang-ist-mehr-als-ein-score</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>46105</v>
+        <v>46197</v>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>DAS INVESTMENT</t>
+          <t>Finanz und Wirtschaft</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Private Credit unter Druck: Wenn das Geld nicht mehr herauskommt</t>
+          <t>Rendite mit gutem Gewissen</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -1402,30 +1398,30 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr"/>
-      <c r="G27" s="4" t="inlineStr">
-        <is>
-          <t>https://www.dasinvestment.com/private-credit-unter-druck-wenn-das-geld-nicht-mehr-herauskommt/</t>
-        </is>
-      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>46105</v>
+        <v>46195</v>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>FONDS exklusiv Oesterreich</t>
+          <t>fem.capital</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Private Credit-Debatte entfacht</t>
+          <t>Warum Unternehmerinnen eher am Kapital als am Markt scheitern</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
@@ -1435,49 +1431,45 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist</t>
-        </is>
-      </c>
-      <c r="G28" s="4" t="inlineStr">
-        <is>
-          <t>https://www.fondsexklusiv.at/private-credit-debatte-entfacht/</t>
-        </is>
-      </c>
+          <t>Louiza Savchenko</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>46102</v>
+        <v>46188</v>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Der Standard</t>
+          <t>Intelligent Investors</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Pakistan spart Milliarden an fossilen Importen: Wie hat es das gemacht?</t>
+          <t>Kreditqualität lässt sich nicht aus der Distanz steuern</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>Online</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr"/>
-      <c r="G29" s="4" t="inlineStr">
-        <is>
-          <t>https://www.derstandard.de/story/3000000313347/pakistan-spart-milliarden-an-fossilen-importen-wie-hat-es-das-gemacht</t>
-        </is>
-      </c>
+          <t>Print</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>46102</v>
+        <v>46183</v>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
@@ -1486,7 +1478,7 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Tokenisierung: Louzia Savchenko ueber Innovation und MK Global Kapital</t>
+          <t>Johannes Feist: «Einer meiner unerfüllter Träume ist der Sportfliegerschein»</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -1501,27 +1493,27 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>Louiza Savchenko</t>
+          <t>Johannes Feist</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>https://www.finews.ch/news/finanzplatz/71578-finews-first-tokenisierung-louzia-savchenko-finanzplatz-schweiz-innovation-mk-global-kapital</t>
+          <t>https://www.finews.ch/themen/high-end/72456-johannes-feist-einer-meiner-unerfuellter-traeume-ist-der-sportfliegerschein-ceo-global-kapital</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>46101</v>
+        <v>46176</v>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>BondGuide</t>
+          <t>BOND MAGAZINE</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Private Credit ist nicht gleich Private Credit: wo die Risiken wirklich liegen</t>
+          <t>Der neue Stresstest für Schwellenländer: Warum Öl, Zinsen und Währungen nur der Anfang sind und letztlich die Finanzierungsstruktur entscheidet</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -1531,7 +1523,7 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Print</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -1541,27 +1533,27 @@
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>https://www.bondguide.de/topnews/private-credit-ist-nicht-gleich-private-credit-wo-die-risiken-wirklich-liegen/</t>
+          <t>https://www.fixed-income.org/fileadmin/pdf/BOND_MAGAZINE_239.pdf</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>46100</v>
+        <v>46174</v>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Moneycab</t>
+          <t>FONDS exklusiv Österreich</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Nicht nur Öl: Wo der Iran-Konflikt Emerging Markets wirklich trifft</t>
+          <t>Schwellenländer: Worauf es jetzt ankommt</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
@@ -1576,22 +1568,22 @@
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>https://www.moneycab.com/finanz/nicht-nur-oel-wo-der-iran-konflikt-emerging-markets-wirklich-trifft/</t>
+          <t>https://www.fondsexklusiv.at/schwellenlaender-worauf-es-jetzt-ankommt/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>46100</v>
+        <v>46174</v>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Institutional Money</t>
+          <t>Intelligent Investors</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Was der Iran-Schock fuer Emerging Markets veraendert</t>
+          <t>Die neue Verwundbarkeit der Schwellenländer</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
@@ -1604,30 +1596,34 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F33" s="4" t="inlineStr"/>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>https://www.institutional-money.com/news/maerkte/headline/was-der-iran-schock-fuer-emerging-markets-veraendert-249420</t>
+          <t>https://intelligent-investors.de/die-neue-verwundbarkeit-der-schwellenlaender/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>46100</v>
+        <v>46174</v>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>fixed-income.org</t>
+          <t>Institutional Money</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Was der Iran-Schock fuer Emerging Markets veraendert</t>
+          <t>Finanzierungsstruktur: Der neue Stresstest für Schwellenländer</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>DACH</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
@@ -1642,27 +1638,27 @@
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>https://www.fixed-income.org/investment/was-der-iran-schock-fuer-emerging-markets-veraendert.html</t>
+          <t>https://www.institutional-money.com/news/maerkte/headline/finanzierungsstruktur-der-neue-stresstest-fuer-schwellenlaender-251058</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>46098</v>
+        <v>46174</v>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>finanznachrichten.de</t>
+          <t>Neo Market Ways</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Private Credit ist nicht gleich Private Credit: Wo die Risiken wirklich liegen</t>
+          <t>From Microfinance to Mobility: How Capital is Driving Growth Across Eastern Europe</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>DACH</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
@@ -1677,22 +1673,22 @@
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>https://www.finanznachrichten.de/nachrichten-2026-03/67998176-private-credit-ist-nicht-gleich-private-credit-wo-die-risiken-wirklich-liegen-144.htm</t>
+          <t>https://neomarketways.com/from-microfinance-to-mobility-how-capital-is-driving-growth-across-eastern-europe/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>46098</v>
+        <v>46171</v>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>cash-online.de</t>
+          <t>NEX24 News</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Gastkommentar: Der blinde Fleck der Private-Credit-Debatte</t>
+          <t>Iran-Krieg: Der neue Stresstest für Schwellenländer</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -1712,27 +1708,27 @@
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>https://www.cash-online.de/a/gastkommentar-der-blinde-fleck-der-private-credit-debatte-713724/</t>
+          <t>https://nex24.news/2026/05/iran-krieg-der-neue-stresstest-fuer-schwellenlaender/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>46097</v>
+        <v>46170</v>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>FONDS exklusiv</t>
+          <t>GELD-Magazin</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Private Credit-Debatte entfacht</t>
+          <t>Stresstest für Schwellenländer</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
@@ -1747,22 +1743,22 @@
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>https://www.fondsexklusiv.de/private-credit-debatte-entfacht/</t>
+          <t>https://www.geld-magazin.at/stresstest-fuer-schwellenlaender/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>46097</v>
+        <v>46169</v>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Kreditwesen (Verlagsgruppe Knapp-Richardi)</t>
+          <t>Markt Einblicke</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Mikrofinanz als Anlageklasse</t>
+          <t>Warum der Blick auf den Ölpreis nicht reicht</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -1772,7 +1768,7 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>Print &amp; Online</t>
+          <t>Online</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
@@ -1782,22 +1778,22 @@
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>https://www.kreditwesen.de/kreditwesen/themenschwerpunkte/aufsaetze/mikrofinanz-anlageklasse-id107511.html</t>
+          <t>https://markteinblicke.de/130696/2026/05/warum-der-blick-auf-den-oelpreis-nicht-reicht/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>46094</v>
+        <v>46164</v>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>investrends.ch</t>
+          <t>Moneycab</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Der blinde Fleck der Private-Credit-Debatte</t>
+          <t>Nicht die Grösse des Kredits entscheidet, sondern seine Wirkung</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -1817,22 +1813,22 @@
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>https://investrends.ch/aktuell/investments/der-blinde-fleck-der-private-credit-debatte/</t>
+          <t>https://www.moneycab.com/dossiers/nicht-die-groesse-des-kredits-entscheidet-sondern-seine-wirkung/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>46093</v>
+        <v>46164</v>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Finanzen100.de</t>
+          <t>finanznachrichten.de</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Marktkommentar: Der Trugschluss der sicheren Häfen</t>
+          <t>Nicht die Grösse des Kredits entscheidet, sondern seine Wirkung</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
@@ -1852,53 +1848,53 @@
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>https://www.finanzen100.de/premium/bernecker-boersenkompass/marktkommentar-der-trugschluss-der-sicheren-haefen_H1356104965_6799449/</t>
+          <t>https://www.finanznachrichten.de/nachrichten-2026-05/68568705-nicht-die-groesse-des-kredits-entscheidet-sondern-seine-wirkung-095.htm</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>46091</v>
+        <v>46150</v>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Swiss Finance AI</t>
+          <t>Finanz- und Wirtschaftsspiegel</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Warum tokenisierte Anleihen mehr sind als ein Trend</t>
+          <t>Entwicklungsfinanzierung mit Mikrokrediten</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>Online</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="inlineStr"/>
-      <c r="G41" s="4" t="inlineStr">
-        <is>
-          <t>https://www.swissfinanceai.ch/blog/swiss-finance/warum-tokenisierte-anleihen-mehr-sind-als-ein-trend</t>
-        </is>
-      </c>
+          <t>Digital newsletter</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>46085</v>
+        <v>46149</v>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>markteinblicke.de</t>
+          <t>Markt Einblicke</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Tokenisierte Anleihen: Mehr Governance erforderlich</t>
+          <t>Mikrofinanz-Anleihen: Ein wachsender Markt</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1913,27 +1909,27 @@
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>Louiza Savchenko</t>
+          <t>Johannes Feist</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>https://markteinblicke.de/128943/2026/03/tokenisierte-anleihen-mehr-governance-erforderlich/</t>
+          <t>https://markteinblicke.de/130263/2026/05/mikrofinanz-anleihen-ein-wachsender-markt/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>46085</v>
+        <v>46125</v>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>gruenderkueche.de</t>
+          <t>cash-online.de</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Weltfrauentag: Unternehmerinnen fehlt weiterhin der Zugang zu Kapital</t>
+          <t>Tokenisierte Anleihen: Was sich für Anleger ändert und was nicht</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1953,22 +1949,22 @@
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>https://www.gruenderkueche.de/news/finanzen-news/weltfrauentag-unternehmerinnen-fehlt-weiterhin-der-zugang-zu-kapital/</t>
+          <t>https://www.cash-online.de/a/tokenisierte-anleihen-was-sich-fuer-anleger-aendert-und-was-nicht-715994/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>46083</v>
+        <v>46109</v>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>altii.de</t>
+          <t>Wirtschaftsvision</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Unternehmerinnen fehlt weltweit der Zugang zu Kapital</t>
+          <t>Der Trugschluss der sicheren Häfen</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1981,25 +1977,29 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F44" s="4" t="inlineStr"/>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>https://www.altii.de/edai-71550571-cb6c-4c09-93da-bd99b822c245/</t>
+          <t>https://wirtschaftsvision.de/der-trugschluss-der-sicheren-haefen/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>46083</v>
+        <v>46108</v>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>dfpa.info</t>
+          <t>Börsen-Zeitung</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Unternehmerinnen fehlt weltweit der Zugang zu Kapital</t>
+          <t>Wasserknappheit als Kreditrisiko</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -2009,32 +2009,32 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Print &amp; Online</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>Louiza Savchenko</t>
+          <t>Johannes Feist</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>https://www.dfpa.info/maerkte-studien-news/unternehmerinnen-fehlt-weltweit-der-zugang-zu-kapital/</t>
+          <t>https://www.boersen-zeitung.de/sonderbeilagen/wasserknappheit-als-kreditrisiko</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>46077</v>
+        <v>46105</v>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>dfpa.info</t>
+          <t>Frankfurter Allgemeine Zeitung</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Wenn Geschäftsbanken passen, helfen Mikrofinanzfonds</t>
+          <t>Sorgen um Privatkredite: Finanzkrise oder silberne Aera?</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -2054,22 +2054,22 @@
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>https://www.dfpa.info/top-story/wenn-geschaeftsbanken-passen-helfen-mikrofinanzfonds.html</t>
+          <t>https://www.faz.net/pro/meine-finanzen/zinsen/sorgen-um-privatkredite-finanzkrise-oder-silberne-aera-110376123.html</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>46076</v>
+        <v>46105</v>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>exxecnews.org</t>
+          <t>DAS INVESTMENT</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Teil I: Wenn Geschäftsbanken passen, helfen Mikrofinanzfonds</t>
+          <t>Private Credit unter Druck: Wenn das Geld nicht mehr herauskommt</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -2082,30 +2082,34 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F47" s="4" t="inlineStr"/>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>https://exxecnews.org/wp-content/uploads/2026/02/Ausgabe-05_2026.pdf</t>
+          <t>https://www.dasinvestment.com/private-credit-unter-druck-wenn-das-geld-nicht-mehr-herauskommt/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>46071</v>
+        <v>46105</v>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>dfpa.info</t>
+          <t>FONDS exklusiv Oesterreich</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Mikrofinanz: Besonderheit Anleihen mit festem Zins</t>
+          <t>Private Credit-Debatte entfacht</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
@@ -2120,27 +2124,27 @@
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>https://www.dfpa.info/interview/mikrofinanz-besonderheit-anleihen-mit-festem-zins.html</t>
+          <t>https://www.fondsexklusiv.at/private-credit-debatte-entfacht/</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>46069</v>
+        <v>46103</v>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Börsen-Kurier</t>
+          <t>Der Standard</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Privates Kapital für noch nicht entwickelte Märkte</t>
+          <t>Pakistan spart Milliarden an fossilen Importen: Wie hat es das gemacht?</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>DACH</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
@@ -2148,26 +2152,34 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F49" s="4" t="inlineStr"/>
-      <c r="G49" s="4" t="inlineStr"/>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t>https://www.derstandard.de/story/3000000313347/pakistan-spart-milliarden-an-fossilen-importen-wie-hat-es-das-gemacht</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
-        <v>46069</v>
+        <v>46101</v>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>boerse-social.com</t>
+          <t>Finews</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>Börse-Inputs auf Spotify zu u.a. Do&amp;Co, Bawag, Nervigem und Mikrokrediten</t>
+          <t>Tokenisierung: Louzia Savchenko ueber Innovation und MK Global Kapital</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
@@ -2177,27 +2189,27 @@
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist</t>
+          <t>Louiza Savchenko</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>https://boerse-social.com/2026/02/16/borse-inputs_auf_spotify_zu_ua_doco_bawag_nervigem_und_mikrokrediten_1</t>
+          <t>https://www.finews.ch/news/finanzplatz/71578-finews-first-tokenisierung-louzia-savchenko-finanzplatz-schweiz-innovation-mk-global-kapital</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
-        <v>46067</v>
+        <v>46101</v>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>finanznachrichten.de</t>
+          <t>BondGuide</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Security Conference München 2026: öffentliche Mittel als Hebel nutzen</t>
+          <t>Private Credit ist nicht gleich Private Credit: wo die Risiken wirklich liegen</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -2217,27 +2229,27 @@
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>https://www.finanznachrichten.de/nachrichten-2026-02/67704129-security-conference-muenchen-2026-oeffentliche-mittel-als-hebel-nutzen-144.htm</t>
+          <t>https://www.bondguide.de/topnews/private-credit-ist-nicht-gleich-private-credit-wo-die-risiken-wirklich-liegen/</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
-        <v>46067</v>
+        <v>46101</v>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>bondguide.de</t>
+          <t>Swiss Finance AI</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>Security Conference München 2026: öffentliche Mittel als Hebel nutzen</t>
+          <t>Warum tokenisierte Anleihen mehr sind als ein Trend</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
@@ -2247,32 +2259,32 @@
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist</t>
+          <t>Louiza Savchenko</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>https://www.bondguide.de/topnews/security-conference-muenchen-2026-oeffentliche-mittel-als-hebel-nutzen/</t>
+          <t>https://www.swissfinanceai.ch/blog/swiss-finance/warum-tokenisierte-anleihen-mehr-sind-als-ein-trend</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
-        <v>46067</v>
+        <v>46100</v>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>geldmeisterin.com</t>
+          <t>Moneycab</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Mikrokredite gerade jetzt zur Risikostreuung</t>
+          <t>Nicht nur Öl: Wo der Iran-Konflikt Emerging Markets wirklich trifft</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
@@ -2287,22 +2299,22 @@
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>https://www.geldmeisterin.com/index.php/2026/02/14/mikrokredite-gerade-jetzt-zur-risikostreuung/</t>
+          <t>https://www.moneycab.com/finanz/nicht-nur-oel-wo-der-iran-konflikt-emerging-markets-wirklich-trifft/</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
-        <v>46067</v>
+        <v>46100</v>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>geldmeisterin.com</t>
+          <t>Institutional Money</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>Mikrokredite als Anlagealternative</t>
+          <t>Was der Iran-Schock fuer Emerging Markets veraendert</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -2322,27 +2334,27 @@
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>https://podcasters.spotify.com/pod/show/geldmeisterin/episodes/Mikrokredite-als-Anlagealternative-e3f11ln</t>
+          <t>https://www.institutional-money.com/news/maerkte/headline/was-der-iran-schock-fuer-emerging-markets-veraendert-249420</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
-        <v>46057</v>
+        <v>46100</v>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>investrends.ch</t>
+          <t>fixed-income.org</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>Private Debt: Warum Prozesse wichtiger sind als Prognosen</t>
+          <t>Was der Iran-Schock fuer Emerging Markets veraendert</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
@@ -2352,32 +2364,32 @@
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>Michele Mattioda</t>
+          <t>Johannes Feist</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>https://investrends.ch/aktuell/investments/private-debt-warum-prozesse-wichtiger-sind-als-prognosen/</t>
+          <t>https://www.fixed-income.org/investment/was-der-iran-schock-fuer-emerging-markets-veraendert.html</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
-        <v>46055</v>
+        <v>46100</v>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Payoff</t>
+          <t>finanznachrichten.de</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>Mikrofinanz als Private Debt: Besicherte KMU-Kredite statt «Entwicklungshilfe»</t>
+          <t>Nicht nur Öl: Wo der Iran-Konflikt Emerging Markets wirklich trifft</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
@@ -2392,22 +2404,22 @@
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>https://www.payoff.ch/news/mikrofinanz-als-private-debt-besicherte-kmu-kredite-statt-entwicklungshilfe</t>
+          <t>https://www.finanznachrichten.de/nachrichten-2026-03/67987291-nicht-nur-oel-wo-der-iran-konflikt-emerging-markets-wirklich-trifft-095.htm</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
-        <v>46049</v>
+        <v>46098</v>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Markt Einblicke</t>
+          <t>finanznachrichten.de</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Mikrofinanzanleihen 2026: Stabile Renditen aus der Realwirtschaft</t>
+          <t>Private Credit ist nicht gleich Private Credit: Wo die Risiken wirklich liegen</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -2417,24 +2429,32 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>Print</t>
-        </is>
-      </c>
-      <c r="F57" s="4" t="inlineStr"/>
-      <c r="G57" s="4" t="inlineStr"/>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F57" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="inlineStr">
+        <is>
+          <t>https://www.finanznachrichten.de/nachrichten-2026-03/67998176-private-credit-ist-nicht-gleich-private-credit-wo-die-risiken-wirklich-liegen-144.htm</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
-        <v>46044</v>
+        <v>46098</v>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Frankfurter Allgemeine Zeitung</t>
+          <t>cash-online.de</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>Beim Klimaschutz mehr Marktwirtschaft wagen</t>
+          <t>Gastkommentar: Der blinde Fleck der Private-Credit-Debatte</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -2447,65 +2467,65 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F58" s="4" t="inlineStr"/>
+      <c r="F58" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>https://www.faz.net/pro/weltwirtschaft/klima-ressourcen/klimapolitik-sollte-auf-mikrofinanzierung-statt-grossprojekte-setzen-accg-200431361.html</t>
+          <t>https://www.cash-online.de/a/gastkommentar-der-blinde-fleck-der-private-credit-debatte-713724/</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
-        <v>46038</v>
+        <v>46098</v>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>E-fundresearch</t>
+          <t>BOND MAGAZINE</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Umfrage: Welche Chancen und Risiken Experten 2026 in den Private Markets sehen</t>
+          <t>Tokenisierte Anleihen: Effizienz, Vertrauen und Marktentwicklung</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>DACH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Print</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist</t>
-        </is>
-      </c>
-      <c r="G59" s="4" t="inlineStr">
-        <is>
-          <t>https://e-fundresearch.com/funds/artikel/57840-umfrage-welche-chancen-und-risiken-experten-2026-in-den-private-markets-sehen?page=5</t>
-        </is>
-      </c>
+          <t>Louiza Savchenko</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
-        <v>46035</v>
+        <v>46097</v>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Finews</t>
+          <t>FONDS exklusiv</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Start 2026: Disziplin als Renditequelle bei KMU-Private Debt</t>
+          <t>Private Credit-Debatte entfacht</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
@@ -2515,27 +2535,27 @@
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>Michele Mattioda</t>
+          <t>Johannes Feist</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>https://www.finews.ch/news/finanzplatz/70792-start2026-assetmanagement-mk-global-kapital-michele-mattioda-privat-debt-kmu-mikro</t>
+          <t>https://www.fondsexklusiv.de/private-credit-debatte-entfacht/</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
-        <v>46029</v>
+        <v>46097</v>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Markt Einblicke</t>
+          <t>Kreditwesen (Verlagsgruppe Knapp-Richardi)</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Mikrofinanzanleihen 2026: Stabile Renditen aus der Realwirtschaft</t>
+          <t>Mikrofinanz als Anlageklasse</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -2545,7 +2565,7 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Print &amp; Online</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
@@ -2555,27 +2575,27 @@
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>https://markteinblicke.de/127407/2026/01/mikrofinanzanleihen-2026-stabile-renditen-aus-der-realwirtschaft/</t>
+          <t>https://www.kreditwesen.de/kreditwesen/themenschwerpunkte/aufsaetze/mikrofinanz-anlageklasse-id107511.html</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
-        <v>46028</v>
+        <v>46097</v>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>portfolio institutionell</t>
+          <t>Payoff</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Große Wirkung mit kleinen Krediten</t>
+          <t>Der blinde Fleck der Private-Credit-Debatte</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
@@ -2590,13 +2610,13 @@
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>https://www.portfolio-institutionell.de/grosse-wirkung-mit-kleinen-krediten/</t>
+          <t>https://www.payoff.ch/news/der-blinde-fleck-der-private-credit-debatte</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
-        <v>46000</v>
+        <v>46094</v>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
@@ -2605,7 +2625,7 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Neue Managementgesellschaft für den Impact-Fonds ALTERNATIVE</t>
+          <t>Der blinde Fleck der Private-Credit-Debatte</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -2625,27 +2645,27 @@
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>https://investrends.ch/aktuell/investments/neue-managementgesellschaft-fur-den-impact-fonds-alternative/</t>
+          <t>https://investrends.ch/aktuell/investments/der-blinde-fleck-der-private-credit-debatte/</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
-        <v>45999</v>
+        <v>46094</v>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Moneycab</t>
+          <t>Private Markets 360</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>MK Global Kapital wird per 1. Januar Managementgesellschaft für den Impact-Fonds ALTERNATIVE</t>
+          <t>Der blinde Fleck der Private-Credit-Debatte</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
@@ -2660,22 +2680,22 @@
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>https://www.moneycab.com/finanz/mk-global-kapital-wird-per-1-januar-managementgesellschaft-fuer-den-impact-fonds-alternative/</t>
+          <t>https://privatemarkets360.com/artikel/58516-der-blinde-fleck-der-private-credit-debatte</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
-        <v>45999</v>
+        <v>46093</v>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>dfpa.info</t>
+          <t>Finanzen100.de</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>MK Global Kapital wird Managementgesellschaft für Impact-Fonds "Alternative"</t>
+          <t>Marktkommentar: Der Trugschluss der sicheren Häfen</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -2695,22 +2715,22 @@
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>https://www.dfpa.info/investmentfonds-news/mk-global-kapital-wird-managementgesellschaft-fuer-impact-fonds-alternative/</t>
+          <t>https://www.finanzen100.de/premium/bernecker-boersenkompass/marktkommentar-der-trugschluss-der-sicheren-haefen_H1356104965_6799449/</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
-        <v>45997</v>
+        <v>46093</v>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>bondguide.de</t>
+          <t>Intelligent Investors</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>Mikro Kapital Management: Impact Investing ist kein Charity</t>
+          <t>Der blinde Fleck der Private-Credit-Debatte</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -2730,22 +2750,22 @@
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>https://www.bondguide.de/topnews/mikro-kapital-management-impact-investing-ist-kein-charity/</t>
+          <t>https://intelligent-investors.de/der-blinde-fleck-der-private-credit-debatte/</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
-        <v>45996</v>
+        <v>46085</v>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>finanznachrichten.de</t>
+          <t>markteinblicke.de</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Mikro Kapital Management: "Impact Investing ist kein Charity"</t>
+          <t>Tokenisierte Anleihen: Mehr Governance erforderlich</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -2760,27 +2780,27 @@
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist</t>
+          <t>Louiza Savchenko</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>https://www.finanznachrichten.de/nachrichten-2025-12/67161108-mikro-kapital-management-impact-investing-ist-kein-charity-144.htm</t>
+          <t>https://markteinblicke.de/128943/2026/03/tokenisierte-anleihen-mehr-governance-erforderlich/</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="n">
-        <v>45995</v>
+        <v>46085</v>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>dfpa.info</t>
+          <t>gruenderkueche.de</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>Mikro Kapital platziert erstmals Anleihe an Luxemburger Börse</t>
+          <t>Weltfrauentag: Unternehmerinnen fehlt weiterhin der Zugang zu Kapital</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -2795,32 +2815,32 @@
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist</t>
+          <t>Louiza Savchenko</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>https://www.dfpa.info/investmentfonds-news/mikro-kapital-platziert-erstmals-emtn-anleihen-des-fonds-alternative-an-luxemburger-boerse/</t>
+          <t>https://www.gruenderkueche.de/news/finanzen-news/weltfrauentag-unternehmerinnen-fehlt-weiterhin-der-zugang-zu-kapital/</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
-        <v>45985</v>
+        <v>46085</v>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Finews</t>
+          <t>Table.Media</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist über Mikrofinanzen: Sollten vom hohen Ross herunterkommen</t>
+          <t>Gleichstellung: Unternehmerinnen fehlt weltweit der Zugang zu Kapital</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
@@ -2830,32 +2850,32 @@
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist</t>
+          <t>Louiza Savchenko</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>https://www.finews.ch/news/finanzplatz/70147-mikro-capital-johannes-feist-kuenstliche-intelligenz-blockchain-rumaenien-europa-mikrofinanzen-finanzplatz-schweiz</t>
+          <t>https://table.media/esg/news/gleichstellung-unternehmerinnen-fehlt-weltweit-der-zugang-zu-kapital</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="n">
-        <v>45973</v>
+        <v>46084</v>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>investrends.ch</t>
+          <t>dfpa.info</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>Mikrofinanz ist Private Debt mit direkter Verbindung zur Realwirtschaft</t>
+          <t>Unternehmerinnen fehlt weltweit der Zugang zu Kapital</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
@@ -2865,27 +2885,27 @@
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist</t>
+          <t>Louiza Savchenko</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>https://investrends.ch/aktuell/investments/mikrofinanz-ist-private-debt-mit-direkter-verbindung-zur-realwirtschaft/</t>
+          <t>https://www.dfpa.info/maerkte-studien-news/unternehmerinnen-fehlt-weltweit-der-zugang-zu-kapital/</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
-        <v>45968</v>
+        <v>46083</v>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Frankfurter Rundschau</t>
+          <t>altii.de</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>Merz in Brasilien: Bundeskanzler fordert „globale Kraftanstrengung“ für Klimaschutz bei COP30</t>
+          <t>Unternehmerinnen fehlt weltweit der Zugang zu Kapital</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -2900,27 +2920,27 @@
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist</t>
+          <t>Louiza Savchenko</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>https://www.fr.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.altii.de/edai-71550571-cb6c-4c09-93da-bd99b822c245/</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="n">
-        <v>45967</v>
+        <v>46083</v>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>Windmesse</t>
+          <t>dapd.de</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>COP30: Klimafinanzierung muss endlich in den Unternehmen ankommen</t>
+          <t>Der Trugschluss der sicheren Häfen</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -2940,22 +2960,22 @@
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
-          <t>https://w3.windmesse.de/windenergie/news/48059-cop30-klimafinanzierung-muss-endlich-in-den-unternehmen-ankommen</t>
+          <t>https://www.dapd.de/der-trugschluss-der-sicheren-haefen/</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="n">
-        <v>45967</v>
+        <v>46078</v>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>BondGuide</t>
+          <t>dfpa.info</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>Klimafinanzierung bei COP 30: von Zusagen zu Wirkung entfalten</t>
+          <t>Mikrofinanz: Besonderheit Anleihen mit festem Zins</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -2975,27 +2995,27 @@
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>https://www.bondguide.de/topnews/klimafinanzierung-bei-cop-30-von-zusagen-zu-wirkung-entfalten/</t>
+          <t>https://www.dfpa.info/interview/mikrofinanz-besonderheit-anleihen-mit-festem-zins.html</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="n">
-        <v>45848</v>
+        <v>46077</v>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>Handelszeitung</t>
+          <t>dfpa.info</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>Zwischen ESG-Müdigkeit und Wirkungsanspruch</t>
+          <t>Wenn Geschäftsbanken passen, helfen Mikrofinanzfonds</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
@@ -3003,45 +3023,2308 @@
           <t>Online</t>
         </is>
       </c>
-      <c r="F74" s="4" t="inlineStr"/>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>https://www.handelszeitung.ch/specials/nachhaltiges-investieren-2024/zwischen-esg-mudigkeit-und-wirkungsanspruch-841576</t>
+          <t>https://www.dfpa.info/top-story/wenn-geschaeftsbanken-passen-helfen-mikrofinanzfonds.html</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="n">
-        <v>45292</v>
+        <v>46077</v>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>FONDS exklusiv Österreich</t>
+          <t>DFPA</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>Schwellenländer: Worauf es jetzt ankommt</t>
+          <t>Die neue EXXECNEWS ist erschienen</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G75" s="4" t="inlineStr">
+        <is>
+          <t>https://www.dfpa.info/pressedigest-news/die-neue-exxecnews-ist-erschienen-78/</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="n">
+        <v>46076</v>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>exxecnews.org</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>Teil I: Wenn Geschäftsbanken passen, helfen Mikrofinanzfonds</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>Print &amp; Online</t>
+        </is>
+      </c>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G76" s="4" t="inlineStr">
+        <is>
+          <t>https://exxecnews.org/wp-content/uploads/2026/02/Ausgabe-05_2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="3" t="n">
+        <v>46076</v>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>EXXECNEWS</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>Teil II: Mikrofinanz-Besonderheit – Anleihen mit festem Zins</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>Print &amp; Online</t>
+        </is>
+      </c>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G77" s="4" t="inlineStr">
+        <is>
+          <t>https://exxecnews.org/wp-content/uploads/2026/02/Ausgabe-05_2026.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="3" t="n">
+        <v>46069</v>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>boerse-social.com</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>Börse-Inputs auf Spotify zu u.a. Do&amp;Co, Bawag, Nervigem und Mikrokrediten</t>
+        </is>
+      </c>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E78" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F78" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G78" s="4" t="inlineStr">
+        <is>
+          <t>https://boerse-social.com/2026/02/16/borse-inputs_auf_spotify_zu_ua_doco_bawag_nervigem_und_mikrokrediten_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="n">
+        <v>46069</v>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
+          <t>bondguide.de</t>
+        </is>
+      </c>
+      <c r="C79" s="4" t="inlineStr">
+        <is>
+          <t>Security Conference München 2026: öffentliche Mittel als Hebel nutzen</t>
+        </is>
+      </c>
+      <c r="D79" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E79" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F79" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G79" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bondguide.de/topnews/security-conference-muenchen-2026-oeffentliche-mittel-als-hebel-nutzen/</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="n">
+        <v>46067</v>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>finanznachrichten.de</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>Security Conference München 2026: öffentliche Mittel als Hebel nutzen</t>
+        </is>
+      </c>
+      <c r="D80" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F80" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G80" s="4" t="inlineStr">
+        <is>
+          <t>https://www.finanznachrichten.de/nachrichten-2026-02/67704129-security-conference-muenchen-2026-oeffentliche-mittel-als-hebel-nutzen-144.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="3" t="n">
+        <v>46067</v>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>geldmeisterin.com</t>
+        </is>
+      </c>
+      <c r="C81" s="4" t="inlineStr">
+        <is>
+          <t>Mikrokredite gerade jetzt zur Risikostreuung</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E81" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G81" s="4" t="inlineStr">
+        <is>
+          <t>https://www.geldmeisterin.com/index.php/2026/02/14/mikrokredite-gerade-jetzt-zur-risikostreuung/</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="3" t="n">
+        <v>46066</v>
+      </c>
+      <c r="B82" s="4" t="inlineStr">
+        <is>
+          <t>Börsen-Kurier</t>
+        </is>
+      </c>
+      <c r="C82" s="4" t="inlineStr">
+        <is>
+          <t>Privates Kapital für noch nicht entwickelte Märkte</t>
+        </is>
+      </c>
+      <c r="D82" s="4" t="inlineStr">
+        <is>
+          <t>DACH</t>
+        </is>
+      </c>
+      <c r="E82" s="4" t="inlineStr">
+        <is>
+          <t>Print</t>
+        </is>
+      </c>
+      <c r="F82" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G82" s="4" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="n">
+        <v>46057</v>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>investrends.ch</t>
+        </is>
+      </c>
+      <c r="C83" s="4" t="inlineStr">
+        <is>
+          <t>Private Debt: Warum Prozesse wichtiger sind als Prognosen</t>
+        </is>
+      </c>
+      <c r="D83" s="4" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>Michele Mattioda</t>
+        </is>
+      </c>
+      <c r="G83" s="4" t="inlineStr">
+        <is>
+          <t>https://investrends.ch/aktuell/investments/private-debt-warum-prozesse-wichtiger-sind-als-prognosen/</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B84" s="4" t="inlineStr">
+        <is>
+          <t>Payoff</t>
+        </is>
+      </c>
+      <c r="C84" s="4" t="inlineStr">
+        <is>
+          <t>Mikrofinanz als Private Debt: Besicherte KMU-Kredite statt «Entwicklungshilfe»</t>
+        </is>
+      </c>
+      <c r="D84" s="4" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F84" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G84" s="4" t="inlineStr">
+        <is>
+          <t>https://www.payoff.ch/news/mikrofinanz-als-private-debt-besicherte-kmu-kredite-statt-entwicklungshilfe</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>Markt Einblicke</t>
+        </is>
+      </c>
+      <c r="C85" s="4" t="inlineStr">
+        <is>
+          <t>Mikrofinanzanleihen 2026: Stabile Renditen aus der Realwirtschaft</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E85" s="4" t="inlineStr">
+        <is>
+          <t>E-Paper</t>
+        </is>
+      </c>
+      <c r="F85" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G85" s="4" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="3" t="n">
+        <v>46044</v>
+      </c>
+      <c r="B86" s="4" t="inlineStr">
+        <is>
+          <t>Frankfurter Allgemeine Zeitung</t>
+        </is>
+      </c>
+      <c r="C86" s="4" t="inlineStr">
+        <is>
+          <t>Beim Klimaschutz mehr Marktwirtschaft wagen</t>
+        </is>
+      </c>
+      <c r="D86" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E86" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F86" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G86" s="4" t="inlineStr">
+        <is>
+          <t>https://www.faz.net/pro/weltwirtschaft/klima-ressourcen/klimapolitik-sollte-auf-mikrofinanzierung-statt-grossprojekte-setzen-accg-200431361.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="3" t="n">
+        <v>46038</v>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>E-fundresearch</t>
+        </is>
+      </c>
+      <c r="C87" s="4" t="inlineStr">
+        <is>
+          <t>Umfrage: Welche Chancen und Risiken Experten 2026 in den Private Markets sehen</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="inlineStr">
+        <is>
+          <t>DACH</t>
+        </is>
+      </c>
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F87" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G87" s="4" t="inlineStr">
+        <is>
+          <t>https://e-fundresearch.com/funds/artikel/57840-umfrage-welche-chancen-und-risiken-experten-2026-in-den-private-markets-sehen?page=5</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="3" t="n">
+        <v>46035</v>
+      </c>
+      <c r="B88" s="4" t="inlineStr">
+        <is>
+          <t>Finews</t>
+        </is>
+      </c>
+      <c r="C88" s="4" t="inlineStr">
+        <is>
+          <t>Start 2026: Disziplin als Renditequelle bei KMU-Private Debt</t>
+        </is>
+      </c>
+      <c r="D88" s="4" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="E88" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F88" s="4" t="inlineStr">
+        <is>
+          <t>Michele Mattioda</t>
+        </is>
+      </c>
+      <c r="G88" s="4" t="inlineStr">
+        <is>
+          <t>https://www.finews.ch/news/finanzplatz/70792-start2026-assetmanagement-mk-global-kapital-michele-mattioda-privat-debt-kmu-mikro</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="n">
+        <v>46031</v>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>portfolio institutionell</t>
+        </is>
+      </c>
+      <c r="C89" s="4" t="inlineStr">
+        <is>
+          <t>Große Wirkung mit kleinen Krediten</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E89" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F89" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G89" s="4" t="inlineStr">
+        <is>
+          <t>https://www.portfolio-institutionell.de/grosse-wirkung-mit-kleinen-krediten/</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="3" t="n">
+        <v>46029</v>
+      </c>
+      <c r="B90" s="4" t="inlineStr">
+        <is>
+          <t>Markt Einblicke</t>
+        </is>
+      </c>
+      <c r="C90" s="4" t="inlineStr">
+        <is>
+          <t>Mikrofinanzanleihen 2026: Stabile Renditen aus der Realwirtschaft</t>
+        </is>
+      </c>
+      <c r="D90" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E90" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F90" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G90" s="4" t="inlineStr">
+        <is>
+          <t>https://markteinblicke.de/127407/2026/01/mikrofinanzanleihen-2026-stabile-renditen-aus-der-realwirtschaft/</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="3" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>portfolio institutionell</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>Große Wirkung mit kleinen Krediten</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E91" s="4" t="inlineStr">
+        <is>
+          <t>Print</t>
+        </is>
+      </c>
+      <c r="F91" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G91" s="4" t="inlineStr">
+        <is>
+          <t>https://www.yumpu.com/de/document/read/70885506/pit-1225</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="3" t="n">
+        <v>46008</v>
+      </c>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t>BondGuide</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>Mikro Kapital Management: „Impact Investing ist kein Charity“</t>
+        </is>
+      </c>
+      <c r="D92" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E92" s="4" t="inlineStr">
+        <is>
+          <t>Print</t>
+        </is>
+      </c>
+      <c r="F92" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G92" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bondguide.de/wp-content/uploads/2025/12/bondguide-25-2025.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="3" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>IPE Institutional Investment</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>Gastbeitrag: Private Debt jenseits von Corporate Loans – Mikrofinanz als Anlageklasse</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="inlineStr">
+        <is>
+          <t>DACH</t>
+        </is>
+      </c>
+      <c r="E93" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F93" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G93" s="4" t="inlineStr">
+        <is>
+          <t>https://www.institutional-investment.de/content/asset-allocation/gastbeitrag-private-debt-jenseits-von-corporate-loans-mikrofinanz-als-anlageklasse.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>Handelszeitung</t>
+        </is>
+      </c>
+      <c r="C94" s="4" t="inlineStr">
+        <is>
+          <t>«In der Schweiz gibt es eine ganz ausgeprägte Kultur für Mikrofinanzierungen»</t>
+        </is>
+      </c>
+      <c r="D94" s="4" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F94" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G94" s="4" t="inlineStr">
+        <is>
+          <t>https://www.handelszeitung.ch/insurance/in-der-schweiz-gibt-es-eine-ganz-ausgepragte-kultur-fur-mikrofinanzierungen-884310</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="n">
+        <v>46001</v>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>altii</t>
+        </is>
+      </c>
+      <c r="C95" s="4" t="inlineStr">
+        <is>
+          <t>MK Global Kapital übernimmt Managementfunktion des Impact-Fonds ALTERNATIVE</t>
+        </is>
+      </c>
+      <c r="D95" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E95" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F95" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G95" s="4" t="inlineStr">
+        <is>
+          <t>https://www.altii.de/20251210_115639_ea0baaad-1f17-42a9-a698-596737b4a5f2/</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="n">
+        <v>46000</v>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>investrends.ch</t>
+        </is>
+      </c>
+      <c r="C96" s="4" t="inlineStr">
+        <is>
+          <t>Neue Managementgesellschaft für den Impact-Fonds ALTERNATIVE</t>
+        </is>
+      </c>
+      <c r="D96" s="4" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="E96" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F96" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G96" s="4" t="inlineStr">
+        <is>
+          <t>https://investrends.ch/aktuell/investments/neue-managementgesellschaft-fur-den-impact-fonds-alternative/</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="3" t="n">
+        <v>45999</v>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>Moneycab</t>
+        </is>
+      </c>
+      <c r="C97" s="4" t="inlineStr">
+        <is>
+          <t>MK Global Kapital wird per 1. Januar Managementgesellschaft für den Impact-Fonds ALTERNATIVE</t>
+        </is>
+      </c>
+      <c r="D97" s="4" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F97" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G97" s="4" t="inlineStr">
+        <is>
+          <t>https://www.moneycab.com/finanz/mk-global-kapital-wird-per-1-januar-managementgesellschaft-fuer-den-impact-fonds-alternative/</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="n">
+        <v>45999</v>
+      </c>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>dfpa.info</t>
+        </is>
+      </c>
+      <c r="C98" s="4" t="inlineStr">
+        <is>
+          <t>MK Global Kapital wird Managementgesellschaft für Impact-Fonds "Alternative"</t>
+        </is>
+      </c>
+      <c r="D98" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E98" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F98" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G98" s="4" t="inlineStr">
+        <is>
+          <t>https://www.dfpa.info/investmentfonds-news/mk-global-kapital-wird-managementgesellschaft-fuer-impact-fonds-alternative/</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="n">
+        <v>45999</v>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>finanznachrichten.de</t>
+        </is>
+      </c>
+      <c r="C99" s="4" t="inlineStr">
+        <is>
+          <t>MK Global Kapital wird per 1. Januar Managementgesellschaft für den Impact-Fonds ALTERNATIVE</t>
+        </is>
+      </c>
+      <c r="D99" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E99" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F99" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G99" s="4" t="inlineStr">
+        <is>
+          <t>https://www.finanznachrichten.de/nachrichten-2025-12/67174021-mk-global-kapital-wird-per-1-januar-managementgesellschaft-fuer-den-impact-fonds-alternative-095.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="n">
+        <v>45997</v>
+      </c>
+      <c r="B100" s="4" t="inlineStr">
+        <is>
+          <t>bondguide.de</t>
+        </is>
+      </c>
+      <c r="C100" s="4" t="inlineStr">
+        <is>
+          <t>Mikro Kapital Management: Impact Investing ist kein Charity</t>
+        </is>
+      </c>
+      <c r="D100" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E100" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F100" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G100" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bondguide.de/topnews/mikro-kapital-management-impact-investing-ist-kein-charity/</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="3" t="n">
+        <v>45996</v>
+      </c>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t>finanznachrichten.de</t>
+        </is>
+      </c>
+      <c r="C101" s="4" t="inlineStr">
+        <is>
+          <t>Mikro Kapital Management: "Impact Investing ist kein Charity"</t>
+        </is>
+      </c>
+      <c r="D101" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E101" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F101" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G101" s="4" t="inlineStr">
+        <is>
+          <t>https://www.finanznachrichten.de/nachrichten-2025-12/67161108-mikro-kapital-management-impact-investing-ist-kein-charity-144.htm</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="n">
+        <v>45996</v>
+      </c>
+      <c r="B102" s="4" t="inlineStr">
+        <is>
+          <t>Investorenplattform.de</t>
+        </is>
+      </c>
+      <c r="C102" s="4" t="inlineStr">
+        <is>
+          <t>Mikro Kapital Management: „Impact Investing ist kein Charity“</t>
+        </is>
+      </c>
+      <c r="D102" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E102" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F102" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G102" s="4" t="inlineStr">
+        <is>
+          <t>https://investorenplattform.de/esg-impact/</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="n">
+        <v>45995</v>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t>dfpa.info</t>
+        </is>
+      </c>
+      <c r="C103" s="4" t="inlineStr">
+        <is>
+          <t>Mikro Kapital platziert erstmals Anleihe an Luxemburger Börse</t>
+        </is>
+      </c>
+      <c r="D103" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E103" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F103" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G103" s="4" t="inlineStr">
+        <is>
+          <t>https://www.dfpa.info/investmentfonds-news/mikro-kapital-platziert-erstmals-emtn-anleihen-des-fonds-alternative-an-luxemburger-boerse/</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="3" t="n">
+        <v>45985</v>
+      </c>
+      <c r="B104" s="4" t="inlineStr">
+        <is>
+          <t>Finews</t>
+        </is>
+      </c>
+      <c r="C104" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist über Mikrofinanzen: Sollten vom hohen Ross herunterkommen</t>
+        </is>
+      </c>
+      <c r="D104" s="4" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="E104" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F104" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G104" s="4" t="inlineStr">
+        <is>
+          <t>https://www.finews.ch/news/finanzplatz/70147-mikro-capital-johannes-feist-kuenstliche-intelligenz-blockchain-rumaenien-europa-mikrofinanzen-finanzplatz-schweiz</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="3" t="n">
+        <v>45982</v>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t>tagesschau24.de (TV interview)</t>
+        </is>
+      </c>
+      <c r="C105" s="4" t="inlineStr">
+        <is>
+          <t>ARD interview: Why “glowworms” matter more than trillion-dollar pledges</t>
+        </is>
+      </c>
+      <c r="D105" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E105" s="4" t="inlineStr">
+        <is>
+          <t>TV &amp; Online</t>
+        </is>
+      </c>
+      <c r="F105" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G105" s="4" t="inlineStr">
+        <is>
+          <t>https://www.tagesschau.de/multimedia/sendung/tagesschau24/boerselive/video-1527674.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="n">
+        <v>45981</v>
+      </c>
+      <c r="B106" s="4" t="inlineStr">
+        <is>
+          <t>Börsen-Kurier</t>
+        </is>
+      </c>
+      <c r="C106" s="4" t="inlineStr">
+        <is>
+          <t>Mikrofinanz: Stabilität aus realer Wertschöpfung</t>
+        </is>
+      </c>
+      <c r="D106" s="4" t="inlineStr">
+        <is>
           <t>A</t>
         </is>
       </c>
-      <c r="E75" s="4" t="inlineStr">
-        <is>
-          <t>Online</t>
-        </is>
-      </c>
-      <c r="F75" s="4" t="inlineStr">
-        <is>
-          <t>Johannes Feist</t>
-        </is>
-      </c>
-      <c r="G75" s="4" t="inlineStr">
-        <is>
-          <t>https://www.fondsexklusiv.at/schwellenlaender-worauf-es-jetzt-ankommt/</t>
+      <c r="E106" s="4" t="inlineStr">
+        <is>
+          <t>Print</t>
+        </is>
+      </c>
+      <c r="F106" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G106" s="4" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="n">
+        <v>45973</v>
+      </c>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t>investrends.ch</t>
+        </is>
+      </c>
+      <c r="C107" s="4" t="inlineStr">
+        <is>
+          <t>Mikrofinanz ist Private Debt mit direkter Verbindung zur Realwirtschaft</t>
+        </is>
+      </c>
+      <c r="D107" s="4" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="E107" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F107" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G107" s="4" t="inlineStr">
+        <is>
+          <t>https://investrends.ch/aktuell/investments/mikrofinanz-ist-private-debt-mit-direkter-verbindung-zur-realwirtschaft/</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="n">
+        <v>45971</v>
+      </c>
+      <c r="B108" s="4" t="inlineStr">
+        <is>
+          <t>photovoltaik.eu</t>
+        </is>
+      </c>
+      <c r="C108" s="4" t="inlineStr">
+        <is>
+          <t>COP30: Klimafinanzierung muss in den Unternehmen ankommen</t>
+        </is>
+      </c>
+      <c r="D108" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E108" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F108" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G108" s="4" t="inlineStr">
+        <is>
+          <t>https://www.photovoltaik.eu/foerderung/cop30-klimafinanzierung-muss-den-unternehmen-ankommen</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="3" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
+          <t>Frankfurter Rundschau</t>
+        </is>
+      </c>
+      <c r="C109" s="4" t="inlineStr">
+        <is>
+          <t>Merz in Brasilien: Bundeskanzler fordert „globale Kraftanstrengung“ für Klimaschutz bei COP30</t>
+        </is>
+      </c>
+      <c r="D109" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E109" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F109" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G109" s="4" t="inlineStr">
+        <is>
+          <t>https://www.fr.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="3" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B110" s="4" t="inlineStr">
+        <is>
+          <t>Windmesse</t>
+        </is>
+      </c>
+      <c r="C110" s="4" t="inlineStr">
+        <is>
+          <t>COP30: Klimafinanzierung muss endlich in den Unternehmen ankommen</t>
+        </is>
+      </c>
+      <c r="D110" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E110" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F110" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G110" s="4" t="inlineStr">
+        <is>
+          <t>https://w3.windmesse.de/windenergie/news/48059-cop30-klimafinanzierung-muss-endlich-in-den-unternehmen-ankommen</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B111" s="4" t="inlineStr">
+        <is>
+          <t>BondGuide</t>
+        </is>
+      </c>
+      <c r="C111" s="4" t="inlineStr">
+        <is>
+          <t>Klimafinanzierung bei COP 30: von Zusagen zu Wirkung entfalten</t>
+        </is>
+      </c>
+      <c r="D111" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E111" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F111" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G111" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bondguide.de/topnews/klimafinanzierung-bei-cop-30-von-zusagen-zu-wirkung-entfalten/</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="3" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B112" s="4" t="inlineStr">
+        <is>
+          <t>AZ online (Allgemeine Zeitung der Lüneburger Heide)</t>
+        </is>
+      </c>
+      <c r="C112" s="4" t="inlineStr">
+        <is>
+          <t>Merz reist nach Brasilien: Deutschlands Klimapolitik bei COP30 auf dem Prüfstein</t>
+        </is>
+      </c>
+      <c r="D112" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E112" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F112" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G112" s="4" t="inlineStr">
+        <is>
+          <t>https://www.az-online.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B113" s="4" t="inlineStr">
+        <is>
+          <t>fehmarn24.de</t>
+        </is>
+      </c>
+      <c r="C113" s="4" t="inlineStr">
+        <is>
+          <t>Merz reist nach Brasilien: Deutschlands Klimapolitik bei COP30 auf dem Prüfstein</t>
+        </is>
+      </c>
+      <c r="D113" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E113" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F113" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G113" s="4" t="inlineStr">
+        <is>
+          <t>https://www.fehmarn24.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="3" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B114" s="4" t="inlineStr">
+        <is>
+          <t>fnp.de (Frankfurter Neue Presse)</t>
+        </is>
+      </c>
+      <c r="C114" s="4" t="inlineStr">
+        <is>
+          <t>Merz reist nach Brasilien: Deutschlands Klimapolitik bei COP30 auf dem Prüfstein</t>
+        </is>
+      </c>
+      <c r="D114" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E114" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F114" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G114" s="4" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="3" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B115" s="4" t="inlineStr">
+        <is>
+          <t>Fuldaer Zeitung.de</t>
+        </is>
+      </c>
+      <c r="C115" s="4" t="inlineStr">
+        <is>
+          <t>Merz reist nach Brasilien: Deutschlands Klimapolitik bei COP30 auf dem Prüfstein</t>
+        </is>
+      </c>
+      <c r="D115" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E115" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F115" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G115" s="4" t="inlineStr">
+        <is>
+          <t>https://www.fuldaerzeitung.de/politik-und-wirtschaft/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="3" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B116" s="4" t="inlineStr">
+        <is>
+          <t>Gießener Allgemeine Online</t>
+        </is>
+      </c>
+      <c r="C116" s="4" t="inlineStr">
+        <is>
+          <t>Merz reist nach Brasilien: Deutschlands Klimapolitik bei COP30 auf dem Prüfstein</t>
+        </is>
+      </c>
+      <c r="D116" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E116" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F116" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G116" s="4" t="inlineStr">
+        <is>
+          <t>https://www.giessener-allgemeine.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="3" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B117" s="4" t="inlineStr">
+        <is>
+          <t>Wetterauer Zeitung Online</t>
+        </is>
+      </c>
+      <c r="C117" s="4" t="inlineStr">
+        <is>
+          <t>Merz reist nach Brasilien: Deutschlands Klimapolitik bei COP30 auf dem Prüfstein</t>
+        </is>
+      </c>
+      <c r="D117" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E117" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F117" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G117" s="4" t="inlineStr">
+        <is>
+          <t>https://www.wetterauer-zeitung.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="3" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B118" s="4" t="inlineStr">
+        <is>
+          <t>giessener-anzeiger.de</t>
+        </is>
+      </c>
+      <c r="C118" s="4" t="inlineStr">
+        <is>
+          <t>Merz reist nach Brasilien: Deutschlands Klimapolitik bei COP30 auf dem Prüfstein</t>
+        </is>
+      </c>
+      <c r="D118" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E118" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F118" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G118" s="4" t="inlineStr">
+        <is>
+          <t>https://www.giessener-anzeiger.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="3" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B119" s="4" t="inlineStr">
+        <is>
+          <t>kreis-anzeiger.de (Zentralhessen)</t>
+        </is>
+      </c>
+      <c r="C119" s="4" t="inlineStr">
+        <is>
+          <t>Merz reist nach Brasilien: Deutschlands Klimapolitik bei COP30 auf dem Prüfstein</t>
+        </is>
+      </c>
+      <c r="D119" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E119" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F119" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G119" s="4" t="inlineStr">
+        <is>
+          <t>https://www.kreis-anzeiger.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="3" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B120" s="4" t="inlineStr">
+        <is>
+          <t>usinger-anzeiger.de</t>
+        </is>
+      </c>
+      <c r="C120" s="4" t="inlineStr">
+        <is>
+          <t>Merz reist nach Brasilien: Deutschlands Klimapolitik bei COP30 auf dem Prüfstein</t>
+        </is>
+      </c>
+      <c r="D120" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E120" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F120" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G120" s="4" t="inlineStr">
+        <is>
+          <t>https://www.usinger-anzeiger.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="3" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B121" s="4" t="inlineStr">
+        <is>
+          <t>hanauer.de (Hanauer Anzeiger)</t>
+        </is>
+      </c>
+      <c r="C121" s="4" t="inlineStr">
+        <is>
+          <t>Merz reist nach Brasilien: Deutschlands Klimapolitik bei COP30 auf dem Prüfstein</t>
+        </is>
+      </c>
+      <c r="D121" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E121" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F121" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G121" s="4" t="inlineStr">
+        <is>
+          <t>https://www.hanauer.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="3" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B122" s="4" t="inlineStr">
+        <is>
+          <t>echo24.de</t>
+        </is>
+      </c>
+      <c r="C122" s="4" t="inlineStr">
+        <is>
+          <t>Merz reist nach Brasilien: Deutschlands Klimapolitik bei COP30 auf dem Prüfstein</t>
+        </is>
+      </c>
+      <c r="D122" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E122" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F122" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G122" s="4" t="inlineStr">
+        <is>
+          <t>https://www.echo24.de/welt/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="3" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B123" s="4" t="inlineStr">
+        <is>
+          <t>hersfelder-zeitung.de</t>
+        </is>
+      </c>
+      <c r="C123" s="4" t="inlineStr">
+        <is>
+          <t>Merz reist nach Brasilien: Deutschlands Klimapolitik bei COP30 auf dem Prüfstein</t>
+        </is>
+      </c>
+      <c r="D123" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E123" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F123" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G123" s="4" t="inlineStr">
+        <is>
+          <t>https://www.hersfelder-zeitung.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="3" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B124" s="4" t="inlineStr">
+        <is>
+          <t>HNA online</t>
+        </is>
+      </c>
+      <c r="C124" s="4" t="inlineStr">
+        <is>
+          <t>Merz reist nach Brasilien: Deutschlands Klimapolitik bei COP30 auf dem Prüfstein</t>
+        </is>
+      </c>
+      <c r="D124" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E124" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F124" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G124" s="4" t="inlineStr">
+        <is>
+          <t>https://www.hna.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="3" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B125" s="4" t="inlineStr">
+        <is>
+          <t>kreisbote.de</t>
+        </is>
+      </c>
+      <c r="C125" s="4" t="inlineStr">
+        <is>
+          <t>Merz reist nach Brasilien: Deutschlands Klimapolitik bei COP30 auf dem Prüfstein</t>
+        </is>
+      </c>
+      <c r="D125" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E125" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F125" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G125" s="4" t="inlineStr">
+        <is>
+          <t>https://www.kreisbote.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="3" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B126" s="4" t="inlineStr">
+        <is>
+          <t>kreiszeitung.de (Syke)</t>
+        </is>
+      </c>
+      <c r="C126" s="4" t="inlineStr">
+        <is>
+          <t>Merz reist nach Brasilien: Deutschlands Klimapolitik bei COP30 auf dem Prüfstein</t>
+        </is>
+      </c>
+      <c r="D126" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E126" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F126" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G126" s="4" t="inlineStr">
+        <is>
+          <t>https://www.kreiszeitung.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="3" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B127" s="4" t="inlineStr">
+        <is>
+          <t>Leinetal24.de</t>
+        </is>
+      </c>
+      <c r="C127" s="4" t="inlineStr">
+        <is>
+          <t>Merz reist nach Brasilien: Deutschlands Klimapolitik bei COP30 auf dem Prüfstein</t>
+        </is>
+      </c>
+      <c r="D127" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E127" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F127" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G127" s="4" t="inlineStr">
+        <is>
+          <t>https://www.leinetal24.de/welt/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="3" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B128" s="4" t="inlineStr">
+        <is>
+          <t>come-on.de (Märkischer Zeitungsverlag)</t>
+        </is>
+      </c>
+      <c r="C128" s="4" t="inlineStr">
+        <is>
+          <t>Merz reist nach Brasilien: Deutschlands Klimapolitik bei COP30 auf dem Prüfstein</t>
+        </is>
+      </c>
+      <c r="D128" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E128" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F128" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G128" s="4" t="inlineStr">
+        <is>
+          <t>https://www.come-on.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="3" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B129" s="4" t="inlineStr">
+        <is>
+          <t>Merkur.de (Münchner Merkur)</t>
+        </is>
+      </c>
+      <c r="C129" s="4" t="inlineStr">
+        <is>
+          <t>Merz reist nach Brasilien: Deutschlands Klimapolitik bei COP30 auf dem Prüfstein</t>
+        </is>
+      </c>
+      <c r="D129" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E129" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F129" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G129" s="4" t="inlineStr">
+        <is>
+          <t>https://www.merkur.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="3" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B130" s="4" t="inlineStr">
+        <is>
+          <t>OVB online (Oberbayerisches Volksblatt)</t>
+        </is>
+      </c>
+      <c r="C130" s="4" t="inlineStr">
+        <is>
+          <t>Merz reist nach Brasilien: Deutschlands Klimapolitik bei COP30 auf dem Prüfstein</t>
+        </is>
+      </c>
+      <c r="D130" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E130" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F130" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G130" s="4" t="inlineStr">
+        <is>
+          <t>https://www.ovb-online.de/weltspiegel/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="3" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B131" s="4" t="inlineStr">
+        <is>
+          <t>oberhessische-zeitung.de</t>
+        </is>
+      </c>
+      <c r="C131" s="4" t="inlineStr">
+        <is>
+          <t>Merz reist nach Brasilien: Deutschlands Klimapolitik bei COP30 auf dem Prüfstein</t>
+        </is>
+      </c>
+      <c r="D131" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E131" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F131" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G131" s="4" t="inlineStr">
+        <is>
+          <t>https://www.oberhessische-zeitung.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="3" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B132" s="4" t="inlineStr">
+        <is>
+          <t>OFFENBACH-POST ONLINE</t>
+        </is>
+      </c>
+      <c r="C132" s="4" t="inlineStr">
+        <is>
+          <t>Merz reist nach Brasilien: Deutschlands Klimapolitik bei COP30 auf dem Prüfstein</t>
+        </is>
+      </c>
+      <c r="D132" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E132" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F132" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G132" s="4" t="inlineStr">
+        <is>
+          <t>https://www.op-online.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="3" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B133" s="4" t="inlineStr">
+        <is>
+          <t>gmuender-tagespost.de</t>
+        </is>
+      </c>
+      <c r="C133" s="4" t="inlineStr">
+        <is>
+          <t>Merz reist nach Brasilien: Deutschlands Klimapolitik bei COP30 auf dem Prüfstein</t>
+        </is>
+      </c>
+      <c r="D133" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E133" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F133" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G133" s="4" t="inlineStr">
+        <is>
+          <t>https://www.gmuender-tagespost.de/welt/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="3" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B134" s="4" t="inlineStr">
+        <is>
+          <t>schwaebische-post.de</t>
+        </is>
+      </c>
+      <c r="C134" s="4" t="inlineStr">
+        <is>
+          <t>Merz reist nach Brasilien: Deutschlands Klimapolitik bei COP30 auf dem Prüfstein</t>
+        </is>
+      </c>
+      <c r="D134" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E134" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F134" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G134" s="4" t="inlineStr">
+        <is>
+          <t>https://www.schwaebische-post.de/welt/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="3" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B135" s="4" t="inlineStr">
+        <is>
+          <t>tz-online.de</t>
+        </is>
+      </c>
+      <c r="C135" s="4" t="inlineStr">
+        <is>
+          <t>Merz reist nach Brasilien: Deutschlands Klimapolitik bei COP30 auf dem Prüfstein</t>
+        </is>
+      </c>
+      <c r="D135" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E135" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F135" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G135" s="4" t="inlineStr">
+        <is>
+          <t>https://www.tz.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="3" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B136" s="4" t="inlineStr">
+        <is>
+          <t>Waldeckische Landeszeitung Online</t>
+        </is>
+      </c>
+      <c r="C136" s="4" t="inlineStr">
+        <is>
+          <t>Merz reist nach Brasilien: Deutschlands Klimapolitik bei COP30 auf dem Prüfstein</t>
+        </is>
+      </c>
+      <c r="D136" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E136" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F136" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G136" s="4" t="inlineStr">
+        <is>
+          <t>https://www.wlz-online.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="3" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B137" s="4" t="inlineStr">
+        <is>
+          <t>werra-rundschau.de</t>
+        </is>
+      </c>
+      <c r="C137" s="4" t="inlineStr">
+        <is>
+          <t>Merz reist nach Brasilien: Deutschlands Klimapolitik bei COP30 auf dem Prüfstein</t>
+        </is>
+      </c>
+      <c r="D137" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E137" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F137" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G137" s="4" t="inlineStr">
+        <is>
+          <t>https://www.werra-rundschau.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="3" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B138" s="4" t="inlineStr">
+        <is>
+          <t>soester-anzeiger.de</t>
+        </is>
+      </c>
+      <c r="C138" s="4" t="inlineStr">
+        <is>
+          <t>Merz reist nach Brasilien: Deutschlands Klimapolitik bei COP30 auf dem Prüfstein</t>
+        </is>
+      </c>
+      <c r="D138" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E138" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F138" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G138" s="4" t="inlineStr">
+        <is>
+          <t>https://www.soester-anzeiger.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="3" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B139" s="4" t="inlineStr">
+        <is>
+          <t>wa.de (Westfälischer Anzeiger)</t>
+        </is>
+      </c>
+      <c r="C139" s="4" t="inlineStr">
+        <is>
+          <t>Merz reist nach Brasilien: Deutschlands Klimapolitik bei COP30 auf dem Prüfstein</t>
+        </is>
+      </c>
+      <c r="D139" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E139" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F139" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G139" s="4" t="inlineStr">
+        <is>
+          <t>https://www.wa.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="3" t="n">
+        <v>45848</v>
+      </c>
+      <c r="B140" s="4" t="inlineStr">
+        <is>
+          <t>Handelszeitung</t>
+        </is>
+      </c>
+      <c r="C140" s="4" t="inlineStr">
+        <is>
+          <t>Zwischen ESG-Müdigkeit und Wirkungsanspruch</t>
+        </is>
+      </c>
+      <c r="D140" s="4" t="inlineStr">
+        <is>
+          <t>CH</t>
+        </is>
+      </c>
+      <c r="E140" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F140" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G140" s="4" t="inlineStr">
+        <is>
+          <t>https://www.handelszeitung.ch/specials/nachhaltiges-investieren-2024/zwischen-esg-mudigkeit-und-wirkungsanspruch-841576</t>
         </is>
       </c>
     </row>
@@ -3059,7 +5342,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -3080,7 +5363,7 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Source: Sheet '2026 Clippings' (A9:G75)</t>
+          <t>Source: Sheet '2026 Clippings' (A9:G140)</t>
         </is>
       </c>
     </row>
@@ -3098,7 +5381,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>67</v>
+        <v>132</v>
       </c>
     </row>
     <row r="6">
@@ -3108,7 +5391,7 @@
         </is>
       </c>
       <c r="B6" s="10" t="n">
-        <v>45292</v>
+        <v>45848</v>
       </c>
     </row>
     <row r="7">
@@ -3128,7 +5411,7 @@
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>36</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9">
@@ -3187,14 +5470,14 @@
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>45</v>
+        <v>115</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>0.6716417910447762</v>
+        <v>0.8712121212121212</v>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>2024-01</t>
+          <t>2025-07</t>
         </is>
       </c>
       <c r="F12" s="8" t="n">
@@ -3208,18 +5491,18 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>0.1343283582089552</v>
+        <v>0.1136363636363636</v>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2025-11</t>
         </is>
       </c>
       <c r="F13" s="8" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
@@ -3232,15 +5515,15 @@
         <v>2</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>0.02985074626865672</v>
+        <v>0.01515151515151515</v>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2025-12</t>
         </is>
       </c>
       <c r="F14" s="8" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
@@ -3250,14 +5533,14 @@
         </is>
       </c>
       <c r="B15" s="8" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>0.1641791044776119</v>
+        <v>0</v>
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="F15" s="8" t="n">
@@ -3267,230 +5550,270 @@
     <row r="16">
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="F16" s="8" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="17">
       <c r="E17" s="8" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="F17" s="8" t="n">
-        <v>11</v>
+        <v>29</v>
       </c>
     </row>
     <row r="18">
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="F18" s="8" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
       <c r="E19" s="8" t="inlineStr">
         <is>
-          <t>2026-04</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="F19" s="8" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>2026-05</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="F20" s="8" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="F21" s="8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22">
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="F22" s="8" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23">
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="F23" s="8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="24">
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="F24" s="8" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="25">
-      <c r="E25" s="8" t="inlineStr">
-        <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="F25" s="8" t="n">
-        <v>2</v>
+    <row r="29">
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t>Clippings by Country</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>Clippings by Type</t>
+        </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>Clippings by Country</t>
-        </is>
-      </c>
-      <c r="E30" s="7" t="inlineStr">
-        <is>
-          <t>Clippings by Type</t>
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>Country</t>
+        </is>
+      </c>
+      <c r="B30" s="9" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>Share</t>
+        </is>
+      </c>
+      <c r="E30" s="9" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="F30" s="9" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+      <c r="G30" s="9" t="inlineStr">
+        <is>
+          <t>Share</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="9" t="inlineStr">
-        <is>
-          <t>Country</t>
-        </is>
-      </c>
-      <c r="B31" s="9" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
-      </c>
-      <c r="C31" s="9" t="inlineStr">
-        <is>
-          <t>Share</t>
-        </is>
-      </c>
-      <c r="E31" s="9" t="inlineStr">
-        <is>
-          <t>Type</t>
-        </is>
-      </c>
-      <c r="F31" s="9" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
-      </c>
-      <c r="G31" s="9" t="inlineStr">
-        <is>
-          <t>Share</t>
-        </is>
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C31" s="11" t="n">
+        <v>0.03787878787878788</v>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>Digital newsletter</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G31" s="11" t="n">
+        <v>0.007575757575757576</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="B32" s="8" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="C32" s="11" t="n">
-        <v>0.04477611940298507</v>
+        <v>0.1590909090909091</v>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>E-Paper</t>
         </is>
       </c>
       <c r="F32" s="8" t="n">
-        <v>65</v>
+        <v>2</v>
       </c>
       <c r="G32" s="11" t="n">
-        <v>0.9701492537313433</v>
+        <v>0.01515151515151515</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="B33" s="8" t="n">
-        <v>17</v>
+        <v>100</v>
       </c>
       <c r="C33" s="11" t="n">
-        <v>0.2537313432835821</v>
+        <v>0.7575757575757576</v>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
-          <t>Print</t>
+          <t>Online</t>
         </is>
       </c>
       <c r="F33" s="8" t="n">
-        <v>1</v>
+        <v>115</v>
       </c>
       <c r="G33" s="11" t="n">
-        <v>0.01492537313432836</v>
+        <v>0.8712121212121212</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>DACH</t>
         </is>
       </c>
       <c r="B34" s="8" t="n">
-        <v>45</v>
+        <v>6</v>
       </c>
       <c r="C34" s="11" t="n">
-        <v>0.6716417910447762</v>
+        <v>0.04545454545454546</v>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
+          <t>Print</t>
+        </is>
+      </c>
+      <c r="F34" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="G34" s="11" t="n">
+        <v>0.06060606060606061</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>Print &amp; Digital</t>
+        </is>
+      </c>
+      <c r="F35" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G35" s="11" t="n">
+        <v>0.007575757575757576</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="E36" s="8" t="inlineStr">
+        <is>
           <t>Print &amp; Online</t>
         </is>
       </c>
-      <c r="F34" s="8" t="n">
+      <c r="F36" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="G36" s="11" t="n">
+        <v>0.0303030303030303</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="E37" s="8" t="inlineStr">
+        <is>
+          <t>TV &amp; Online</t>
+        </is>
+      </c>
+      <c r="F37" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="G34" s="11" t="n">
-        <v>0.01492537313432836</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="8" t="inlineStr">
-        <is>
-          <t>DACH</t>
-        </is>
-      </c>
-      <c r="B35" s="8" t="n">
-        <v>2</v>
-      </c>
-      <c r="C35" s="11" t="n">
-        <v>0.02985074626865672</v>
+      <c r="G37" s="11" t="n">
+        <v>0.007575757575757576</v>
       </c>
     </row>
   </sheetData>

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -694,7 +694,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G140"/>
+  <dimension ref="A1:G141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46311.76219818254</v>
+        <v>46312.06450534537</v>
       </c>
     </row>
     <row r="8">
@@ -824,16 +824,16 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>46294</v>
+        <v>46299</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Markt Einblicke</t>
+          <t>Spotify</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Nach dem Ernteeinbruch: Warum es jetzt auf die richtige Finanzierung ankommt</t>
+          <t>Mikrokredite als Anlagealternative von Geldmeisterin</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -853,22 +853,22 @@
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>https://markteinblicke.de/133297/2026/09/nach-dem-ernteeinbruch-warum-es-jetzt-auf-die-richtige-finanzierung-ankommt/</t>
+          <t>https://podcasters.spotify.com/pod/show/geldmeisterin/episodes/Mikrokredite-als-Anlagealternative-e3f11ln</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>46273</v>
+        <v>46294</v>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Private Banking Magazin</t>
+          <t>Markt Einblicke</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Private Credit in Zentralasien</t>
+          <t>Nach dem Ernteeinbruch: Warum es jetzt auf die richtige Finanzierung ankommt</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -888,22 +888,22 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>https://www.private-banking-magazin.de/private-credit-zentralasien-lokale-unternehmenskredite/</t>
+          <t>https://markteinblicke.de/133297/2026/09/nach-dem-ernteeinbruch-warum-es-jetzt-auf-die-richtige-finanzierung-ankommt/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>46256</v>
+        <v>46273</v>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>BondGuide</t>
+          <t>Private Banking Magazin</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Niedrigwasser zeigt die Geografie des Kreditrisikos</t>
+          <t>Private Credit in Zentralasien</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -923,27 +923,27 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>https://www.bondguide.de/topnews/niedrigwasser-zeigt-die-geografie-des-kreditrisikos/</t>
+          <t>https://www.private-banking-magazin.de/private-credit-zentralasien-lokale-unternehmenskredite/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>46251</v>
+        <v>46256</v>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Finanz und Wirtschaft</t>
+          <t>BondGuide</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Die Schweiz finanziert Wasserresilienz überall – nur nicht im Inland</t>
+          <t>Niedrigwasser zeigt die Geografie des Kreditrisikos</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -953,32 +953,32 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Louiza Savchenko</t>
+          <t>Johannes Feist</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>https://www.fuw.ch/wasserrisiko-was-die-schweiz-von-zentralasien-lernen-kann-152625611421</t>
+          <t>https://www.bondguide.de/topnews/niedrigwasser-zeigt-die-geografie-des-kreditrisikos/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>46247</v>
+        <v>46251</v>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Markt Einblicke</t>
+          <t>Finanz und Wirtschaft</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Mikrofinanzanleihen: Worauf es bei Kreditqualität und Struktur ankommt</t>
+          <t>Die Schweiz finanziert Wasserresilienz überall – nur nicht im Inland</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -988,27 +988,27 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist</t>
+          <t>Louiza Savchenko</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>https://markteinblicke.de/132318/2026/08/mikrofinanzanleihen-worauf-es-bei-kreditqualitaet-und-struktur-ankommt/</t>
+          <t>https://www.fuw.ch/wasserrisiko-was-die-schweiz-von-zentralasien-lernen-kann-152625611421</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>FUELS+LUBES+ENERGY</t>
+          <t>Markt Einblicke</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Der Ölpreis und die Kapitalmärkte</t>
+          <t>Mikrofinanzanleihen: Worauf es bei Kreditqualität und Struktur ankommt</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
@@ -1018,7 +1018,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Print</t>
+          <t>Online</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -1026,30 +1026,34 @@
           <t>Johannes Feist</t>
         </is>
       </c>
-      <c r="G16" s="4" t="inlineStr"/>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>https://markteinblicke.de/132318/2026/08/mikrofinanzanleihen-worauf-es-bei-kreditqualitaet-und-struktur-ankommt/</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>e-fundresearch</t>
+          <t>FUELS+LUBES+ENERGY</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Experten-Umfrage: Worüber im zweiten Halbjahr 2026 keiner redet (Teil 2/2)</t>
+          <t>Der Ölpreis und die Kapitalmärkte</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>DACH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Print</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -1057,34 +1061,30 @@
           <t>Johannes Feist</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>https://e-fundresearch.com/managers/artikel/60333-experten-umfrage-worueber-im-zweiten-halbjahr-2026-keiner-redet-teil-22</t>
-        </is>
-      </c>
+      <c r="G17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>46241</v>
+        <v>46245</v>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>marktEINBLICKE</t>
+          <t>e-fundresearch</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Euro-Kupon, lokale Cashflows: Wo das Währungsrisiko wirklich liegt</t>
+          <t>Experten-Umfrage: Worüber im zweiten Halbjahr 2026 keiner redet (Teil 2/2)</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>DACH</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>E-Paper</t>
+          <t>Online</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -1094,17 +1094,17 @@
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>https://markteinblicke.de/wp-content/uploads/meg/mEGeldanlage_2026_15.pdf</t>
+          <t>https://e-fundresearch.com/managers/artikel/60333-experten-umfrage-worueber-im-zweiten-halbjahr-2026-keiner-redet-teil-22</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>46238</v>
+        <v>46241</v>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Markt Einblicke</t>
+          <t>marktEINBLICKE</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>E-Paper</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -1129,27 +1129,27 @@
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>https://markteinblicke.de/132045/2026/08/euro-kupon-lokale-cashflows-wo-das-waehrungsrisiko-wirklich-liegt/</t>
+          <t>https://markteinblicke.de/wp-content/uploads/meg/mEGeldanlage_2026_15.pdf</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>46234</v>
+        <v>46238</v>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Moneycab</t>
+          <t>Markt Einblicke</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist, CEO MK Global Kapital, im Interview</t>
+          <t>Euro-Kupon, lokale Cashflows: Wo das Währungsrisiko wirklich liegt</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>https://www.moneycab.com/interviews/ceo-interviews/johannes-feist-ceo-mk-global-kapital-im-interview/</t>
+          <t>https://markteinblicke.de/132045/2026/08/euro-kupon-lokale-cashflows-wo-das-waehrungsrisiko-wirklich-liegt/</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>finanznachrichten.de</t>
+          <t>Moneycab</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -1199,22 +1199,22 @@
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>https://www.finanznachrichten.de/nachrichten-2026-07/69177994-johannes-feist-ceo-mk-global-kapital-im-interview-095.htm</t>
+          <t>https://www.moneycab.com/interviews/ceo-interviews/johannes-feist-ceo-mk-global-kapital-im-interview/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>46231</v>
+        <v>46234</v>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>BondGuide</t>
+          <t>finanznachrichten.de</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Private Credit: Was Anleiheinvestoren hinter dem Kupon prüfen sollten</t>
+          <t>Johannes Feist, CEO MK Global Kapital, im Interview</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>https://www.bondguide.de/topnews/private-credit-was-anleiheinvestoren-hinter-dem-kupon-pruefen-sollten/</t>
+          <t>https://www.finanznachrichten.de/nachrichten-2026-07/69177994-johannes-feist-ceo-mk-global-kapital-im-interview-095.htm</t>
         </is>
       </c>
     </row>
@@ -1244,12 +1244,12 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>ExportManager OST</t>
+          <t>BondGuide</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Wenn der klassische Bankkredit schlecht greift</t>
+          <t>Private Credit: Was Anleiheinvestoren hinter dem Kupon prüfen sollten</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -1259,7 +1259,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Print &amp; Digital</t>
+          <t>Online</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -1267,7 +1267,11 @@
           <t>Johannes Feist</t>
         </is>
       </c>
-      <c r="G23" s="4" t="inlineStr"/>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bondguide.de/topnews/private-credit-was-anleiheinvestoren-hinter-dem-kupon-pruefen-sollten/</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
@@ -1275,12 +1279,12 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>finanznachrichten.de</t>
+          <t>ExportManager OST</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Private Credit: Was Anleiheinvestoren hinter dem Kupon prüfen sollten</t>
+          <t>Wenn der klassische Bankkredit schlecht greift</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -1290,7 +1294,7 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Print &amp; Digital</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -1298,29 +1302,25 @@
           <t>Johannes Feist</t>
         </is>
       </c>
-      <c r="G24" s="4" t="inlineStr">
-        <is>
-          <t>https://www.finanznachrichten.de/nachrichten-2026-07/69141450-private-credit-was-anleiheinvestoren-hinter-dem-kupon-pruefen-sollten-144.htm</t>
-        </is>
-      </c>
+      <c r="G24" s="4" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>46205</v>
+        <v>46231</v>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Finews</t>
+          <t>finanznachrichten.de</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Ferienlektüre: Was Finanzprofis diesen Sommer lesen</t>
+          <t>Private Credit: Was Anleiheinvestoren hinter dem Kupon prüfen sollten</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
@@ -1330,32 +1330,32 @@
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>Louiza Savchenko</t>
+          <t>Johannes Feist</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>https://www.finews.ch/themen/leben-karriere/72628-sommer-buchempfehlungen-2026-von-persoenlichkeiten-aus-der-finanzbranche-roman-sommerlektuere-lesen-ferien-andreas-feller-thomas-studhalter-karsten-dirk-steffens-anna-bretschneider-finanzplatz-schweiz</t>
+          <t>https://www.finanznachrichten.de/nachrichten-2026-07/69141450-private-credit-was-anleiheinvestoren-hinter-dem-kupon-pruefen-sollten-144.htm</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>46198</v>
+        <v>46205</v>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>background.tagesspiegel</t>
+          <t>Finews</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Digitale Kreditvergabe : Kreditzugang ist mehr als ein Score</t>
+          <t>Ferienlektüre: Was Finanzprofis diesen Sommer lesen</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
@@ -1370,27 +1370,27 @@
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>https://background.tagesspiegel.de/finance/briefing/kreditzugang-ist-mehr-als-ein-score</t>
+          <t>https://www.finews.ch/themen/leben-karriere/72628-sommer-buchempfehlungen-2026-von-persoenlichkeiten-aus-der-finanzbranche-roman-sommerlektuere-lesen-ferien-andreas-feller-thomas-studhalter-karsten-dirk-steffens-anna-bretschneider-finanzplatz-schweiz</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Finanz und Wirtschaft</t>
+          <t>background.tagesspiegel</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Rendite mit gutem Gewissen</t>
+          <t>Digitale Kreditvergabe : Kreditzugang ist mehr als ein Score</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -1400,28 +1400,32 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist</t>
-        </is>
-      </c>
-      <c r="G27" s="4" t="inlineStr"/>
+          <t>Louiza Savchenko</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>https://background.tagesspiegel.de/finance/briefing/kreditzugang-ist-mehr-als-ein-score</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>46195</v>
+        <v>46197</v>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>fem.capital</t>
+          <t>Finanz und Wirtschaft</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Warum Unternehmerinnen eher am Kapital als am Markt scheitern</t>
+          <t>Rendite mit gutem Gewissen</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
@@ -1431,23 +1435,23 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Louiza Savchenko</t>
+          <t>Johannes Feist</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Intelligent Investors</t>
+          <t>fem.capital</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Kreditqualität lässt sich nicht aus der Distanz steuern</t>
+          <t>Warum Unternehmerinnen eher am Kapital als am Markt scheitern</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
@@ -1457,38 +1461,38 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>Print</t>
+          <t>Online</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist</t>
+          <t>Louiza Savchenko</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>46183</v>
+        <v>46188</v>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Finews</t>
+          <t>Intelligent Investors</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist: «Einer meiner unerfüllter Träume ist der Sportfliegerschein»</t>
+          <t>Kreditqualität lässt sich nicht aus der Distanz steuern</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Print</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
@@ -1496,34 +1500,30 @@
           <t>Johannes Feist</t>
         </is>
       </c>
-      <c r="G30" s="4" t="inlineStr">
-        <is>
-          <t>https://www.finews.ch/themen/high-end/72456-johannes-feist-einer-meiner-unerfuellter-traeume-ist-der-sportfliegerschein-ceo-global-kapital</t>
-        </is>
-      </c>
+      <c r="G30" s="4" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>46176</v>
+        <v>46183</v>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>BOND MAGAZINE</t>
+          <t>Finews</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Der neue Stresstest für Schwellenländer: Warum Öl, Zinsen und Währungen nur der Anfang sind und letztlich die Finanzierungsstruktur entscheidet</t>
+          <t>Johannes Feist: «Einer meiner unerfüllter Träume ist der Sportfliegerschein»</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>Print</t>
+          <t>Online</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -1533,32 +1533,32 @@
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>https://www.fixed-income.org/fileadmin/pdf/BOND_MAGAZINE_239.pdf</t>
+          <t>https://www.finews.ch/themen/high-end/72456-johannes-feist-einer-meiner-unerfuellter-traeume-ist-der-sportfliegerschein-ceo-global-kapital</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>46174</v>
+        <v>46176</v>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>FONDS exklusiv Österreich</t>
+          <t>BOND MAGAZINE</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Schwellenländer: Worauf es jetzt ankommt</t>
+          <t>Der neue Stresstest für Schwellenländer: Warum Öl, Zinsen und Währungen nur der Anfang sind und letztlich die Finanzierungsstruktur entscheidet</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Print</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -1568,7 +1568,7 @@
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>https://www.fondsexklusiv.at/schwellenlaender-worauf-es-jetzt-ankommt/</t>
+          <t>https://www.fixed-income.org/fileadmin/pdf/BOND_MAGAZINE_239.pdf</t>
         </is>
       </c>
     </row>
@@ -1578,17 +1578,17 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Intelligent Investors</t>
+          <t>FONDS exklusiv Österreich</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Die neue Verwundbarkeit der Schwellenländer</t>
+          <t>Schwellenländer: Worauf es jetzt ankommt</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
@@ -1603,7 +1603,7 @@
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>https://intelligent-investors.de/die-neue-verwundbarkeit-der-schwellenlaender/</t>
+          <t>https://www.fondsexklusiv.at/schwellenlaender-worauf-es-jetzt-ankommt/</t>
         </is>
       </c>
     </row>
@@ -1613,17 +1613,17 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Institutional Money</t>
+          <t>Intelligent Investors</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Finanzierungsstruktur: Der neue Stresstest für Schwellenländer</t>
+          <t>Die neue Verwundbarkeit der Schwellenländer</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>DACH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>https://www.institutional-money.com/news/maerkte/headline/finanzierungsstruktur-der-neue-stresstest-fuer-schwellenlaender-251058</t>
+          <t>https://intelligent-investors.de/die-neue-verwundbarkeit-der-schwellenlaender/</t>
         </is>
       </c>
     </row>
@@ -1648,12 +1648,12 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Neo Market Ways</t>
+          <t>Institutional Money</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>From Microfinance to Mobility: How Capital is Driving Growth Across Eastern Europe</t>
+          <t>Finanzierungsstruktur: Der neue Stresstest für Schwellenländer</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
@@ -1673,27 +1673,27 @@
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>https://neomarketways.com/from-microfinance-to-mobility-how-capital-is-driving-growth-across-eastern-europe/</t>
+          <t>https://www.institutional-money.com/news/maerkte/headline/finanzierungsstruktur-der-neue-stresstest-fuer-schwellenlaender-251058</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>NEX24 News</t>
+          <t>Neo Market Ways</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Iran-Krieg: Der neue Stresstest für Schwellenländer</t>
+          <t>From Microfinance to Mobility: How Capital is Driving Growth Across Eastern Europe</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>DACH</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
@@ -1708,27 +1708,27 @@
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>https://nex24.news/2026/05/iran-krieg-der-neue-stresstest-fuer-schwellenlaender/</t>
+          <t>https://neomarketways.com/from-microfinance-to-mobility-how-capital-is-driving-growth-across-eastern-europe/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>GELD-Magazin</t>
+          <t>NEX24 News</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Stresstest für Schwellenländer</t>
+          <t>Iran-Krieg: Der neue Stresstest für Schwellenländer</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
@@ -1743,27 +1743,27 @@
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>https://www.geld-magazin.at/stresstest-fuer-schwellenlaender/</t>
+          <t>https://nex24.news/2026/05/iran-krieg-der-neue-stresstest-fuer-schwellenlaender/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>Markt Einblicke</t>
+          <t>GELD-Magazin</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Warum der Blick auf den Ölpreis nicht reicht</t>
+          <t>Stresstest für Schwellenländer</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
@@ -1778,27 +1778,27 @@
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>https://markteinblicke.de/130696/2026/05/warum-der-blick-auf-den-oelpreis-nicht-reicht/</t>
+          <t>https://www.geld-magazin.at/stresstest-fuer-schwellenlaender/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>46164</v>
+        <v>46169</v>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Moneycab</t>
+          <t>Markt Einblicke</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Nicht die Grösse des Kredits entscheidet, sondern seine Wirkung</t>
+          <t>Warum der Blick auf den Ölpreis nicht reicht</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>https://www.moneycab.com/dossiers/nicht-die-groesse-des-kredits-entscheidet-sondern-seine-wirkung/</t>
+          <t>https://markteinblicke.de/130696/2026/05/warum-der-blick-auf-den-oelpreis-nicht-reicht/</t>
         </is>
       </c>
     </row>
@@ -1823,7 +1823,7 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>finanznachrichten.de</t>
+          <t>Moneycab</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
@@ -1848,22 +1848,22 @@
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>https://www.finanznachrichten.de/nachrichten-2026-05/68568705-nicht-die-groesse-des-kredits-entscheidet-sondern-seine-wirkung-095.htm</t>
+          <t>https://www.moneycab.com/dossiers/nicht-die-groesse-des-kredits-entscheidet-sondern-seine-wirkung/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>46150</v>
+        <v>46164</v>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Finanz- und Wirtschaftsspiegel</t>
+          <t>finanznachrichten.de</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Entwicklungsfinanzierung mit Mikrokrediten</t>
+          <t>Nicht die Grösse des Kredits entscheidet, sondern seine Wirkung</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -1873,7 +1873,7 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>Digital newsletter</t>
+          <t>Online</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
@@ -1881,20 +1881,24 @@
           <t>Johannes Feist</t>
         </is>
       </c>
-      <c r="G41" s="4" t="inlineStr"/>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>https://www.finanznachrichten.de/nachrichten-2026-05/68568705-nicht-die-groesse-des-kredits-entscheidet-sondern-seine-wirkung-095.htm</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Markt Einblicke</t>
+          <t>Finanz- und Wirtschaftsspiegel</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Mikrofinanz-Anleihen: Ein wachsender Markt</t>
+          <t>Entwicklungsfinanzierung mit Mikrokrediten</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1904,7 +1908,7 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Digital newsletter</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
@@ -1912,24 +1916,20 @@
           <t>Johannes Feist</t>
         </is>
       </c>
-      <c r="G42" s="4" t="inlineStr">
-        <is>
-          <t>https://markteinblicke.de/130263/2026/05/mikrofinanz-anleihen-ein-wachsender-markt/</t>
-        </is>
-      </c>
+      <c r="G42" s="4" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>46125</v>
+        <v>46149</v>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>cash-online.de</t>
+          <t>Markt Einblicke</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Tokenisierte Anleihen: Was sich für Anleger ändert und was nicht</t>
+          <t>Mikrofinanz-Anleihen: Ein wachsender Markt</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1944,27 +1944,27 @@
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>Louiza Savchenko</t>
+          <t>Johannes Feist</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>https://www.cash-online.de/a/tokenisierte-anleihen-was-sich-fuer-anleger-aendert-und-was-nicht-715994/</t>
+          <t>https://markteinblicke.de/130263/2026/05/mikrofinanz-anleihen-ein-wachsender-markt/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>46109</v>
+        <v>46125</v>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Wirtschaftsvision</t>
+          <t>cash-online.de</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Der Trugschluss der sicheren Häfen</t>
+          <t>Tokenisierte Anleihen: Was sich für Anleger ändert und was nicht</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1979,27 +1979,27 @@
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist</t>
+          <t>Louiza Savchenko</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>https://wirtschaftsvision.de/der-trugschluss-der-sicheren-haefen/</t>
+          <t>https://www.cash-online.de/a/tokenisierte-anleihen-was-sich-fuer-anleger-aendert-und-was-nicht-715994/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Börsen-Zeitung</t>
+          <t>Wirtschaftsvision</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Wasserknappheit als Kreditrisiko</t>
+          <t>Der Trugschluss der sicheren Häfen</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -2009,7 +2009,7 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>Print &amp; Online</t>
+          <t>Online</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
@@ -2019,22 +2019,22 @@
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>https://www.boersen-zeitung.de/sonderbeilagen/wasserknappheit-als-kreditrisiko</t>
+          <t>https://wirtschaftsvision.de/der-trugschluss-der-sicheren-haefen/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>46105</v>
+        <v>46108</v>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Frankfurter Allgemeine Zeitung</t>
+          <t>Börsen-Zeitung</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Sorgen um Privatkredite: Finanzkrise oder silberne Aera?</t>
+          <t>Wasserknappheit als Kreditrisiko</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Print &amp; Online</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>https://www.faz.net/pro/meine-finanzen/zinsen/sorgen-um-privatkredite-finanzkrise-oder-silberne-aera-110376123.html</t>
+          <t>https://www.boersen-zeitung.de/sonderbeilagen/wasserknappheit-als-kreditrisiko</t>
         </is>
       </c>
     </row>
@@ -2064,12 +2064,12 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>DAS INVESTMENT</t>
+          <t>Frankfurter Allgemeine Zeitung</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Private Credit unter Druck: Wenn das Geld nicht mehr herauskommt</t>
+          <t>Sorgen um Privatkredite: Finanzkrise oder silberne Aera?</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>https://www.dasinvestment.com/private-credit-unter-druck-wenn-das-geld-nicht-mehr-herauskommt/</t>
+          <t>https://www.faz.net/pro/meine-finanzen/zinsen/sorgen-um-privatkredite-finanzkrise-oder-silberne-aera-110376123.html</t>
         </is>
       </c>
     </row>
@@ -2099,17 +2099,17 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>FONDS exklusiv Oesterreich</t>
+          <t>DAS INVESTMENT</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Private Credit-Debatte entfacht</t>
+          <t>Private Credit unter Druck: Wenn das Geld nicht mehr herauskommt</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>https://www.fondsexklusiv.at/private-credit-debatte-entfacht/</t>
+          <t>https://www.dasinvestment.com/private-credit-unter-druck-wenn-das-geld-nicht-mehr-herauskommt/</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>46103</v>
+        <v>46105</v>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Der Standard</t>
+          <t>FONDS exklusiv Oesterreich</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Pakistan spart Milliarden an fossilen Importen: Wie hat es das gemacht?</t>
+          <t>Private Credit-Debatte entfacht</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -2159,27 +2159,27 @@
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>https://www.derstandard.de/story/3000000313347/pakistan-spart-milliarden-an-fossilen-importen-wie-hat-es-das-gemacht</t>
+          <t>https://www.fondsexklusiv.at/private-credit-debatte-entfacht/</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
-        <v>46101</v>
+        <v>46103</v>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Finews</t>
+          <t>Der Standard</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>Tokenisierung: Louzia Savchenko ueber Innovation und MK Global Kapital</t>
+          <t>Pakistan spart Milliarden an fossilen Importen: Wie hat es das gemacht?</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>Louiza Savchenko</t>
+          <t>Johannes Feist</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>https://www.finews.ch/news/finanzplatz/71578-finews-first-tokenisierung-louzia-savchenko-finanzplatz-schweiz-innovation-mk-global-kapital</t>
+          <t>https://www.derstandard.de/story/3000000313347/pakistan-spart-milliarden-an-fossilen-importen-wie-hat-es-das-gemacht</t>
         </is>
       </c>
     </row>
@@ -2204,17 +2204,17 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>BondGuide</t>
+          <t>Finews</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Private Credit ist nicht gleich Private Credit: wo die Risiken wirklich liegen</t>
+          <t>Tokenisierung: Louzia Savchenko ueber Innovation und MK Global Kapital</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist</t>
+          <t>Louiza Savchenko</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>https://www.bondguide.de/topnews/private-credit-ist-nicht-gleich-private-credit-wo-die-risiken-wirklich-liegen/</t>
+          <t>https://www.finews.ch/news/finanzplatz/71578-finews-first-tokenisierung-louzia-savchenko-finanzplatz-schweiz-innovation-mk-global-kapital</t>
         </is>
       </c>
     </row>
@@ -2239,17 +2239,17 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Swiss Finance AI</t>
+          <t>BondGuide</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>Warum tokenisierte Anleihen mehr sind als ein Trend</t>
+          <t>Private Credit ist nicht gleich Private Credit: wo die Risiken wirklich liegen</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
@@ -2259,27 +2259,27 @@
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>Louiza Savchenko</t>
+          <t>Johannes Feist</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>https://www.swissfinanceai.ch/blog/swiss-finance/warum-tokenisierte-anleihen-mehr-sind-als-ein-trend</t>
+          <t>https://www.bondguide.de/topnews/private-credit-ist-nicht-gleich-private-credit-wo-die-risiken-wirklich-liegen/</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Moneycab</t>
+          <t>Swiss Finance AI</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Nicht nur Öl: Wo der Iran-Konflikt Emerging Markets wirklich trifft</t>
+          <t>Warum tokenisierte Anleihen mehr sind als ein Trend</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist</t>
+          <t>Louiza Savchenko</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>https://www.moneycab.com/finanz/nicht-nur-oel-wo-der-iran-konflikt-emerging-markets-wirklich-trifft/</t>
+          <t>https://www.swissfinanceai.ch/blog/swiss-finance/warum-tokenisierte-anleihen-mehr-sind-als-ein-trend</t>
         </is>
       </c>
     </row>
@@ -2309,17 +2309,17 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Institutional Money</t>
+          <t>Moneycab</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>Was der Iran-Schock fuer Emerging Markets veraendert</t>
+          <t>Nicht nur Öl: Wo der Iran-Konflikt Emerging Markets wirklich trifft</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
@@ -2334,7 +2334,7 @@
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>https://www.institutional-money.com/news/maerkte/headline/was-der-iran-schock-fuer-emerging-markets-veraendert-249420</t>
+          <t>https://www.moneycab.com/finanz/nicht-nur-oel-wo-der-iran-konflikt-emerging-markets-wirklich-trifft/</t>
         </is>
       </c>
     </row>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>fixed-income.org</t>
+          <t>Institutional Money</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>https://www.fixed-income.org/investment/was-der-iran-schock-fuer-emerging-markets-veraendert.html</t>
+          <t>https://www.institutional-money.com/news/maerkte/headline/was-der-iran-schock-fuer-emerging-markets-veraendert-249420</t>
         </is>
       </c>
     </row>
@@ -2379,12 +2379,12 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>finanznachrichten.de</t>
+          <t>fixed-income.org</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>Nicht nur Öl: Wo der Iran-Konflikt Emerging Markets wirklich trifft</t>
+          <t>Was der Iran-Schock fuer Emerging Markets veraendert</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
@@ -2404,13 +2404,13 @@
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>https://www.finanznachrichten.de/nachrichten-2026-03/67987291-nicht-nur-oel-wo-der-iran-konflikt-emerging-markets-wirklich-trifft-095.htm</t>
+          <t>https://www.fixed-income.org/investment/was-der-iran-schock-fuer-emerging-markets-veraendert.html</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
-        <v>46098</v>
+        <v>46100</v>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
@@ -2419,7 +2419,7 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Private Credit ist nicht gleich Private Credit: Wo die Risiken wirklich liegen</t>
+          <t>Nicht nur Öl: Wo der Iran-Konflikt Emerging Markets wirklich trifft</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>https://www.finanznachrichten.de/nachrichten-2026-03/67998176-private-credit-ist-nicht-gleich-private-credit-wo-die-risiken-wirklich-liegen-144.htm</t>
+          <t>https://www.finanznachrichten.de/nachrichten-2026-03/67987291-nicht-nur-oel-wo-der-iran-konflikt-emerging-markets-wirklich-trifft-095.htm</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>cash-online.de</t>
+          <t>finanznachrichten.de</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>Gastkommentar: Der blinde Fleck der Private-Credit-Debatte</t>
+          <t>Private Credit ist nicht gleich Private Credit: Wo die Risiken wirklich liegen</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>https://www.cash-online.de/a/gastkommentar-der-blinde-fleck-der-private-credit-debatte-713724/</t>
+          <t>https://www.finanznachrichten.de/nachrichten-2026-03/67998176-private-credit-ist-nicht-gleich-private-credit-wo-die-risiken-wirklich-liegen-144.htm</t>
         </is>
       </c>
     </row>
@@ -2484,12 +2484,12 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>BOND MAGAZINE</t>
+          <t>cash-online.de</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Tokenisierte Anleihen: Effizienz, Vertrauen und Marktentwicklung</t>
+          <t>Gastkommentar: Der blinde Fleck der Private-Credit-Debatte</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -2499,28 +2499,32 @@
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>Print</t>
+          <t>Online</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>Louiza Savchenko</t>
-        </is>
-      </c>
-      <c r="G59" s="4" t="inlineStr"/>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="inlineStr">
+        <is>
+          <t>https://www.cash-online.de/a/gastkommentar-der-blinde-fleck-der-private-credit-debatte-713724/</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>FONDS exklusiv</t>
+          <t>BOND MAGAZINE</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Private Credit-Debatte entfacht</t>
+          <t>Tokenisierte Anleihen: Effizienz, Vertrauen und Marktentwicklung</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -2530,19 +2534,15 @@
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Print</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist</t>
-        </is>
-      </c>
-      <c r="G60" s="4" t="inlineStr">
-        <is>
-          <t>https://www.fondsexklusiv.de/private-credit-debatte-entfacht/</t>
-        </is>
-      </c>
+          <t>Louiza Savchenko</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
@@ -2550,12 +2550,12 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Kreditwesen (Verlagsgruppe Knapp-Richardi)</t>
+          <t>FONDS exklusiv</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Mikrofinanz als Anlageklasse</t>
+          <t>Private Credit-Debatte entfacht</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>Print &amp; Online</t>
+          <t>Online</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>https://www.kreditwesen.de/kreditwesen/themenschwerpunkte/aufsaetze/mikrofinanz-anlageklasse-id107511.html</t>
+          <t>https://www.fondsexklusiv.de/private-credit-debatte-entfacht/</t>
         </is>
       </c>
     </row>
@@ -2585,22 +2585,22 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Payoff</t>
+          <t>Kreditwesen (Verlagsgruppe Knapp-Richardi)</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Der blinde Fleck der Private-Credit-Debatte</t>
+          <t>Mikrofinanz als Anlageklasse</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Print &amp; Online</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
@@ -2610,17 +2610,17 @@
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>https://www.payoff.ch/news/der-blinde-fleck-der-private-credit-debatte</t>
+          <t>https://www.kreditwesen.de/kreditwesen/themenschwerpunkte/aufsaetze/mikrofinanz-anlageklasse-id107511.html</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>investrends.ch</t>
+          <t>Payoff</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>https://investrends.ch/aktuell/investments/der-blinde-fleck-der-private-credit-debatte/</t>
+          <t>https://www.payoff.ch/news/der-blinde-fleck-der-private-credit-debatte</t>
         </is>
       </c>
     </row>
@@ -2655,7 +2655,7 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Private Markets 360</t>
+          <t>investrends.ch</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -2665,7 +2665,7 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
@@ -2680,22 +2680,22 @@
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>https://privatemarkets360.com/artikel/58516-der-blinde-fleck-der-private-credit-debatte</t>
+          <t>https://investrends.ch/aktuell/investments/der-blinde-fleck-der-private-credit-debatte/</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Finanzen100.de</t>
+          <t>Private Markets 360</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>Marktkommentar: Der Trugschluss der sicheren Häfen</t>
+          <t>Der blinde Fleck der Private-Credit-Debatte</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>https://www.finanzen100.de/premium/bernecker-boersenkompass/marktkommentar-der-trugschluss-der-sicheren-haefen_H1356104965_6799449/</t>
+          <t>https://privatemarkets360.com/artikel/58516-der-blinde-fleck-der-private-credit-debatte</t>
         </is>
       </c>
     </row>
@@ -2725,12 +2725,12 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Intelligent Investors</t>
+          <t>Finanzen100.de</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>Der blinde Fleck der Private-Credit-Debatte</t>
+          <t>Marktkommentar: Der Trugschluss der sicheren Häfen</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -2750,22 +2750,22 @@
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>https://intelligent-investors.de/der-blinde-fleck-der-private-credit-debatte/</t>
+          <t>https://www.finanzen100.de/premium/bernecker-boersenkompass/marktkommentar-der-trugschluss-der-sicheren-haefen_H1356104965_6799449/</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
-        <v>46085</v>
+        <v>46093</v>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>markteinblicke.de</t>
+          <t>Intelligent Investors</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Tokenisierte Anleihen: Mehr Governance erforderlich</t>
+          <t>Der blinde Fleck der Private-Credit-Debatte</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -2780,12 +2780,12 @@
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>Louiza Savchenko</t>
+          <t>Johannes Feist</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>https://markteinblicke.de/128943/2026/03/tokenisierte-anleihen-mehr-governance-erforderlich/</t>
+          <t>https://intelligent-investors.de/der-blinde-fleck-der-private-credit-debatte/</t>
         </is>
       </c>
     </row>
@@ -2795,12 +2795,12 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>gruenderkueche.de</t>
+          <t>markteinblicke.de</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>Weltfrauentag: Unternehmerinnen fehlt weiterhin der Zugang zu Kapital</t>
+          <t>Tokenisierte Anleihen: Mehr Governance erforderlich</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>https://www.gruenderkueche.de/news/finanzen-news/weltfrauentag-unternehmerinnen-fehlt-weiterhin-der-zugang-zu-kapital/</t>
+          <t>https://markteinblicke.de/128943/2026/03/tokenisierte-anleihen-mehr-governance-erforderlich/</t>
         </is>
       </c>
     </row>
@@ -2830,12 +2830,12 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>Table.Media</t>
+          <t>gruenderkueche.de</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>Gleichstellung: Unternehmerinnen fehlt weltweit der Zugang zu Kapital</t>
+          <t>Weltfrauentag: Unternehmerinnen fehlt weiterhin der Zugang zu Kapital</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -2855,22 +2855,22 @@
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>https://table.media/esg/news/gleichstellung-unternehmerinnen-fehlt-weltweit-der-zugang-zu-kapital</t>
+          <t>https://www.gruenderkueche.de/news/finanzen-news/weltfrauentag-unternehmerinnen-fehlt-weiterhin-der-zugang-zu-kapital/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>dfpa.info</t>
+          <t>Table.Media</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>Unternehmerinnen fehlt weltweit der Zugang zu Kapital</t>
+          <t>Gleichstellung: Unternehmerinnen fehlt weltweit der Zugang zu Kapital</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -2890,17 +2890,17 @@
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>https://www.dfpa.info/maerkte-studien-news/unternehmerinnen-fehlt-weltweit-der-zugang-zu-kapital/</t>
+          <t>https://table.media/esg/news/gleichstellung-unternehmerinnen-fehlt-weltweit-der-zugang-zu-kapital</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>altii.de</t>
+          <t>dfpa.info</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
@@ -2925,7 +2925,7 @@
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>https://www.altii.de/edai-71550571-cb6c-4c09-93da-bd99b822c245/</t>
+          <t>https://www.dfpa.info/maerkte-studien-news/unternehmerinnen-fehlt-weltweit-der-zugang-zu-kapital/</t>
         </is>
       </c>
     </row>
@@ -2935,12 +2935,12 @@
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>dapd.de</t>
+          <t>altii.de</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>Der Trugschluss der sicheren Häfen</t>
+          <t>Unternehmerinnen fehlt weltweit der Zugang zu Kapital</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -2955,27 +2955,27 @@
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist</t>
+          <t>Louiza Savchenko</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
-          <t>https://www.dapd.de/der-trugschluss-der-sicheren-haefen/</t>
+          <t>https://www.altii.de/edai-71550571-cb6c-4c09-93da-bd99b822c245/</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="n">
-        <v>46078</v>
+        <v>46083</v>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>dfpa.info</t>
+          <t>dapd.de</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>Mikrofinanz: Besonderheit Anleihen mit festem Zins</t>
+          <t>Der Trugschluss der sicheren Häfen</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -2995,13 +2995,13 @@
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>https://www.dfpa.info/interview/mikrofinanz-besonderheit-anleihen-mit-festem-zins.html</t>
+          <t>https://www.dapd.de/der-trugschluss-der-sicheren-haefen/</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>Wenn Geschäftsbanken passen, helfen Mikrofinanzfonds</t>
+          <t>Mikrofinanz: Besonderheit Anleihen mit festem Zins</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>https://www.dfpa.info/top-story/wenn-geschaeftsbanken-passen-helfen-mikrofinanzfonds.html</t>
+          <t>https://www.dfpa.info/interview/mikrofinanz-besonderheit-anleihen-mit-festem-zins.html</t>
         </is>
       </c>
     </row>
@@ -3040,12 +3040,12 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>DFPA</t>
+          <t>dfpa.info</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>Die neue EXXECNEWS ist erschienen</t>
+          <t>Wenn Geschäftsbanken passen, helfen Mikrofinanzfonds</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -3065,22 +3065,22 @@
       </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
-          <t>https://www.dfpa.info/pressedigest-news/die-neue-exxecnews-ist-erschienen-78/</t>
+          <t>https://www.dfpa.info/top-story/wenn-geschaeftsbanken-passen-helfen-mikrofinanzfonds.html</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>exxecnews.org</t>
+          <t>DFPA</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>Teil I: Wenn Geschäftsbanken passen, helfen Mikrofinanzfonds</t>
+          <t>Die neue EXXECNEWS ist erschienen</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -3090,7 +3090,7 @@
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>Print &amp; Online</t>
+          <t>Online</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
@@ -3100,7 +3100,7 @@
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
-          <t>https://exxecnews.org/wp-content/uploads/2026/02/Ausgabe-05_2026.pdf</t>
+          <t>https://www.dfpa.info/pressedigest-news/die-neue-exxecnews-ist-erschienen-78/</t>
         </is>
       </c>
     </row>
@@ -3110,12 +3110,12 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>EXXECNEWS</t>
+          <t>exxecnews.org</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>Teil II: Mikrofinanz-Besonderheit – Anleihen mit festem Zins</t>
+          <t>Teil I: Wenn Geschäftsbanken passen, helfen Mikrofinanzfonds</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -3141,16 +3141,16 @@
     </row>
     <row r="78">
       <c r="A78" s="3" t="n">
-        <v>46069</v>
+        <v>46076</v>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>boerse-social.com</t>
+          <t>EXXECNEWS</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>Börse-Inputs auf Spotify zu u.a. Do&amp;Co, Bawag, Nervigem und Mikrokrediten</t>
+          <t>Teil II: Mikrofinanz-Besonderheit – Anleihen mit festem Zins</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Print &amp; Online</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
-          <t>https://boerse-social.com/2026/02/16/borse-inputs_auf_spotify_zu_ua_doco_bawag_nervigem_und_mikrokrediten_1</t>
+          <t>https://exxecnews.org/wp-content/uploads/2026/02/Ausgabe-05_2026.pdf</t>
         </is>
       </c>
     </row>
@@ -3180,12 +3180,12 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>bondguide.de</t>
+          <t>boerse-social.com</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>Security Conference München 2026: öffentliche Mittel als Hebel nutzen</t>
+          <t>Börse-Inputs auf Spotify zu u.a. Do&amp;Co, Bawag, Nervigem und Mikrokrediten</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -3205,17 +3205,17 @@
       </c>
       <c r="G79" s="4" t="inlineStr">
         <is>
-          <t>https://www.bondguide.de/topnews/security-conference-muenchen-2026-oeffentliche-mittel-als-hebel-nutzen/</t>
+          <t>https://boerse-social.com/2026/02/16/borse-inputs_auf_spotify_zu_ua_doco_bawag_nervigem_und_mikrokrediten_1</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="n">
-        <v>46067</v>
+        <v>46069</v>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>finanznachrichten.de</t>
+          <t>bondguide.de</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
-          <t>https://www.finanznachrichten.de/nachrichten-2026-02/67704129-security-conference-muenchen-2026-oeffentliche-mittel-als-hebel-nutzen-144.htm</t>
+          <t>https://www.bondguide.de/topnews/security-conference-muenchen-2026-oeffentliche-mittel-als-hebel-nutzen/</t>
         </is>
       </c>
     </row>
@@ -3250,12 +3250,12 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>geldmeisterin.com</t>
+          <t>finanznachrichten.de</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>Mikrokredite gerade jetzt zur Risikostreuung</t>
+          <t>Security Conference München 2026: öffentliche Mittel als Hebel nutzen</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -3275,32 +3275,32 @@
       </c>
       <c r="G81" s="4" t="inlineStr">
         <is>
-          <t>https://www.geldmeisterin.com/index.php/2026/02/14/mikrokredite-gerade-jetzt-zur-risikostreuung/</t>
+          <t>https://www.finanznachrichten.de/nachrichten-2026-02/67704129-security-conference-muenchen-2026-oeffentliche-mittel-als-hebel-nutzen-144.htm</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="n">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>Börsen-Kurier</t>
+          <t>geldmeisterin.com</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>Privates Kapital für noch nicht entwickelte Märkte</t>
+          <t>Mikrokredite gerade jetzt zur Risikostreuung</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>DACH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>Print</t>
+          <t>Online</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
@@ -3308,55 +3308,55 @@
           <t>Johannes Feist</t>
         </is>
       </c>
-      <c r="G82" s="4" t="inlineStr"/>
+      <c r="G82" s="4" t="inlineStr">
+        <is>
+          <t>https://www.geldmeisterin.com/index.php/2026/02/14/mikrokredite-gerade-jetzt-zur-risikostreuung/</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="n">
-        <v>46057</v>
+        <v>46066</v>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>investrends.ch</t>
+          <t>Börsen-Kurier</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>Private Debt: Warum Prozesse wichtiger sind als Prognosen</t>
+          <t>Privates Kapital für noch nicht entwickelte Märkte</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>DACH</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Print</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>Michele Mattioda</t>
-        </is>
-      </c>
-      <c r="G83" s="4" t="inlineStr">
-        <is>
-          <t>https://investrends.ch/aktuell/investments/private-debt-warum-prozesse-wichtiger-sind-als-prognosen/</t>
-        </is>
-      </c>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G83" s="4" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="3" t="n">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>Payoff</t>
+          <t>investrends.ch</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>Mikrofinanz als Private Debt: Besicherte KMU-Kredite statt «Entwicklungshilfe»</t>
+          <t>Private Debt: Warum Prozesse wichtiger sind als Prognosen</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
@@ -3371,37 +3371,37 @@
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist</t>
+          <t>Michele Mattioda</t>
         </is>
       </c>
       <c r="G84" s="4" t="inlineStr">
         <is>
-          <t>https://www.payoff.ch/news/mikrofinanz-als-private-debt-besicherte-kmu-kredite-statt-entwicklungshilfe</t>
+          <t>https://investrends.ch/aktuell/investments/private-debt-warum-prozesse-wichtiger-sind-als-prognosen/</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="n">
-        <v>46049</v>
+        <v>46055</v>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Markt Einblicke</t>
+          <t>Payoff</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>Mikrofinanzanleihen 2026: Stabile Renditen aus der Realwirtschaft</t>
+          <t>Mikrofinanz als Private Debt: Besicherte KMU-Kredite statt «Entwicklungshilfe»</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>E-Paper</t>
+          <t>Online</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
@@ -3409,20 +3409,24 @@
           <t>Johannes Feist</t>
         </is>
       </c>
-      <c r="G85" s="4" t="inlineStr"/>
+      <c r="G85" s="4" t="inlineStr">
+        <is>
+          <t>https://www.payoff.ch/news/mikrofinanz-als-private-debt-besicherte-kmu-kredite-statt-entwicklungshilfe</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="n">
-        <v>46044</v>
+        <v>46049</v>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>Frankfurter Allgemeine Zeitung</t>
+          <t>Markt Einblicke</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>Beim Klimaschutz mehr Marktwirtschaft wagen</t>
+          <t>Mikrofinanzanleihen 2026: Stabile Renditen aus der Realwirtschaft</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -3432,7 +3436,7 @@
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>E-Paper</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
@@ -3440,29 +3444,25 @@
           <t>Johannes Feist</t>
         </is>
       </c>
-      <c r="G86" s="4" t="inlineStr">
-        <is>
-          <t>https://www.faz.net/pro/weltwirtschaft/klima-ressourcen/klimapolitik-sollte-auf-mikrofinanzierung-statt-grossprojekte-setzen-accg-200431361.html</t>
-        </is>
-      </c>
+      <c r="G86" s="4" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="3" t="n">
-        <v>46038</v>
+        <v>46044</v>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>E-fundresearch</t>
+          <t>Frankfurter Allgemeine Zeitung</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>Umfrage: Welche Chancen und Risiken Experten 2026 in den Private Markets sehen</t>
+          <t>Beim Klimaschutz mehr Marktwirtschaft wagen</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>DACH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
@@ -3477,27 +3477,27 @@
       </c>
       <c r="G87" s="4" t="inlineStr">
         <is>
-          <t>https://e-fundresearch.com/funds/artikel/57840-umfrage-welche-chancen-und-risiken-experten-2026-in-den-private-markets-sehen?page=5</t>
+          <t>https://www.faz.net/pro/weltwirtschaft/klima-ressourcen/klimapolitik-sollte-auf-mikrofinanzierung-statt-grossprojekte-setzen-accg-200431361.html</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="n">
-        <v>46035</v>
+        <v>46038</v>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>Finews</t>
+          <t>E-fundresearch</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>Start 2026: Disziplin als Renditequelle bei KMU-Private Debt</t>
+          <t>Umfrage: Welche Chancen und Risiken Experten 2026 in den Private Markets sehen</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>DACH</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
@@ -3507,32 +3507,32 @@
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>Michele Mattioda</t>
+          <t>Johannes Feist</t>
         </is>
       </c>
       <c r="G88" s="4" t="inlineStr">
         <is>
-          <t>https://www.finews.ch/news/finanzplatz/70792-start2026-assetmanagement-mk-global-kapital-michele-mattioda-privat-debt-kmu-mikro</t>
+          <t>https://e-fundresearch.com/funds/artikel/57840-umfrage-welche-chancen-und-risiken-experten-2026-in-den-private-markets-sehen?page=5</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="n">
-        <v>46031</v>
+        <v>46035</v>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>portfolio institutionell</t>
+          <t>Finews</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>Große Wirkung mit kleinen Krediten</t>
+          <t>Start 2026: Disziplin als Renditequelle bei KMU-Private Debt</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
@@ -3542,27 +3542,27 @@
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist</t>
+          <t>Michele Mattioda</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr">
         <is>
-          <t>https://www.portfolio-institutionell.de/grosse-wirkung-mit-kleinen-krediten/</t>
+          <t>https://www.finews.ch/news/finanzplatz/70792-start2026-assetmanagement-mk-global-kapital-michele-mattioda-privat-debt-kmu-mikro</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="n">
-        <v>46029</v>
+        <v>46031</v>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>Markt Einblicke</t>
+          <t>portfolio institutionell</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>Mikrofinanzanleihen 2026: Stabile Renditen aus der Realwirtschaft</t>
+          <t>Große Wirkung mit kleinen Krediten</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
@@ -3582,22 +3582,22 @@
       </c>
       <c r="G90" s="4" t="inlineStr">
         <is>
-          <t>https://markteinblicke.de/127407/2026/01/mikrofinanzanleihen-2026-stabile-renditen-aus-der-realwirtschaft/</t>
+          <t>https://www.portfolio-institutionell.de/grosse-wirkung-mit-kleinen-krediten/</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="n">
-        <v>46009</v>
+        <v>46029</v>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>portfolio institutionell</t>
+          <t>Markt Einblicke</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>Große Wirkung mit kleinen Krediten</t>
+          <t>Mikrofinanzanleihen 2026: Stabile Renditen aus der Realwirtschaft</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
@@ -3607,7 +3607,7 @@
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>Print</t>
+          <t>Online</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
@@ -3617,22 +3617,22 @@
       </c>
       <c r="G91" s="4" t="inlineStr">
         <is>
-          <t>https://www.yumpu.com/de/document/read/70885506/pit-1225</t>
+          <t>https://markteinblicke.de/127407/2026/01/mikrofinanzanleihen-2026-stabile-renditen-aus-der-realwirtschaft/</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>BondGuide</t>
+          <t>portfolio institutionell</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>Mikro Kapital Management: „Impact Investing ist kein Charity“</t>
+          <t>Große Wirkung mit kleinen Krediten</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="G92" s="4" t="inlineStr">
         <is>
-          <t>https://www.bondguide.de/wp-content/uploads/2025/12/bondguide-25-2025.pdf</t>
+          <t>https://www.yumpu.com/de/document/read/70885506/pit-1225</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="n">
-        <v>46006</v>
+        <v>46008</v>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>IPE Institutional Investment</t>
+          <t>BondGuide</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>Gastbeitrag: Private Debt jenseits von Corporate Loans – Mikrofinanz als Anlageklasse</t>
+          <t>Mikro Kapital Management: „Impact Investing ist kein Charity“</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>DACH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Print</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
@@ -3687,7 +3687,7 @@
       </c>
       <c r="G93" s="4" t="inlineStr">
         <is>
-          <t>https://www.institutional-investment.de/content/asset-allocation/gastbeitrag-private-debt-jenseits-von-corporate-loans-mikrofinanz-als-anlageklasse.html</t>
+          <t>https://www.bondguide.de/wp-content/uploads/2025/12/bondguide-25-2025.pdf</t>
         </is>
       </c>
     </row>
@@ -3697,17 +3697,17 @@
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>Handelszeitung</t>
+          <t>IPE Institutional Investment</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>«In der Schweiz gibt es eine ganz ausgeprägte Kultur für Mikrofinanzierungen»</t>
+          <t>Gastbeitrag: Private Debt jenseits von Corporate Loans – Mikrofinanz als Anlageklasse</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>DACH</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
@@ -3722,27 +3722,27 @@
       </c>
       <c r="G94" s="4" t="inlineStr">
         <is>
-          <t>https://www.handelszeitung.ch/insurance/in-der-schweiz-gibt-es-eine-ganz-ausgepragte-kultur-fur-mikrofinanzierungen-884310</t>
+          <t>https://www.institutional-investment.de/content/asset-allocation/gastbeitrag-private-debt-jenseits-von-corporate-loans-mikrofinanz-als-anlageklasse.html</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="n">
-        <v>46001</v>
+        <v>46006</v>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>altii</t>
+          <t>Handelszeitung</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>MK Global Kapital übernimmt Managementfunktion des Impact-Fonds ALTERNATIVE</t>
+          <t>«In der Schweiz gibt es eine ganz ausgeprägte Kultur für Mikrofinanzierungen»</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
@@ -3757,27 +3757,27 @@
       </c>
       <c r="G95" s="4" t="inlineStr">
         <is>
-          <t>https://www.altii.de/20251210_115639_ea0baaad-1f17-42a9-a698-596737b4a5f2/</t>
+          <t>https://www.handelszeitung.ch/insurance/in-der-schweiz-gibt-es-eine-ganz-ausgepragte-kultur-fur-mikrofinanzierungen-884310</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>investrends.ch</t>
+          <t>altii</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>Neue Managementgesellschaft für den Impact-Fonds ALTERNATIVE</t>
+          <t>MK Global Kapital übernimmt Managementfunktion des Impact-Fonds ALTERNATIVE</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
@@ -3792,22 +3792,22 @@
       </c>
       <c r="G96" s="4" t="inlineStr">
         <is>
-          <t>https://investrends.ch/aktuell/investments/neue-managementgesellschaft-fur-den-impact-fonds-alternative/</t>
+          <t>https://www.altii.de/20251210_115639_ea0baaad-1f17-42a9-a698-596737b4a5f2/</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>Moneycab</t>
+          <t>investrends.ch</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>MK Global Kapital wird per 1. Januar Managementgesellschaft für den Impact-Fonds ALTERNATIVE</t>
+          <t>Neue Managementgesellschaft für den Impact-Fonds ALTERNATIVE</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="G97" s="4" t="inlineStr">
         <is>
-          <t>https://www.moneycab.com/finanz/mk-global-kapital-wird-per-1-januar-managementgesellschaft-fuer-den-impact-fonds-alternative/</t>
+          <t>https://investrends.ch/aktuell/investments/neue-managementgesellschaft-fur-den-impact-fonds-alternative/</t>
         </is>
       </c>
     </row>
@@ -3837,17 +3837,17 @@
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>dfpa.info</t>
+          <t>Moneycab</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>MK Global Kapital wird Managementgesellschaft für Impact-Fonds "Alternative"</t>
+          <t>MK Global Kapital wird per 1. Januar Managementgesellschaft für den Impact-Fonds ALTERNATIVE</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="G98" s="4" t="inlineStr">
         <is>
-          <t>https://www.dfpa.info/investmentfonds-news/mk-global-kapital-wird-managementgesellschaft-fuer-impact-fonds-alternative/</t>
+          <t>https://www.moneycab.com/finanz/mk-global-kapital-wird-per-1-januar-managementgesellschaft-fuer-den-impact-fonds-alternative/</t>
         </is>
       </c>
     </row>
@@ -3872,12 +3872,12 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>finanznachrichten.de</t>
+          <t>dfpa.info</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>MK Global Kapital wird per 1. Januar Managementgesellschaft für den Impact-Fonds ALTERNATIVE</t>
+          <t>MK Global Kapital wird Managementgesellschaft für Impact-Fonds "Alternative"</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
@@ -3897,22 +3897,22 @@
       </c>
       <c r="G99" s="4" t="inlineStr">
         <is>
-          <t>https://www.finanznachrichten.de/nachrichten-2025-12/67174021-mk-global-kapital-wird-per-1-januar-managementgesellschaft-fuer-den-impact-fonds-alternative-095.htm</t>
+          <t>https://www.dfpa.info/investmentfonds-news/mk-global-kapital-wird-managementgesellschaft-fuer-impact-fonds-alternative/</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="n">
-        <v>45997</v>
+        <v>45999</v>
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>bondguide.de</t>
+          <t>finanznachrichten.de</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>Mikro Kapital Management: Impact Investing ist kein Charity</t>
+          <t>MK Global Kapital wird per 1. Januar Managementgesellschaft für den Impact-Fonds ALTERNATIVE</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
@@ -3932,22 +3932,22 @@
       </c>
       <c r="G100" s="4" t="inlineStr">
         <is>
-          <t>https://www.bondguide.de/topnews/mikro-kapital-management-impact-investing-ist-kein-charity/</t>
+          <t>https://www.finanznachrichten.de/nachrichten-2025-12/67174021-mk-global-kapital-wird-per-1-januar-managementgesellschaft-fuer-den-impact-fonds-alternative-095.htm</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="n">
-        <v>45996</v>
+        <v>45997</v>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>finanznachrichten.de</t>
+          <t>bondguide.de</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>Mikro Kapital Management: "Impact Investing ist kein Charity"</t>
+          <t>Mikro Kapital Management: Impact Investing ist kein Charity</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="G101" s="4" t="inlineStr">
         <is>
-          <t>https://www.finanznachrichten.de/nachrichten-2025-12/67161108-mikro-kapital-management-impact-investing-ist-kein-charity-144.htm</t>
+          <t>https://www.bondguide.de/topnews/mikro-kapital-management-impact-investing-ist-kein-charity/</t>
         </is>
       </c>
     </row>
@@ -3977,12 +3977,12 @@
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>Investorenplattform.de</t>
+          <t>finanznachrichten.de</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>Mikro Kapital Management: „Impact Investing ist kein Charity“</t>
+          <t>Mikro Kapital Management: "Impact Investing ist kein Charity"</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
@@ -4002,22 +4002,22 @@
       </c>
       <c r="G102" s="4" t="inlineStr">
         <is>
-          <t>https://investorenplattform.de/esg-impact/</t>
+          <t>https://www.finanznachrichten.de/nachrichten-2025-12/67161108-mikro-kapital-management-impact-investing-ist-kein-charity-144.htm</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>dfpa.info</t>
+          <t>Investorenplattform.de</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>Mikro Kapital platziert erstmals Anleihe an Luxemburger Börse</t>
+          <t>Mikro Kapital Management: „Impact Investing ist kein Charity“</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
@@ -4037,27 +4037,27 @@
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
-          <t>https://www.dfpa.info/investmentfonds-news/mikro-kapital-platziert-erstmals-emtn-anleihen-des-fonds-alternative-an-luxemburger-boerse/</t>
+          <t>https://investorenplattform.de/esg-impact/</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="n">
-        <v>45985</v>
+        <v>45995</v>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>Finews</t>
+          <t>dfpa.info</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist über Mikrofinanzen: Sollten vom hohen Ross herunterkommen</t>
+          <t>Mikro Kapital platziert erstmals Anleihe an Luxemburger Börse</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
@@ -4072,32 +4072,32 @@
       </c>
       <c r="G104" s="4" t="inlineStr">
         <is>
-          <t>https://www.finews.ch/news/finanzplatz/70147-mikro-capital-johannes-feist-kuenstliche-intelligenz-blockchain-rumaenien-europa-mikrofinanzen-finanzplatz-schweiz</t>
+          <t>https://www.dfpa.info/investmentfonds-news/mikro-kapital-platziert-erstmals-emtn-anleihen-des-fonds-alternative-an-luxemburger-boerse/</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>tagesschau24.de (TV interview)</t>
+          <t>Finews</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>ARD interview: Why “glowworms” matter more than trillion-dollar pledges</t>
+          <t>Johannes Feist über Mikrofinanzen: Sollten vom hohen Ross herunterkommen</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>TV &amp; Online</t>
+          <t>Online</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
@@ -4107,32 +4107,32 @@
       </c>
       <c r="G105" s="4" t="inlineStr">
         <is>
-          <t>https://www.tagesschau.de/multimedia/sendung/tagesschau24/boerselive/video-1527674.html</t>
+          <t>https://www.finews.ch/news/finanzplatz/70147-mikro-capital-johannes-feist-kuenstliche-intelligenz-blockchain-rumaenien-europa-mikrofinanzen-finanzplatz-schweiz</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>Börsen-Kurier</t>
+          <t>tagesschau24.de (TV interview)</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>Mikrofinanz: Stabilität aus realer Wertschöpfung</t>
+          <t>ARD interview: Why “glowworms” matter more than trillion-dollar pledges</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>Print</t>
+          <t>TV &amp; Online</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
@@ -4140,30 +4140,34 @@
           <t>Johannes Feist</t>
         </is>
       </c>
-      <c r="G106" s="4" t="inlineStr"/>
+      <c r="G106" s="4" t="inlineStr">
+        <is>
+          <t>https://www.tagesschau.de/multimedia/sendung/tagesschau24/boerselive/video-1527674.html</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="n">
-        <v>45973</v>
+        <v>45981</v>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>investrends.ch</t>
+          <t>Börsen-Kurier</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>Mikrofinanz ist Private Debt mit direkter Verbindung zur Realwirtschaft</t>
+          <t>Mikrofinanz: Stabilität aus realer Wertschöpfung</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Print</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
@@ -4171,29 +4175,25 @@
           <t>Johannes Feist</t>
         </is>
       </c>
-      <c r="G107" s="4" t="inlineStr">
-        <is>
-          <t>https://investrends.ch/aktuell/investments/mikrofinanz-ist-private-debt-mit-direkter-verbindung-zur-realwirtschaft/</t>
-        </is>
-      </c>
+      <c r="G107" s="4" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="3" t="n">
-        <v>45971</v>
+        <v>45973</v>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>photovoltaik.eu</t>
+          <t>investrends.ch</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>COP30: Klimafinanzierung muss in den Unternehmen ankommen</t>
+          <t>Mikrofinanz ist Private Debt mit direkter Verbindung zur Realwirtschaft</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
@@ -4208,22 +4208,22 @@
       </c>
       <c r="G108" s="4" t="inlineStr">
         <is>
-          <t>https://www.photovoltaik.eu/foerderung/cop30-klimafinanzierung-muss-den-unternehmen-ankommen</t>
+          <t>https://investrends.ch/aktuell/investments/mikrofinanz-ist-private-debt-mit-direkter-verbindung-zur-realwirtschaft/</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="n">
-        <v>45967</v>
+        <v>45971</v>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>Frankfurter Rundschau</t>
+          <t>photovoltaik.eu</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>Merz in Brasilien: Bundeskanzler fordert „globale Kraftanstrengung“ für Klimaschutz bei COP30</t>
+          <t>COP30: Klimafinanzierung muss in den Unternehmen ankommen</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
@@ -4243,7 +4243,7 @@
       </c>
       <c r="G109" s="4" t="inlineStr">
         <is>
-          <t>https://www.fr.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.photovoltaik.eu/foerderung/cop30-klimafinanzierung-muss-den-unternehmen-ankommen</t>
         </is>
       </c>
     </row>
@@ -4253,12 +4253,12 @@
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>Windmesse</t>
+          <t>Frankfurter Rundschau</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>COP30: Klimafinanzierung muss endlich in den Unternehmen ankommen</t>
+          <t>Merz in Brasilien: Bundeskanzler fordert „globale Kraftanstrengung“ für Klimaschutz bei COP30</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
@@ -4278,7 +4278,7 @@
       </c>
       <c r="G110" s="4" t="inlineStr">
         <is>
-          <t>https://w3.windmesse.de/windenergie/news/48059-cop30-klimafinanzierung-muss-endlich-in-den-unternehmen-ankommen</t>
+          <t>https://www.fr.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
@@ -4288,12 +4288,12 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>BondGuide</t>
+          <t>Windmesse</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>Klimafinanzierung bei COP 30: von Zusagen zu Wirkung entfalten</t>
+          <t>COP30: Klimafinanzierung muss endlich in den Unternehmen ankommen</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
@@ -4313,7 +4313,7 @@
       </c>
       <c r="G111" s="4" t="inlineStr">
         <is>
-          <t>https://www.bondguide.de/topnews/klimafinanzierung-bei-cop-30-von-zusagen-zu-wirkung-entfalten/</t>
+          <t>https://w3.windmesse.de/windenergie/news/48059-cop30-klimafinanzierung-muss-endlich-in-den-unternehmen-ankommen</t>
         </is>
       </c>
     </row>
@@ -4323,12 +4323,12 @@
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>AZ online (Allgemeine Zeitung der Lüneburger Heide)</t>
+          <t>BondGuide</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>Merz reist nach Brasilien: Deutschlands Klimapolitik bei COP30 auf dem Prüfstein</t>
+          <t>Klimafinanzierung bei COP 30: von Zusagen zu Wirkung entfalten</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
@@ -4348,7 +4348,7 @@
       </c>
       <c r="G112" s="4" t="inlineStr">
         <is>
-          <t>https://www.az-online.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.bondguide.de/topnews/klimafinanzierung-bei-cop-30-von-zusagen-zu-wirkung-entfalten/</t>
         </is>
       </c>
     </row>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>fehmarn24.de</t>
+          <t>AZ online (Allgemeine Zeitung der Lüneburger Heide)</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="G113" s="4" t="inlineStr">
         <is>
-          <t>https://www.fehmarn24.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.az-online.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
@@ -4393,7 +4393,7 @@
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>fnp.de (Frankfurter Neue Presse)</t>
+          <t>fehmarn24.de</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
@@ -4416,7 +4416,11 @@
           <t>Johannes Feist</t>
         </is>
       </c>
-      <c r="G114" s="4" t="inlineStr"/>
+      <c r="G114" s="4" t="inlineStr">
+        <is>
+          <t>https://www.fehmarn24.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="n">
@@ -4424,7 +4428,7 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>Fuldaer Zeitung.de</t>
+          <t>fnp.de (Frankfurter Neue Presse)</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
@@ -4447,11 +4451,7 @@
           <t>Johannes Feist</t>
         </is>
       </c>
-      <c r="G115" s="4" t="inlineStr">
-        <is>
-          <t>https://www.fuldaerzeitung.de/politik-und-wirtschaft/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
-        </is>
-      </c>
+      <c r="G115" s="4" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="3" t="n">
@@ -4459,7 +4459,7 @@
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>Gießener Allgemeine Online</t>
+          <t>Fuldaer Zeitung.de</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
@@ -4484,7 +4484,7 @@
       </c>
       <c r="G116" s="4" t="inlineStr">
         <is>
-          <t>https://www.giessener-allgemeine.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.fuldaerzeitung.de/politik-und-wirtschaft/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>Wetterauer Zeitung Online</t>
+          <t>Gießener Allgemeine Online</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="G117" s="4" t="inlineStr">
         <is>
-          <t>https://www.wetterauer-zeitung.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.giessener-allgemeine.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
@@ -4529,7 +4529,7 @@
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>giessener-anzeiger.de</t>
+          <t>Wetterauer Zeitung Online</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
@@ -4554,7 +4554,7 @@
       </c>
       <c r="G118" s="4" t="inlineStr">
         <is>
-          <t>https://www.giessener-anzeiger.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.wetterauer-zeitung.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
@@ -4564,7 +4564,7 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>kreis-anzeiger.de (Zentralhessen)</t>
+          <t>giessener-anzeiger.de</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
@@ -4589,7 +4589,7 @@
       </c>
       <c r="G119" s="4" t="inlineStr">
         <is>
-          <t>https://www.kreis-anzeiger.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.giessener-anzeiger.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
@@ -4599,7 +4599,7 @@
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>usinger-anzeiger.de</t>
+          <t>kreis-anzeiger.de (Zentralhessen)</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
@@ -4624,7 +4624,7 @@
       </c>
       <c r="G120" s="4" t="inlineStr">
         <is>
-          <t>https://www.usinger-anzeiger.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.kreis-anzeiger.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
@@ -4634,7 +4634,7 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>hanauer.de (Hanauer Anzeiger)</t>
+          <t>usinger-anzeiger.de</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
@@ -4659,7 +4659,7 @@
       </c>
       <c r="G121" s="4" t="inlineStr">
         <is>
-          <t>https://www.hanauer.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.usinger-anzeiger.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>echo24.de</t>
+          <t>hanauer.de (Hanauer Anzeiger)</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
@@ -4694,7 +4694,7 @@
       </c>
       <c r="G122" s="4" t="inlineStr">
         <is>
-          <t>https://www.echo24.de/welt/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.hanauer.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
@@ -4704,7 +4704,7 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>hersfelder-zeitung.de</t>
+          <t>echo24.de</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
@@ -4729,7 +4729,7 @@
       </c>
       <c r="G123" s="4" t="inlineStr">
         <is>
-          <t>https://www.hersfelder-zeitung.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.echo24.de/welt/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
@@ -4739,7 +4739,7 @@
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>HNA online</t>
+          <t>hersfelder-zeitung.de</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
@@ -4764,7 +4764,7 @@
       </c>
       <c r="G124" s="4" t="inlineStr">
         <is>
-          <t>https://www.hna.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.hersfelder-zeitung.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
@@ -4774,7 +4774,7 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>kreisbote.de</t>
+          <t>HNA online</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="G125" s="4" t="inlineStr">
         <is>
-          <t>https://www.kreisbote.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.hna.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
@@ -4809,7 +4809,7 @@
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>kreiszeitung.de (Syke)</t>
+          <t>kreisbote.de</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr">
@@ -4834,7 +4834,7 @@
       </c>
       <c r="G126" s="4" t="inlineStr">
         <is>
-          <t>https://www.kreiszeitung.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.kreisbote.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>Leinetal24.de</t>
+          <t>kreiszeitung.de (Syke)</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="G127" s="4" t="inlineStr">
         <is>
-          <t>https://www.leinetal24.de/welt/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.kreiszeitung.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
@@ -4879,7 +4879,7 @@
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>come-on.de (Märkischer Zeitungsverlag)</t>
+          <t>Leinetal24.de</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="G128" s="4" t="inlineStr">
         <is>
-          <t>https://www.come-on.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.leinetal24.de/welt/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>Merkur.de (Münchner Merkur)</t>
+          <t>come-on.de (Märkischer Zeitungsverlag)</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="G129" s="4" t="inlineStr">
         <is>
-          <t>https://www.merkur.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.come-on.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>OVB online (Oberbayerisches Volksblatt)</t>
+          <t>Merkur.de (Münchner Merkur)</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
@@ -4974,7 +4974,7 @@
       </c>
       <c r="G130" s="4" t="inlineStr">
         <is>
-          <t>https://www.ovb-online.de/weltspiegel/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.merkur.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
@@ -4984,7 +4984,7 @@
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>oberhessische-zeitung.de</t>
+          <t>OVB online (Oberbayerisches Volksblatt)</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
@@ -5009,7 +5009,7 @@
       </c>
       <c r="G131" s="4" t="inlineStr">
         <is>
-          <t>https://www.oberhessische-zeitung.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.ovb-online.de/weltspiegel/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>OFFENBACH-POST ONLINE</t>
+          <t>oberhessische-zeitung.de</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
@@ -5044,7 +5044,7 @@
       </c>
       <c r="G132" s="4" t="inlineStr">
         <is>
-          <t>https://www.op-online.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.oberhessische-zeitung.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
@@ -5054,7 +5054,7 @@
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>gmuender-tagespost.de</t>
+          <t>OFFENBACH-POST ONLINE</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
@@ -5079,7 +5079,7 @@
       </c>
       <c r="G133" s="4" t="inlineStr">
         <is>
-          <t>https://www.gmuender-tagespost.de/welt/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.op-online.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
@@ -5089,7 +5089,7 @@
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>schwaebische-post.de</t>
+          <t>gmuender-tagespost.de</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="G134" s="4" t="inlineStr">
         <is>
-          <t>https://www.schwaebische-post.de/welt/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.gmuender-tagespost.de/welt/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
@@ -5124,7 +5124,7 @@
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>tz-online.de</t>
+          <t>schwaebische-post.de</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
@@ -5149,7 +5149,7 @@
       </c>
       <c r="G135" s="4" t="inlineStr">
         <is>
-          <t>https://www.tz.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.schwaebische-post.de/welt/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>Waldeckische Landeszeitung Online</t>
+          <t>tz-online.de</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
@@ -5184,7 +5184,7 @@
       </c>
       <c r="G136" s="4" t="inlineStr">
         <is>
-          <t>https://www.wlz-online.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.tz.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
@@ -5194,7 +5194,7 @@
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>werra-rundschau.de</t>
+          <t>Waldeckische Landeszeitung Online</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="G137" s="4" t="inlineStr">
         <is>
-          <t>https://www.werra-rundschau.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.wlz-online.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
@@ -5229,7 +5229,7 @@
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>soester-anzeiger.de</t>
+          <t>werra-rundschau.de</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
@@ -5254,7 +5254,7 @@
       </c>
       <c r="G138" s="4" t="inlineStr">
         <is>
-          <t>https://www.soester-anzeiger.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.werra-rundschau.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>wa.de (Westfälischer Anzeiger)</t>
+          <t>soester-anzeiger.de</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
@@ -5289,40 +5289,75 @@
       </c>
       <c r="G139" s="4" t="inlineStr">
         <is>
-          <t>https://www.wa.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.soester-anzeiger.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="3" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B140" s="4" t="inlineStr">
+        <is>
+          <t>wa.de (Westfälischer Anzeiger)</t>
+        </is>
+      </c>
+      <c r="C140" s="4" t="inlineStr">
+        <is>
+          <t>Merz reist nach Brasilien: Deutschlands Klimapolitik bei COP30 auf dem Prüfstein</t>
+        </is>
+      </c>
+      <c r="D140" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E140" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F140" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G140" s="4" t="inlineStr">
+        <is>
+          <t>https://www.wa.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="3" t="n">
         <v>45848</v>
       </c>
-      <c r="B140" s="4" t="inlineStr">
+      <c r="B141" s="4" t="inlineStr">
         <is>
           <t>Handelszeitung</t>
         </is>
       </c>
-      <c r="C140" s="4" t="inlineStr">
+      <c r="C141" s="4" t="inlineStr">
         <is>
           <t>Zwischen ESG-Müdigkeit und Wirkungsanspruch</t>
         </is>
       </c>
-      <c r="D140" s="4" t="inlineStr">
+      <c r="D141" s="4" t="inlineStr">
         <is>
           <t>CH</t>
         </is>
       </c>
-      <c r="E140" s="4" t="inlineStr">
-        <is>
-          <t>Online</t>
-        </is>
-      </c>
-      <c r="F140" s="4" t="inlineStr">
-        <is>
-          <t>Johannes Feist</t>
-        </is>
-      </c>
-      <c r="G140" s="4" t="inlineStr">
+      <c r="E141" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F141" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G141" s="4" t="inlineStr">
         <is>
           <t>https://www.handelszeitung.ch/specials/nachhaltiges-investieren-2024/zwischen-esg-mudigkeit-und-wirkungsanspruch-841576</t>
         </is>
@@ -5363,7 +5398,7 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Source: Sheet '2026 Clippings' (A9:G140)</t>
+          <t>Source: Sheet '2026 Clippings' (A9:G141)</t>
         </is>
       </c>
     </row>
@@ -5381,7 +5416,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6">
@@ -5411,7 +5446,7 @@
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="9">
@@ -5470,10 +5505,10 @@
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>0.8712121212121212</v>
+        <v>0.8721804511278195</v>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
@@ -5494,7 +5529,7 @@
         <v>15</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>0.1136363636363636</v>
+        <v>0.112781954887218</v>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
@@ -5515,7 +5550,7 @@
         <v>2</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>0.01515151515151515</v>
+        <v>0.01503759398496241</v>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
@@ -5634,7 +5669,7 @@
         </is>
       </c>
       <c r="F24" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -5691,7 +5726,7 @@
         <v>5</v>
       </c>
       <c r="C31" s="11" t="n">
-        <v>0.03787878787878788</v>
+        <v>0.03759398496240601</v>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
@@ -5702,7 +5737,7 @@
         <v>1</v>
       </c>
       <c r="G31" s="11" t="n">
-        <v>0.007575757575757576</v>
+        <v>0.007518796992481203</v>
       </c>
     </row>
     <row r="32">
@@ -5715,7 +5750,7 @@
         <v>21</v>
       </c>
       <c r="C32" s="11" t="n">
-        <v>0.1590909090909091</v>
+        <v>0.1578947368421053</v>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
@@ -5726,7 +5761,7 @@
         <v>2</v>
       </c>
       <c r="G32" s="11" t="n">
-        <v>0.01515151515151515</v>
+        <v>0.01503759398496241</v>
       </c>
     </row>
     <row r="33">
@@ -5736,10 +5771,10 @@
         </is>
       </c>
       <c r="B33" s="8" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C33" s="11" t="n">
-        <v>0.7575757575757576</v>
+        <v>0.7593984962406015</v>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
@@ -5747,10 +5782,10 @@
         </is>
       </c>
       <c r="F33" s="8" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G33" s="11" t="n">
-        <v>0.8712121212121212</v>
+        <v>0.8721804511278195</v>
       </c>
     </row>
     <row r="34">
@@ -5763,7 +5798,7 @@
         <v>6</v>
       </c>
       <c r="C34" s="11" t="n">
-        <v>0.04545454545454546</v>
+        <v>0.04511278195488722</v>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
@@ -5774,7 +5809,7 @@
         <v>8</v>
       </c>
       <c r="G34" s="11" t="n">
-        <v>0.06060606060606061</v>
+        <v>0.06015037593984962</v>
       </c>
     </row>
     <row r="35">
@@ -5787,7 +5822,7 @@
         <v>1</v>
       </c>
       <c r="G35" s="11" t="n">
-        <v>0.007575757575757576</v>
+        <v>0.007518796992481203</v>
       </c>
     </row>
     <row r="36">
@@ -5800,7 +5835,7 @@
         <v>4</v>
       </c>
       <c r="G36" s="11" t="n">
-        <v>0.0303030303030303</v>
+        <v>0.03007518796992481</v>
       </c>
     </row>
     <row r="37">
@@ -5813,7 +5848,7 @@
         <v>1</v>
       </c>
       <c r="G37" s="11" t="n">
-        <v>0.007575757575757576</v>
+        <v>0.007518796992481203</v>
       </c>
     </row>
   </sheetData>

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46312.06450534537</v>
+        <v>46313.053637399</v>
       </c>
     </row>
     <row r="8">

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -694,7 +694,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G141"/>
+  <dimension ref="A1:G142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46313.053637399</v>
+        <v>46314.06149721704</v>
       </c>
     </row>
     <row r="8">
@@ -894,16 +894,16 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>46273</v>
+        <v>46275</v>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Private Banking Magazin</t>
+          <t>Börsen-Zeitung</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Private Credit in Zentralasien</t>
+          <t>Private Debt: Wenn Diversifikation nur auf dem Papier besteht</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -923,22 +923,22 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>https://www.private-banking-magazin.de/private-credit-zentralasien-lokale-unternehmenskredite/</t>
+          <t>https://www.boersen-zeitung.de/boersen-zeitung-spezial/private-debt-wenn-diversifikation-nur-auf-dem-papier-besteht</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>46256</v>
+        <v>46273</v>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>BondGuide</t>
+          <t>Private Banking Magazin</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Niedrigwasser zeigt die Geografie des Kreditrisikos</t>
+          <t>Private Credit in Zentralasien</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -958,27 +958,27 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>https://www.bondguide.de/topnews/niedrigwasser-zeigt-die-geografie-des-kreditrisikos/</t>
+          <t>https://www.private-banking-magazin.de/private-credit-zentralasien-lokale-unternehmenskredite/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>46251</v>
+        <v>46256</v>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Finanz und Wirtschaft</t>
+          <t>BondGuide</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Die Schweiz finanziert Wasserresilienz überall – nur nicht im Inland</t>
+          <t>Niedrigwasser zeigt die Geografie des Kreditrisikos</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -988,32 +988,32 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Louiza Savchenko</t>
+          <t>Johannes Feist</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>https://www.fuw.ch/wasserrisiko-was-die-schweiz-von-zentralasien-lernen-kann-152625611421</t>
+          <t>https://www.bondguide.de/topnews/niedrigwasser-zeigt-die-geografie-des-kreditrisikos/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>46247</v>
+        <v>46251</v>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Markt Einblicke</t>
+          <t>Finanz und Wirtschaft</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Mikrofinanzanleihen: Worauf es bei Kreditqualität und Struktur ankommt</t>
+          <t>Die Schweiz finanziert Wasserresilienz überall – nur nicht im Inland</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -1023,27 +1023,27 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist</t>
+          <t>Louiza Savchenko</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>https://markteinblicke.de/132318/2026/08/mikrofinanzanleihen-worauf-es-bei-kreditqualitaet-und-struktur-ankommt/</t>
+          <t>https://www.fuw.ch/wasserrisiko-was-die-schweiz-von-zentralasien-lernen-kann-152625611421</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>FUELS+LUBES+ENERGY</t>
+          <t>Markt Einblicke</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Der Ölpreis und die Kapitalmärkte</t>
+          <t>Mikrofinanzanleihen: Worauf es bei Kreditqualität und Struktur ankommt</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Print</t>
+          <t>Online</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -1061,30 +1061,34 @@
           <t>Johannes Feist</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr"/>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>https://markteinblicke.de/132318/2026/08/mikrofinanzanleihen-worauf-es-bei-kreditqualitaet-und-struktur-ankommt/</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>e-fundresearch</t>
+          <t>FUELS+LUBES+ENERGY</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Experten-Umfrage: Worüber im zweiten Halbjahr 2026 keiner redet (Teil 2/2)</t>
+          <t>Der Ölpreis und die Kapitalmärkte</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>DACH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Print</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -1092,34 +1096,30 @@
           <t>Johannes Feist</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr">
-        <is>
-          <t>https://e-fundresearch.com/managers/artikel/60333-experten-umfrage-worueber-im-zweiten-halbjahr-2026-keiner-redet-teil-22</t>
-        </is>
-      </c>
+      <c r="G18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>46241</v>
+        <v>46245</v>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>marktEINBLICKE</t>
+          <t>e-fundresearch</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Euro-Kupon, lokale Cashflows: Wo das Währungsrisiko wirklich liegt</t>
+          <t>Experten-Umfrage: Worüber im zweiten Halbjahr 2026 keiner redet (Teil 2/2)</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>DACH</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>E-Paper</t>
+          <t>Online</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -1129,17 +1129,17 @@
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>https://markteinblicke.de/wp-content/uploads/meg/mEGeldanlage_2026_15.pdf</t>
+          <t>https://e-fundresearch.com/managers/artikel/60333-experten-umfrage-worueber-im-zweiten-halbjahr-2026-keiner-redet-teil-22</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>46238</v>
+        <v>46241</v>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Markt Einblicke</t>
+          <t>marktEINBLICKE</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>E-Paper</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -1164,27 +1164,27 @@
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>https://markteinblicke.de/132045/2026/08/euro-kupon-lokale-cashflows-wo-das-waehrungsrisiko-wirklich-liegt/</t>
+          <t>https://markteinblicke.de/wp-content/uploads/meg/mEGeldanlage_2026_15.pdf</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>46234</v>
+        <v>46238</v>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Moneycab</t>
+          <t>Markt Einblicke</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist, CEO MK Global Kapital, im Interview</t>
+          <t>Euro-Kupon, lokale Cashflows: Wo das Währungsrisiko wirklich liegt</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>https://www.moneycab.com/interviews/ceo-interviews/johannes-feist-ceo-mk-global-kapital-im-interview/</t>
+          <t>https://markteinblicke.de/132045/2026/08/euro-kupon-lokale-cashflows-wo-das-waehrungsrisiko-wirklich-liegt/</t>
         </is>
       </c>
     </row>
@@ -1209,7 +1209,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>finanznachrichten.de</t>
+          <t>Moneycab</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -1219,7 +1219,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
@@ -1234,22 +1234,22 @@
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>https://www.finanznachrichten.de/nachrichten-2026-07/69177994-johannes-feist-ceo-mk-global-kapital-im-interview-095.htm</t>
+          <t>https://www.moneycab.com/interviews/ceo-interviews/johannes-feist-ceo-mk-global-kapital-im-interview/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>46231</v>
+        <v>46234</v>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>BondGuide</t>
+          <t>finanznachrichten.de</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Private Credit: Was Anleiheinvestoren hinter dem Kupon prüfen sollten</t>
+          <t>Johannes Feist, CEO MK Global Kapital, im Interview</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>https://www.bondguide.de/topnews/private-credit-was-anleiheinvestoren-hinter-dem-kupon-pruefen-sollten/</t>
+          <t>https://www.finanznachrichten.de/nachrichten-2026-07/69177994-johannes-feist-ceo-mk-global-kapital-im-interview-095.htm</t>
         </is>
       </c>
     </row>
@@ -1279,12 +1279,12 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>ExportManager OST</t>
+          <t>BondGuide</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Wenn der klassische Bankkredit schlecht greift</t>
+          <t>Private Credit: Was Anleiheinvestoren hinter dem Kupon prüfen sollten</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>Print &amp; Digital</t>
+          <t>Online</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -1302,7 +1302,11 @@
           <t>Johannes Feist</t>
         </is>
       </c>
-      <c r="G24" s="4" t="inlineStr"/>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bondguide.de/topnews/private-credit-was-anleiheinvestoren-hinter-dem-kupon-pruefen-sollten/</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
@@ -1310,12 +1314,12 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>finanznachrichten.de</t>
+          <t>ExportManager OST</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Private Credit: Was Anleiheinvestoren hinter dem Kupon prüfen sollten</t>
+          <t>Wenn der klassische Bankkredit schlecht greift</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -1325,7 +1329,7 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Print &amp; Digital</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -1333,29 +1337,25 @@
           <t>Johannes Feist</t>
         </is>
       </c>
-      <c r="G25" s="4" t="inlineStr">
-        <is>
-          <t>https://www.finanznachrichten.de/nachrichten-2026-07/69141450-private-credit-was-anleiheinvestoren-hinter-dem-kupon-pruefen-sollten-144.htm</t>
-        </is>
-      </c>
+      <c r="G25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>46205</v>
+        <v>46231</v>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Finews</t>
+          <t>finanznachrichten.de</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Ferienlektüre: Was Finanzprofis diesen Sommer lesen</t>
+          <t>Private Credit: Was Anleiheinvestoren hinter dem Kupon prüfen sollten</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
@@ -1365,32 +1365,32 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Louiza Savchenko</t>
+          <t>Johannes Feist</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>https://www.finews.ch/themen/leben-karriere/72628-sommer-buchempfehlungen-2026-von-persoenlichkeiten-aus-der-finanzbranche-roman-sommerlektuere-lesen-ferien-andreas-feller-thomas-studhalter-karsten-dirk-steffens-anna-bretschneider-finanzplatz-schweiz</t>
+          <t>https://www.finanznachrichten.de/nachrichten-2026-07/69141450-private-credit-was-anleiheinvestoren-hinter-dem-kupon-pruefen-sollten-144.htm</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>46198</v>
+        <v>46205</v>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>background.tagesspiegel</t>
+          <t>Finews</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Digitale Kreditvergabe : Kreditzugang ist mehr als ein Score</t>
+          <t>Ferienlektüre: Was Finanzprofis diesen Sommer lesen</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -1405,27 +1405,27 @@
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>https://background.tagesspiegel.de/finance/briefing/kreditzugang-ist-mehr-als-ein-score</t>
+          <t>https://www.finews.ch/themen/leben-karriere/72628-sommer-buchempfehlungen-2026-von-persoenlichkeiten-aus-der-finanzbranche-roman-sommerlektuere-lesen-ferien-andreas-feller-thomas-studhalter-karsten-dirk-steffens-anna-bretschneider-finanzplatz-schweiz</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Finanz und Wirtschaft</t>
+          <t>background.tagesspiegel</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Rendite mit gutem Gewissen</t>
+          <t>Digitale Kreditvergabe : Kreditzugang ist mehr als ein Score</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
@@ -1435,28 +1435,32 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist</t>
-        </is>
-      </c>
-      <c r="G28" s="4" t="inlineStr"/>
+          <t>Louiza Savchenko</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>https://background.tagesspiegel.de/finance/briefing/kreditzugang-ist-mehr-als-ein-score</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>46195</v>
+        <v>46197</v>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>fem.capital</t>
+          <t>Finanz und Wirtschaft</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Warum Unternehmerinnen eher am Kapital als am Markt scheitern</t>
+          <t>Rendite mit gutem Gewissen</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
@@ -1466,23 +1470,23 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>Louiza Savchenko</t>
+          <t>Johannes Feist</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Intelligent Investors</t>
+          <t>fem.capital</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Kreditqualität lässt sich nicht aus der Distanz steuern</t>
+          <t>Warum Unternehmerinnen eher am Kapital als am Markt scheitern</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -1492,38 +1496,38 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>Print</t>
+          <t>Online</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist</t>
+          <t>Louiza Savchenko</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>46183</v>
+        <v>46188</v>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Finews</t>
+          <t>Intelligent Investors</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist: «Einer meiner unerfüllter Träume ist der Sportfliegerschein»</t>
+          <t>Kreditqualität lässt sich nicht aus der Distanz steuern</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Print</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -1531,34 +1535,30 @@
           <t>Johannes Feist</t>
         </is>
       </c>
-      <c r="G31" s="4" t="inlineStr">
-        <is>
-          <t>https://www.finews.ch/themen/high-end/72456-johannes-feist-einer-meiner-unerfuellter-traeume-ist-der-sportfliegerschein-ceo-global-kapital</t>
-        </is>
-      </c>
+      <c r="G31" s="4" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>46176</v>
+        <v>46183</v>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>BOND MAGAZINE</t>
+          <t>Finews</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Der neue Stresstest für Schwellenländer: Warum Öl, Zinsen und Währungen nur der Anfang sind und letztlich die Finanzierungsstruktur entscheidet</t>
+          <t>Johannes Feist: «Einer meiner unerfüllter Träume ist der Sportfliegerschein»</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>Print</t>
+          <t>Online</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -1568,32 +1568,32 @@
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>https://www.fixed-income.org/fileadmin/pdf/BOND_MAGAZINE_239.pdf</t>
+          <t>https://www.finews.ch/themen/high-end/72456-johannes-feist-einer-meiner-unerfuellter-traeume-ist-der-sportfliegerschein-ceo-global-kapital</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>46174</v>
+        <v>46176</v>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>FONDS exklusiv Österreich</t>
+          <t>BOND MAGAZINE</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Schwellenländer: Worauf es jetzt ankommt</t>
+          <t>Der neue Stresstest für Schwellenländer: Warum Öl, Zinsen und Währungen nur der Anfang sind und letztlich die Finanzierungsstruktur entscheidet</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Print</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -1603,7 +1603,7 @@
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>https://www.fondsexklusiv.at/schwellenlaender-worauf-es-jetzt-ankommt/</t>
+          <t>https://www.fixed-income.org/fileadmin/pdf/BOND_MAGAZINE_239.pdf</t>
         </is>
       </c>
     </row>
@@ -1613,17 +1613,17 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Intelligent Investors</t>
+          <t>FONDS exklusiv Österreich</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Die neue Verwundbarkeit der Schwellenländer</t>
+          <t>Schwellenländer: Worauf es jetzt ankommt</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>https://intelligent-investors.de/die-neue-verwundbarkeit-der-schwellenlaender/</t>
+          <t>https://www.fondsexklusiv.at/schwellenlaender-worauf-es-jetzt-ankommt/</t>
         </is>
       </c>
     </row>
@@ -1648,17 +1648,17 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Institutional Money</t>
+          <t>Intelligent Investors</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Finanzierungsstruktur: Der neue Stresstest für Schwellenländer</t>
+          <t>Die neue Verwundbarkeit der Schwellenländer</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>DACH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>https://www.institutional-money.com/news/maerkte/headline/finanzierungsstruktur-der-neue-stresstest-fuer-schwellenlaender-251058</t>
+          <t>https://intelligent-investors.de/die-neue-verwundbarkeit-der-schwellenlaender/</t>
         </is>
       </c>
     </row>
@@ -1683,12 +1683,12 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Neo Market Ways</t>
+          <t>Institutional Money</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>From Microfinance to Mobility: How Capital is Driving Growth Across Eastern Europe</t>
+          <t>Finanzierungsstruktur: Der neue Stresstest für Schwellenländer</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -1708,27 +1708,27 @@
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>https://neomarketways.com/from-microfinance-to-mobility-how-capital-is-driving-growth-across-eastern-europe/</t>
+          <t>https://www.institutional-money.com/news/maerkte/headline/finanzierungsstruktur-der-neue-stresstest-fuer-schwellenlaender-251058</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>NEX24 News</t>
+          <t>Neo Market Ways</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>Iran-Krieg: Der neue Stresstest für Schwellenländer</t>
+          <t>From Microfinance to Mobility: How Capital is Driving Growth Across Eastern Europe</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>DACH</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
@@ -1743,27 +1743,27 @@
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>https://nex24.news/2026/05/iran-krieg-der-neue-stresstest-fuer-schwellenlaender/</t>
+          <t>https://neomarketways.com/from-microfinance-to-mobility-how-capital-is-driving-growth-across-eastern-europe/</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>GELD-Magazin</t>
+          <t>NEX24 News</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Stresstest für Schwellenländer</t>
+          <t>Iran-Krieg: Der neue Stresstest für Schwellenländer</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
@@ -1778,27 +1778,27 @@
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>https://www.geld-magazin.at/stresstest-fuer-schwellenlaender/</t>
+          <t>https://nex24.news/2026/05/iran-krieg-der-neue-stresstest-fuer-schwellenlaender/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Markt Einblicke</t>
+          <t>GELD-Magazin</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Warum der Blick auf den Ölpreis nicht reicht</t>
+          <t>Stresstest für Schwellenländer</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
@@ -1813,27 +1813,27 @@
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>https://markteinblicke.de/130696/2026/05/warum-der-blick-auf-den-oelpreis-nicht-reicht/</t>
+          <t>https://www.geld-magazin.at/stresstest-fuer-schwellenlaender/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>46164</v>
+        <v>46169</v>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Moneycab</t>
+          <t>Markt Einblicke</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Nicht die Grösse des Kredits entscheidet, sondern seine Wirkung</t>
+          <t>Warum der Blick auf den Ölpreis nicht reicht</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>https://www.moneycab.com/dossiers/nicht-die-groesse-des-kredits-entscheidet-sondern-seine-wirkung/</t>
+          <t>https://markteinblicke.de/130696/2026/05/warum-der-blick-auf-den-oelpreis-nicht-reicht/</t>
         </is>
       </c>
     </row>
@@ -1858,7 +1858,7 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>finanznachrichten.de</t>
+          <t>Moneycab</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -1868,7 +1868,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
@@ -1883,22 +1883,22 @@
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>https://www.finanznachrichten.de/nachrichten-2026-05/68568705-nicht-die-groesse-des-kredits-entscheidet-sondern-seine-wirkung-095.htm</t>
+          <t>https://www.moneycab.com/dossiers/nicht-die-groesse-des-kredits-entscheidet-sondern-seine-wirkung/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>46150</v>
+        <v>46164</v>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>Finanz- und Wirtschaftsspiegel</t>
+          <t>finanznachrichten.de</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>Entwicklungsfinanzierung mit Mikrokrediten</t>
+          <t>Nicht die Grösse des Kredits entscheidet, sondern seine Wirkung</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>Digital newsletter</t>
+          <t>Online</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
@@ -1916,20 +1916,24 @@
           <t>Johannes Feist</t>
         </is>
       </c>
-      <c r="G42" s="4" t="inlineStr"/>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>https://www.finanznachrichten.de/nachrichten-2026-05/68568705-nicht-die-groesse-des-kredits-entscheidet-sondern-seine-wirkung-095.htm</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Markt Einblicke</t>
+          <t>Finanz- und Wirtschaftsspiegel</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Mikrofinanz-Anleihen: Ein wachsender Markt</t>
+          <t>Entwicklungsfinanzierung mit Mikrokrediten</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1939,7 +1943,7 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Digital newsletter</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
@@ -1947,24 +1951,20 @@
           <t>Johannes Feist</t>
         </is>
       </c>
-      <c r="G43" s="4" t="inlineStr">
-        <is>
-          <t>https://markteinblicke.de/130263/2026/05/mikrofinanz-anleihen-ein-wachsender-markt/</t>
-        </is>
-      </c>
+      <c r="G43" s="4" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>46125</v>
+        <v>46149</v>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>cash-online.de</t>
+          <t>Markt Einblicke</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Tokenisierte Anleihen: Was sich für Anleger ändert und was nicht</t>
+          <t>Mikrofinanz-Anleihen: Ein wachsender Markt</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1979,27 +1979,27 @@
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>Louiza Savchenko</t>
+          <t>Johannes Feist</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>https://www.cash-online.de/a/tokenisierte-anleihen-was-sich-fuer-anleger-aendert-und-was-nicht-715994/</t>
+          <t>https://markteinblicke.de/130263/2026/05/mikrofinanz-anleihen-ein-wachsender-markt/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>46109</v>
+        <v>46125</v>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>Wirtschaftsvision</t>
+          <t>cash-online.de</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Der Trugschluss der sicheren Häfen</t>
+          <t>Tokenisierte Anleihen: Was sich für Anleger ändert und was nicht</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -2014,27 +2014,27 @@
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist</t>
+          <t>Louiza Savchenko</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>https://wirtschaftsvision.de/der-trugschluss-der-sicheren-haefen/</t>
+          <t>https://www.cash-online.de/a/tokenisierte-anleihen-was-sich-fuer-anleger-aendert-und-was-nicht-715994/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Börsen-Zeitung</t>
+          <t>Wirtschaftsvision</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Wasserknappheit als Kreditrisiko</t>
+          <t>Der Trugschluss der sicheren Häfen</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>Print &amp; Online</t>
+          <t>Online</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
@@ -2054,22 +2054,22 @@
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>https://www.boersen-zeitung.de/sonderbeilagen/wasserknappheit-als-kreditrisiko</t>
+          <t>https://wirtschaftsvision.de/der-trugschluss-der-sicheren-haefen/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>46105</v>
+        <v>46108</v>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Frankfurter Allgemeine Zeitung</t>
+          <t>Börsen-Zeitung</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Sorgen um Privatkredite: Finanzkrise oder silberne Aera?</t>
+          <t>Wasserknappheit als Kreditrisiko</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Print &amp; Online</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
@@ -2089,7 +2089,7 @@
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>https://www.faz.net/pro/meine-finanzen/zinsen/sorgen-um-privatkredite-finanzkrise-oder-silberne-aera-110376123.html</t>
+          <t>https://www.boersen-zeitung.de/sonderbeilagen/wasserknappheit-als-kreditrisiko</t>
         </is>
       </c>
     </row>
@@ -2099,12 +2099,12 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>DAS INVESTMENT</t>
+          <t>Frankfurter Allgemeine Zeitung</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Private Credit unter Druck: Wenn das Geld nicht mehr herauskommt</t>
+          <t>Sorgen um Privatkredite: Finanzkrise oder silberne Aera?</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>https://www.dasinvestment.com/private-credit-unter-druck-wenn-das-geld-nicht-mehr-herauskommt/</t>
+          <t>https://www.faz.net/pro/meine-finanzen/zinsen/sorgen-um-privatkredite-finanzkrise-oder-silberne-aera-110376123.html</t>
         </is>
       </c>
     </row>
@@ -2134,17 +2134,17 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>FONDS exklusiv Oesterreich</t>
+          <t>DAS INVESTMENT</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Private Credit-Debatte entfacht</t>
+          <t>Private Credit unter Druck: Wenn das Geld nicht mehr herauskommt</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
@@ -2159,22 +2159,22 @@
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>https://www.fondsexklusiv.at/private-credit-debatte-entfacht/</t>
+          <t>https://www.dasinvestment.com/private-credit-unter-druck-wenn-das-geld-nicht-mehr-herauskommt/</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
-        <v>46103</v>
+        <v>46105</v>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Der Standard</t>
+          <t>FONDS exklusiv Oesterreich</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>Pakistan spart Milliarden an fossilen Importen: Wie hat es das gemacht?</t>
+          <t>Private Credit-Debatte entfacht</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
@@ -2194,27 +2194,27 @@
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>https://www.derstandard.de/story/3000000313347/pakistan-spart-milliarden-an-fossilen-importen-wie-hat-es-das-gemacht</t>
+          <t>https://www.fondsexklusiv.at/private-credit-debatte-entfacht/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
-        <v>46101</v>
+        <v>46103</v>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Finews</t>
+          <t>Der Standard</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Tokenisierung: Louzia Savchenko ueber Innovation und MK Global Kapital</t>
+          <t>Pakistan spart Milliarden an fossilen Importen: Wie hat es das gemacht?</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>Louiza Savchenko</t>
+          <t>Johannes Feist</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>https://www.finews.ch/news/finanzplatz/71578-finews-first-tokenisierung-louzia-savchenko-finanzplatz-schweiz-innovation-mk-global-kapital</t>
+          <t>https://www.derstandard.de/story/3000000313347/pakistan-spart-milliarden-an-fossilen-importen-wie-hat-es-das-gemacht</t>
         </is>
       </c>
     </row>
@@ -2239,17 +2239,17 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>BondGuide</t>
+          <t>Finews</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>Private Credit ist nicht gleich Private Credit: wo die Risiken wirklich liegen</t>
+          <t>Tokenisierung: Louzia Savchenko ueber Innovation und MK Global Kapital</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist</t>
+          <t>Louiza Savchenko</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>https://www.bondguide.de/topnews/private-credit-ist-nicht-gleich-private-credit-wo-die-risiken-wirklich-liegen/</t>
+          <t>https://www.finews.ch/news/finanzplatz/71578-finews-first-tokenisierung-louzia-savchenko-finanzplatz-schweiz-innovation-mk-global-kapital</t>
         </is>
       </c>
     </row>
@@ -2274,17 +2274,17 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Swiss Finance AI</t>
+          <t>BondGuide</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Warum tokenisierte Anleihen mehr sind als ein Trend</t>
+          <t>Private Credit ist nicht gleich Private Credit: wo die Risiken wirklich liegen</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
@@ -2294,27 +2294,27 @@
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>Louiza Savchenko</t>
+          <t>Johannes Feist</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>https://www.swissfinanceai.ch/blog/swiss-finance/warum-tokenisierte-anleihen-mehr-sind-als-ein-trend</t>
+          <t>https://www.bondguide.de/topnews/private-credit-ist-nicht-gleich-private-credit-wo-die-risiken-wirklich-liegen/</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Moneycab</t>
+          <t>Swiss Finance AI</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>Nicht nur Öl: Wo der Iran-Konflikt Emerging Markets wirklich trifft</t>
+          <t>Warum tokenisierte Anleihen mehr sind als ein Trend</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -2329,12 +2329,12 @@
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist</t>
+          <t>Louiza Savchenko</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>https://www.moneycab.com/finanz/nicht-nur-oel-wo-der-iran-konflikt-emerging-markets-wirklich-trifft/</t>
+          <t>https://www.swissfinanceai.ch/blog/swiss-finance/warum-tokenisierte-anleihen-mehr-sind-als-ein-trend</t>
         </is>
       </c>
     </row>
@@ -2344,17 +2344,17 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Institutional Money</t>
+          <t>Moneycab</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>Was der Iran-Schock fuer Emerging Markets veraendert</t>
+          <t>Nicht nur Öl: Wo der Iran-Konflikt Emerging Markets wirklich trifft</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
@@ -2369,7 +2369,7 @@
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>https://www.institutional-money.com/news/maerkte/headline/was-der-iran-schock-fuer-emerging-markets-veraendert-249420</t>
+          <t>https://www.moneycab.com/finanz/nicht-nur-oel-wo-der-iran-konflikt-emerging-markets-wirklich-trifft/</t>
         </is>
       </c>
     </row>
@@ -2379,7 +2379,7 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>fixed-income.org</t>
+          <t>Institutional Money</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>https://www.fixed-income.org/investment/was-der-iran-schock-fuer-emerging-markets-veraendert.html</t>
+          <t>https://www.institutional-money.com/news/maerkte/headline/was-der-iran-schock-fuer-emerging-markets-veraendert-249420</t>
         </is>
       </c>
     </row>
@@ -2414,12 +2414,12 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>finanznachrichten.de</t>
+          <t>fixed-income.org</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>Nicht nur Öl: Wo der Iran-Konflikt Emerging Markets wirklich trifft</t>
+          <t>Was der Iran-Schock fuer Emerging Markets veraendert</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -2439,13 +2439,13 @@
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>https://www.finanznachrichten.de/nachrichten-2026-03/67987291-nicht-nur-oel-wo-der-iran-konflikt-emerging-markets-wirklich-trifft-095.htm</t>
+          <t>https://www.fixed-income.org/investment/was-der-iran-schock-fuer-emerging-markets-veraendert.html</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
-        <v>46098</v>
+        <v>46100</v>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>Private Credit ist nicht gleich Private Credit: Wo die Risiken wirklich liegen</t>
+          <t>Nicht nur Öl: Wo der Iran-Konflikt Emerging Markets wirklich trifft</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>https://www.finanznachrichten.de/nachrichten-2026-03/67998176-private-credit-ist-nicht-gleich-private-credit-wo-die-risiken-wirklich-liegen-144.htm</t>
+          <t>https://www.finanznachrichten.de/nachrichten-2026-03/67987291-nicht-nur-oel-wo-der-iran-konflikt-emerging-markets-wirklich-trifft-095.htm</t>
         </is>
       </c>
     </row>
@@ -2484,12 +2484,12 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>cash-online.de</t>
+          <t>finanznachrichten.de</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Gastkommentar: Der blinde Fleck der Private-Credit-Debatte</t>
+          <t>Private Credit ist nicht gleich Private Credit: Wo die Risiken wirklich liegen</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>https://www.cash-online.de/a/gastkommentar-der-blinde-fleck-der-private-credit-debatte-713724/</t>
+          <t>https://www.finanznachrichten.de/nachrichten-2026-03/67998176-private-credit-ist-nicht-gleich-private-credit-wo-die-risiken-wirklich-liegen-144.htm</t>
         </is>
       </c>
     </row>
@@ -2519,12 +2519,12 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>BOND MAGAZINE</t>
+          <t>cash-online.de</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Tokenisierte Anleihen: Effizienz, Vertrauen und Marktentwicklung</t>
+          <t>Gastkommentar: Der blinde Fleck der Private-Credit-Debatte</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -2534,28 +2534,32 @@
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>Print</t>
+          <t>Online</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>Louiza Savchenko</t>
-        </is>
-      </c>
-      <c r="G60" s="4" t="inlineStr"/>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="inlineStr">
+        <is>
+          <t>https://www.cash-online.de/a/gastkommentar-der-blinde-fleck-der-private-credit-debatte-713724/</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>FONDS exklusiv</t>
+          <t>BOND MAGAZINE</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Private Credit-Debatte entfacht</t>
+          <t>Tokenisierte Anleihen: Effizienz, Vertrauen und Marktentwicklung</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -2565,19 +2569,15 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Print</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist</t>
-        </is>
-      </c>
-      <c r="G61" s="4" t="inlineStr">
-        <is>
-          <t>https://www.fondsexklusiv.de/private-credit-debatte-entfacht/</t>
-        </is>
-      </c>
+          <t>Louiza Savchenko</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Kreditwesen (Verlagsgruppe Knapp-Richardi)</t>
+          <t>FONDS exklusiv</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Mikrofinanz als Anlageklasse</t>
+          <t>Private Credit-Debatte entfacht</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>Print &amp; Online</t>
+          <t>Online</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>https://www.kreditwesen.de/kreditwesen/themenschwerpunkte/aufsaetze/mikrofinanz-anlageklasse-id107511.html</t>
+          <t>https://www.fondsexklusiv.de/private-credit-debatte-entfacht/</t>
         </is>
       </c>
     </row>
@@ -2620,22 +2620,22 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Payoff</t>
+          <t>Kreditwesen (Verlagsgruppe Knapp-Richardi)</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Der blinde Fleck der Private-Credit-Debatte</t>
+          <t>Mikrofinanz als Anlageklasse</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Print &amp; Online</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
@@ -2645,17 +2645,17 @@
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>https://www.payoff.ch/news/der-blinde-fleck-der-private-credit-debatte</t>
+          <t>https://www.kreditwesen.de/kreditwesen/themenschwerpunkte/aufsaetze/mikrofinanz-anlageklasse-id107511.html</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>investrends.ch</t>
+          <t>Payoff</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>https://investrends.ch/aktuell/investments/der-blinde-fleck-der-private-credit-debatte/</t>
+          <t>https://www.payoff.ch/news/der-blinde-fleck-der-private-credit-debatte</t>
         </is>
       </c>
     </row>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>Private Markets 360</t>
+          <t>investrends.ch</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
@@ -2715,22 +2715,22 @@
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>https://privatemarkets360.com/artikel/58516-der-blinde-fleck-der-private-credit-debatte</t>
+          <t>https://investrends.ch/aktuell/investments/der-blinde-fleck-der-private-credit-debatte/</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Finanzen100.de</t>
+          <t>Private Markets 360</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>Marktkommentar: Der Trugschluss der sicheren Häfen</t>
+          <t>Der blinde Fleck der Private-Credit-Debatte</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>https://www.finanzen100.de/premium/bernecker-boersenkompass/marktkommentar-der-trugschluss-der-sicheren-haefen_H1356104965_6799449/</t>
+          <t>https://privatemarkets360.com/artikel/58516-der-blinde-fleck-der-private-credit-debatte</t>
         </is>
       </c>
     </row>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Intelligent Investors</t>
+          <t>Finanzen100.de</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Der blinde Fleck der Private-Credit-Debatte</t>
+          <t>Marktkommentar: Der Trugschluss der sicheren Häfen</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -2785,22 +2785,22 @@
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>https://intelligent-investors.de/der-blinde-fleck-der-private-credit-debatte/</t>
+          <t>https://www.finanzen100.de/premium/bernecker-boersenkompass/marktkommentar-der-trugschluss-der-sicheren-haefen_H1356104965_6799449/</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="n">
-        <v>46085</v>
+        <v>46093</v>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>markteinblicke.de</t>
+          <t>Intelligent Investors</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>Tokenisierte Anleihen: Mehr Governance erforderlich</t>
+          <t>Der blinde Fleck der Private-Credit-Debatte</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>Louiza Savchenko</t>
+          <t>Johannes Feist</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>https://markteinblicke.de/128943/2026/03/tokenisierte-anleihen-mehr-governance-erforderlich/</t>
+          <t>https://intelligent-investors.de/der-blinde-fleck-der-private-credit-debatte/</t>
         </is>
       </c>
     </row>
@@ -2830,12 +2830,12 @@
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>gruenderkueche.de</t>
+          <t>markteinblicke.de</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>Weltfrauentag: Unternehmerinnen fehlt weiterhin der Zugang zu Kapital</t>
+          <t>Tokenisierte Anleihen: Mehr Governance erforderlich</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -2855,7 +2855,7 @@
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>https://www.gruenderkueche.de/news/finanzen-news/weltfrauentag-unternehmerinnen-fehlt-weiterhin-der-zugang-zu-kapital/</t>
+          <t>https://markteinblicke.de/128943/2026/03/tokenisierte-anleihen-mehr-governance-erforderlich/</t>
         </is>
       </c>
     </row>
@@ -2865,12 +2865,12 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>Table.Media</t>
+          <t>gruenderkueche.de</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>Gleichstellung: Unternehmerinnen fehlt weltweit der Zugang zu Kapital</t>
+          <t>Weltfrauentag: Unternehmerinnen fehlt weiterhin der Zugang zu Kapital</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -2890,22 +2890,22 @@
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>https://table.media/esg/news/gleichstellung-unternehmerinnen-fehlt-weltweit-der-zugang-zu-kapital</t>
+          <t>https://www.gruenderkueche.de/news/finanzen-news/weltfrauentag-unternehmerinnen-fehlt-weiterhin-der-zugang-zu-kapital/</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>dfpa.info</t>
+          <t>Table.Media</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>Unternehmerinnen fehlt weltweit der Zugang zu Kapital</t>
+          <t>Gleichstellung: Unternehmerinnen fehlt weltweit der Zugang zu Kapital</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -2925,17 +2925,17 @@
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>https://www.dfpa.info/maerkte-studien-news/unternehmerinnen-fehlt-weltweit-der-zugang-zu-kapital/</t>
+          <t>https://table.media/esg/news/gleichstellung-unternehmerinnen-fehlt-weltweit-der-zugang-zu-kapital</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>altii.de</t>
+          <t>dfpa.info</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
@@ -2960,7 +2960,7 @@
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
-          <t>https://www.altii.de/edai-71550571-cb6c-4c09-93da-bd99b822c245/</t>
+          <t>https://www.dfpa.info/maerkte-studien-news/unternehmerinnen-fehlt-weltweit-der-zugang-zu-kapital/</t>
         </is>
       </c>
     </row>
@@ -2970,12 +2970,12 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>dapd.de</t>
+          <t>altii.de</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>Der Trugschluss der sicheren Häfen</t>
+          <t>Unternehmerinnen fehlt weltweit der Zugang zu Kapital</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
@@ -2990,27 +2990,27 @@
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist</t>
+          <t>Louiza Savchenko</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>https://www.dapd.de/der-trugschluss-der-sicheren-haefen/</t>
+          <t>https://www.altii.de/edai-71550571-cb6c-4c09-93da-bd99b822c245/</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="n">
-        <v>46078</v>
+        <v>46083</v>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>dfpa.info</t>
+          <t>dapd.de</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>Mikrofinanz: Besonderheit Anleihen mit festem Zins</t>
+          <t>Der Trugschluss der sicheren Häfen</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -3030,13 +3030,13 @@
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>https://www.dfpa.info/interview/mikrofinanz-besonderheit-anleihen-mit-festem-zins.html</t>
+          <t>https://www.dapd.de/der-trugschluss-der-sicheren-haefen/</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>Wenn Geschäftsbanken passen, helfen Mikrofinanzfonds</t>
+          <t>Mikrofinanz: Besonderheit Anleihen mit festem Zins</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -3065,7 +3065,7 @@
       </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
-          <t>https://www.dfpa.info/top-story/wenn-geschaeftsbanken-passen-helfen-mikrofinanzfonds.html</t>
+          <t>https://www.dfpa.info/interview/mikrofinanz-besonderheit-anleihen-mit-festem-zins.html</t>
         </is>
       </c>
     </row>
@@ -3075,12 +3075,12 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
-          <t>DFPA</t>
+          <t>dfpa.info</t>
         </is>
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>Die neue EXXECNEWS ist erschienen</t>
+          <t>Wenn Geschäftsbanken passen, helfen Mikrofinanzfonds</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -3100,22 +3100,22 @@
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
-          <t>https://www.dfpa.info/pressedigest-news/die-neue-exxecnews-ist-erschienen-78/</t>
+          <t>https://www.dfpa.info/top-story/wenn-geschaeftsbanken-passen-helfen-mikrofinanzfonds.html</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>exxecnews.org</t>
+          <t>DFPA</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>Teil I: Wenn Geschäftsbanken passen, helfen Mikrofinanzfonds</t>
+          <t>Die neue EXXECNEWS ist erschienen</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -3125,7 +3125,7 @@
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>Print &amp; Online</t>
+          <t>Online</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="G77" s="4" t="inlineStr">
         <is>
-          <t>https://exxecnews.org/wp-content/uploads/2026/02/Ausgabe-05_2026.pdf</t>
+          <t>https://www.dfpa.info/pressedigest-news/die-neue-exxecnews-ist-erschienen-78/</t>
         </is>
       </c>
     </row>
@@ -3145,12 +3145,12 @@
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>EXXECNEWS</t>
+          <t>exxecnews.org</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>Teil II: Mikrofinanz-Besonderheit – Anleihen mit festem Zins</t>
+          <t>Teil I: Wenn Geschäftsbanken passen, helfen Mikrofinanzfonds</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -3176,16 +3176,16 @@
     </row>
     <row r="79">
       <c r="A79" s="3" t="n">
-        <v>46069</v>
+        <v>46076</v>
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>boerse-social.com</t>
+          <t>EXXECNEWS</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>Börse-Inputs auf Spotify zu u.a. Do&amp;Co, Bawag, Nervigem und Mikrokrediten</t>
+          <t>Teil II: Mikrofinanz-Besonderheit – Anleihen mit festem Zins</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -3195,7 +3195,7 @@
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Print &amp; Online</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="G79" s="4" t="inlineStr">
         <is>
-          <t>https://boerse-social.com/2026/02/16/borse-inputs_auf_spotify_zu_ua_doco_bawag_nervigem_und_mikrokrediten_1</t>
+          <t>https://exxecnews.org/wp-content/uploads/2026/02/Ausgabe-05_2026.pdf</t>
         </is>
       </c>
     </row>
@@ -3215,12 +3215,12 @@
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>bondguide.de</t>
+          <t>boerse-social.com</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>Security Conference München 2026: öffentliche Mittel als Hebel nutzen</t>
+          <t>Börse-Inputs auf Spotify zu u.a. Do&amp;Co, Bawag, Nervigem und Mikrokrediten</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -3240,17 +3240,17 @@
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
-          <t>https://www.bondguide.de/topnews/security-conference-muenchen-2026-oeffentliche-mittel-als-hebel-nutzen/</t>
+          <t>https://boerse-social.com/2026/02/16/borse-inputs_auf_spotify_zu_ua_doco_bawag_nervigem_und_mikrokrediten_1</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="n">
-        <v>46067</v>
+        <v>46069</v>
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>finanznachrichten.de</t>
+          <t>bondguide.de</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
@@ -3275,7 +3275,7 @@
       </c>
       <c r="G81" s="4" t="inlineStr">
         <is>
-          <t>https://www.finanznachrichten.de/nachrichten-2026-02/67704129-security-conference-muenchen-2026-oeffentliche-mittel-als-hebel-nutzen-144.htm</t>
+          <t>https://www.bondguide.de/topnews/security-conference-muenchen-2026-oeffentliche-mittel-als-hebel-nutzen/</t>
         </is>
       </c>
     </row>
@@ -3285,12 +3285,12 @@
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>geldmeisterin.com</t>
+          <t>finanznachrichten.de</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
         <is>
-          <t>Mikrokredite gerade jetzt zur Risikostreuung</t>
+          <t>Security Conference München 2026: öffentliche Mittel als Hebel nutzen</t>
         </is>
       </c>
       <c r="D82" s="4" t="inlineStr">
@@ -3310,32 +3310,32 @@
       </c>
       <c r="G82" s="4" t="inlineStr">
         <is>
-          <t>https://www.geldmeisterin.com/index.php/2026/02/14/mikrokredite-gerade-jetzt-zur-risikostreuung/</t>
+          <t>https://www.finanznachrichten.de/nachrichten-2026-02/67704129-security-conference-muenchen-2026-oeffentliche-mittel-als-hebel-nutzen-144.htm</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="n">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>Börsen-Kurier</t>
+          <t>geldmeisterin.com</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>Privates Kapital für noch nicht entwickelte Märkte</t>
+          <t>Mikrokredite gerade jetzt zur Risikostreuung</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>DACH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>Print</t>
+          <t>Online</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
@@ -3343,55 +3343,55 @@
           <t>Johannes Feist</t>
         </is>
       </c>
-      <c r="G83" s="4" t="inlineStr"/>
+      <c r="G83" s="4" t="inlineStr">
+        <is>
+          <t>https://www.geldmeisterin.com/index.php/2026/02/14/mikrokredite-gerade-jetzt-zur-risikostreuung/</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="n">
-        <v>46057</v>
+        <v>46066</v>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>investrends.ch</t>
+          <t>Börsen-Kurier</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>Private Debt: Warum Prozesse wichtiger sind als Prognosen</t>
+          <t>Privates Kapital für noch nicht entwickelte Märkte</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>DACH</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Print</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>Michele Mattioda</t>
-        </is>
-      </c>
-      <c r="G84" s="4" t="inlineStr">
-        <is>
-          <t>https://investrends.ch/aktuell/investments/private-debt-warum-prozesse-wichtiger-sind-als-prognosen/</t>
-        </is>
-      </c>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G84" s="4" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="3" t="n">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>Payoff</t>
+          <t>investrends.ch</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>Mikrofinanz als Private Debt: Besicherte KMU-Kredite statt «Entwicklungshilfe»</t>
+          <t>Private Debt: Warum Prozesse wichtiger sind als Prognosen</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
@@ -3406,37 +3406,37 @@
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist</t>
+          <t>Michele Mattioda</t>
         </is>
       </c>
       <c r="G85" s="4" t="inlineStr">
         <is>
-          <t>https://www.payoff.ch/news/mikrofinanz-als-private-debt-besicherte-kmu-kredite-statt-entwicklungshilfe</t>
+          <t>https://investrends.ch/aktuell/investments/private-debt-warum-prozesse-wichtiger-sind-als-prognosen/</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="n">
-        <v>46049</v>
+        <v>46055</v>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>Markt Einblicke</t>
+          <t>Payoff</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>Mikrofinanzanleihen 2026: Stabile Renditen aus der Realwirtschaft</t>
+          <t>Mikrofinanz als Private Debt: Besicherte KMU-Kredite statt «Entwicklungshilfe»</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>E-Paper</t>
+          <t>Online</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
@@ -3444,20 +3444,24 @@
           <t>Johannes Feist</t>
         </is>
       </c>
-      <c r="G86" s="4" t="inlineStr"/>
+      <c r="G86" s="4" t="inlineStr">
+        <is>
+          <t>https://www.payoff.ch/news/mikrofinanz-als-private-debt-besicherte-kmu-kredite-statt-entwicklungshilfe</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="n">
-        <v>46044</v>
+        <v>46049</v>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Frankfurter Allgemeine Zeitung</t>
+          <t>Markt Einblicke</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>Beim Klimaschutz mehr Marktwirtschaft wagen</t>
+          <t>Mikrofinanzanleihen 2026: Stabile Renditen aus der Realwirtschaft</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
@@ -3467,7 +3471,7 @@
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>E-Paper</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
@@ -3475,29 +3479,25 @@
           <t>Johannes Feist</t>
         </is>
       </c>
-      <c r="G87" s="4" t="inlineStr">
-        <is>
-          <t>https://www.faz.net/pro/weltwirtschaft/klima-ressourcen/klimapolitik-sollte-auf-mikrofinanzierung-statt-grossprojekte-setzen-accg-200431361.html</t>
-        </is>
-      </c>
+      <c r="G87" s="4" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="3" t="n">
-        <v>46038</v>
+        <v>46044</v>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>E-fundresearch</t>
+          <t>Frankfurter Allgemeine Zeitung</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>Umfrage: Welche Chancen und Risiken Experten 2026 in den Private Markets sehen</t>
+          <t>Beim Klimaschutz mehr Marktwirtschaft wagen</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>DACH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
@@ -3512,27 +3512,27 @@
       </c>
       <c r="G88" s="4" t="inlineStr">
         <is>
-          <t>https://e-fundresearch.com/funds/artikel/57840-umfrage-welche-chancen-und-risiken-experten-2026-in-den-private-markets-sehen?page=5</t>
+          <t>https://www.faz.net/pro/weltwirtschaft/klima-ressourcen/klimapolitik-sollte-auf-mikrofinanzierung-statt-grossprojekte-setzen-accg-200431361.html</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="n">
-        <v>46035</v>
+        <v>46038</v>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>Finews</t>
+          <t>E-fundresearch</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>Start 2026: Disziplin als Renditequelle bei KMU-Private Debt</t>
+          <t>Umfrage: Welche Chancen und Risiken Experten 2026 in den Private Markets sehen</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>DACH</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
@@ -3542,32 +3542,32 @@
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>Michele Mattioda</t>
+          <t>Johannes Feist</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr">
         <is>
-          <t>https://www.finews.ch/news/finanzplatz/70792-start2026-assetmanagement-mk-global-kapital-michele-mattioda-privat-debt-kmu-mikro</t>
+          <t>https://e-fundresearch.com/funds/artikel/57840-umfrage-welche-chancen-und-risiken-experten-2026-in-den-private-markets-sehen?page=5</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="n">
-        <v>46031</v>
+        <v>46035</v>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>portfolio institutionell</t>
+          <t>Finews</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>Große Wirkung mit kleinen Krediten</t>
+          <t>Start 2026: Disziplin als Renditequelle bei KMU-Private Debt</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
@@ -3577,27 +3577,27 @@
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist</t>
+          <t>Michele Mattioda</t>
         </is>
       </c>
       <c r="G90" s="4" t="inlineStr">
         <is>
-          <t>https://www.portfolio-institutionell.de/grosse-wirkung-mit-kleinen-krediten/</t>
+          <t>https://www.finews.ch/news/finanzplatz/70792-start2026-assetmanagement-mk-global-kapital-michele-mattioda-privat-debt-kmu-mikro</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="n">
-        <v>46029</v>
+        <v>46031</v>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>Markt Einblicke</t>
+          <t>portfolio institutionell</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>Mikrofinanzanleihen 2026: Stabile Renditen aus der Realwirtschaft</t>
+          <t>Große Wirkung mit kleinen Krediten</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
@@ -3617,22 +3617,22 @@
       </c>
       <c r="G91" s="4" t="inlineStr">
         <is>
-          <t>https://markteinblicke.de/127407/2026/01/mikrofinanzanleihen-2026-stabile-renditen-aus-der-realwirtschaft/</t>
+          <t>https://www.portfolio-institutionell.de/grosse-wirkung-mit-kleinen-krediten/</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="n">
-        <v>46009</v>
+        <v>46029</v>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>portfolio institutionell</t>
+          <t>Markt Einblicke</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>Große Wirkung mit kleinen Krediten</t>
+          <t>Mikrofinanzanleihen 2026: Stabile Renditen aus der Realwirtschaft</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
@@ -3642,7 +3642,7 @@
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>Print</t>
+          <t>Online</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
@@ -3652,22 +3652,22 @@
       </c>
       <c r="G92" s="4" t="inlineStr">
         <is>
-          <t>https://www.yumpu.com/de/document/read/70885506/pit-1225</t>
+          <t>https://markteinblicke.de/127407/2026/01/mikrofinanzanleihen-2026-stabile-renditen-aus-der-realwirtschaft/</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>BondGuide</t>
+          <t>portfolio institutionell</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>Mikro Kapital Management: „Impact Investing ist kein Charity“</t>
+          <t>Große Wirkung mit kleinen Krediten</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
@@ -3687,32 +3687,32 @@
       </c>
       <c r="G93" s="4" t="inlineStr">
         <is>
-          <t>https://www.bondguide.de/wp-content/uploads/2025/12/bondguide-25-2025.pdf</t>
+          <t>https://www.yumpu.com/de/document/read/70885506/pit-1225</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="n">
-        <v>46006</v>
+        <v>46008</v>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>IPE Institutional Investment</t>
+          <t>BondGuide</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>Gastbeitrag: Private Debt jenseits von Corporate Loans – Mikrofinanz als Anlageklasse</t>
+          <t>Mikro Kapital Management: „Impact Investing ist kein Charity“</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>DACH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Print</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
@@ -3722,7 +3722,7 @@
       </c>
       <c r="G94" s="4" t="inlineStr">
         <is>
-          <t>https://www.institutional-investment.de/content/asset-allocation/gastbeitrag-private-debt-jenseits-von-corporate-loans-mikrofinanz-als-anlageklasse.html</t>
+          <t>https://www.bondguide.de/wp-content/uploads/2025/12/bondguide-25-2025.pdf</t>
         </is>
       </c>
     </row>
@@ -3732,17 +3732,17 @@
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>Handelszeitung</t>
+          <t>IPE Institutional Investment</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>«In der Schweiz gibt es eine ganz ausgeprägte Kultur für Mikrofinanzierungen»</t>
+          <t>Gastbeitrag: Private Debt jenseits von Corporate Loans – Mikrofinanz als Anlageklasse</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>DACH</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
@@ -3757,27 +3757,27 @@
       </c>
       <c r="G95" s="4" t="inlineStr">
         <is>
-          <t>https://www.handelszeitung.ch/insurance/in-der-schweiz-gibt-es-eine-ganz-ausgepragte-kultur-fur-mikrofinanzierungen-884310</t>
+          <t>https://www.institutional-investment.de/content/asset-allocation/gastbeitrag-private-debt-jenseits-von-corporate-loans-mikrofinanz-als-anlageklasse.html</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="n">
-        <v>46001</v>
+        <v>46006</v>
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>altii</t>
+          <t>Handelszeitung</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>MK Global Kapital übernimmt Managementfunktion des Impact-Fonds ALTERNATIVE</t>
+          <t>«In der Schweiz gibt es eine ganz ausgeprägte Kultur für Mikrofinanzierungen»</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
@@ -3792,27 +3792,27 @@
       </c>
       <c r="G96" s="4" t="inlineStr">
         <is>
-          <t>https://www.altii.de/20251210_115639_ea0baaad-1f17-42a9-a698-596737b4a5f2/</t>
+          <t>https://www.handelszeitung.ch/insurance/in-der-schweiz-gibt-es-eine-ganz-ausgepragte-kultur-fur-mikrofinanzierungen-884310</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>investrends.ch</t>
+          <t>altii</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>Neue Managementgesellschaft für den Impact-Fonds ALTERNATIVE</t>
+          <t>MK Global Kapital übernimmt Managementfunktion des Impact-Fonds ALTERNATIVE</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
@@ -3827,22 +3827,22 @@
       </c>
       <c r="G97" s="4" t="inlineStr">
         <is>
-          <t>https://investrends.ch/aktuell/investments/neue-managementgesellschaft-fur-den-impact-fonds-alternative/</t>
+          <t>https://www.altii.de/20251210_115639_ea0baaad-1f17-42a9-a698-596737b4a5f2/</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>Moneycab</t>
+          <t>investrends.ch</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>MK Global Kapital wird per 1. Januar Managementgesellschaft für den Impact-Fonds ALTERNATIVE</t>
+          <t>Neue Managementgesellschaft für den Impact-Fonds ALTERNATIVE</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="G98" s="4" t="inlineStr">
         <is>
-          <t>https://www.moneycab.com/finanz/mk-global-kapital-wird-per-1-januar-managementgesellschaft-fuer-den-impact-fonds-alternative/</t>
+          <t>https://investrends.ch/aktuell/investments/neue-managementgesellschaft-fur-den-impact-fonds-alternative/</t>
         </is>
       </c>
     </row>
@@ -3872,17 +3872,17 @@
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>dfpa.info</t>
+          <t>Moneycab</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>MK Global Kapital wird Managementgesellschaft für Impact-Fonds "Alternative"</t>
+          <t>MK Global Kapital wird per 1. Januar Managementgesellschaft für den Impact-Fonds ALTERNATIVE</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
@@ -3897,7 +3897,7 @@
       </c>
       <c r="G99" s="4" t="inlineStr">
         <is>
-          <t>https://www.dfpa.info/investmentfonds-news/mk-global-kapital-wird-managementgesellschaft-fuer-impact-fonds-alternative/</t>
+          <t>https://www.moneycab.com/finanz/mk-global-kapital-wird-per-1-januar-managementgesellschaft-fuer-den-impact-fonds-alternative/</t>
         </is>
       </c>
     </row>
@@ -3907,12 +3907,12 @@
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>finanznachrichten.de</t>
+          <t>dfpa.info</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>MK Global Kapital wird per 1. Januar Managementgesellschaft für den Impact-Fonds ALTERNATIVE</t>
+          <t>MK Global Kapital wird Managementgesellschaft für Impact-Fonds "Alternative"</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
@@ -3932,22 +3932,22 @@
       </c>
       <c r="G100" s="4" t="inlineStr">
         <is>
-          <t>https://www.finanznachrichten.de/nachrichten-2025-12/67174021-mk-global-kapital-wird-per-1-januar-managementgesellschaft-fuer-den-impact-fonds-alternative-095.htm</t>
+          <t>https://www.dfpa.info/investmentfonds-news/mk-global-kapital-wird-managementgesellschaft-fuer-impact-fonds-alternative/</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="n">
-        <v>45997</v>
+        <v>45999</v>
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>bondguide.de</t>
+          <t>finanznachrichten.de</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>Mikro Kapital Management: Impact Investing ist kein Charity</t>
+          <t>MK Global Kapital wird per 1. Januar Managementgesellschaft für den Impact-Fonds ALTERNATIVE</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
@@ -3967,22 +3967,22 @@
       </c>
       <c r="G101" s="4" t="inlineStr">
         <is>
-          <t>https://www.bondguide.de/topnews/mikro-kapital-management-impact-investing-ist-kein-charity/</t>
+          <t>https://www.finanznachrichten.de/nachrichten-2025-12/67174021-mk-global-kapital-wird-per-1-januar-managementgesellschaft-fuer-den-impact-fonds-alternative-095.htm</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="n">
-        <v>45996</v>
+        <v>45997</v>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>finanznachrichten.de</t>
+          <t>bondguide.de</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>Mikro Kapital Management: "Impact Investing ist kein Charity"</t>
+          <t>Mikro Kapital Management: Impact Investing ist kein Charity</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
@@ -4002,7 +4002,7 @@
       </c>
       <c r="G102" s="4" t="inlineStr">
         <is>
-          <t>https://www.finanznachrichten.de/nachrichten-2025-12/67161108-mikro-kapital-management-impact-investing-ist-kein-charity-144.htm</t>
+          <t>https://www.bondguide.de/topnews/mikro-kapital-management-impact-investing-ist-kein-charity/</t>
         </is>
       </c>
     </row>
@@ -4012,12 +4012,12 @@
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>Investorenplattform.de</t>
+          <t>finanznachrichten.de</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>Mikro Kapital Management: „Impact Investing ist kein Charity“</t>
+          <t>Mikro Kapital Management: "Impact Investing ist kein Charity"</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
@@ -4037,22 +4037,22 @@
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
-          <t>https://investorenplattform.de/esg-impact/</t>
+          <t>https://www.finanznachrichten.de/nachrichten-2025-12/67161108-mikro-kapital-management-impact-investing-ist-kein-charity-144.htm</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>dfpa.info</t>
+          <t>Investorenplattform.de</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>Mikro Kapital platziert erstmals Anleihe an Luxemburger Börse</t>
+          <t>Mikro Kapital Management: „Impact Investing ist kein Charity“</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
@@ -4072,27 +4072,27 @@
       </c>
       <c r="G104" s="4" t="inlineStr">
         <is>
-          <t>https://www.dfpa.info/investmentfonds-news/mikro-kapital-platziert-erstmals-emtn-anleihen-des-fonds-alternative-an-luxemburger-boerse/</t>
+          <t>https://investorenplattform.de/esg-impact/</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="n">
-        <v>45985</v>
+        <v>45995</v>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>Finews</t>
+          <t>dfpa.info</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist über Mikrofinanzen: Sollten vom hohen Ross herunterkommen</t>
+          <t>Mikro Kapital platziert erstmals Anleihe an Luxemburger Börse</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
@@ -4107,32 +4107,32 @@
       </c>
       <c r="G105" s="4" t="inlineStr">
         <is>
-          <t>https://www.finews.ch/news/finanzplatz/70147-mikro-capital-johannes-feist-kuenstliche-intelligenz-blockchain-rumaenien-europa-mikrofinanzen-finanzplatz-schweiz</t>
+          <t>https://www.dfpa.info/investmentfonds-news/mikro-kapital-platziert-erstmals-emtn-anleihen-des-fonds-alternative-an-luxemburger-boerse/</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>tagesschau24.de (TV interview)</t>
+          <t>Finews</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>ARD interview: Why “glowworms” matter more than trillion-dollar pledges</t>
+          <t>Johannes Feist über Mikrofinanzen: Sollten vom hohen Ross herunterkommen</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>TV &amp; Online</t>
+          <t>Online</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
@@ -4142,32 +4142,32 @@
       </c>
       <c r="G106" s="4" t="inlineStr">
         <is>
-          <t>https://www.tagesschau.de/multimedia/sendung/tagesschau24/boerselive/video-1527674.html</t>
+          <t>https://www.finews.ch/news/finanzplatz/70147-mikro-capital-johannes-feist-kuenstliche-intelligenz-blockchain-rumaenien-europa-mikrofinanzen-finanzplatz-schweiz</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>Börsen-Kurier</t>
+          <t>tagesschau24.de (TV interview)</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>Mikrofinanz: Stabilität aus realer Wertschöpfung</t>
+          <t>ARD interview: Why “glowworms” matter more than trillion-dollar pledges</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>Print</t>
+          <t>TV &amp; Online</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
@@ -4175,30 +4175,34 @@
           <t>Johannes Feist</t>
         </is>
       </c>
-      <c r="G107" s="4" t="inlineStr"/>
+      <c r="G107" s="4" t="inlineStr">
+        <is>
+          <t>https://www.tagesschau.de/multimedia/sendung/tagesschau24/boerselive/video-1527674.html</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="n">
-        <v>45973</v>
+        <v>45981</v>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>investrends.ch</t>
+          <t>Börsen-Kurier</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>Mikrofinanz ist Private Debt mit direkter Verbindung zur Realwirtschaft</t>
+          <t>Mikrofinanz: Stabilität aus realer Wertschöpfung</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Print</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
@@ -4206,29 +4210,25 @@
           <t>Johannes Feist</t>
         </is>
       </c>
-      <c r="G108" s="4" t="inlineStr">
-        <is>
-          <t>https://investrends.ch/aktuell/investments/mikrofinanz-ist-private-debt-mit-direkter-verbindung-zur-realwirtschaft/</t>
-        </is>
-      </c>
+      <c r="G108" s="4" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="3" t="n">
-        <v>45971</v>
+        <v>45973</v>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>photovoltaik.eu</t>
+          <t>investrends.ch</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>COP30: Klimafinanzierung muss in den Unternehmen ankommen</t>
+          <t>Mikrofinanz ist Private Debt mit direkter Verbindung zur Realwirtschaft</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
@@ -4243,22 +4243,22 @@
       </c>
       <c r="G109" s="4" t="inlineStr">
         <is>
-          <t>https://www.photovoltaik.eu/foerderung/cop30-klimafinanzierung-muss-den-unternehmen-ankommen</t>
+          <t>https://investrends.ch/aktuell/investments/mikrofinanz-ist-private-debt-mit-direkter-verbindung-zur-realwirtschaft/</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="3" t="n">
-        <v>45967</v>
+        <v>45971</v>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>Frankfurter Rundschau</t>
+          <t>photovoltaik.eu</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>Merz in Brasilien: Bundeskanzler fordert „globale Kraftanstrengung“ für Klimaschutz bei COP30</t>
+          <t>COP30: Klimafinanzierung muss in den Unternehmen ankommen</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
@@ -4278,7 +4278,7 @@
       </c>
       <c r="G110" s="4" t="inlineStr">
         <is>
-          <t>https://www.fr.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.photovoltaik.eu/foerderung/cop30-klimafinanzierung-muss-den-unternehmen-ankommen</t>
         </is>
       </c>
     </row>
@@ -4288,12 +4288,12 @@
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>Windmesse</t>
+          <t>Frankfurter Rundschau</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>COP30: Klimafinanzierung muss endlich in den Unternehmen ankommen</t>
+          <t>Merz in Brasilien: Bundeskanzler fordert „globale Kraftanstrengung“ für Klimaschutz bei COP30</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
@@ -4313,7 +4313,7 @@
       </c>
       <c r="G111" s="4" t="inlineStr">
         <is>
-          <t>https://w3.windmesse.de/windenergie/news/48059-cop30-klimafinanzierung-muss-endlich-in-den-unternehmen-ankommen</t>
+          <t>https://www.fr.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
@@ -4323,12 +4323,12 @@
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>BondGuide</t>
+          <t>Windmesse</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>Klimafinanzierung bei COP 30: von Zusagen zu Wirkung entfalten</t>
+          <t>COP30: Klimafinanzierung muss endlich in den Unternehmen ankommen</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
@@ -4348,7 +4348,7 @@
       </c>
       <c r="G112" s="4" t="inlineStr">
         <is>
-          <t>https://www.bondguide.de/topnews/klimafinanzierung-bei-cop-30-von-zusagen-zu-wirkung-entfalten/</t>
+          <t>https://w3.windmesse.de/windenergie/news/48059-cop30-klimafinanzierung-muss-endlich-in-den-unternehmen-ankommen</t>
         </is>
       </c>
     </row>
@@ -4358,12 +4358,12 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>AZ online (Allgemeine Zeitung der Lüneburger Heide)</t>
+          <t>BondGuide</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>Merz reist nach Brasilien: Deutschlands Klimapolitik bei COP30 auf dem Prüfstein</t>
+          <t>Klimafinanzierung bei COP 30: von Zusagen zu Wirkung entfalten</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="G113" s="4" t="inlineStr">
         <is>
-          <t>https://www.az-online.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.bondguide.de/topnews/klimafinanzierung-bei-cop-30-von-zusagen-zu-wirkung-entfalten/</t>
         </is>
       </c>
     </row>
@@ -4393,7 +4393,7 @@
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>fehmarn24.de</t>
+          <t>AZ online (Allgemeine Zeitung der Lüneburger Heide)</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="G114" s="4" t="inlineStr">
         <is>
-          <t>https://www.fehmarn24.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.az-online.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
@@ -4428,7 +4428,7 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>fnp.de (Frankfurter Neue Presse)</t>
+          <t>fehmarn24.de</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
@@ -4451,7 +4451,11 @@
           <t>Johannes Feist</t>
         </is>
       </c>
-      <c r="G115" s="4" t="inlineStr"/>
+      <c r="G115" s="4" t="inlineStr">
+        <is>
+          <t>https://www.fehmarn24.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="n">
@@ -4459,7 +4463,7 @@
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>Fuldaer Zeitung.de</t>
+          <t>fnp.de (Frankfurter Neue Presse)</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
@@ -4482,11 +4486,7 @@
           <t>Johannes Feist</t>
         </is>
       </c>
-      <c r="G116" s="4" t="inlineStr">
-        <is>
-          <t>https://www.fuldaerzeitung.de/politik-und-wirtschaft/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
-        </is>
-      </c>
+      <c r="G116" s="4" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="3" t="n">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>Gießener Allgemeine Online</t>
+          <t>Fuldaer Zeitung.de</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="G117" s="4" t="inlineStr">
         <is>
-          <t>https://www.giessener-allgemeine.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.fuldaerzeitung.de/politik-und-wirtschaft/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
@@ -4529,7 +4529,7 @@
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>Wetterauer Zeitung Online</t>
+          <t>Gießener Allgemeine Online</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
@@ -4554,7 +4554,7 @@
       </c>
       <c r="G118" s="4" t="inlineStr">
         <is>
-          <t>https://www.wetterauer-zeitung.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.giessener-allgemeine.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
@@ -4564,7 +4564,7 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>giessener-anzeiger.de</t>
+          <t>Wetterauer Zeitung Online</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
@@ -4589,7 +4589,7 @@
       </c>
       <c r="G119" s="4" t="inlineStr">
         <is>
-          <t>https://www.giessener-anzeiger.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.wetterauer-zeitung.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
@@ -4599,7 +4599,7 @@
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>kreis-anzeiger.de (Zentralhessen)</t>
+          <t>giessener-anzeiger.de</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
@@ -4624,7 +4624,7 @@
       </c>
       <c r="G120" s="4" t="inlineStr">
         <is>
-          <t>https://www.kreis-anzeiger.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.giessener-anzeiger.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
@@ -4634,7 +4634,7 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>usinger-anzeiger.de</t>
+          <t>kreis-anzeiger.de (Zentralhessen)</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
@@ -4659,7 +4659,7 @@
       </c>
       <c r="G121" s="4" t="inlineStr">
         <is>
-          <t>https://www.usinger-anzeiger.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.kreis-anzeiger.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>hanauer.de (Hanauer Anzeiger)</t>
+          <t>usinger-anzeiger.de</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
@@ -4694,7 +4694,7 @@
       </c>
       <c r="G122" s="4" t="inlineStr">
         <is>
-          <t>https://www.hanauer.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.usinger-anzeiger.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
@@ -4704,7 +4704,7 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>echo24.de</t>
+          <t>hanauer.de (Hanauer Anzeiger)</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
@@ -4729,7 +4729,7 @@
       </c>
       <c r="G123" s="4" t="inlineStr">
         <is>
-          <t>https://www.echo24.de/welt/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.hanauer.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
@@ -4739,7 +4739,7 @@
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>hersfelder-zeitung.de</t>
+          <t>echo24.de</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
@@ -4764,7 +4764,7 @@
       </c>
       <c r="G124" s="4" t="inlineStr">
         <is>
-          <t>https://www.hersfelder-zeitung.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.echo24.de/welt/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
@@ -4774,7 +4774,7 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>HNA online</t>
+          <t>hersfelder-zeitung.de</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="G125" s="4" t="inlineStr">
         <is>
-          <t>https://www.hna.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.hersfelder-zeitung.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
@@ -4809,7 +4809,7 @@
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>kreisbote.de</t>
+          <t>HNA online</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr">
@@ -4834,7 +4834,7 @@
       </c>
       <c r="G126" s="4" t="inlineStr">
         <is>
-          <t>https://www.kreisbote.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.hna.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>kreiszeitung.de (Syke)</t>
+          <t>kreisbote.de</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="G127" s="4" t="inlineStr">
         <is>
-          <t>https://www.kreiszeitung.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.kreisbote.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
@@ -4879,7 +4879,7 @@
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>Leinetal24.de</t>
+          <t>kreiszeitung.de (Syke)</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="G128" s="4" t="inlineStr">
         <is>
-          <t>https://www.leinetal24.de/welt/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.kreiszeitung.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>come-on.de (Märkischer Zeitungsverlag)</t>
+          <t>Leinetal24.de</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="G129" s="4" t="inlineStr">
         <is>
-          <t>https://www.come-on.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.leinetal24.de/welt/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>Merkur.de (Münchner Merkur)</t>
+          <t>come-on.de (Märkischer Zeitungsverlag)</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
@@ -4974,7 +4974,7 @@
       </c>
       <c r="G130" s="4" t="inlineStr">
         <is>
-          <t>https://www.merkur.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.come-on.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
@@ -4984,7 +4984,7 @@
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>OVB online (Oberbayerisches Volksblatt)</t>
+          <t>Merkur.de (Münchner Merkur)</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
@@ -5009,7 +5009,7 @@
       </c>
       <c r="G131" s="4" t="inlineStr">
         <is>
-          <t>https://www.ovb-online.de/weltspiegel/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.merkur.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>oberhessische-zeitung.de</t>
+          <t>OVB online (Oberbayerisches Volksblatt)</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
@@ -5044,7 +5044,7 @@
       </c>
       <c r="G132" s="4" t="inlineStr">
         <is>
-          <t>https://www.oberhessische-zeitung.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.ovb-online.de/weltspiegel/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
@@ -5054,7 +5054,7 @@
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>OFFENBACH-POST ONLINE</t>
+          <t>oberhessische-zeitung.de</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
@@ -5079,7 +5079,7 @@
       </c>
       <c r="G133" s="4" t="inlineStr">
         <is>
-          <t>https://www.op-online.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.oberhessische-zeitung.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
@@ -5089,7 +5089,7 @@
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>gmuender-tagespost.de</t>
+          <t>OFFENBACH-POST ONLINE</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="G134" s="4" t="inlineStr">
         <is>
-          <t>https://www.gmuender-tagespost.de/welt/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.op-online.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
@@ -5124,7 +5124,7 @@
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>schwaebische-post.de</t>
+          <t>gmuender-tagespost.de</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
@@ -5149,7 +5149,7 @@
       </c>
       <c r="G135" s="4" t="inlineStr">
         <is>
-          <t>https://www.schwaebische-post.de/welt/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.gmuender-tagespost.de/welt/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>tz-online.de</t>
+          <t>schwaebische-post.de</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
@@ -5184,7 +5184,7 @@
       </c>
       <c r="G136" s="4" t="inlineStr">
         <is>
-          <t>https://www.tz.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.schwaebische-post.de/welt/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
@@ -5194,7 +5194,7 @@
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>Waldeckische Landeszeitung Online</t>
+          <t>tz-online.de</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="G137" s="4" t="inlineStr">
         <is>
-          <t>https://www.wlz-online.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.tz.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
@@ -5229,7 +5229,7 @@
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>werra-rundschau.de</t>
+          <t>Waldeckische Landeszeitung Online</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
@@ -5254,7 +5254,7 @@
       </c>
       <c r="G138" s="4" t="inlineStr">
         <is>
-          <t>https://www.werra-rundschau.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.wlz-online.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>soester-anzeiger.de</t>
+          <t>werra-rundschau.de</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
@@ -5289,7 +5289,7 @@
       </c>
       <c r="G139" s="4" t="inlineStr">
         <is>
-          <t>https://www.soester-anzeiger.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.werra-rundschau.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>wa.de (Westfälischer Anzeiger)</t>
+          <t>soester-anzeiger.de</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
@@ -5324,40 +5324,75 @@
       </c>
       <c r="G140" s="4" t="inlineStr">
         <is>
-          <t>https://www.wa.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.soester-anzeiger.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="3" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B141" s="4" t="inlineStr">
+        <is>
+          <t>wa.de (Westfälischer Anzeiger)</t>
+        </is>
+      </c>
+      <c r="C141" s="4" t="inlineStr">
+        <is>
+          <t>Merz reist nach Brasilien: Deutschlands Klimapolitik bei COP30 auf dem Prüfstein</t>
+        </is>
+      </c>
+      <c r="D141" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E141" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F141" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G141" s="4" t="inlineStr">
+        <is>
+          <t>https://www.wa.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="3" t="n">
         <v>45848</v>
       </c>
-      <c r="B141" s="4" t="inlineStr">
+      <c r="B142" s="4" t="inlineStr">
         <is>
           <t>Handelszeitung</t>
         </is>
       </c>
-      <c r="C141" s="4" t="inlineStr">
+      <c r="C142" s="4" t="inlineStr">
         <is>
           <t>Zwischen ESG-Müdigkeit und Wirkungsanspruch</t>
         </is>
       </c>
-      <c r="D141" s="4" t="inlineStr">
+      <c r="D142" s="4" t="inlineStr">
         <is>
           <t>CH</t>
         </is>
       </c>
-      <c r="E141" s="4" t="inlineStr">
-        <is>
-          <t>Online</t>
-        </is>
-      </c>
-      <c r="F141" s="4" t="inlineStr">
-        <is>
-          <t>Johannes Feist</t>
-        </is>
-      </c>
-      <c r="G141" s="4" t="inlineStr">
+      <c r="E142" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F142" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G142" s="4" t="inlineStr">
         <is>
           <t>https://www.handelszeitung.ch/specials/nachhaltiges-investieren-2024/zwischen-esg-mudigkeit-und-wirkungsanspruch-841576</t>
         </is>
@@ -5398,7 +5433,7 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Source: Sheet '2026 Clippings' (A9:G141)</t>
+          <t>Source: Sheet '2026 Clippings' (A9:G142)</t>
         </is>
       </c>
     </row>
@@ -5416,7 +5451,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6">
@@ -5505,10 +5540,10 @@
         </is>
       </c>
       <c r="B12" s="8" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>0.8721804511278195</v>
+        <v>0.8731343283582089</v>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
@@ -5529,7 +5564,7 @@
         <v>15</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>0.112781954887218</v>
+        <v>0.1119402985074627</v>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
@@ -5550,7 +5585,7 @@
         <v>2</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>0.01503759398496241</v>
+        <v>0.01492537313432836</v>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
@@ -5659,7 +5694,7 @@
         </is>
       </c>
       <c r="F23" s="8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -5726,7 +5761,7 @@
         <v>5</v>
       </c>
       <c r="C31" s="11" t="n">
-        <v>0.03759398496240601</v>
+        <v>0.03731343283582089</v>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
@@ -5737,7 +5772,7 @@
         <v>1</v>
       </c>
       <c r="G31" s="11" t="n">
-        <v>0.007518796992481203</v>
+        <v>0.007462686567164179</v>
       </c>
     </row>
     <row r="32">
@@ -5750,7 +5785,7 @@
         <v>21</v>
       </c>
       <c r="C32" s="11" t="n">
-        <v>0.1578947368421053</v>
+        <v>0.1567164179104478</v>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
@@ -5761,7 +5796,7 @@
         <v>2</v>
       </c>
       <c r="G32" s="11" t="n">
-        <v>0.01503759398496241</v>
+        <v>0.01492537313432836</v>
       </c>
     </row>
     <row r="33">
@@ -5771,10 +5806,10 @@
         </is>
       </c>
       <c r="B33" s="8" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C33" s="11" t="n">
-        <v>0.7593984962406015</v>
+        <v>0.7611940298507462</v>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
@@ -5782,10 +5817,10 @@
         </is>
       </c>
       <c r="F33" s="8" t="n">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="G33" s="11" t="n">
-        <v>0.8721804511278195</v>
+        <v>0.8731343283582089</v>
       </c>
     </row>
     <row r="34">
@@ -5798,7 +5833,7 @@
         <v>6</v>
       </c>
       <c r="C34" s="11" t="n">
-        <v>0.04511278195488722</v>
+        <v>0.04477611940298507</v>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
@@ -5809,7 +5844,7 @@
         <v>8</v>
       </c>
       <c r="G34" s="11" t="n">
-        <v>0.06015037593984962</v>
+        <v>0.05970149253731343</v>
       </c>
     </row>
     <row r="35">
@@ -5822,7 +5857,7 @@
         <v>1</v>
       </c>
       <c r="G35" s="11" t="n">
-        <v>0.007518796992481203</v>
+        <v>0.007462686567164179</v>
       </c>
     </row>
     <row r="36">
@@ -5835,7 +5870,7 @@
         <v>4</v>
       </c>
       <c r="G36" s="11" t="n">
-        <v>0.03007518796992481</v>
+        <v>0.02985074626865672</v>
       </c>
     </row>
     <row r="37">
@@ -5848,7 +5883,7 @@
         <v>1</v>
       </c>
       <c r="G37" s="11" t="n">
-        <v>0.007518796992481203</v>
+        <v>0.007462686567164179</v>
       </c>
     </row>
   </sheetData>

--- a/docs/latest_report.xlsx
+++ b/docs/latest_report.xlsx
@@ -694,7 +694,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G142"/>
+  <dimension ref="A1:G143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -712,7 +712,7 @@
     <row r="4"/>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46314.06149721704</v>
+        <v>46315.08451658329</v>
       </c>
     </row>
     <row r="8">
@@ -754,16 +754,16 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>46304</v>
+        <v>46315</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Moneycab</t>
+          <t>Allnews</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Die Obligation ist tokenisiert. Doch womit wird sie bezahlt?</t>
+          <t>L'eau, un risque financier sous-estimé</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>https://www.moneycab.com/dossiers/die-obligation-ist-tokenisiert-doch-womit-wird-sie-bezahlt/</t>
+          <t>https://www.allnews.ch/content/points-de-vue/leau-un-risque-financier-sous-estime</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>finanznachrichten.de</t>
+          <t>Moneycab</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -818,22 +818,22 @@
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>https://www.finanznachrichten.de/nachrichten-2026-10/69801367-die-obligation-ist-tokenisiert-doch-womit-wird-sie-bezahlt-095.htm</t>
+          <t>https://www.moneycab.com/dossiers/die-obligation-ist-tokenisiert-doch-womit-wird-sie-bezahlt/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
-        <v>46299</v>
+        <v>46304</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Spotify</t>
+          <t>finanznachrichten.de</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Mikrokredite als Anlagealternative von Geldmeisterin</t>
+          <t>Die Obligation ist tokenisiert. Doch womit wird sie bezahlt?</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
@@ -848,27 +848,27 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist</t>
+          <t>Louiza Savchenko</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>https://podcasters.spotify.com/pod/show/geldmeisterin/episodes/Mikrokredite-als-Anlagealternative-e3f11ln</t>
+          <t>https://www.finanznachrichten.de/nachrichten-2026-10/69801367-die-obligation-ist-tokenisiert-doch-womit-wird-sie-bezahlt-095.htm</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
-        <v>46294</v>
+        <v>46299</v>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Markt Einblicke</t>
+          <t>Spotify</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Nach dem Ernteeinbruch: Warum es jetzt auf die richtige Finanzierung ankommt</t>
+          <t>Mikrokredite als Anlagealternative von Geldmeisterin</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
@@ -888,22 +888,22 @@
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>https://markteinblicke.de/133297/2026/09/nach-dem-ernteeinbruch-warum-es-jetzt-auf-die-richtige-finanzierung-ankommt/</t>
+          <t>https://podcasters.spotify.com/pod/show/geldmeisterin/episodes/Mikrokredite-als-Anlagealternative-e3f11ln</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
-        <v>46275</v>
+        <v>46294</v>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Börsen-Zeitung</t>
+          <t>Markt Einblicke</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Private Debt: Wenn Diversifikation nur auf dem Papier besteht</t>
+          <t>Nach dem Ernteeinbruch: Warum es jetzt auf die richtige Finanzierung ankommt</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
@@ -923,22 +923,22 @@
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>https://www.boersen-zeitung.de/boersen-zeitung-spezial/private-debt-wenn-diversifikation-nur-auf-dem-papier-besteht</t>
+          <t>https://markteinblicke.de/133297/2026/09/nach-dem-ernteeinbruch-warum-es-jetzt-auf-die-richtige-finanzierung-ankommt/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
-        <v>46273</v>
+        <v>46275</v>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Private Banking Magazin</t>
+          <t>Börsen-Zeitung</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Private Credit in Zentralasien</t>
+          <t>Private Debt: Wenn Diversifikation nur auf dem Papier besteht</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
@@ -958,22 +958,22 @@
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>https://www.private-banking-magazin.de/private-credit-zentralasien-lokale-unternehmenskredite/</t>
+          <t>https://www.boersen-zeitung.de/boersen-zeitung-spezial/private-debt-wenn-diversifikation-nur-auf-dem-papier-besteht</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
-        <v>46256</v>
+        <v>46273</v>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>BondGuide</t>
+          <t>Private Banking Magazin</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Niedrigwasser zeigt die Geografie des Kreditrisikos</t>
+          <t>Private Credit in Zentralasien</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
@@ -993,27 +993,27 @@
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>https://www.bondguide.de/topnews/niedrigwasser-zeigt-die-geografie-des-kreditrisikos/</t>
+          <t>https://www.private-banking-magazin.de/private-credit-zentralasien-lokale-unternehmenskredite/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
-        <v>46251</v>
+        <v>46256</v>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Finanz und Wirtschaft</t>
+          <t>BondGuide</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Die Schweiz finanziert Wasserresilienz überall – nur nicht im Inland</t>
+          <t>Niedrigwasser zeigt die Geografie des Kreditrisikos</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
@@ -1023,32 +1023,32 @@
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Louiza Savchenko</t>
+          <t>Johannes Feist</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>https://www.fuw.ch/wasserrisiko-was-die-schweiz-von-zentralasien-lernen-kann-152625611421</t>
+          <t>https://www.bondguide.de/topnews/niedrigwasser-zeigt-die-geografie-des-kreditrisikos/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
-        <v>46247</v>
+        <v>46251</v>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Markt Einblicke</t>
+          <t>Finanz und Wirtschaft</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Mikrofinanzanleihen: Worauf es bei Kreditqualität und Struktur ankommt</t>
+          <t>Die Schweiz finanziert Wasserresilienz überall – nur nicht im Inland</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -1058,27 +1058,27 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist</t>
+          <t>Louiza Savchenko</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>https://markteinblicke.de/132318/2026/08/mikrofinanzanleihen-worauf-es-bei-kreditqualitaet-und-struktur-ankommt/</t>
+          <t>https://www.fuw.ch/wasserrisiko-was-die-schweiz-von-zentralasien-lernen-kann-152625611421</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>FUELS+LUBES+ENERGY</t>
+          <t>Markt Einblicke</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Der Ölpreis und die Kapitalmärkte</t>
+          <t>Mikrofinanzanleihen: Worauf es bei Kreditqualität und Struktur ankommt</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>Print</t>
+          <t>Online</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -1096,30 +1096,34 @@
           <t>Johannes Feist</t>
         </is>
       </c>
-      <c r="G18" s="4" t="inlineStr"/>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>https://markteinblicke.de/132318/2026/08/mikrofinanzanleihen-worauf-es-bei-kreditqualitaet-und-struktur-ankommt/</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>e-fundresearch</t>
+          <t>FUELS+LUBES+ENERGY</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Experten-Umfrage: Worüber im zweiten Halbjahr 2026 keiner redet (Teil 2/2)</t>
+          <t>Der Ölpreis und die Kapitalmärkte</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>DACH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Print</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -1127,34 +1131,30 @@
           <t>Johannes Feist</t>
         </is>
       </c>
-      <c r="G19" s="4" t="inlineStr">
-        <is>
-          <t>https://e-fundresearch.com/managers/artikel/60333-experten-umfrage-worueber-im-zweiten-halbjahr-2026-keiner-redet-teil-22</t>
-        </is>
-      </c>
+      <c r="G19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>46241</v>
+        <v>46245</v>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>marktEINBLICKE</t>
+          <t>e-fundresearch</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Euro-Kupon, lokale Cashflows: Wo das Währungsrisiko wirklich liegt</t>
+          <t>Experten-Umfrage: Worüber im zweiten Halbjahr 2026 keiner redet (Teil 2/2)</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>DACH</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>E-Paper</t>
+          <t>Online</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -1164,17 +1164,17 @@
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>https://markteinblicke.de/wp-content/uploads/meg/mEGeldanlage_2026_15.pdf</t>
+          <t>https://e-fundresearch.com/managers/artikel/60333-experten-umfrage-worueber-im-zweiten-halbjahr-2026-keiner-redet-teil-22</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>46238</v>
+        <v>46241</v>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Markt Einblicke</t>
+          <t>marktEINBLICKE</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>E-Paper</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -1199,27 +1199,27 @@
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>https://markteinblicke.de/132045/2026/08/euro-kupon-lokale-cashflows-wo-das-waehrungsrisiko-wirklich-liegt/</t>
+          <t>https://markteinblicke.de/wp-content/uploads/meg/mEGeldanlage_2026_15.pdf</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>46234</v>
+        <v>46238</v>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Moneycab</t>
+          <t>Markt Einblicke</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist, CEO MK Global Kapital, im Interview</t>
+          <t>Euro-Kupon, lokale Cashflows: Wo das Währungsrisiko wirklich liegt</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>https://www.moneycab.com/interviews/ceo-interviews/johannes-feist-ceo-mk-global-kapital-im-interview/</t>
+          <t>https://markteinblicke.de/132045/2026/08/euro-kupon-lokale-cashflows-wo-das-waehrungsrisiko-wirklich-liegt/</t>
         </is>
       </c>
     </row>
@@ -1244,7 +1244,7 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>finanznachrichten.de</t>
+          <t>Moneycab</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
@@ -1254,7 +1254,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
@@ -1269,22 +1269,22 @@
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>https://www.finanznachrichten.de/nachrichten-2026-07/69177994-johannes-feist-ceo-mk-global-kapital-im-interview-095.htm</t>
+          <t>https://www.moneycab.com/interviews/ceo-interviews/johannes-feist-ceo-mk-global-kapital-im-interview/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>46231</v>
+        <v>46234</v>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>BondGuide</t>
+          <t>finanznachrichten.de</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Private Credit: Was Anleiheinvestoren hinter dem Kupon prüfen sollten</t>
+          <t>Johannes Feist, CEO MK Global Kapital, im Interview</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
@@ -1304,7 +1304,7 @@
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>https://www.bondguide.de/topnews/private-credit-was-anleiheinvestoren-hinter-dem-kupon-pruefen-sollten/</t>
+          <t>https://www.finanznachrichten.de/nachrichten-2026-07/69177994-johannes-feist-ceo-mk-global-kapital-im-interview-095.htm</t>
         </is>
       </c>
     </row>
@@ -1314,12 +1314,12 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>ExportManager OST</t>
+          <t>BondGuide</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Wenn der klassische Bankkredit schlecht greift</t>
+          <t>Private Credit: Was Anleiheinvestoren hinter dem Kupon prüfen sollten</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Print &amp; Digital</t>
+          <t>Online</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -1337,7 +1337,11 @@
           <t>Johannes Feist</t>
         </is>
       </c>
-      <c r="G25" s="4" t="inlineStr"/>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>https://www.bondguide.de/topnews/private-credit-was-anleiheinvestoren-hinter-dem-kupon-pruefen-sollten/</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
@@ -1345,12 +1349,12 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>finanznachrichten.de</t>
+          <t>ExportManager OST</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Private Credit: Was Anleiheinvestoren hinter dem Kupon prüfen sollten</t>
+          <t>Wenn der klassische Bankkredit schlecht greift</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -1360,7 +1364,7 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Print &amp; Digital</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -1368,29 +1372,25 @@
           <t>Johannes Feist</t>
         </is>
       </c>
-      <c r="G26" s="4" t="inlineStr">
-        <is>
-          <t>https://www.finanznachrichten.de/nachrichten-2026-07/69141450-private-credit-was-anleiheinvestoren-hinter-dem-kupon-pruefen-sollten-144.htm</t>
-        </is>
-      </c>
+      <c r="G26" s="4" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>46205</v>
+        <v>46231</v>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Finews</t>
+          <t>finanznachrichten.de</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Ferienlektüre: Was Finanzprofis diesen Sommer lesen</t>
+          <t>Private Credit: Was Anleiheinvestoren hinter dem Kupon prüfen sollten</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -1400,32 +1400,32 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>Louiza Savchenko</t>
+          <t>Johannes Feist</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>https://www.finews.ch/themen/leben-karriere/72628-sommer-buchempfehlungen-2026-von-persoenlichkeiten-aus-der-finanzbranche-roman-sommerlektuere-lesen-ferien-andreas-feller-thomas-studhalter-karsten-dirk-steffens-anna-bretschneider-finanzplatz-schweiz</t>
+          <t>https://www.finanznachrichten.de/nachrichten-2026-07/69141450-private-credit-was-anleiheinvestoren-hinter-dem-kupon-pruefen-sollten-144.htm</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>46198</v>
+        <v>46205</v>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>background.tagesspiegel</t>
+          <t>Finews</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Digitale Kreditvergabe : Kreditzugang ist mehr als ein Score</t>
+          <t>Ferienlektüre: Was Finanzprofis diesen Sommer lesen</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
@@ -1440,27 +1440,27 @@
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>https://background.tagesspiegel.de/finance/briefing/kreditzugang-ist-mehr-als-ein-score</t>
+          <t>https://www.finews.ch/themen/leben-karriere/72628-sommer-buchempfehlungen-2026-von-persoenlichkeiten-aus-der-finanzbranche-roman-sommerlektuere-lesen-ferien-andreas-feller-thomas-studhalter-karsten-dirk-steffens-anna-bretschneider-finanzplatz-schweiz</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Finanz und Wirtschaft</t>
+          <t>background.tagesspiegel</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Rendite mit gutem Gewissen</t>
+          <t>Digitale Kreditvergabe : Kreditzugang ist mehr als ein Score</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
@@ -1470,28 +1470,32 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist</t>
-        </is>
-      </c>
-      <c r="G29" s="4" t="inlineStr"/>
+          <t>Louiza Savchenko</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>https://background.tagesspiegel.de/finance/briefing/kreditzugang-ist-mehr-als-ein-score</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>46195</v>
+        <v>46197</v>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>fem.capital</t>
+          <t>Finanz und Wirtschaft</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Warum Unternehmerinnen eher am Kapital als am Markt scheitern</t>
+          <t>Rendite mit gutem Gewissen</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
@@ -1501,23 +1505,23 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>Louiza Savchenko</t>
+          <t>Johannes Feist</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>46188</v>
+        <v>46195</v>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Intelligent Investors</t>
+          <t>fem.capital</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Kreditqualität lässt sich nicht aus der Distanz steuern</t>
+          <t>Warum Unternehmerinnen eher am Kapital als am Markt scheitern</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -1527,38 +1531,38 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>Print</t>
+          <t>Online</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist</t>
+          <t>Louiza Savchenko</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>46183</v>
+        <v>46188</v>
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Finews</t>
+          <t>Intelligent Investors</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist: «Einer meiner unerfüllter Träume ist der Sportfliegerschein»</t>
+          <t>Kreditqualität lässt sich nicht aus der Distanz steuern</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Print</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -1566,34 +1570,30 @@
           <t>Johannes Feist</t>
         </is>
       </c>
-      <c r="G32" s="4" t="inlineStr">
-        <is>
-          <t>https://www.finews.ch/themen/high-end/72456-johannes-feist-einer-meiner-unerfuellter-traeume-ist-der-sportfliegerschein-ceo-global-kapital</t>
-        </is>
-      </c>
+      <c r="G32" s="4" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>46176</v>
+        <v>46183</v>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>BOND MAGAZINE</t>
+          <t>Finews</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Der neue Stresstest für Schwellenländer: Warum Öl, Zinsen und Währungen nur der Anfang sind und letztlich die Finanzierungsstruktur entscheidet</t>
+          <t>Johannes Feist: «Einer meiner unerfüllter Träume ist der Sportfliegerschein»</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>Print</t>
+          <t>Online</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -1603,32 +1603,32 @@
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>https://www.fixed-income.org/fileadmin/pdf/BOND_MAGAZINE_239.pdf</t>
+          <t>https://www.finews.ch/themen/high-end/72456-johannes-feist-einer-meiner-unerfuellter-traeume-ist-der-sportfliegerschein-ceo-global-kapital</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>46174</v>
+        <v>46176</v>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>FONDS exklusiv Österreich</t>
+          <t>BOND MAGAZINE</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Schwellenländer: Worauf es jetzt ankommt</t>
+          <t>Der neue Stresstest für Schwellenländer: Warum Öl, Zinsen und Währungen nur der Anfang sind und letztlich die Finanzierungsstruktur entscheidet</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Print</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>https://www.fondsexklusiv.at/schwellenlaender-worauf-es-jetzt-ankommt/</t>
+          <t>https://www.fixed-income.org/fileadmin/pdf/BOND_MAGAZINE_239.pdf</t>
         </is>
       </c>
     </row>
@@ -1648,17 +1648,17 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Intelligent Investors</t>
+          <t>FONDS exklusiv Österreich</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Die neue Verwundbarkeit der Schwellenländer</t>
+          <t>Schwellenländer: Worauf es jetzt ankommt</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>https://intelligent-investors.de/die-neue-verwundbarkeit-der-schwellenlaender/</t>
+          <t>https://www.fondsexklusiv.at/schwellenlaender-worauf-es-jetzt-ankommt/</t>
         </is>
       </c>
     </row>
@@ -1683,17 +1683,17 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>Institutional Money</t>
+          <t>Intelligent Investors</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>Finanzierungsstruktur: Der neue Stresstest für Schwellenländer</t>
+          <t>Die neue Verwundbarkeit der Schwellenländer</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>DACH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>https://www.institutional-money.com/news/maerkte/headline/finanzierungsstruktur-der-neue-stresstest-fuer-schwellenlaender-251058</t>
+          <t>https://intelligent-investors.de/die-neue-verwundbarkeit-der-schwellenlaender/</t>
         </is>
       </c>
     </row>
@@ -1718,12 +1718,12 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>Neo Market Ways</t>
+          <t>Institutional Money</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>From Microfinance to Mobility: How Capital is Driving Growth Across Eastern Europe</t>
+          <t>Finanzierungsstruktur: Der neue Stresstest für Schwellenländer</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -1743,27 +1743,27 @@
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>https://neomarketways.com/from-microfinance-to-mobility-how-capital-is-driving-growth-across-eastern-europe/</t>
+          <t>https://www.institutional-money.com/news/maerkte/headline/finanzierungsstruktur-der-neue-stresstest-fuer-schwellenlaender-251058</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>NEX24 News</t>
+          <t>Neo Market Ways</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Iran-Krieg: Der neue Stresstest für Schwellenländer</t>
+          <t>From Microfinance to Mobility: How Capital is Driving Growth Across Eastern Europe</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>DACH</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
@@ -1778,27 +1778,27 @@
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>https://nex24.news/2026/05/iran-krieg-der-neue-stresstest-fuer-schwellenlaender/</t>
+          <t>https://neomarketways.com/from-microfinance-to-mobility-how-capital-is-driving-growth-across-eastern-europe/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>GELD-Magazin</t>
+          <t>NEX24 News</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Stresstest für Schwellenländer</t>
+          <t>Iran-Krieg: Der neue Stresstest für Schwellenländer</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
@@ -1813,27 +1813,27 @@
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>https://www.geld-magazin.at/stresstest-fuer-schwellenlaender/</t>
+          <t>https://nex24.news/2026/05/iran-krieg-der-neue-stresstest-fuer-schwellenlaender/</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Markt Einblicke</t>
+          <t>GELD-Magazin</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Warum der Blick auf den Ölpreis nicht reicht</t>
+          <t>Stresstest für Schwellenländer</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
@@ -1848,27 +1848,27 @@
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>https://markteinblicke.de/130696/2026/05/warum-der-blick-auf-den-oelpreis-nicht-reicht/</t>
+          <t>https://www.geld-magazin.at/stresstest-fuer-schwellenlaender/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>46164</v>
+        <v>46169</v>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>Moneycab</t>
+          <t>Markt Einblicke</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Nicht die Grösse des Kredits entscheidet, sondern seine Wirkung</t>
+          <t>Warum der Blick auf den Ölpreis nicht reicht</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
@@ -1883,7 +1883,7 @@
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>https://www.moneycab.com/dossiers/nicht-die-groesse-des-kredits-entscheidet-sondern-seine-wirkung/</t>
+          <t>https://markteinblicke.de/130696/2026/05/warum-der-blick-auf-den-oelpreis-nicht-reicht/</t>
         </is>
       </c>
     </row>
@@ -1893,7 +1893,7 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>finanznachrichten.de</t>
+          <t>Moneycab</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -1903,7 +1903,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
@@ -1918,22 +1918,22 @@
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>https://www.finanznachrichten.de/nachrichten-2026-05/68568705-nicht-die-groesse-des-kredits-entscheidet-sondern-seine-wirkung-095.htm</t>
+          <t>https://www.moneycab.com/dossiers/nicht-die-groesse-des-kredits-entscheidet-sondern-seine-wirkung/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>46150</v>
+        <v>46164</v>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>Finanz- und Wirtschaftsspiegel</t>
+          <t>finanznachrichten.de</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>Entwicklungsfinanzierung mit Mikrokrediten</t>
+          <t>Nicht die Grösse des Kredits entscheidet, sondern seine Wirkung</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1943,7 +1943,7 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>Digital newsletter</t>
+          <t>Online</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
@@ -1951,20 +1951,24 @@
           <t>Johannes Feist</t>
         </is>
       </c>
-      <c r="G43" s="4" t="inlineStr"/>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>https://www.finanznachrichten.de/nachrichten-2026-05/68568705-nicht-die-groesse-des-kredits-entscheidet-sondern-seine-wirkung-095.htm</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>Markt Einblicke</t>
+          <t>Finanz- und Wirtschaftsspiegel</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>Mikrofinanz-Anleihen: Ein wachsender Markt</t>
+          <t>Entwicklungsfinanzierung mit Mikrokrediten</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1974,7 +1978,7 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Digital newsletter</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
@@ -1982,24 +1986,20 @@
           <t>Johannes Feist</t>
         </is>
       </c>
-      <c r="G44" s="4" t="inlineStr">
-        <is>
-          <t>https://markteinblicke.de/130263/2026/05/mikrofinanz-anleihen-ein-wachsender-markt/</t>
-        </is>
-      </c>
+      <c r="G44" s="4" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>46125</v>
+        <v>46149</v>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>cash-online.de</t>
+          <t>Markt Einblicke</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>Tokenisierte Anleihen: Was sich für Anleger ändert und was nicht</t>
+          <t>Mikrofinanz-Anleihen: Ein wachsender Markt</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -2014,27 +2014,27 @@
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>Louiza Savchenko</t>
+          <t>Johannes Feist</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>https://www.cash-online.de/a/tokenisierte-anleihen-was-sich-fuer-anleger-aendert-und-was-nicht-715994/</t>
+          <t>https://markteinblicke.de/130263/2026/05/mikrofinanz-anleihen-ein-wachsender-markt/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>46109</v>
+        <v>46125</v>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>Wirtschaftsvision</t>
+          <t>cash-online.de</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Der Trugschluss der sicheren Häfen</t>
+          <t>Tokenisierte Anleihen: Was sich für Anleger ändert und was nicht</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -2049,27 +2049,27 @@
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist</t>
+          <t>Louiza Savchenko</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>https://wirtschaftsvision.de/der-trugschluss-der-sicheren-haefen/</t>
+          <t>https://www.cash-online.de/a/tokenisierte-anleihen-was-sich-fuer-anleger-aendert-und-was-nicht-715994/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>46108</v>
+        <v>46109</v>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Börsen-Zeitung</t>
+          <t>Wirtschaftsvision</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>Wasserknappheit als Kreditrisiko</t>
+          <t>Der Trugschluss der sicheren Häfen</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>Print &amp; Online</t>
+          <t>Online</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
@@ -2089,22 +2089,22 @@
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>https://www.boersen-zeitung.de/sonderbeilagen/wasserknappheit-als-kreditrisiko</t>
+          <t>https://wirtschaftsvision.de/der-trugschluss-der-sicheren-haefen/</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>46105</v>
+        <v>46108</v>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Frankfurter Allgemeine Zeitung</t>
+          <t>Börsen-Zeitung</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>Sorgen um Privatkredite: Finanzkrise oder silberne Aera?</t>
+          <t>Wasserknappheit als Kreditrisiko</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Print &amp; Online</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>https://www.faz.net/pro/meine-finanzen/zinsen/sorgen-um-privatkredite-finanzkrise-oder-silberne-aera-110376123.html</t>
+          <t>https://www.boersen-zeitung.de/sonderbeilagen/wasserknappheit-als-kreditrisiko</t>
         </is>
       </c>
     </row>
@@ -2134,12 +2134,12 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>DAS INVESTMENT</t>
+          <t>Frankfurter Allgemeine Zeitung</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Private Credit unter Druck: Wenn das Geld nicht mehr herauskommt</t>
+          <t>Sorgen um Privatkredite: Finanzkrise oder silberne Aera?</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>https://www.dasinvestment.com/private-credit-unter-druck-wenn-das-geld-nicht-mehr-herauskommt/</t>
+          <t>https://www.faz.net/pro/meine-finanzen/zinsen/sorgen-um-privatkredite-finanzkrise-oder-silberne-aera-110376123.html</t>
         </is>
       </c>
     </row>
@@ -2169,17 +2169,17 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>FONDS exklusiv Oesterreich</t>
+          <t>DAS INVESTMENT</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>Private Credit-Debatte entfacht</t>
+          <t>Private Credit unter Druck: Wenn das Geld nicht mehr herauskommt</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
@@ -2194,22 +2194,22 @@
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>https://www.fondsexklusiv.at/private-credit-debatte-entfacht/</t>
+          <t>https://www.dasinvestment.com/private-credit-unter-druck-wenn-das-geld-nicht-mehr-herauskommt/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
-        <v>46103</v>
+        <v>46105</v>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Der Standard</t>
+          <t>FONDS exklusiv Oesterreich</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>Pakistan spart Milliarden an fossilen Importen: Wie hat es das gemacht?</t>
+          <t>Private Credit-Debatte entfacht</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
@@ -2229,27 +2229,27 @@
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>https://www.derstandard.de/story/3000000313347/pakistan-spart-milliarden-an-fossilen-importen-wie-hat-es-das-gemacht</t>
+          <t>https://www.fondsexklusiv.at/private-credit-debatte-entfacht/</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
-        <v>46101</v>
+        <v>46103</v>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Finews</t>
+          <t>Der Standard</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>Tokenisierung: Louzia Savchenko ueber Innovation und MK Global Kapital</t>
+          <t>Pakistan spart Milliarden an fossilen Importen: Wie hat es das gemacht?</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>Louiza Savchenko</t>
+          <t>Johannes Feist</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>https://www.finews.ch/news/finanzplatz/71578-finews-first-tokenisierung-louzia-savchenko-finanzplatz-schweiz-innovation-mk-global-kapital</t>
+          <t>https://www.derstandard.de/story/3000000313347/pakistan-spart-milliarden-an-fossilen-importen-wie-hat-es-das-gemacht</t>
         </is>
       </c>
     </row>
@@ -2274,17 +2274,17 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>BondGuide</t>
+          <t>Finews</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Private Credit ist nicht gleich Private Credit: wo die Risiken wirklich liegen</t>
+          <t>Tokenisierung: Louzia Savchenko ueber Innovation und MK Global Kapital</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist</t>
+          <t>Louiza Savchenko</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>https://www.bondguide.de/topnews/private-credit-ist-nicht-gleich-private-credit-wo-die-risiken-wirklich-liegen/</t>
+          <t>https://www.finews.ch/news/finanzplatz/71578-finews-first-tokenisierung-louzia-savchenko-finanzplatz-schweiz-innovation-mk-global-kapital</t>
         </is>
       </c>
     </row>
@@ -2309,17 +2309,17 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Swiss Finance AI</t>
+          <t>BondGuide</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>Warum tokenisierte Anleihen mehr sind als ein Trend</t>
+          <t>Private Credit ist nicht gleich Private Credit: wo die Risiken wirklich liegen</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
@@ -2329,27 +2329,27 @@
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>Louiza Savchenko</t>
+          <t>Johannes Feist</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>https://www.swissfinanceai.ch/blog/swiss-finance/warum-tokenisierte-anleihen-mehr-sind-als-ein-trend</t>
+          <t>https://www.bondguide.de/topnews/private-credit-ist-nicht-gleich-private-credit-wo-die-risiken-wirklich-liegen/</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Moneycab</t>
+          <t>Swiss Finance AI</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>Nicht nur Öl: Wo der Iran-Konflikt Emerging Markets wirklich trifft</t>
+          <t>Warum tokenisierte Anleihen mehr sind als ein Trend</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist</t>
+          <t>Louiza Savchenko</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>https://www.moneycab.com/finanz/nicht-nur-oel-wo-der-iran-konflikt-emerging-markets-wirklich-trifft/</t>
+          <t>https://www.swissfinanceai.ch/blog/swiss-finance/warum-tokenisierte-anleihen-mehr-sind-als-ein-trend</t>
         </is>
       </c>
     </row>
@@ -2379,17 +2379,17 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Institutional Money</t>
+          <t>Moneycab</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>Was der Iran-Schock fuer Emerging Markets veraendert</t>
+          <t>Nicht nur Öl: Wo der Iran-Konflikt Emerging Markets wirklich trifft</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>https://www.institutional-money.com/news/maerkte/headline/was-der-iran-schock-fuer-emerging-markets-veraendert-249420</t>
+          <t>https://www.moneycab.com/finanz/nicht-nur-oel-wo-der-iran-konflikt-emerging-markets-wirklich-trifft/</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>fixed-income.org</t>
+          <t>Institutional Money</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>https://www.fixed-income.org/investment/was-der-iran-schock-fuer-emerging-markets-veraendert.html</t>
+          <t>https://www.institutional-money.com/news/maerkte/headline/was-der-iran-schock-fuer-emerging-markets-veraendert-249420</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>finanznachrichten.de</t>
+          <t>fixed-income.org</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>Nicht nur Öl: Wo der Iran-Konflikt Emerging Markets wirklich trifft</t>
+          <t>Was der Iran-Schock fuer Emerging Markets veraendert</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -2474,13 +2474,13 @@
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>https://www.finanznachrichten.de/nachrichten-2026-03/67987291-nicht-nur-oel-wo-der-iran-konflikt-emerging-markets-wirklich-trifft-095.htm</t>
+          <t>https://www.fixed-income.org/investment/was-der-iran-schock-fuer-emerging-markets-veraendert.html</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
-        <v>46098</v>
+        <v>46100</v>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>Private Credit ist nicht gleich Private Credit: Wo die Risiken wirklich liegen</t>
+          <t>Nicht nur Öl: Wo der Iran-Konflikt Emerging Markets wirklich trifft</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>https://www.finanznachrichten.de/nachrichten-2026-03/67998176-private-credit-ist-nicht-gleich-private-credit-wo-die-risiken-wirklich-liegen-144.htm</t>
+          <t>https://www.finanznachrichten.de/nachrichten-2026-03/67987291-nicht-nur-oel-wo-der-iran-konflikt-emerging-markets-wirklich-trifft-095.htm</t>
         </is>
       </c>
     </row>
@@ -2519,12 +2519,12 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>cash-online.de</t>
+          <t>finanznachrichten.de</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Gastkommentar: Der blinde Fleck der Private-Credit-Debatte</t>
+          <t>Private Credit ist nicht gleich Private Credit: Wo die Risiken wirklich liegen</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -2544,7 +2544,7 @@
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>https://www.cash-online.de/a/gastkommentar-der-blinde-fleck-der-private-credit-debatte-713724/</t>
+          <t>https://www.finanznachrichten.de/nachrichten-2026-03/67998176-private-credit-ist-nicht-gleich-private-credit-wo-die-risiken-wirklich-liegen-144.htm</t>
         </is>
       </c>
     </row>
@@ -2554,12 +2554,12 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>BOND MAGAZINE</t>
+          <t>cash-online.de</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Tokenisierte Anleihen: Effizienz, Vertrauen und Marktentwicklung</t>
+          <t>Gastkommentar: Der blinde Fleck der Private-Credit-Debatte</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
@@ -2569,28 +2569,32 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>Print</t>
+          <t>Online</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>Louiza Savchenko</t>
-        </is>
-      </c>
-      <c r="G61" s="4" t="inlineStr"/>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="inlineStr">
+        <is>
+          <t>https://www.cash-online.de/a/gastkommentar-der-blinde-fleck-der-private-credit-debatte-713724/</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>FONDS exklusiv</t>
+          <t>BOND MAGAZINE</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Private Credit-Debatte entfacht</t>
+          <t>Tokenisierte Anleihen: Effizienz, Vertrauen und Marktentwicklung</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
@@ -2600,19 +2604,15 @@
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Print</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist</t>
-        </is>
-      </c>
-      <c r="G62" s="4" t="inlineStr">
-        <is>
-          <t>https://www.fondsexklusiv.de/private-credit-debatte-entfacht/</t>
-        </is>
-      </c>
+          <t>Louiza Savchenko</t>
+        </is>
+      </c>
+      <c r="G62" s="4" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Kreditwesen (Verlagsgruppe Knapp-Richardi)</t>
+          <t>FONDS exklusiv</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Mikrofinanz als Anlageklasse</t>
+          <t>Private Credit-Debatte entfacht</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -2635,7 +2635,7 @@
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>Print &amp; Online</t>
+          <t>Online</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>https://www.kreditwesen.de/kreditwesen/themenschwerpunkte/aufsaetze/mikrofinanz-anlageklasse-id107511.html</t>
+          <t>https://www.fondsexklusiv.de/private-credit-debatte-entfacht/</t>
         </is>
       </c>
     </row>
@@ -2655,22 +2655,22 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Payoff</t>
+          <t>Kreditwesen (Verlagsgruppe Knapp-Richardi)</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>Der blinde Fleck der Private-Credit-Debatte</t>
+          <t>Mikrofinanz als Anlageklasse</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Print &amp; Online</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
@@ -2680,17 +2680,17 @@
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>https://www.payoff.ch/news/der-blinde-fleck-der-private-credit-debatte</t>
+          <t>https://www.kreditwesen.de/kreditwesen/themenschwerpunkte/aufsaetze/mikrofinanz-anlageklasse-id107511.html</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>investrends.ch</t>
+          <t>Payoff</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>https://investrends.ch/aktuell/investments/der-blinde-fleck-der-private-credit-debatte/</t>
+          <t>https://www.payoff.ch/news/der-blinde-fleck-der-private-credit-debatte</t>
         </is>
       </c>
     </row>
@@ -2725,7 +2725,7 @@
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>Private Markets 360</t>
+          <t>investrends.ch</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
@@ -2750,22 +2750,22 @@
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>https://privatemarkets360.com/artikel/58516-der-blinde-fleck-der-private-credit-debatte</t>
+          <t>https://investrends.ch/aktuell/investments/der-blinde-fleck-der-private-credit-debatte/</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>Finanzen100.de</t>
+          <t>Private Markets 360</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>Marktkommentar: Der Trugschluss der sicheren Häfen</t>
+          <t>Der blinde Fleck der Private-Credit-Debatte</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
@@ -2785,7 +2785,7 @@
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>https://www.finanzen100.de/premium/bernecker-boersenkompass/marktkommentar-der-trugschluss-der-sicheren-haefen_H1356104965_6799449/</t>
+          <t>https://privatemarkets360.com/artikel/58516-der-blinde-fleck-der-private-credit-debatte</t>
         </is>
       </c>
     </row>
@@ -2795,12 +2795,12 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>Intelligent Investors</t>
+          <t>Finanzen100.de</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>Der blinde Fleck der Private-Credit-Debatte</t>
+          <t>Marktkommentar: Der Trugschluss der sicheren Häfen</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -2820,22 +2820,22 @@
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>https://intelligent-investors.de/der-blinde-fleck-der-private-credit-debatte/</t>
+          <t>https://www.finanzen100.de/premium/bernecker-boersenkompass/marktkommentar-der-trugschluss-der-sicheren-haefen_H1356104965_6799449/</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
-        <v>46085</v>
+        <v>46093</v>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>markteinblicke.de</t>
+          <t>Intelligent Investors</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>Tokenisierte Anleihen: Mehr Governance erforderlich</t>
+          <t>Der blinde Fleck der Private-Credit-Debatte</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
@@ -2850,12 +2850,12 @@
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>Louiza Savchenko</t>
+          <t>Johannes Feist</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>https://markteinblicke.de/128943/2026/03/tokenisierte-anleihen-mehr-governance-erforderlich/</t>
+          <t>https://intelligent-investors.de/der-blinde-fleck-der-private-credit-debatte/</t>
         </is>
       </c>
     </row>
@@ -2865,12 +2865,12 @@
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>gruenderkueche.de</t>
+          <t>markteinblicke.de</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>Weltfrauentag: Unternehmerinnen fehlt weiterhin der Zugang zu Kapital</t>
+          <t>Tokenisierte Anleihen: Mehr Governance erforderlich</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -2890,7 +2890,7 @@
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>https://www.gruenderkueche.de/news/finanzen-news/weltfrauentag-unternehmerinnen-fehlt-weiterhin-der-zugang-zu-kapital/</t>
+          <t>https://markteinblicke.de/128943/2026/03/tokenisierte-anleihen-mehr-governance-erforderlich/</t>
         </is>
       </c>
     </row>
@@ -2900,12 +2900,12 @@
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
-          <t>Table.Media</t>
+          <t>gruenderkueche.de</t>
         </is>
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>Gleichstellung: Unternehmerinnen fehlt weltweit der Zugang zu Kapital</t>
+          <t>Weltfrauentag: Unternehmerinnen fehlt weiterhin der Zugang zu Kapital</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -2925,22 +2925,22 @@
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>https://table.media/esg/news/gleichstellung-unternehmerinnen-fehlt-weltweit-der-zugang-zu-kapital</t>
+          <t>https://www.gruenderkueche.de/news/finanzen-news/weltfrauentag-unternehmerinnen-fehlt-weiterhin-der-zugang-zu-kapital/</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>dfpa.info</t>
+          <t>Table.Media</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>Unternehmerinnen fehlt weltweit der Zugang zu Kapital</t>
+          <t>Gleichstellung: Unternehmerinnen fehlt weltweit der Zugang zu Kapital</t>
         </is>
       </c>
       <c r="D72" s="4" t="inlineStr">
@@ -2960,17 +2960,17 @@
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
-          <t>https://www.dfpa.info/maerkte-studien-news/unternehmerinnen-fehlt-weltweit-der-zugang-zu-kapital/</t>
+          <t>https://table.media/esg/news/gleichstellung-unternehmerinnen-fehlt-weltweit-der-zugang-zu-kapital</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>altii.de</t>
+          <t>dfpa.info</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
@@ -2995,7 +2995,7 @@
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>https://www.altii.de/edai-71550571-cb6c-4c09-93da-bd99b822c245/</t>
+          <t>https://www.dfpa.info/maerkte-studien-news/unternehmerinnen-fehlt-weltweit-der-zugang-zu-kapital/</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>dapd.de</t>
+          <t>altii.de</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>Der Trugschluss der sicheren Häfen</t>
+          <t>Unternehmerinnen fehlt weltweit der Zugang zu Kapital</t>
         </is>
       </c>
       <c r="D74" s="4" t="inlineStr">
@@ -3025,27 +3025,27 @@
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist</t>
+          <t>Louiza Savchenko</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>https://www.dapd.de/der-trugschluss-der-sicheren-haefen/</t>
+          <t>https://www.altii.de/edai-71550571-cb6c-4c09-93da-bd99b822c245/</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="n">
-        <v>46078</v>
+        <v>46083</v>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>dfpa.info</t>
+          <t>dapd.de</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>Mikrofinanz: Besonderheit Anleihen mit festem Zins</t>
+          <t>Der Trugschluss der sicheren Häfen</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
@@ -3065,13 +3065,13 @@
       </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
-          <t>https://www.dfpa.info/interview/mikrofinanz-besonderheit-anleihen-mit-festem-zins.html</t>
+          <t>https://www.dapd.de/der-trugschluss-der-sicheren-haefen/</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
       </c>
       <c r="C76" s="4" t="inlineStr">
         <is>
-          <t>Wenn Geschäftsbanken passen, helfen Mikrofinanzfonds</t>
+          <t>Mikrofinanz: Besonderheit Anleihen mit festem Zins</t>
         </is>
       </c>
       <c r="D76" s="4" t="inlineStr">
@@ -3100,7 +3100,7 @@
       </c>
       <c r="G76" s="4" t="inlineStr">
         <is>
-          <t>https://www.dfpa.info/top-story/wenn-geschaeftsbanken-passen-helfen-mikrofinanzfonds.html</t>
+          <t>https://www.dfpa.info/interview/mikrofinanz-besonderheit-anleihen-mit-festem-zins.html</t>
         </is>
       </c>
     </row>
@@ -3110,12 +3110,12 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>DFPA</t>
+          <t>dfpa.info</t>
         </is>
       </c>
       <c r="C77" s="4" t="inlineStr">
         <is>
-          <t>Die neue EXXECNEWS ist erschienen</t>
+          <t>Wenn Geschäftsbanken passen, helfen Mikrofinanzfonds</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
@@ -3135,22 +3135,22 @@
       </c>
       <c r="G77" s="4" t="inlineStr">
         <is>
-          <t>https://www.dfpa.info/pressedigest-news/die-neue-exxecnews-ist-erschienen-78/</t>
+          <t>https://www.dfpa.info/top-story/wenn-geschaeftsbanken-passen-helfen-mikrofinanzfonds.html</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B78" s="4" t="inlineStr">
         <is>
-          <t>exxecnews.org</t>
+          <t>DFPA</t>
         </is>
       </c>
       <c r="C78" s="4" t="inlineStr">
         <is>
-          <t>Teil I: Wenn Geschäftsbanken passen, helfen Mikrofinanzfonds</t>
+          <t>Die neue EXXECNEWS ist erschienen</t>
         </is>
       </c>
       <c r="D78" s="4" t="inlineStr">
@@ -3160,7 +3160,7 @@
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>Print &amp; Online</t>
+          <t>Online</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="G78" s="4" t="inlineStr">
         <is>
-          <t>https://exxecnews.org/wp-content/uploads/2026/02/Ausgabe-05_2026.pdf</t>
+          <t>https://www.dfpa.info/pressedigest-news/die-neue-exxecnews-ist-erschienen-78/</t>
         </is>
       </c>
     </row>
@@ -3180,12 +3180,12 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>EXXECNEWS</t>
+          <t>exxecnews.org</t>
         </is>
       </c>
       <c r="C79" s="4" t="inlineStr">
         <is>
-          <t>Teil II: Mikrofinanz-Besonderheit – Anleihen mit festem Zins</t>
+          <t>Teil I: Wenn Geschäftsbanken passen, helfen Mikrofinanzfonds</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
@@ -3211,16 +3211,16 @@
     </row>
     <row r="80">
       <c r="A80" s="3" t="n">
-        <v>46069</v>
+        <v>46076</v>
       </c>
       <c r="B80" s="4" t="inlineStr">
         <is>
-          <t>boerse-social.com</t>
+          <t>EXXECNEWS</t>
         </is>
       </c>
       <c r="C80" s="4" t="inlineStr">
         <is>
-          <t>Börse-Inputs auf Spotify zu u.a. Do&amp;Co, Bawag, Nervigem und Mikrokrediten</t>
+          <t>Teil II: Mikrofinanz-Besonderheit – Anleihen mit festem Zins</t>
         </is>
       </c>
       <c r="D80" s="4" t="inlineStr">
@@ -3230,7 +3230,7 @@
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Print &amp; Online</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="G80" s="4" t="inlineStr">
         <is>
-          <t>https://boerse-social.com/2026/02/16/borse-inputs_auf_spotify_zu_ua_doco_bawag_nervigem_und_mikrokrediten_1</t>
+          <t>https://exxecnews.org/wp-content/uploads/2026/02/Ausgabe-05_2026.pdf</t>
         </is>
       </c>
     </row>
@@ -3250,12 +3250,12 @@
       </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
-          <t>bondguide.de</t>
+          <t>boerse-social.com</t>
         </is>
       </c>
       <c r="C81" s="4" t="inlineStr">
         <is>
-          <t>Security Conference München 2026: öffentliche Mittel als Hebel nutzen</t>
+          <t>Börse-Inputs auf Spotify zu u.a. Do&amp;Co, Bawag, Nervigem und Mikrokrediten</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -3275,17 +3275,17 @@
       </c>
       <c r="G81" s="4" t="inlineStr">
         <is>
-          <t>https://www.bondguide.de/topnews/security-conference-muenchen-2026-oeffentliche-mittel-als-hebel-nutzen/</t>
+          <t>https://boerse-social.com/2026/02/16/borse-inputs_auf_spotify_zu_ua_doco_bawag_nervigem_und_mikrokrediten_1</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="n">
-        <v>46067</v>
+        <v>46069</v>
       </c>
       <c r="B82" s="4" t="inlineStr">
         <is>
-          <t>finanznachrichten.de</t>
+          <t>bondguide.de</t>
         </is>
       </c>
       <c r="C82" s="4" t="inlineStr">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="G82" s="4" t="inlineStr">
         <is>
-          <t>https://www.finanznachrichten.de/nachrichten-2026-02/67704129-security-conference-muenchen-2026-oeffentliche-mittel-als-hebel-nutzen-144.htm</t>
+          <t>https://www.bondguide.de/topnews/security-conference-muenchen-2026-oeffentliche-mittel-als-hebel-nutzen/</t>
         </is>
       </c>
     </row>
@@ -3320,12 +3320,12 @@
       </c>
       <c r="B83" s="4" t="inlineStr">
         <is>
-          <t>geldmeisterin.com</t>
+          <t>finanznachrichten.de</t>
         </is>
       </c>
       <c r="C83" s="4" t="inlineStr">
         <is>
-          <t>Mikrokredite gerade jetzt zur Risikostreuung</t>
+          <t>Security Conference München 2026: öffentliche Mittel als Hebel nutzen</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
@@ -3345,32 +3345,32 @@
       </c>
       <c r="G83" s="4" t="inlineStr">
         <is>
-          <t>https://www.geldmeisterin.com/index.php/2026/02/14/mikrokredite-gerade-jetzt-zur-risikostreuung/</t>
+          <t>https://www.finanznachrichten.de/nachrichten-2026-02/67704129-security-conference-muenchen-2026-oeffentliche-mittel-als-hebel-nutzen-144.htm</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="n">
-        <v>46066</v>
+        <v>46067</v>
       </c>
       <c r="B84" s="4" t="inlineStr">
         <is>
-          <t>Börsen-Kurier</t>
+          <t>geldmeisterin.com</t>
         </is>
       </c>
       <c r="C84" s="4" t="inlineStr">
         <is>
-          <t>Privates Kapital für noch nicht entwickelte Märkte</t>
+          <t>Mikrokredite gerade jetzt zur Risikostreuung</t>
         </is>
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>DACH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>Print</t>
+          <t>Online</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
@@ -3378,55 +3378,55 @@
           <t>Johannes Feist</t>
         </is>
       </c>
-      <c r="G84" s="4" t="inlineStr"/>
+      <c r="G84" s="4" t="inlineStr">
+        <is>
+          <t>https://www.geldmeisterin.com/index.php/2026/02/14/mikrokredite-gerade-jetzt-zur-risikostreuung/</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="n">
-        <v>46057</v>
+        <v>46066</v>
       </c>
       <c r="B85" s="4" t="inlineStr">
         <is>
-          <t>investrends.ch</t>
+          <t>Börsen-Kurier</t>
         </is>
       </c>
       <c r="C85" s="4" t="inlineStr">
         <is>
-          <t>Private Debt: Warum Prozesse wichtiger sind als Prognosen</t>
+          <t>Privates Kapital für noch nicht entwickelte Märkte</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>DACH</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Print</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>Michele Mattioda</t>
-        </is>
-      </c>
-      <c r="G85" s="4" t="inlineStr">
-        <is>
-          <t>https://investrends.ch/aktuell/investments/private-debt-warum-prozesse-wichtiger-sind-als-prognosen/</t>
-        </is>
-      </c>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G85" s="4" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="3" t="n">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B86" s="4" t="inlineStr">
         <is>
-          <t>Payoff</t>
+          <t>investrends.ch</t>
         </is>
       </c>
       <c r="C86" s="4" t="inlineStr">
         <is>
-          <t>Mikrofinanz als Private Debt: Besicherte KMU-Kredite statt «Entwicklungshilfe»</t>
+          <t>Private Debt: Warum Prozesse wichtiger sind als Prognosen</t>
         </is>
       </c>
       <c r="D86" s="4" t="inlineStr">
@@ -3441,37 +3441,37 @@
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist</t>
+          <t>Michele Mattioda</t>
         </is>
       </c>
       <c r="G86" s="4" t="inlineStr">
         <is>
-          <t>https://www.payoff.ch/news/mikrofinanz-als-private-debt-besicherte-kmu-kredite-statt-entwicklungshilfe</t>
+          <t>https://investrends.ch/aktuell/investments/private-debt-warum-prozesse-wichtiger-sind-als-prognosen/</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="n">
-        <v>46049</v>
+        <v>46055</v>
       </c>
       <c r="B87" s="4" t="inlineStr">
         <is>
-          <t>Markt Einblicke</t>
+          <t>Payoff</t>
         </is>
       </c>
       <c r="C87" s="4" t="inlineStr">
         <is>
-          <t>Mikrofinanzanleihen 2026: Stabile Renditen aus der Realwirtschaft</t>
+          <t>Mikrofinanz als Private Debt: Besicherte KMU-Kredite statt «Entwicklungshilfe»</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>E-Paper</t>
+          <t>Online</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
@@ -3479,20 +3479,24 @@
           <t>Johannes Feist</t>
         </is>
       </c>
-      <c r="G87" s="4" t="inlineStr"/>
+      <c r="G87" s="4" t="inlineStr">
+        <is>
+          <t>https://www.payoff.ch/news/mikrofinanz-als-private-debt-besicherte-kmu-kredite-statt-entwicklungshilfe</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="3" t="n">
-        <v>46044</v>
+        <v>46049</v>
       </c>
       <c r="B88" s="4" t="inlineStr">
         <is>
-          <t>Frankfurter Allgemeine Zeitung</t>
+          <t>Markt Einblicke</t>
         </is>
       </c>
       <c r="C88" s="4" t="inlineStr">
         <is>
-          <t>Beim Klimaschutz mehr Marktwirtschaft wagen</t>
+          <t>Mikrofinanzanleihen 2026: Stabile Renditen aus der Realwirtschaft</t>
         </is>
       </c>
       <c r="D88" s="4" t="inlineStr">
@@ -3502,7 +3506,7 @@
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>E-Paper</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
@@ -3510,29 +3514,25 @@
           <t>Johannes Feist</t>
         </is>
       </c>
-      <c r="G88" s="4" t="inlineStr">
-        <is>
-          <t>https://www.faz.net/pro/weltwirtschaft/klima-ressourcen/klimapolitik-sollte-auf-mikrofinanzierung-statt-grossprojekte-setzen-accg-200431361.html</t>
-        </is>
-      </c>
+      <c r="G88" s="4" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" s="3" t="n">
-        <v>46038</v>
+        <v>46044</v>
       </c>
       <c r="B89" s="4" t="inlineStr">
         <is>
-          <t>E-fundresearch</t>
+          <t>Frankfurter Allgemeine Zeitung</t>
         </is>
       </c>
       <c r="C89" s="4" t="inlineStr">
         <is>
-          <t>Umfrage: Welche Chancen und Risiken Experten 2026 in den Private Markets sehen</t>
+          <t>Beim Klimaschutz mehr Marktwirtschaft wagen</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>DACH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
@@ -3547,27 +3547,27 @@
       </c>
       <c r="G89" s="4" t="inlineStr">
         <is>
-          <t>https://e-fundresearch.com/funds/artikel/57840-umfrage-welche-chancen-und-risiken-experten-2026-in-den-private-markets-sehen?page=5</t>
+          <t>https://www.faz.net/pro/weltwirtschaft/klima-ressourcen/klimapolitik-sollte-auf-mikrofinanzierung-statt-grossprojekte-setzen-accg-200431361.html</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="n">
-        <v>46035</v>
+        <v>46038</v>
       </c>
       <c r="B90" s="4" t="inlineStr">
         <is>
-          <t>Finews</t>
+          <t>E-fundresearch</t>
         </is>
       </c>
       <c r="C90" s="4" t="inlineStr">
         <is>
-          <t>Start 2026: Disziplin als Renditequelle bei KMU-Private Debt</t>
+          <t>Umfrage: Welche Chancen und Risiken Experten 2026 in den Private Markets sehen</t>
         </is>
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>DACH</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
@@ -3577,32 +3577,32 @@
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>Michele Mattioda</t>
+          <t>Johannes Feist</t>
         </is>
       </c>
       <c r="G90" s="4" t="inlineStr">
         <is>
-          <t>https://www.finews.ch/news/finanzplatz/70792-start2026-assetmanagement-mk-global-kapital-michele-mattioda-privat-debt-kmu-mikro</t>
+          <t>https://e-fundresearch.com/funds/artikel/57840-umfrage-welche-chancen-und-risiken-experten-2026-in-den-private-markets-sehen?page=5</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="n">
-        <v>46031</v>
+        <v>46035</v>
       </c>
       <c r="B91" s="4" t="inlineStr">
         <is>
-          <t>portfolio institutionell</t>
+          <t>Finews</t>
         </is>
       </c>
       <c r="C91" s="4" t="inlineStr">
         <is>
-          <t>Große Wirkung mit kleinen Krediten</t>
+          <t>Start 2026: Disziplin als Renditequelle bei KMU-Private Debt</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
@@ -3612,27 +3612,27 @@
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist</t>
+          <t>Michele Mattioda</t>
         </is>
       </c>
       <c r="G91" s="4" t="inlineStr">
         <is>
-          <t>https://www.portfolio-institutionell.de/grosse-wirkung-mit-kleinen-krediten/</t>
+          <t>https://www.finews.ch/news/finanzplatz/70792-start2026-assetmanagement-mk-global-kapital-michele-mattioda-privat-debt-kmu-mikro</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="3" t="n">
-        <v>46029</v>
+        <v>46031</v>
       </c>
       <c r="B92" s="4" t="inlineStr">
         <is>
-          <t>Markt Einblicke</t>
+          <t>portfolio institutionell</t>
         </is>
       </c>
       <c r="C92" s="4" t="inlineStr">
         <is>
-          <t>Mikrofinanzanleihen 2026: Stabile Renditen aus der Realwirtschaft</t>
+          <t>Große Wirkung mit kleinen Krediten</t>
         </is>
       </c>
       <c r="D92" s="4" t="inlineStr">
@@ -3652,22 +3652,22 @@
       </c>
       <c r="G92" s="4" t="inlineStr">
         <is>
-          <t>https://markteinblicke.de/127407/2026/01/mikrofinanzanleihen-2026-stabile-renditen-aus-der-realwirtschaft/</t>
+          <t>https://www.portfolio-institutionell.de/grosse-wirkung-mit-kleinen-krediten/</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="3" t="n">
-        <v>46009</v>
+        <v>46029</v>
       </c>
       <c r="B93" s="4" t="inlineStr">
         <is>
-          <t>portfolio institutionell</t>
+          <t>Markt Einblicke</t>
         </is>
       </c>
       <c r="C93" s="4" t="inlineStr">
         <is>
-          <t>Große Wirkung mit kleinen Krediten</t>
+          <t>Mikrofinanzanleihen 2026: Stabile Renditen aus der Realwirtschaft</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
@@ -3677,7 +3677,7 @@
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>Print</t>
+          <t>Online</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
@@ -3687,22 +3687,22 @@
       </c>
       <c r="G93" s="4" t="inlineStr">
         <is>
-          <t>https://www.yumpu.com/de/document/read/70885506/pit-1225</t>
+          <t>https://markteinblicke.de/127407/2026/01/mikrofinanzanleihen-2026-stabile-renditen-aus-der-realwirtschaft/</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B94" s="4" t="inlineStr">
         <is>
-          <t>BondGuide</t>
+          <t>portfolio institutionell</t>
         </is>
       </c>
       <c r="C94" s="4" t="inlineStr">
         <is>
-          <t>Mikro Kapital Management: „Impact Investing ist kein Charity“</t>
+          <t>Große Wirkung mit kleinen Krediten</t>
         </is>
       </c>
       <c r="D94" s="4" t="inlineStr">
@@ -3722,32 +3722,32 @@
       </c>
       <c r="G94" s="4" t="inlineStr">
         <is>
-          <t>https://www.bondguide.de/wp-content/uploads/2025/12/bondguide-25-2025.pdf</t>
+          <t>https://www.yumpu.com/de/document/read/70885506/pit-1225</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="n">
-        <v>46006</v>
+        <v>46008</v>
       </c>
       <c r="B95" s="4" t="inlineStr">
         <is>
-          <t>IPE Institutional Investment</t>
+          <t>BondGuide</t>
         </is>
       </c>
       <c r="C95" s="4" t="inlineStr">
         <is>
-          <t>Gastbeitrag: Private Debt jenseits von Corporate Loans – Mikrofinanz als Anlageklasse</t>
+          <t>Mikro Kapital Management: „Impact Investing ist kein Charity“</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>DACH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Print</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
@@ -3757,7 +3757,7 @@
       </c>
       <c r="G95" s="4" t="inlineStr">
         <is>
-          <t>https://www.institutional-investment.de/content/asset-allocation/gastbeitrag-private-debt-jenseits-von-corporate-loans-mikrofinanz-als-anlageklasse.html</t>
+          <t>https://www.bondguide.de/wp-content/uploads/2025/12/bondguide-25-2025.pdf</t>
         </is>
       </c>
     </row>
@@ -3767,17 +3767,17 @@
       </c>
       <c r="B96" s="4" t="inlineStr">
         <is>
-          <t>Handelszeitung</t>
+          <t>IPE Institutional Investment</t>
         </is>
       </c>
       <c r="C96" s="4" t="inlineStr">
         <is>
-          <t>«In der Schweiz gibt es eine ganz ausgeprägte Kultur für Mikrofinanzierungen»</t>
+          <t>Gastbeitrag: Private Debt jenseits von Corporate Loans – Mikrofinanz als Anlageklasse</t>
         </is>
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>DACH</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
@@ -3792,27 +3792,27 @@
       </c>
       <c r="G96" s="4" t="inlineStr">
         <is>
-          <t>https://www.handelszeitung.ch/insurance/in-der-schweiz-gibt-es-eine-ganz-ausgepragte-kultur-fur-mikrofinanzierungen-884310</t>
+          <t>https://www.institutional-investment.de/content/asset-allocation/gastbeitrag-private-debt-jenseits-von-corporate-loans-mikrofinanz-als-anlageklasse.html</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="n">
-        <v>46001</v>
+        <v>46006</v>
       </c>
       <c r="B97" s="4" t="inlineStr">
         <is>
-          <t>altii</t>
+          <t>Handelszeitung</t>
         </is>
       </c>
       <c r="C97" s="4" t="inlineStr">
         <is>
-          <t>MK Global Kapital übernimmt Managementfunktion des Impact-Fonds ALTERNATIVE</t>
+          <t>«In der Schweiz gibt es eine ganz ausgeprägte Kultur für Mikrofinanzierungen»</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
@@ -3827,27 +3827,27 @@
       </c>
       <c r="G97" s="4" t="inlineStr">
         <is>
-          <t>https://www.altii.de/20251210_115639_ea0baaad-1f17-42a9-a698-596737b4a5f2/</t>
+          <t>https://www.handelszeitung.ch/insurance/in-der-schweiz-gibt-es-eine-ganz-ausgepragte-kultur-fur-mikrofinanzierungen-884310</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B98" s="4" t="inlineStr">
         <is>
-          <t>investrends.ch</t>
+          <t>altii</t>
         </is>
       </c>
       <c r="C98" s="4" t="inlineStr">
         <is>
-          <t>Neue Managementgesellschaft für den Impact-Fonds ALTERNATIVE</t>
+          <t>MK Global Kapital übernimmt Managementfunktion des Impact-Fonds ALTERNATIVE</t>
         </is>
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
@@ -3862,22 +3862,22 @@
       </c>
       <c r="G98" s="4" t="inlineStr">
         <is>
-          <t>https://investrends.ch/aktuell/investments/neue-managementgesellschaft-fur-den-impact-fonds-alternative/</t>
+          <t>https://www.altii.de/20251210_115639_ea0baaad-1f17-42a9-a698-596737b4a5f2/</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="3" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B99" s="4" t="inlineStr">
         <is>
-          <t>Moneycab</t>
+          <t>investrends.ch</t>
         </is>
       </c>
       <c r="C99" s="4" t="inlineStr">
         <is>
-          <t>MK Global Kapital wird per 1. Januar Managementgesellschaft für den Impact-Fonds ALTERNATIVE</t>
+          <t>Neue Managementgesellschaft für den Impact-Fonds ALTERNATIVE</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
@@ -3897,7 +3897,7 @@
       </c>
       <c r="G99" s="4" t="inlineStr">
         <is>
-          <t>https://www.moneycab.com/finanz/mk-global-kapital-wird-per-1-januar-managementgesellschaft-fuer-den-impact-fonds-alternative/</t>
+          <t>https://investrends.ch/aktuell/investments/neue-managementgesellschaft-fur-den-impact-fonds-alternative/</t>
         </is>
       </c>
     </row>
@@ -3907,17 +3907,17 @@
       </c>
       <c r="B100" s="4" t="inlineStr">
         <is>
-          <t>dfpa.info</t>
+          <t>Moneycab</t>
         </is>
       </c>
       <c r="C100" s="4" t="inlineStr">
         <is>
-          <t>MK Global Kapital wird Managementgesellschaft für Impact-Fonds "Alternative"</t>
+          <t>MK Global Kapital wird per 1. Januar Managementgesellschaft für den Impact-Fonds ALTERNATIVE</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="G100" s="4" t="inlineStr">
         <is>
-          <t>https://www.dfpa.info/investmentfonds-news/mk-global-kapital-wird-managementgesellschaft-fuer-impact-fonds-alternative/</t>
+          <t>https://www.moneycab.com/finanz/mk-global-kapital-wird-per-1-januar-managementgesellschaft-fuer-den-impact-fonds-alternative/</t>
         </is>
       </c>
     </row>
@@ -3942,12 +3942,12 @@
       </c>
       <c r="B101" s="4" t="inlineStr">
         <is>
-          <t>finanznachrichten.de</t>
+          <t>dfpa.info</t>
         </is>
       </c>
       <c r="C101" s="4" t="inlineStr">
         <is>
-          <t>MK Global Kapital wird per 1. Januar Managementgesellschaft für den Impact-Fonds ALTERNATIVE</t>
+          <t>MK Global Kapital wird Managementgesellschaft für Impact-Fonds "Alternative"</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
@@ -3967,22 +3967,22 @@
       </c>
       <c r="G101" s="4" t="inlineStr">
         <is>
-          <t>https://www.finanznachrichten.de/nachrichten-2025-12/67174021-mk-global-kapital-wird-per-1-januar-managementgesellschaft-fuer-den-impact-fonds-alternative-095.htm</t>
+          <t>https://www.dfpa.info/investmentfonds-news/mk-global-kapital-wird-managementgesellschaft-fuer-impact-fonds-alternative/</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="n">
-        <v>45997</v>
+        <v>45999</v>
       </c>
       <c r="B102" s="4" t="inlineStr">
         <is>
-          <t>bondguide.de</t>
+          <t>finanznachrichten.de</t>
         </is>
       </c>
       <c r="C102" s="4" t="inlineStr">
         <is>
-          <t>Mikro Kapital Management: Impact Investing ist kein Charity</t>
+          <t>MK Global Kapital wird per 1. Januar Managementgesellschaft für den Impact-Fonds ALTERNATIVE</t>
         </is>
       </c>
       <c r="D102" s="4" t="inlineStr">
@@ -4002,22 +4002,22 @@
       </c>
       <c r="G102" s="4" t="inlineStr">
         <is>
-          <t>https://www.bondguide.de/topnews/mikro-kapital-management-impact-investing-ist-kein-charity/</t>
+          <t>https://www.finanznachrichten.de/nachrichten-2025-12/67174021-mk-global-kapital-wird-per-1-januar-managementgesellschaft-fuer-den-impact-fonds-alternative-095.htm</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="n">
-        <v>45996</v>
+        <v>45997</v>
       </c>
       <c r="B103" s="4" t="inlineStr">
         <is>
-          <t>finanznachrichten.de</t>
+          <t>bondguide.de</t>
         </is>
       </c>
       <c r="C103" s="4" t="inlineStr">
         <is>
-          <t>Mikro Kapital Management: "Impact Investing ist kein Charity"</t>
+          <t>Mikro Kapital Management: Impact Investing ist kein Charity</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
@@ -4037,7 +4037,7 @@
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
-          <t>https://www.finanznachrichten.de/nachrichten-2025-12/67161108-mikro-kapital-management-impact-investing-ist-kein-charity-144.htm</t>
+          <t>https://www.bondguide.de/topnews/mikro-kapital-management-impact-investing-ist-kein-charity/</t>
         </is>
       </c>
     </row>
@@ -4047,12 +4047,12 @@
       </c>
       <c r="B104" s="4" t="inlineStr">
         <is>
-          <t>Investorenplattform.de</t>
+          <t>finanznachrichten.de</t>
         </is>
       </c>
       <c r="C104" s="4" t="inlineStr">
         <is>
-          <t>Mikro Kapital Management: „Impact Investing ist kein Charity“</t>
+          <t>Mikro Kapital Management: "Impact Investing ist kein Charity"</t>
         </is>
       </c>
       <c r="D104" s="4" t="inlineStr">
@@ -4072,22 +4072,22 @@
       </c>
       <c r="G104" s="4" t="inlineStr">
         <is>
-          <t>https://investorenplattform.de/esg-impact/</t>
+          <t>https://www.finanznachrichten.de/nachrichten-2025-12/67161108-mikro-kapital-management-impact-investing-ist-kein-charity-144.htm</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B105" s="4" t="inlineStr">
         <is>
-          <t>dfpa.info</t>
+          <t>Investorenplattform.de</t>
         </is>
       </c>
       <c r="C105" s="4" t="inlineStr">
         <is>
-          <t>Mikro Kapital platziert erstmals Anleihe an Luxemburger Börse</t>
+          <t>Mikro Kapital Management: „Impact Investing ist kein Charity“</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
@@ -4107,27 +4107,27 @@
       </c>
       <c r="G105" s="4" t="inlineStr">
         <is>
-          <t>https://www.dfpa.info/investmentfonds-news/mikro-kapital-platziert-erstmals-emtn-anleihen-des-fonds-alternative-an-luxemburger-boerse/</t>
+          <t>https://investorenplattform.de/esg-impact/</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="n">
-        <v>45985</v>
+        <v>45995</v>
       </c>
       <c r="B106" s="4" t="inlineStr">
         <is>
-          <t>Finews</t>
+          <t>dfpa.info</t>
         </is>
       </c>
       <c r="C106" s="4" t="inlineStr">
         <is>
-          <t>Johannes Feist über Mikrofinanzen: Sollten vom hohen Ross herunterkommen</t>
+          <t>Mikro Kapital platziert erstmals Anleihe an Luxemburger Börse</t>
         </is>
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
@@ -4142,32 +4142,32 @@
       </c>
       <c r="G106" s="4" t="inlineStr">
         <is>
-          <t>https://www.finews.ch/news/finanzplatz/70147-mikro-capital-johannes-feist-kuenstliche-intelligenz-blockchain-rumaenien-europa-mikrofinanzen-finanzplatz-schweiz</t>
+          <t>https://www.dfpa.info/investmentfonds-news/mikro-kapital-platziert-erstmals-emtn-anleihen-des-fonds-alternative-an-luxemburger-boerse/</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B107" s="4" t="inlineStr">
         <is>
-          <t>tagesschau24.de (TV interview)</t>
+          <t>Finews</t>
         </is>
       </c>
       <c r="C107" s="4" t="inlineStr">
         <is>
-          <t>ARD interview: Why “glowworms” matter more than trillion-dollar pledges</t>
+          <t>Johannes Feist über Mikrofinanzen: Sollten vom hohen Ross herunterkommen</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>TV &amp; Online</t>
+          <t>Online</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
@@ -4177,32 +4177,32 @@
       </c>
       <c r="G107" s="4" t="inlineStr">
         <is>
-          <t>https://www.tagesschau.de/multimedia/sendung/tagesschau24/boerselive/video-1527674.html</t>
+          <t>https://www.finews.ch/news/finanzplatz/70147-mikro-capital-johannes-feist-kuenstliche-intelligenz-blockchain-rumaenien-europa-mikrofinanzen-finanzplatz-schweiz</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B108" s="4" t="inlineStr">
         <is>
-          <t>Börsen-Kurier</t>
+          <t>tagesschau24.de (TV interview)</t>
         </is>
       </c>
       <c r="C108" s="4" t="inlineStr">
         <is>
-          <t>Mikrofinanz: Stabilität aus realer Wertschöpfung</t>
+          <t>ARD interview: Why “glowworms” matter more than trillion-dollar pledges</t>
         </is>
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>Print</t>
+          <t>TV &amp; Online</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
@@ -4210,30 +4210,34 @@
           <t>Johannes Feist</t>
         </is>
       </c>
-      <c r="G108" s="4" t="inlineStr"/>
+      <c r="G108" s="4" t="inlineStr">
+        <is>
+          <t>https://www.tagesschau.de/multimedia/sendung/tagesschau24/boerselive/video-1527674.html</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="3" t="n">
-        <v>45973</v>
+        <v>45981</v>
       </c>
       <c r="B109" s="4" t="inlineStr">
         <is>
-          <t>investrends.ch</t>
+          <t>Börsen-Kurier</t>
         </is>
       </c>
       <c r="C109" s="4" t="inlineStr">
         <is>
-          <t>Mikrofinanz ist Private Debt mit direkter Verbindung zur Realwirtschaft</t>
+          <t>Mikrofinanz: Stabilität aus realer Wertschöpfung</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>CH</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>Online</t>
+          <t>Print</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
@@ -4241,29 +4245,25 @@
           <t>Johannes Feist</t>
         </is>
       </c>
-      <c r="G109" s="4" t="inlineStr">
-        <is>
-          <t>https://investrends.ch/aktuell/investments/mikrofinanz-ist-private-debt-mit-direkter-verbindung-zur-realwirtschaft/</t>
-        </is>
-      </c>
+      <c r="G109" s="4" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="3" t="n">
-        <v>45971</v>
+        <v>45973</v>
       </c>
       <c r="B110" s="4" t="inlineStr">
         <is>
-          <t>photovoltaik.eu</t>
+          <t>investrends.ch</t>
         </is>
       </c>
       <c r="C110" s="4" t="inlineStr">
         <is>
-          <t>COP30: Klimafinanzierung muss in den Unternehmen ankommen</t>
+          <t>Mikrofinanz ist Private Debt mit direkter Verbindung zur Realwirtschaft</t>
         </is>
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
@@ -4278,22 +4278,22 @@
       </c>
       <c r="G110" s="4" t="inlineStr">
         <is>
-          <t>https://www.photovoltaik.eu/foerderung/cop30-klimafinanzierung-muss-den-unternehmen-ankommen</t>
+          <t>https://investrends.ch/aktuell/investments/mikrofinanz-ist-private-debt-mit-direkter-verbindung-zur-realwirtschaft/</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="3" t="n">
-        <v>45967</v>
+        <v>45971</v>
       </c>
       <c r="B111" s="4" t="inlineStr">
         <is>
-          <t>Frankfurter Rundschau</t>
+          <t>photovoltaik.eu</t>
         </is>
       </c>
       <c r="C111" s="4" t="inlineStr">
         <is>
-          <t>Merz in Brasilien: Bundeskanzler fordert „globale Kraftanstrengung“ für Klimaschutz bei COP30</t>
+          <t>COP30: Klimafinanzierung muss in den Unternehmen ankommen</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
@@ -4313,7 +4313,7 @@
       </c>
       <c r="G111" s="4" t="inlineStr">
         <is>
-          <t>https://www.fr.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.photovoltaik.eu/foerderung/cop30-klimafinanzierung-muss-den-unternehmen-ankommen</t>
         </is>
       </c>
     </row>
@@ -4323,12 +4323,12 @@
       </c>
       <c r="B112" s="4" t="inlineStr">
         <is>
-          <t>Windmesse</t>
+          <t>Frankfurter Rundschau</t>
         </is>
       </c>
       <c r="C112" s="4" t="inlineStr">
         <is>
-          <t>COP30: Klimafinanzierung muss endlich in den Unternehmen ankommen</t>
+          <t>Merz in Brasilien: Bundeskanzler fordert „globale Kraftanstrengung“ für Klimaschutz bei COP30</t>
         </is>
       </c>
       <c r="D112" s="4" t="inlineStr">
@@ -4348,7 +4348,7 @@
       </c>
       <c r="G112" s="4" t="inlineStr">
         <is>
-          <t>https://w3.windmesse.de/windenergie/news/48059-cop30-klimafinanzierung-muss-endlich-in-den-unternehmen-ankommen</t>
+          <t>https://www.fr.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
@@ -4358,12 +4358,12 @@
       </c>
       <c r="B113" s="4" t="inlineStr">
         <is>
-          <t>BondGuide</t>
+          <t>Windmesse</t>
         </is>
       </c>
       <c r="C113" s="4" t="inlineStr">
         <is>
-          <t>Klimafinanzierung bei COP 30: von Zusagen zu Wirkung entfalten</t>
+          <t>COP30: Klimafinanzierung muss endlich in den Unternehmen ankommen</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="G113" s="4" t="inlineStr">
         <is>
-          <t>https://www.bondguide.de/topnews/klimafinanzierung-bei-cop-30-von-zusagen-zu-wirkung-entfalten/</t>
+          <t>https://w3.windmesse.de/windenergie/news/48059-cop30-klimafinanzierung-muss-endlich-in-den-unternehmen-ankommen</t>
         </is>
       </c>
     </row>
@@ -4393,12 +4393,12 @@
       </c>
       <c r="B114" s="4" t="inlineStr">
         <is>
-          <t>AZ online (Allgemeine Zeitung der Lüneburger Heide)</t>
+          <t>BondGuide</t>
         </is>
       </c>
       <c r="C114" s="4" t="inlineStr">
         <is>
-          <t>Merz reist nach Brasilien: Deutschlands Klimapolitik bei COP30 auf dem Prüfstein</t>
+          <t>Klimafinanzierung bei COP 30: von Zusagen zu Wirkung entfalten</t>
         </is>
       </c>
       <c r="D114" s="4" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="G114" s="4" t="inlineStr">
         <is>
-          <t>https://www.az-online.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.bondguide.de/topnews/klimafinanzierung-bei-cop-30-von-zusagen-zu-wirkung-entfalten/</t>
         </is>
       </c>
     </row>
@@ -4428,7 +4428,7 @@
       </c>
       <c r="B115" s="4" t="inlineStr">
         <is>
-          <t>fehmarn24.de</t>
+          <t>AZ online (Allgemeine Zeitung der Lüneburger Heide)</t>
         </is>
       </c>
       <c r="C115" s="4" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="G115" s="4" t="inlineStr">
         <is>
-          <t>https://www.fehmarn24.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.az-online.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
@@ -4463,7 +4463,7 @@
       </c>
       <c r="B116" s="4" t="inlineStr">
         <is>
-          <t>fnp.de (Frankfurter Neue Presse)</t>
+          <t>fehmarn24.de</t>
         </is>
       </c>
       <c r="C116" s="4" t="inlineStr">
@@ -4486,7 +4486,11 @@
           <t>Johannes Feist</t>
         </is>
       </c>
-      <c r="G116" s="4" t="inlineStr"/>
+      <c r="G116" s="4" t="inlineStr">
+        <is>
+          <t>https://www.fehmarn24.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="n">
@@ -4494,7 +4498,7 @@
       </c>
       <c r="B117" s="4" t="inlineStr">
         <is>
-          <t>Fuldaer Zeitung.de</t>
+          <t>fnp.de (Frankfurter Neue Presse)</t>
         </is>
       </c>
       <c r="C117" s="4" t="inlineStr">
@@ -4517,11 +4521,7 @@
           <t>Johannes Feist</t>
         </is>
       </c>
-      <c r="G117" s="4" t="inlineStr">
-        <is>
-          <t>https://www.fuldaerzeitung.de/politik-und-wirtschaft/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
-        </is>
-      </c>
+      <c r="G117" s="4" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="3" t="n">
@@ -4529,7 +4529,7 @@
       </c>
       <c r="B118" s="4" t="inlineStr">
         <is>
-          <t>Gießener Allgemeine Online</t>
+          <t>Fuldaer Zeitung.de</t>
         </is>
       </c>
       <c r="C118" s="4" t="inlineStr">
@@ -4554,7 +4554,7 @@
       </c>
       <c r="G118" s="4" t="inlineStr">
         <is>
-          <t>https://www.giessener-allgemeine.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.fuldaerzeitung.de/politik-und-wirtschaft/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
@@ -4564,7 +4564,7 @@
       </c>
       <c r="B119" s="4" t="inlineStr">
         <is>
-          <t>Wetterauer Zeitung Online</t>
+          <t>Gießener Allgemeine Online</t>
         </is>
       </c>
       <c r="C119" s="4" t="inlineStr">
@@ -4589,7 +4589,7 @@
       </c>
       <c r="G119" s="4" t="inlineStr">
         <is>
-          <t>https://www.wetterauer-zeitung.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.giessener-allgemeine.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
@@ -4599,7 +4599,7 @@
       </c>
       <c r="B120" s="4" t="inlineStr">
         <is>
-          <t>giessener-anzeiger.de</t>
+          <t>Wetterauer Zeitung Online</t>
         </is>
       </c>
       <c r="C120" s="4" t="inlineStr">
@@ -4624,7 +4624,7 @@
       </c>
       <c r="G120" s="4" t="inlineStr">
         <is>
-          <t>https://www.giessener-anzeiger.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.wetterauer-zeitung.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
@@ -4634,7 +4634,7 @@
       </c>
       <c r="B121" s="4" t="inlineStr">
         <is>
-          <t>kreis-anzeiger.de (Zentralhessen)</t>
+          <t>giessener-anzeiger.de</t>
         </is>
       </c>
       <c r="C121" s="4" t="inlineStr">
@@ -4659,7 +4659,7 @@
       </c>
       <c r="G121" s="4" t="inlineStr">
         <is>
-          <t>https://www.kreis-anzeiger.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.giessener-anzeiger.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="B122" s="4" t="inlineStr">
         <is>
-          <t>usinger-anzeiger.de</t>
+          <t>kreis-anzeiger.de (Zentralhessen)</t>
         </is>
       </c>
       <c r="C122" s="4" t="inlineStr">
@@ -4694,7 +4694,7 @@
       </c>
       <c r="G122" s="4" t="inlineStr">
         <is>
-          <t>https://www.usinger-anzeiger.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.kreis-anzeiger.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
@@ -4704,7 +4704,7 @@
       </c>
       <c r="B123" s="4" t="inlineStr">
         <is>
-          <t>hanauer.de (Hanauer Anzeiger)</t>
+          <t>usinger-anzeiger.de</t>
         </is>
       </c>
       <c r="C123" s="4" t="inlineStr">
@@ -4729,7 +4729,7 @@
       </c>
       <c r="G123" s="4" t="inlineStr">
         <is>
-          <t>https://www.hanauer.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.usinger-anzeiger.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
@@ -4739,7 +4739,7 @@
       </c>
       <c r="B124" s="4" t="inlineStr">
         <is>
-          <t>echo24.de</t>
+          <t>hanauer.de (Hanauer Anzeiger)</t>
         </is>
       </c>
       <c r="C124" s="4" t="inlineStr">
@@ -4764,7 +4764,7 @@
       </c>
       <c r="G124" s="4" t="inlineStr">
         <is>
-          <t>https://www.echo24.de/welt/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.hanauer.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
@@ -4774,7 +4774,7 @@
       </c>
       <c r="B125" s="4" t="inlineStr">
         <is>
-          <t>hersfelder-zeitung.de</t>
+          <t>echo24.de</t>
         </is>
       </c>
       <c r="C125" s="4" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="G125" s="4" t="inlineStr">
         <is>
-          <t>https://www.hersfelder-zeitung.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.echo24.de/welt/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
@@ -4809,7 +4809,7 @@
       </c>
       <c r="B126" s="4" t="inlineStr">
         <is>
-          <t>HNA online</t>
+          <t>hersfelder-zeitung.de</t>
         </is>
       </c>
       <c r="C126" s="4" t="inlineStr">
@@ -4834,7 +4834,7 @@
       </c>
       <c r="G126" s="4" t="inlineStr">
         <is>
-          <t>https://www.hna.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.hersfelder-zeitung.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4844,7 @@
       </c>
       <c r="B127" s="4" t="inlineStr">
         <is>
-          <t>kreisbote.de</t>
+          <t>HNA online</t>
         </is>
       </c>
       <c r="C127" s="4" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="G127" s="4" t="inlineStr">
         <is>
-          <t>https://www.kreisbote.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.hna.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
@@ -4879,7 +4879,7 @@
       </c>
       <c r="B128" s="4" t="inlineStr">
         <is>
-          <t>kreiszeitung.de (Syke)</t>
+          <t>kreisbote.de</t>
         </is>
       </c>
       <c r="C128" s="4" t="inlineStr">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="G128" s="4" t="inlineStr">
         <is>
-          <t>https://www.kreiszeitung.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.kreisbote.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
@@ -4914,7 +4914,7 @@
       </c>
       <c r="B129" s="4" t="inlineStr">
         <is>
-          <t>Leinetal24.de</t>
+          <t>kreiszeitung.de (Syke)</t>
         </is>
       </c>
       <c r="C129" s="4" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="G129" s="4" t="inlineStr">
         <is>
-          <t>https://www.leinetal24.de/welt/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.kreiszeitung.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="B130" s="4" t="inlineStr">
         <is>
-          <t>come-on.de (Märkischer Zeitungsverlag)</t>
+          <t>Leinetal24.de</t>
         </is>
       </c>
       <c r="C130" s="4" t="inlineStr">
@@ -4974,7 +4974,7 @@
       </c>
       <c r="G130" s="4" t="inlineStr">
         <is>
-          <t>https://www.come-on.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.leinetal24.de/welt/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
@@ -4984,7 +4984,7 @@
       </c>
       <c r="B131" s="4" t="inlineStr">
         <is>
-          <t>Merkur.de (Münchner Merkur)</t>
+          <t>come-on.de (Märkischer Zeitungsverlag)</t>
         </is>
       </c>
       <c r="C131" s="4" t="inlineStr">
@@ -5009,7 +5009,7 @@
       </c>
       <c r="G131" s="4" t="inlineStr">
         <is>
-          <t>https://www.merkur.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.come-on.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="B132" s="4" t="inlineStr">
         <is>
-          <t>OVB online (Oberbayerisches Volksblatt)</t>
+          <t>Merkur.de (Münchner Merkur)</t>
         </is>
       </c>
       <c r="C132" s="4" t="inlineStr">
@@ -5044,7 +5044,7 @@
       </c>
       <c r="G132" s="4" t="inlineStr">
         <is>
-          <t>https://www.ovb-online.de/weltspiegel/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.merkur.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
@@ -5054,7 +5054,7 @@
       </c>
       <c r="B133" s="4" t="inlineStr">
         <is>
-          <t>oberhessische-zeitung.de</t>
+          <t>OVB online (Oberbayerisches Volksblatt)</t>
         </is>
       </c>
       <c r="C133" s="4" t="inlineStr">
@@ -5079,7 +5079,7 @@
       </c>
       <c r="G133" s="4" t="inlineStr">
         <is>
-          <t>https://www.oberhessische-zeitung.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.ovb-online.de/weltspiegel/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
@@ -5089,7 +5089,7 @@
       </c>
       <c r="B134" s="4" t="inlineStr">
         <is>
-          <t>OFFENBACH-POST ONLINE</t>
+          <t>oberhessische-zeitung.de</t>
         </is>
       </c>
       <c r="C134" s="4" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="G134" s="4" t="inlineStr">
         <is>
-          <t>https://www.op-online.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.oberhessische-zeitung.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
@@ -5124,7 +5124,7 @@
       </c>
       <c r="B135" s="4" t="inlineStr">
         <is>
-          <t>gmuender-tagespost.de</t>
+          <t>OFFENBACH-POST ONLINE</t>
         </is>
       </c>
       <c r="C135" s="4" t="inlineStr">
@@ -5149,7 +5149,7 @@
       </c>
       <c r="G135" s="4" t="inlineStr">
         <is>
-          <t>https://www.gmuender-tagespost.de/welt/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.op-online.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5159,7 @@
       </c>
       <c r="B136" s="4" t="inlineStr">
         <is>
-          <t>schwaebische-post.de</t>
+          <t>gmuender-tagespost.de</t>
         </is>
       </c>
       <c r="C136" s="4" t="inlineStr">
@@ -5184,7 +5184,7 @@
       </c>
       <c r="G136" s="4" t="inlineStr">
         <is>
-          <t>https://www.schwaebische-post.de/welt/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.gmuender-tagespost.de/welt/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
@@ -5194,7 +5194,7 @@
       </c>
       <c r="B137" s="4" t="inlineStr">
         <is>
-          <t>tz-online.de</t>
+          <t>schwaebische-post.de</t>
         </is>
       </c>
       <c r="C137" s="4" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="G137" s="4" t="inlineStr">
         <is>
-          <t>https://www.tz.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.schwaebische-post.de/welt/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
@@ -5229,7 +5229,7 @@
       </c>
       <c r="B138" s="4" t="inlineStr">
         <is>
-          <t>Waldeckische Landeszeitung Online</t>
+          <t>tz-online.de</t>
         </is>
       </c>
       <c r="C138" s="4" t="inlineStr">
@@ -5254,7 +5254,7 @@
       </c>
       <c r="G138" s="4" t="inlineStr">
         <is>
-          <t>https://www.wlz-online.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.tz.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
@@ -5264,7 +5264,7 @@
       </c>
       <c r="B139" s="4" t="inlineStr">
         <is>
-          <t>werra-rundschau.de</t>
+          <t>Waldeckische Landeszeitung Online</t>
         </is>
       </c>
       <c r="C139" s="4" t="inlineStr">
@@ -5289,7 +5289,7 @@
       </c>
       <c r="G139" s="4" t="inlineStr">
         <is>
-          <t>https://www.werra-rundschau.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.wlz-online.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="B140" s="4" t="inlineStr">
         <is>
-          <t>soester-anzeiger.de</t>
+          <t>werra-rundschau.de</t>
         </is>
       </c>
       <c r="C140" s="4" t="inlineStr">
@@ -5324,7 +5324,7 @@
       </c>
       <c r="G140" s="4" t="inlineStr">
         <is>
-          <t>https://www.soester-anzeiger.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.werra-rundschau.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
@@ -5334,7 +5334,7 @@
       </c>
       <c r="B141" s="4" t="inlineStr">
         <is>
-          <t>wa.de (Westfälischer Anzeiger)</t>
+          <t>soester-anzeiger.de</t>
         </is>
       </c>
       <c r="C141" s="4" t="inlineStr">
@@ -5359,40 +5359,75 @@
       </c>
       <c r="G141" s="4" t="inlineStr">
         <is>
-          <t>https://www.wa.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+          <t>https://www.soester-anzeiger.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="3" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B142" s="4" t="inlineStr">
+        <is>
+          <t>wa.de (Westfälischer Anzeiger)</t>
+        </is>
+      </c>
+      <c r="C142" s="4" t="inlineStr">
+        <is>
+          <t>Merz reist nach Brasilien: Deutschlands Klimapolitik bei COP30 auf dem Prüfstein</t>
+        </is>
+      </c>
+      <c r="D142" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E142" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F142" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G142" s="4" t="inlineStr">
+        <is>
+          <t>https://www.wa.de/politik/merz-reist-zur-klimakonferenz-cop30-nach-brasilien-klimapolitik-auf-dem-pruefstein-zr-94025730.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="3" t="n">
         <v>45848</v>
       </c>
-      <c r="B142" s="4" t="inlineStr">
+      <c r="B143" s="4" t="inlineStr">
         <is>
           <t>Handelszeitung</t>
         </is>
       </c>
-      <c r="C142" s="4" t="inlineStr">
+      <c r="C143" s="4" t="inlineStr">
         <is>
           <t>Zwischen ESG-Müdigkeit und Wirkungsanspruch</t>
         </is>
       </c>
-      <c r="D142" s="4" t="inlineStr">
+      <c r="D143" s="4" t="inlineStr">
         <is>
           <t>CH</t>
         </is>
       </c>
-      <c r="E142" s="4" t="inlineStr">
-        <is>
-          <t>Online</t>
-        </is>
-      </c>
-      <c r="F142" s="4" t="inlineStr">
-        <is>
-          <t>Johannes Feist</t>
-        </is>
-      </c>
-      <c r="G142" s="4" t="inlineStr">
+      <c r="E143" s="4" t="inlineStr">
+        <is>
+          <t>Online</t>
+        </is>
+      </c>
+      <c r="F143" s="4" t="inlineStr">
+        <is>
+          <t>Johannes Feist</t>
+        </is>
+      </c>
+      <c r="G143" s="4" t="inlineStr">
         <is>
           <t>https://www.handelszeitung.ch/specials/nachhaltiges-investieren-2024/zwischen-esg-mudigkeit-und-wirkungsanspruch-841576</t>
         </is>
@@ -5433,7 +5468,7 @@
     <row r="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>Source: Sheet '2026 Clippings' (A9:G142)</t>
+          <t>Source: Sheet '2026 Clippings' (A9:G143)</t>
         </is>
       </c>
     </row>
@@ -5451,7 +5486,7 @@
         </is>
       </c>
       <c r="B5" s="9" t="n">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6">
@@ -5471,7 +5506,7 @@
         </is>
       </c>
       <c r="B7" s="10" t="n">
-        <v>46304</v>
+        <v>46315</v>
       </c>
     </row>
     <row r="8">
@@ -5481,7 +5516,7 @@
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9">
@@ -5543,7 +5578,7 @@
         <v>117</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>0.8731343283582089</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
@@ -5561,10 +5596,10 @@
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>0.1119402985074627</v>
+        <v>0.1185185185185185</v>
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
@@ -5585,7 +5620,7 @@
         <v>2</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>0.01492537313432836</v>
+        <v>0.01481481481481482</v>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
@@ -5704,7 +5739,7 @@
         </is>
       </c>
       <c r="F24" s="8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="29">
@@ -5761,7 +5796,7 @@
         <v>5</v>
       </c>
       <c r="C31" s="11" t="n">
-        <v>0.03731343283582089</v>
+        <v>0.03703703703703703</v>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
@@ -5772,7 +5807,7 @@
         <v>1</v>
       </c>
       <c r="G31" s="11" t="n">
-        <v>0.007462686567164179</v>
+        <v>0.007407407407407408</v>
       </c>
     </row>
     <row r="32">
@@ -5782,10 +5817,10 @@
         </is>
       </c>
       <c r="B32" s="8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C32" s="11" t="n">
-        <v>0.1567164179104478</v>
+        <v>0.162962962962963</v>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
@@ -5796,7 +5831,7 @@
         <v>2</v>
       </c>
       <c r="G32" s="11" t="n">
-        <v>0.01492537313432836</v>
+        <v>0.01481481481481482</v>
       </c>
     </row>
     <row r="33">
@@ -5809,7 +5844,7 @@
         <v>102</v>
       </c>
       <c r="C33" s="11" t="n">
-        <v>0.7611940298507462</v>
+        <v>0.7555555555555555</v>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
@@ -5817,10 +5852,10 @@
         </is>
       </c>
       <c r="F33" s="8" t="n">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G33" s="11" t="n">
-        <v>0.8731343283582089</v>
+        <v>0.8740740740740741</v>
       </c>
     </row>
     <row r="34">
@@ -5833,7 +5868,7 @@
         <v>6</v>
       </c>
       <c r="C34" s="11" t="n">
-        <v>0.04477611940298507</v>
+        <v>0.04444444444444445</v>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
@@ -5844,7 +5879,7 @@
         <v>8</v>
       </c>
       <c r="G34" s="11" t="n">
-        <v>0.05970149253731343</v>
+        <v>0.05925925925925926</v>
       </c>
     </row>
     <row r="35">
@@ -5857,7 +5892,7 @@
         <v>1</v>
       </c>
       <c r="G35" s="11" t="n">
-        <v>0.007462686567164179</v>
+        <v>0.007407407407407408</v>
       </c>
     </row>
     <row r="36">
@@ -5870,7 +5905,7 @@
         <v>4</v>
       </c>
       <c r="G36" s="11" t="n">
-        <v>0.02985074626865672</v>
+        <v>0.02962962962962963</v>
       </c>
     </row>
     <row r="37">
@@ -5883,7 +5918,7 @@
         <v>1</v>
       </c>
       <c r="G37" s="11" t="n">
-        <v>0.007462686567164179</v>
+        <v>0.007407407407407408</v>
       </c>
     </row>
   </sheetData>
